--- a/UISS_Batch_PartListUpload_v2.xlsx
+++ b/UISS_Batch_PartListUpload_v2.xlsx
@@ -23970,7 +23970,7 @@
       <c r="S13" s="856" t="n"/>
       <c r="T13" s="1012" t="inlineStr">
         <is>
-          <t>minimum_mad</t>
+          <t>mad</t>
         </is>
       </c>
       <c r="U13" s="855" t="n"/>
@@ -23994,7 +23994,7 @@
       <c r="AN13" s="856" t="n"/>
       <c r="AO13" s="1015" t="inlineStr">
         <is>
-          <t>MIN_MAD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="AP13" s="855" t="n"/>
@@ -24007,7 +24007,11 @@
       <c r="AW13" s="855" t="n"/>
       <c r="AX13" s="855" t="n"/>
       <c r="AY13" s="855" t="n"/>
-      <c r="AZ13" s="1015" t="n"/>
+      <c r="AZ13" s="1015" t="inlineStr">
+        <is>
+          <t>Optional; blank = NULL until the MAD calculation function fills it</t>
+        </is>
+      </c>
       <c r="BA13" s="855" t="n"/>
       <c r="BB13" s="855" t="n"/>
       <c r="BC13" s="855" t="n"/>
@@ -28493,7 +28497,7 @@
       <c r="S54" s="856" t="n"/>
       <c r="T54" s="1012" t="inlineStr">
         <is>
-          <t>minimum_mad</t>
+          <t>mad</t>
         </is>
       </c>
       <c r="U54" s="855" t="n"/>
@@ -28517,7 +28521,7 @@
       <c r="AN54" s="856" t="n"/>
       <c r="AO54" s="1015" t="inlineStr">
         <is>
-          <t>MIN_MAD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="AP54" s="855" t="n"/>
@@ -28530,7 +28534,11 @@
       <c r="AW54" s="855" t="n"/>
       <c r="AX54" s="855" t="n"/>
       <c r="AY54" s="855" t="n"/>
-      <c r="AZ54" s="1015" t="n"/>
+      <c r="AZ54" s="1015" t="inlineStr">
+        <is>
+          <t>Optional; blank = not changed</t>
+        </is>
+      </c>
       <c r="BA54" s="855" t="n"/>
       <c r="BB54" s="855" t="n"/>
       <c r="BC54" s="855" t="n"/>
@@ -34423,7 +34431,7 @@
       <c r="BD14" s="955" t="n"/>
       <c r="BE14" s="956" t="inlineStr">
         <is>
-          <t>Min MAD (0 or more), Pcs/Case and Max Case/Day (more</t>
+          <t>Pcs/Case and Max Case/Day are whole numbers greater than</t>
         </is>
       </c>
       <c r="BF14" s="957" t="n"/>
@@ -34458,7 +34466,7 @@
       <c r="CI14" s="955" t="n"/>
       <c r="CJ14" s="956" t="inlineStr">
         <is>
-          <t>minimum_mad,</t>
+          <t>pcs_case,</t>
         </is>
       </c>
       <c r="CK14" s="957" t="n"/>
@@ -34536,7 +34544,7 @@
       <c r="BD15" s="959" t="n"/>
       <c r="BE15" s="963" t="inlineStr">
         <is>
-          <t>than 0) are whole numbers. Required on every row, no blank</t>
+          <t>0, required on every row. MAD is optional (filled later by the</t>
         </is>
       </c>
       <c r="BF15" s="961" t="n"/>
@@ -34571,7 +34579,7 @@
       <c r="CI15" s="959" t="n"/>
       <c r="CJ15" s="963" t="inlineStr">
         <is>
-          <t>pcs_case,</t>
+          <t>max_case_day, mad</t>
         </is>
       </c>
       <c r="CK15" s="961" t="n"/>
@@ -34653,7 +34661,7 @@
       <c r="BD16" s="959" t="n"/>
       <c r="BE16" s="963" t="inlineStr">
         <is>
-          <t>cell.</t>
+          <t>MAD calculation function); when filled it is a whole number, 0</t>
         </is>
       </c>
       <c r="BF16" s="961" t="n"/>
@@ -34686,11 +34694,7 @@
       <c r="CG16" s="961" t="n"/>
       <c r="CH16" s="961" t="n"/>
       <c r="CI16" s="959" t="n"/>
-      <c r="CJ16" s="963" t="inlineStr">
-        <is>
-          <t>max_case_day</t>
-        </is>
-      </c>
+      <c r="CJ16" s="963" t="n"/>
       <c r="CK16" s="961" t="n"/>
       <c r="CL16" s="961" t="n"/>
       <c r="CM16" s="961" t="n"/>
@@ -34769,64 +34773,56 @@
       <c r="AY17" s="941" t="n"/>
       <c r="AZ17" s="943" t="n"/>
       <c r="BA17" s="941" t="n"/>
-      <c r="BB17" s="954" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BC17" s="957" t="n"/>
-      <c r="BD17" s="955" t="n"/>
-      <c r="BE17" s="956" t="inlineStr">
-        <is>
-          <t>Status: flag A must be blank (a new part is always Candidate).</t>
-        </is>
-      </c>
-      <c r="BF17" s="957" t="n"/>
-      <c r="BG17" s="957" t="n"/>
-      <c r="BH17" s="957" t="n"/>
-      <c r="BI17" s="957" t="n"/>
-      <c r="BJ17" s="957" t="n"/>
-      <c r="BK17" s="957" t="n"/>
-      <c r="BL17" s="957" t="n"/>
-      <c r="BM17" s="957" t="n"/>
-      <c r="BN17" s="957" t="n"/>
-      <c r="BO17" s="957" t="n"/>
-      <c r="BP17" s="957" t="n"/>
-      <c r="BQ17" s="957" t="n"/>
-      <c r="BR17" s="957" t="n"/>
-      <c r="BS17" s="957" t="n"/>
-      <c r="BT17" s="957" t="n"/>
-      <c r="BU17" s="957" t="n"/>
-      <c r="BV17" s="957" t="n"/>
-      <c r="BW17" s="957" t="n"/>
-      <c r="BX17" s="957" t="n"/>
-      <c r="BY17" s="957" t="n"/>
-      <c r="BZ17" s="957" t="n"/>
-      <c r="CA17" s="957" t="n"/>
-      <c r="CB17" s="957" t="n"/>
-      <c r="CC17" s="957" t="n"/>
-      <c r="CD17" s="957" t="n"/>
-      <c r="CE17" s="957" t="n"/>
-      <c r="CF17" s="957" t="n"/>
-      <c r="CG17" s="957" t="n"/>
-      <c r="CH17" s="957" t="n"/>
-      <c r="CI17" s="955" t="n"/>
-      <c r="CJ17" s="956" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="CK17" s="957" t="n"/>
-      <c r="CL17" s="957" t="n"/>
-      <c r="CM17" s="957" t="n"/>
-      <c r="CN17" s="957" t="n"/>
-      <c r="CO17" s="957" t="n"/>
-      <c r="CP17" s="957" t="n"/>
-      <c r="CQ17" s="957" t="n"/>
-      <c r="CR17" s="957" t="n"/>
-      <c r="CS17" s="957" t="n"/>
-      <c r="CT17" s="957" t="n"/>
-      <c r="CU17" s="955" t="n"/>
+      <c r="BB17" s="962" t="n"/>
+      <c r="BC17" s="961" t="n"/>
+      <c r="BD17" s="959" t="n"/>
+      <c r="BE17" s="963" t="inlineStr">
+        <is>
+          <t>or more.</t>
+        </is>
+      </c>
+      <c r="BF17" s="961" t="n"/>
+      <c r="BG17" s="961" t="n"/>
+      <c r="BH17" s="961" t="n"/>
+      <c r="BI17" s="961" t="n"/>
+      <c r="BJ17" s="961" t="n"/>
+      <c r="BK17" s="961" t="n"/>
+      <c r="BL17" s="961" t="n"/>
+      <c r="BM17" s="961" t="n"/>
+      <c r="BN17" s="961" t="n"/>
+      <c r="BO17" s="961" t="n"/>
+      <c r="BP17" s="961" t="n"/>
+      <c r="BQ17" s="961" t="n"/>
+      <c r="BR17" s="961" t="n"/>
+      <c r="BS17" s="961" t="n"/>
+      <c r="BT17" s="961" t="n"/>
+      <c r="BU17" s="961" t="n"/>
+      <c r="BV17" s="961" t="n"/>
+      <c r="BW17" s="961" t="n"/>
+      <c r="BX17" s="961" t="n"/>
+      <c r="BY17" s="961" t="n"/>
+      <c r="BZ17" s="961" t="n"/>
+      <c r="CA17" s="961" t="n"/>
+      <c r="CB17" s="961" t="n"/>
+      <c r="CC17" s="961" t="n"/>
+      <c r="CD17" s="961" t="n"/>
+      <c r="CE17" s="961" t="n"/>
+      <c r="CF17" s="961" t="n"/>
+      <c r="CG17" s="961" t="n"/>
+      <c r="CH17" s="961" t="n"/>
+      <c r="CI17" s="959" t="n"/>
+      <c r="CJ17" s="963" t="n"/>
+      <c r="CK17" s="961" t="n"/>
+      <c r="CL17" s="961" t="n"/>
+      <c r="CM17" s="961" t="n"/>
+      <c r="CN17" s="961" t="n"/>
+      <c r="CO17" s="961" t="n"/>
+      <c r="CP17" s="961" t="n"/>
+      <c r="CQ17" s="961" t="n"/>
+      <c r="CR17" s="961" t="n"/>
+      <c r="CS17" s="961" t="n"/>
+      <c r="CT17" s="961" t="n"/>
+      <c r="CU17" s="959" t="n"/>
       <c r="CV17" s="941" t="n"/>
       <c r="CW17" s="941" t="n"/>
       <c r="CX17" s="944" t="n"/>
@@ -34894,56 +34890,64 @@
       <c r="AY18" s="941" t="n"/>
       <c r="AZ18" s="943" t="n"/>
       <c r="BA18" s="941" t="n"/>
-      <c r="BB18" s="962" t="n"/>
-      <c r="BC18" s="961" t="n"/>
-      <c r="BD18" s="959" t="n"/>
-      <c r="BE18" s="963" t="inlineStr">
-        <is>
-          <t>Flag E: a Candidate part must stay Candidate (blank or</t>
-        </is>
-      </c>
-      <c r="BF18" s="961" t="n"/>
-      <c r="BG18" s="961" t="n"/>
-      <c r="BH18" s="961" t="n"/>
-      <c r="BI18" s="961" t="n"/>
-      <c r="BJ18" s="961" t="n"/>
-      <c r="BK18" s="961" t="n"/>
-      <c r="BL18" s="961" t="n"/>
-      <c r="BM18" s="961" t="n"/>
-      <c r="BN18" s="961" t="n"/>
-      <c r="BO18" s="961" t="n"/>
-      <c r="BP18" s="961" t="n"/>
-      <c r="BQ18" s="961" t="n"/>
-      <c r="BR18" s="961" t="n"/>
-      <c r="BS18" s="961" t="n"/>
-      <c r="BT18" s="961" t="n"/>
-      <c r="BU18" s="961" t="n"/>
-      <c r="BV18" s="961" t="n"/>
-      <c r="BW18" s="961" t="n"/>
-      <c r="BX18" s="961" t="n"/>
-      <c r="BY18" s="961" t="n"/>
-      <c r="BZ18" s="961" t="n"/>
-      <c r="CA18" s="961" t="n"/>
-      <c r="CB18" s="961" t="n"/>
-      <c r="CC18" s="961" t="n"/>
-      <c r="CD18" s="961" t="n"/>
-      <c r="CE18" s="961" t="n"/>
-      <c r="CF18" s="961" t="n"/>
-      <c r="CG18" s="961" t="n"/>
-      <c r="CH18" s="961" t="n"/>
-      <c r="CI18" s="959" t="n"/>
-      <c r="CJ18" s="963" t="n"/>
-      <c r="CK18" s="961" t="n"/>
-      <c r="CL18" s="961" t="n"/>
-      <c r="CM18" s="961" t="n"/>
-      <c r="CN18" s="961" t="n"/>
-      <c r="CO18" s="961" t="n"/>
-      <c r="CP18" s="961" t="n"/>
-      <c r="CQ18" s="961" t="n"/>
-      <c r="CR18" s="961" t="n"/>
-      <c r="CS18" s="961" t="n"/>
-      <c r="CT18" s="961" t="n"/>
-      <c r="CU18" s="959" t="n"/>
+      <c r="BB18" s="954" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BC18" s="957" t="n"/>
+      <c r="BD18" s="955" t="n"/>
+      <c r="BE18" s="956" t="inlineStr">
+        <is>
+          <t>Status: flag A must be blank (a new part is always Candidate).</t>
+        </is>
+      </c>
+      <c r="BF18" s="957" t="n"/>
+      <c r="BG18" s="957" t="n"/>
+      <c r="BH18" s="957" t="n"/>
+      <c r="BI18" s="957" t="n"/>
+      <c r="BJ18" s="957" t="n"/>
+      <c r="BK18" s="957" t="n"/>
+      <c r="BL18" s="957" t="n"/>
+      <c r="BM18" s="957" t="n"/>
+      <c r="BN18" s="957" t="n"/>
+      <c r="BO18" s="957" t="n"/>
+      <c r="BP18" s="957" t="n"/>
+      <c r="BQ18" s="957" t="n"/>
+      <c r="BR18" s="957" t="n"/>
+      <c r="BS18" s="957" t="n"/>
+      <c r="BT18" s="957" t="n"/>
+      <c r="BU18" s="957" t="n"/>
+      <c r="BV18" s="957" t="n"/>
+      <c r="BW18" s="957" t="n"/>
+      <c r="BX18" s="957" t="n"/>
+      <c r="BY18" s="957" t="n"/>
+      <c r="BZ18" s="957" t="n"/>
+      <c r="CA18" s="957" t="n"/>
+      <c r="CB18" s="957" t="n"/>
+      <c r="CC18" s="957" t="n"/>
+      <c r="CD18" s="957" t="n"/>
+      <c r="CE18" s="957" t="n"/>
+      <c r="CF18" s="957" t="n"/>
+      <c r="CG18" s="957" t="n"/>
+      <c r="CH18" s="957" t="n"/>
+      <c r="CI18" s="955" t="n"/>
+      <c r="CJ18" s="956" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="CK18" s="957" t="n"/>
+      <c r="CL18" s="957" t="n"/>
+      <c r="CM18" s="957" t="n"/>
+      <c r="CN18" s="957" t="n"/>
+      <c r="CO18" s="957" t="n"/>
+      <c r="CP18" s="957" t="n"/>
+      <c r="CQ18" s="957" t="n"/>
+      <c r="CR18" s="957" t="n"/>
+      <c r="CS18" s="957" t="n"/>
+      <c r="CT18" s="957" t="n"/>
+      <c r="CU18" s="955" t="n"/>
       <c r="CV18" s="941" t="n"/>
       <c r="CW18" s="941" t="n"/>
       <c r="CX18" s="944" t="n"/>
@@ -35016,7 +35020,7 @@
       <c r="BD19" s="959" t="n"/>
       <c r="BE19" s="963" t="inlineStr">
         <is>
-          <t>Candidate); an Active part may be changed to Inactive and an</t>
+          <t>Flag E: a Candidate part must stay Candidate (blank or</t>
         </is>
       </c>
       <c r="BF19" s="961" t="n"/>
@@ -35133,7 +35137,7 @@
       <c r="BD20" s="959" t="n"/>
       <c r="BE20" s="963" t="inlineStr">
         <is>
-          <t>Inactive part to Active; no part can be changed to Candidate.</t>
+          <t>Candidate); an Active part may be changed to Inactive and an</t>
         </is>
       </c>
       <c r="BF20" s="961" t="n"/>
@@ -35245,64 +35249,56 @@
       <c r="AY21" s="941" t="n"/>
       <c r="AZ21" s="943" t="n"/>
       <c r="BA21" s="941" t="n"/>
-      <c r="BB21" s="954" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BC21" s="957" t="n"/>
-      <c r="BD21" s="955" t="n"/>
-      <c r="BE21" s="956" t="inlineStr">
-        <is>
-          <t>Effective Start Date is required when the part status is</t>
-        </is>
-      </c>
-      <c r="BF21" s="957" t="n"/>
-      <c r="BG21" s="957" t="n"/>
-      <c r="BH21" s="957" t="n"/>
-      <c r="BI21" s="957" t="n"/>
-      <c r="BJ21" s="957" t="n"/>
-      <c r="BK21" s="957" t="n"/>
-      <c r="BL21" s="957" t="n"/>
-      <c r="BM21" s="957" t="n"/>
-      <c r="BN21" s="957" t="n"/>
-      <c r="BO21" s="957" t="n"/>
-      <c r="BP21" s="957" t="n"/>
-      <c r="BQ21" s="957" t="n"/>
-      <c r="BR21" s="957" t="n"/>
-      <c r="BS21" s="957" t="n"/>
-      <c r="BT21" s="957" t="n"/>
-      <c r="BU21" s="957" t="n"/>
-      <c r="BV21" s="957" t="n"/>
-      <c r="BW21" s="957" t="n"/>
-      <c r="BX21" s="957" t="n"/>
-      <c r="BY21" s="957" t="n"/>
-      <c r="BZ21" s="957" t="n"/>
-      <c r="CA21" s="957" t="n"/>
-      <c r="CB21" s="957" t="n"/>
-      <c r="CC21" s="957" t="n"/>
-      <c r="CD21" s="957" t="n"/>
-      <c r="CE21" s="957" t="n"/>
-      <c r="CF21" s="957" t="n"/>
-      <c r="CG21" s="957" t="n"/>
-      <c r="CH21" s="957" t="n"/>
-      <c r="CI21" s="955" t="n"/>
-      <c r="CJ21" s="956" t="inlineStr">
-        <is>
-          <t>effective_start_date</t>
-        </is>
-      </c>
-      <c r="CK21" s="957" t="n"/>
-      <c r="CL21" s="957" t="n"/>
-      <c r="CM21" s="957" t="n"/>
-      <c r="CN21" s="957" t="n"/>
-      <c r="CO21" s="957" t="n"/>
-      <c r="CP21" s="957" t="n"/>
-      <c r="CQ21" s="957" t="n"/>
-      <c r="CR21" s="957" t="n"/>
-      <c r="CS21" s="957" t="n"/>
-      <c r="CT21" s="957" t="n"/>
-      <c r="CU21" s="955" t="n"/>
+      <c r="BB21" s="962" t="n"/>
+      <c r="BC21" s="961" t="n"/>
+      <c r="BD21" s="959" t="n"/>
+      <c r="BE21" s="963" t="inlineStr">
+        <is>
+          <t>Inactive part to Active; no part can be changed to Candidate.</t>
+        </is>
+      </c>
+      <c r="BF21" s="961" t="n"/>
+      <c r="BG21" s="961" t="n"/>
+      <c r="BH21" s="961" t="n"/>
+      <c r="BI21" s="961" t="n"/>
+      <c r="BJ21" s="961" t="n"/>
+      <c r="BK21" s="961" t="n"/>
+      <c r="BL21" s="961" t="n"/>
+      <c r="BM21" s="961" t="n"/>
+      <c r="BN21" s="961" t="n"/>
+      <c r="BO21" s="961" t="n"/>
+      <c r="BP21" s="961" t="n"/>
+      <c r="BQ21" s="961" t="n"/>
+      <c r="BR21" s="961" t="n"/>
+      <c r="BS21" s="961" t="n"/>
+      <c r="BT21" s="961" t="n"/>
+      <c r="BU21" s="961" t="n"/>
+      <c r="BV21" s="961" t="n"/>
+      <c r="BW21" s="961" t="n"/>
+      <c r="BX21" s="961" t="n"/>
+      <c r="BY21" s="961" t="n"/>
+      <c r="BZ21" s="961" t="n"/>
+      <c r="CA21" s="961" t="n"/>
+      <c r="CB21" s="961" t="n"/>
+      <c r="CC21" s="961" t="n"/>
+      <c r="CD21" s="961" t="n"/>
+      <c r="CE21" s="961" t="n"/>
+      <c r="CF21" s="961" t="n"/>
+      <c r="CG21" s="961" t="n"/>
+      <c r="CH21" s="961" t="n"/>
+      <c r="CI21" s="959" t="n"/>
+      <c r="CJ21" s="963" t="n"/>
+      <c r="CK21" s="961" t="n"/>
+      <c r="CL21" s="961" t="n"/>
+      <c r="CM21" s="961" t="n"/>
+      <c r="CN21" s="961" t="n"/>
+      <c r="CO21" s="961" t="n"/>
+      <c r="CP21" s="961" t="n"/>
+      <c r="CQ21" s="961" t="n"/>
+      <c r="CR21" s="961" t="n"/>
+      <c r="CS21" s="961" t="n"/>
+      <c r="CT21" s="961" t="n"/>
+      <c r="CU21" s="959" t="n"/>
       <c r="CV21" s="941" t="n"/>
       <c r="CW21" s="941" t="n"/>
       <c r="CX21" s="944" t="n"/>
@@ -35362,56 +35358,64 @@
       <c r="AY22" s="941" t="n"/>
       <c r="AZ22" s="943" t="n"/>
       <c r="BA22" s="941" t="n"/>
-      <c r="BB22" s="962" t="n"/>
-      <c r="BC22" s="961" t="n"/>
-      <c r="BD22" s="959" t="n"/>
-      <c r="BE22" s="963" t="inlineStr">
-        <is>
-          <t>Candidate (always for flag A) and must be today or later when</t>
-        </is>
-      </c>
-      <c r="BF22" s="961" t="n"/>
-      <c r="BG22" s="961" t="n"/>
-      <c r="BH22" s="961" t="n"/>
-      <c r="BI22" s="961" t="n"/>
-      <c r="BJ22" s="961" t="n"/>
-      <c r="BK22" s="961" t="n"/>
-      <c r="BL22" s="961" t="n"/>
-      <c r="BM22" s="961" t="n"/>
-      <c r="BN22" s="961" t="n"/>
-      <c r="BO22" s="961" t="n"/>
-      <c r="BP22" s="961" t="n"/>
-      <c r="BQ22" s="961" t="n"/>
-      <c r="BR22" s="961" t="n"/>
-      <c r="BS22" s="961" t="n"/>
-      <c r="BT22" s="961" t="n"/>
-      <c r="BU22" s="961" t="n"/>
-      <c r="BV22" s="961" t="n"/>
-      <c r="BW22" s="961" t="n"/>
-      <c r="BX22" s="961" t="n"/>
-      <c r="BY22" s="961" t="n"/>
-      <c r="BZ22" s="961" t="n"/>
-      <c r="CA22" s="961" t="n"/>
-      <c r="CB22" s="961" t="n"/>
-      <c r="CC22" s="961" t="n"/>
-      <c r="CD22" s="961" t="n"/>
-      <c r="CE22" s="961" t="n"/>
-      <c r="CF22" s="961" t="n"/>
-      <c r="CG22" s="961" t="n"/>
-      <c r="CH22" s="961" t="n"/>
-      <c r="CI22" s="959" t="n"/>
-      <c r="CJ22" s="963" t="n"/>
-      <c r="CK22" s="961" t="n"/>
-      <c r="CL22" s="961" t="n"/>
-      <c r="CM22" s="961" t="n"/>
-      <c r="CN22" s="961" t="n"/>
-      <c r="CO22" s="961" t="n"/>
-      <c r="CP22" s="961" t="n"/>
-      <c r="CQ22" s="961" t="n"/>
-      <c r="CR22" s="961" t="n"/>
-      <c r="CS22" s="961" t="n"/>
-      <c r="CT22" s="961" t="n"/>
-      <c r="CU22" s="959" t="n"/>
+      <c r="BB22" s="954" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BC22" s="957" t="n"/>
+      <c r="BD22" s="955" t="n"/>
+      <c r="BE22" s="956" t="inlineStr">
+        <is>
+          <t>Effective Start Date is required when the part status is</t>
+        </is>
+      </c>
+      <c r="BF22" s="957" t="n"/>
+      <c r="BG22" s="957" t="n"/>
+      <c r="BH22" s="957" t="n"/>
+      <c r="BI22" s="957" t="n"/>
+      <c r="BJ22" s="957" t="n"/>
+      <c r="BK22" s="957" t="n"/>
+      <c r="BL22" s="957" t="n"/>
+      <c r="BM22" s="957" t="n"/>
+      <c r="BN22" s="957" t="n"/>
+      <c r="BO22" s="957" t="n"/>
+      <c r="BP22" s="957" t="n"/>
+      <c r="BQ22" s="957" t="n"/>
+      <c r="BR22" s="957" t="n"/>
+      <c r="BS22" s="957" t="n"/>
+      <c r="BT22" s="957" t="n"/>
+      <c r="BU22" s="957" t="n"/>
+      <c r="BV22" s="957" t="n"/>
+      <c r="BW22" s="957" t="n"/>
+      <c r="BX22" s="957" t="n"/>
+      <c r="BY22" s="957" t="n"/>
+      <c r="BZ22" s="957" t="n"/>
+      <c r="CA22" s="957" t="n"/>
+      <c r="CB22" s="957" t="n"/>
+      <c r="CC22" s="957" t="n"/>
+      <c r="CD22" s="957" t="n"/>
+      <c r="CE22" s="957" t="n"/>
+      <c r="CF22" s="957" t="n"/>
+      <c r="CG22" s="957" t="n"/>
+      <c r="CH22" s="957" t="n"/>
+      <c r="CI22" s="955" t="n"/>
+      <c r="CJ22" s="956" t="inlineStr">
+        <is>
+          <t>effective_start_date</t>
+        </is>
+      </c>
+      <c r="CK22" s="957" t="n"/>
+      <c r="CL22" s="957" t="n"/>
+      <c r="CM22" s="957" t="n"/>
+      <c r="CN22" s="957" t="n"/>
+      <c r="CO22" s="957" t="n"/>
+      <c r="CP22" s="957" t="n"/>
+      <c r="CQ22" s="957" t="n"/>
+      <c r="CR22" s="957" t="n"/>
+      <c r="CS22" s="957" t="n"/>
+      <c r="CT22" s="957" t="n"/>
+      <c r="CU22" s="955" t="n"/>
       <c r="CV22" s="941" t="n"/>
       <c r="CW22" s="941" t="n"/>
       <c r="CX22" s="944" t="n"/>
@@ -35480,7 +35484,7 @@
       <c r="BD23" s="959" t="n"/>
       <c r="BE23" s="963" t="inlineStr">
         <is>
-          <t>new or changed.</t>
+          <t>Candidate (always for flag A) and must be today or later when</t>
         </is>
       </c>
       <c r="BF23" s="961" t="n"/>
@@ -35588,64 +35592,56 @@
       <c r="AY24" s="941" t="n"/>
       <c r="AZ24" s="943" t="n"/>
       <c r="BA24" s="941" t="n"/>
-      <c r="BB24" s="954" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BC24" s="957" t="n"/>
-      <c r="BD24" s="955" t="n"/>
-      <c r="BE24" s="956" t="inlineStr">
-        <is>
-          <t>Flag E: Effective Start Date can only change while the part</t>
-        </is>
-      </c>
-      <c r="BF24" s="957" t="n"/>
-      <c r="BG24" s="957" t="n"/>
-      <c r="BH24" s="957" t="n"/>
-      <c r="BI24" s="957" t="n"/>
-      <c r="BJ24" s="957" t="n"/>
-      <c r="BK24" s="957" t="n"/>
-      <c r="BL24" s="957" t="n"/>
-      <c r="BM24" s="957" t="n"/>
-      <c r="BN24" s="957" t="n"/>
-      <c r="BO24" s="957" t="n"/>
-      <c r="BP24" s="957" t="n"/>
-      <c r="BQ24" s="957" t="n"/>
-      <c r="BR24" s="957" t="n"/>
-      <c r="BS24" s="957" t="n"/>
-      <c r="BT24" s="957" t="n"/>
-      <c r="BU24" s="957" t="n"/>
-      <c r="BV24" s="957" t="n"/>
-      <c r="BW24" s="957" t="n"/>
-      <c r="BX24" s="957" t="n"/>
-      <c r="BY24" s="957" t="n"/>
-      <c r="BZ24" s="957" t="n"/>
-      <c r="CA24" s="957" t="n"/>
-      <c r="CB24" s="957" t="n"/>
-      <c r="CC24" s="957" t="n"/>
-      <c r="CD24" s="957" t="n"/>
-      <c r="CE24" s="957" t="n"/>
-      <c r="CF24" s="957" t="n"/>
-      <c r="CG24" s="957" t="n"/>
-      <c r="CH24" s="957" t="n"/>
-      <c r="CI24" s="955" t="n"/>
-      <c r="CJ24" s="956" t="inlineStr">
-        <is>
-          <t>effective_start_date</t>
-        </is>
-      </c>
-      <c r="CK24" s="957" t="n"/>
-      <c r="CL24" s="957" t="n"/>
-      <c r="CM24" s="957" t="n"/>
-      <c r="CN24" s="957" t="n"/>
-      <c r="CO24" s="957" t="n"/>
-      <c r="CP24" s="957" t="n"/>
-      <c r="CQ24" s="957" t="n"/>
-      <c r="CR24" s="957" t="n"/>
-      <c r="CS24" s="957" t="n"/>
-      <c r="CT24" s="957" t="n"/>
-      <c r="CU24" s="955" t="n"/>
+      <c r="BB24" s="962" t="n"/>
+      <c r="BC24" s="961" t="n"/>
+      <c r="BD24" s="959" t="n"/>
+      <c r="BE24" s="963" t="inlineStr">
+        <is>
+          <t>new or changed.</t>
+        </is>
+      </c>
+      <c r="BF24" s="961" t="n"/>
+      <c r="BG24" s="961" t="n"/>
+      <c r="BH24" s="961" t="n"/>
+      <c r="BI24" s="961" t="n"/>
+      <c r="BJ24" s="961" t="n"/>
+      <c r="BK24" s="961" t="n"/>
+      <c r="BL24" s="961" t="n"/>
+      <c r="BM24" s="961" t="n"/>
+      <c r="BN24" s="961" t="n"/>
+      <c r="BO24" s="961" t="n"/>
+      <c r="BP24" s="961" t="n"/>
+      <c r="BQ24" s="961" t="n"/>
+      <c r="BR24" s="961" t="n"/>
+      <c r="BS24" s="961" t="n"/>
+      <c r="BT24" s="961" t="n"/>
+      <c r="BU24" s="961" t="n"/>
+      <c r="BV24" s="961" t="n"/>
+      <c r="BW24" s="961" t="n"/>
+      <c r="BX24" s="961" t="n"/>
+      <c r="BY24" s="961" t="n"/>
+      <c r="BZ24" s="961" t="n"/>
+      <c r="CA24" s="961" t="n"/>
+      <c r="CB24" s="961" t="n"/>
+      <c r="CC24" s="961" t="n"/>
+      <c r="CD24" s="961" t="n"/>
+      <c r="CE24" s="961" t="n"/>
+      <c r="CF24" s="961" t="n"/>
+      <c r="CG24" s="961" t="n"/>
+      <c r="CH24" s="961" t="n"/>
+      <c r="CI24" s="959" t="n"/>
+      <c r="CJ24" s="963" t="n"/>
+      <c r="CK24" s="961" t="n"/>
+      <c r="CL24" s="961" t="n"/>
+      <c r="CM24" s="961" t="n"/>
+      <c r="CN24" s="961" t="n"/>
+      <c r="CO24" s="961" t="n"/>
+      <c r="CP24" s="961" t="n"/>
+      <c r="CQ24" s="961" t="n"/>
+      <c r="CR24" s="961" t="n"/>
+      <c r="CS24" s="961" t="n"/>
+      <c r="CT24" s="961" t="n"/>
+      <c r="CU24" s="959" t="n"/>
       <c r="CV24" s="941" t="n"/>
       <c r="CW24" s="941" t="n"/>
       <c r="CX24" s="944" t="n"/>
@@ -35705,56 +35701,64 @@
       <c r="AY25" s="941" t="n"/>
       <c r="AZ25" s="943" t="n"/>
       <c r="BA25" s="941" t="n"/>
-      <c r="BB25" s="962" t="n"/>
-      <c r="BC25" s="961" t="n"/>
-      <c r="BD25" s="959" t="n"/>
-      <c r="BE25" s="963" t="inlineStr">
-        <is>
-          <t>status is Candidate.</t>
-        </is>
-      </c>
-      <c r="BF25" s="961" t="n"/>
-      <c r="BG25" s="961" t="n"/>
-      <c r="BH25" s="961" t="n"/>
-      <c r="BI25" s="961" t="n"/>
-      <c r="BJ25" s="961" t="n"/>
-      <c r="BK25" s="961" t="n"/>
-      <c r="BL25" s="961" t="n"/>
-      <c r="BM25" s="961" t="n"/>
-      <c r="BN25" s="961" t="n"/>
-      <c r="BO25" s="961" t="n"/>
-      <c r="BP25" s="961" t="n"/>
-      <c r="BQ25" s="961" t="n"/>
-      <c r="BR25" s="961" t="n"/>
-      <c r="BS25" s="961" t="n"/>
-      <c r="BT25" s="961" t="n"/>
-      <c r="BU25" s="961" t="n"/>
-      <c r="BV25" s="961" t="n"/>
-      <c r="BW25" s="961" t="n"/>
-      <c r="BX25" s="961" t="n"/>
-      <c r="BY25" s="961" t="n"/>
-      <c r="BZ25" s="961" t="n"/>
-      <c r="CA25" s="961" t="n"/>
-      <c r="CB25" s="961" t="n"/>
-      <c r="CC25" s="961" t="n"/>
-      <c r="CD25" s="961" t="n"/>
-      <c r="CE25" s="961" t="n"/>
-      <c r="CF25" s="961" t="n"/>
-      <c r="CG25" s="961" t="n"/>
-      <c r="CH25" s="961" t="n"/>
-      <c r="CI25" s="959" t="n"/>
-      <c r="CJ25" s="963" t="n"/>
-      <c r="CK25" s="961" t="n"/>
-      <c r="CL25" s="961" t="n"/>
-      <c r="CM25" s="961" t="n"/>
-      <c r="CN25" s="961" t="n"/>
-      <c r="CO25" s="961" t="n"/>
-      <c r="CP25" s="961" t="n"/>
-      <c r="CQ25" s="961" t="n"/>
-      <c r="CR25" s="961" t="n"/>
-      <c r="CS25" s="961" t="n"/>
-      <c r="CT25" s="961" t="n"/>
-      <c r="CU25" s="959" t="n"/>
+      <c r="BB25" s="954" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BC25" s="957" t="n"/>
+      <c r="BD25" s="955" t="n"/>
+      <c r="BE25" s="956" t="inlineStr">
+        <is>
+          <t>Flag E: Effective Start Date can only change while the part</t>
+        </is>
+      </c>
+      <c r="BF25" s="957" t="n"/>
+      <c r="BG25" s="957" t="n"/>
+      <c r="BH25" s="957" t="n"/>
+      <c r="BI25" s="957" t="n"/>
+      <c r="BJ25" s="957" t="n"/>
+      <c r="BK25" s="957" t="n"/>
+      <c r="BL25" s="957" t="n"/>
+      <c r="BM25" s="957" t="n"/>
+      <c r="BN25" s="957" t="n"/>
+      <c r="BO25" s="957" t="n"/>
+      <c r="BP25" s="957" t="n"/>
+      <c r="BQ25" s="957" t="n"/>
+      <c r="BR25" s="957" t="n"/>
+      <c r="BS25" s="957" t="n"/>
+      <c r="BT25" s="957" t="n"/>
+      <c r="BU25" s="957" t="n"/>
+      <c r="BV25" s="957" t="n"/>
+      <c r="BW25" s="957" t="n"/>
+      <c r="BX25" s="957" t="n"/>
+      <c r="BY25" s="957" t="n"/>
+      <c r="BZ25" s="957" t="n"/>
+      <c r="CA25" s="957" t="n"/>
+      <c r="CB25" s="957" t="n"/>
+      <c r="CC25" s="957" t="n"/>
+      <c r="CD25" s="957" t="n"/>
+      <c r="CE25" s="957" t="n"/>
+      <c r="CF25" s="957" t="n"/>
+      <c r="CG25" s="957" t="n"/>
+      <c r="CH25" s="957" t="n"/>
+      <c r="CI25" s="955" t="n"/>
+      <c r="CJ25" s="956" t="inlineStr">
+        <is>
+          <t>effective_start_date</t>
+        </is>
+      </c>
+      <c r="CK25" s="957" t="n"/>
+      <c r="CL25" s="957" t="n"/>
+      <c r="CM25" s="957" t="n"/>
+      <c r="CN25" s="957" t="n"/>
+      <c r="CO25" s="957" t="n"/>
+      <c r="CP25" s="957" t="n"/>
+      <c r="CQ25" s="957" t="n"/>
+      <c r="CR25" s="957" t="n"/>
+      <c r="CS25" s="957" t="n"/>
+      <c r="CT25" s="957" t="n"/>
+      <c r="CU25" s="955" t="n"/>
       <c r="CV25" s="941" t="n"/>
       <c r="CW25" s="941" t="n"/>
       <c r="CX25" s="944" t="n"/>
@@ -35818,64 +35822,56 @@
       <c r="AY26" s="941" t="n"/>
       <c r="AZ26" s="943" t="n"/>
       <c r="BA26" s="941" t="n"/>
-      <c r="BB26" s="954" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BC26" s="957" t="n"/>
-      <c r="BD26" s="955" t="n"/>
-      <c r="BE26" s="956" t="inlineStr">
-        <is>
-          <t>Flag E: Max Case/Day is not below the total Case/Day already</t>
-        </is>
-      </c>
-      <c r="BF26" s="957" t="n"/>
-      <c r="BG26" s="957" t="n"/>
-      <c r="BH26" s="957" t="n"/>
-      <c r="BI26" s="957" t="n"/>
-      <c r="BJ26" s="957" t="n"/>
-      <c r="BK26" s="957" t="n"/>
-      <c r="BL26" s="957" t="n"/>
-      <c r="BM26" s="957" t="n"/>
-      <c r="BN26" s="957" t="n"/>
-      <c r="BO26" s="957" t="n"/>
-      <c r="BP26" s="957" t="n"/>
-      <c r="BQ26" s="957" t="n"/>
-      <c r="BR26" s="957" t="n"/>
-      <c r="BS26" s="957" t="n"/>
-      <c r="BT26" s="957" t="n"/>
-      <c r="BU26" s="957" t="n"/>
-      <c r="BV26" s="957" t="n"/>
-      <c r="BW26" s="957" t="n"/>
-      <c r="BX26" s="957" t="n"/>
-      <c r="BY26" s="957" t="n"/>
-      <c r="BZ26" s="957" t="n"/>
-      <c r="CA26" s="957" t="n"/>
-      <c r="CB26" s="957" t="n"/>
-      <c r="CC26" s="957" t="n"/>
-      <c r="CD26" s="957" t="n"/>
-      <c r="CE26" s="957" t="n"/>
-      <c r="CF26" s="957" t="n"/>
-      <c r="CG26" s="957" t="n"/>
-      <c r="CH26" s="957" t="n"/>
-      <c r="CI26" s="955" t="n"/>
-      <c r="CJ26" s="956" t="inlineStr">
-        <is>
-          <t>max_case_day</t>
-        </is>
-      </c>
-      <c r="CK26" s="957" t="n"/>
-      <c r="CL26" s="957" t="n"/>
-      <c r="CM26" s="957" t="n"/>
-      <c r="CN26" s="957" t="n"/>
-      <c r="CO26" s="957" t="n"/>
-      <c r="CP26" s="957" t="n"/>
-      <c r="CQ26" s="957" t="n"/>
-      <c r="CR26" s="957" t="n"/>
-      <c r="CS26" s="957" t="n"/>
-      <c r="CT26" s="957" t="n"/>
-      <c r="CU26" s="955" t="n"/>
+      <c r="BB26" s="962" t="n"/>
+      <c r="BC26" s="961" t="n"/>
+      <c r="BD26" s="959" t="n"/>
+      <c r="BE26" s="963" t="inlineStr">
+        <is>
+          <t>status is Candidate.</t>
+        </is>
+      </c>
+      <c r="BF26" s="961" t="n"/>
+      <c r="BG26" s="961" t="n"/>
+      <c r="BH26" s="961" t="n"/>
+      <c r="BI26" s="961" t="n"/>
+      <c r="BJ26" s="961" t="n"/>
+      <c r="BK26" s="961" t="n"/>
+      <c r="BL26" s="961" t="n"/>
+      <c r="BM26" s="961" t="n"/>
+      <c r="BN26" s="961" t="n"/>
+      <c r="BO26" s="961" t="n"/>
+      <c r="BP26" s="961" t="n"/>
+      <c r="BQ26" s="961" t="n"/>
+      <c r="BR26" s="961" t="n"/>
+      <c r="BS26" s="961" t="n"/>
+      <c r="BT26" s="961" t="n"/>
+      <c r="BU26" s="961" t="n"/>
+      <c r="BV26" s="961" t="n"/>
+      <c r="BW26" s="961" t="n"/>
+      <c r="BX26" s="961" t="n"/>
+      <c r="BY26" s="961" t="n"/>
+      <c r="BZ26" s="961" t="n"/>
+      <c r="CA26" s="961" t="n"/>
+      <c r="CB26" s="961" t="n"/>
+      <c r="CC26" s="961" t="n"/>
+      <c r="CD26" s="961" t="n"/>
+      <c r="CE26" s="961" t="n"/>
+      <c r="CF26" s="961" t="n"/>
+      <c r="CG26" s="961" t="n"/>
+      <c r="CH26" s="961" t="n"/>
+      <c r="CI26" s="959" t="n"/>
+      <c r="CJ26" s="963" t="n"/>
+      <c r="CK26" s="961" t="n"/>
+      <c r="CL26" s="961" t="n"/>
+      <c r="CM26" s="961" t="n"/>
+      <c r="CN26" s="961" t="n"/>
+      <c r="CO26" s="961" t="n"/>
+      <c r="CP26" s="961" t="n"/>
+      <c r="CQ26" s="961" t="n"/>
+      <c r="CR26" s="961" t="n"/>
+      <c r="CS26" s="961" t="n"/>
+      <c r="CT26" s="961" t="n"/>
+      <c r="CU26" s="959" t="n"/>
       <c r="CV26" s="941" t="n"/>
       <c r="CW26" s="941" t="n"/>
       <c r="CX26" s="944" t="n"/>
@@ -35943,56 +35939,64 @@
       <c r="AY27" s="941" t="n"/>
       <c r="AZ27" s="943" t="n"/>
       <c r="BA27" s="941" t="n"/>
-      <c r="BB27" s="962" t="n"/>
-      <c r="BC27" s="961" t="n"/>
-      <c r="BD27" s="959" t="n"/>
-      <c r="BE27" s="963" t="inlineStr">
-        <is>
-          <t>mapped per destination in the ongoing calculation period of</t>
-        </is>
-      </c>
-      <c r="BF27" s="961" t="n"/>
-      <c r="BG27" s="961" t="n"/>
-      <c r="BH27" s="961" t="n"/>
-      <c r="BI27" s="961" t="n"/>
-      <c r="BJ27" s="961" t="n"/>
-      <c r="BK27" s="961" t="n"/>
-      <c r="BL27" s="961" t="n"/>
-      <c r="BM27" s="961" t="n"/>
-      <c r="BN27" s="961" t="n"/>
-      <c r="BO27" s="961" t="n"/>
-      <c r="BP27" s="961" t="n"/>
-      <c r="BQ27" s="961" t="n"/>
-      <c r="BR27" s="961" t="n"/>
-      <c r="BS27" s="961" t="n"/>
-      <c r="BT27" s="961" t="n"/>
-      <c r="BU27" s="961" t="n"/>
-      <c r="BV27" s="961" t="n"/>
-      <c r="BW27" s="961" t="n"/>
-      <c r="BX27" s="961" t="n"/>
-      <c r="BY27" s="961" t="n"/>
-      <c r="BZ27" s="961" t="n"/>
-      <c r="CA27" s="961" t="n"/>
-      <c r="CB27" s="961" t="n"/>
-      <c r="CC27" s="961" t="n"/>
-      <c r="CD27" s="961" t="n"/>
-      <c r="CE27" s="961" t="n"/>
-      <c r="CF27" s="961" t="n"/>
-      <c r="CG27" s="961" t="n"/>
-      <c r="CH27" s="961" t="n"/>
-      <c r="CI27" s="959" t="n"/>
-      <c r="CJ27" s="963" t="n"/>
-      <c r="CK27" s="961" t="n"/>
-      <c r="CL27" s="961" t="n"/>
-      <c r="CM27" s="961" t="n"/>
-      <c r="CN27" s="961" t="n"/>
-      <c r="CO27" s="961" t="n"/>
-      <c r="CP27" s="961" t="n"/>
-      <c r="CQ27" s="961" t="n"/>
-      <c r="CR27" s="961" t="n"/>
-      <c r="CS27" s="961" t="n"/>
-      <c r="CT27" s="961" t="n"/>
-      <c r="CU27" s="959" t="n"/>
+      <c r="BB27" s="954" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BC27" s="957" t="n"/>
+      <c r="BD27" s="955" t="n"/>
+      <c r="BE27" s="956" t="inlineStr">
+        <is>
+          <t>Flag E: Max Case/Day is not below the total Case/Day already</t>
+        </is>
+      </c>
+      <c r="BF27" s="957" t="n"/>
+      <c r="BG27" s="957" t="n"/>
+      <c r="BH27" s="957" t="n"/>
+      <c r="BI27" s="957" t="n"/>
+      <c r="BJ27" s="957" t="n"/>
+      <c r="BK27" s="957" t="n"/>
+      <c r="BL27" s="957" t="n"/>
+      <c r="BM27" s="957" t="n"/>
+      <c r="BN27" s="957" t="n"/>
+      <c r="BO27" s="957" t="n"/>
+      <c r="BP27" s="957" t="n"/>
+      <c r="BQ27" s="957" t="n"/>
+      <c r="BR27" s="957" t="n"/>
+      <c r="BS27" s="957" t="n"/>
+      <c r="BT27" s="957" t="n"/>
+      <c r="BU27" s="957" t="n"/>
+      <c r="BV27" s="957" t="n"/>
+      <c r="BW27" s="957" t="n"/>
+      <c r="BX27" s="957" t="n"/>
+      <c r="BY27" s="957" t="n"/>
+      <c r="BZ27" s="957" t="n"/>
+      <c r="CA27" s="957" t="n"/>
+      <c r="CB27" s="957" t="n"/>
+      <c r="CC27" s="957" t="n"/>
+      <c r="CD27" s="957" t="n"/>
+      <c r="CE27" s="957" t="n"/>
+      <c r="CF27" s="957" t="n"/>
+      <c r="CG27" s="957" t="n"/>
+      <c r="CH27" s="957" t="n"/>
+      <c r="CI27" s="955" t="n"/>
+      <c r="CJ27" s="956" t="inlineStr">
+        <is>
+          <t>max_case_day</t>
+        </is>
+      </c>
+      <c r="CK27" s="957" t="n"/>
+      <c r="CL27" s="957" t="n"/>
+      <c r="CM27" s="957" t="n"/>
+      <c r="CN27" s="957" t="n"/>
+      <c r="CO27" s="957" t="n"/>
+      <c r="CP27" s="957" t="n"/>
+      <c r="CQ27" s="957" t="n"/>
+      <c r="CR27" s="957" t="n"/>
+      <c r="CS27" s="957" t="n"/>
+      <c r="CT27" s="957" t="n"/>
+      <c r="CU27" s="955" t="n"/>
       <c r="CV27" s="941" t="n"/>
       <c r="CW27" s="941" t="n"/>
       <c r="CX27" s="944" t="n"/>
@@ -36061,7 +36065,7 @@
       <c r="BD28" s="959" t="n"/>
       <c r="BE28" s="963" t="inlineStr">
         <is>
-          <t>Mapping per Destination (TB_M_PART_CANDIDATE_DEST)</t>
+          <t>mapped per destination in the ongoing calculation period of</t>
         </is>
       </c>
       <c r="BF28" s="961" t="n"/>
@@ -36178,7 +36182,7 @@
       <c r="BD29" s="959" t="n"/>
       <c r="BE29" s="963" t="inlineStr">
         <is>
-          <t>(e.g. mapped 100, new Max Case/Day 80 is rejected). The</t>
+          <t>Mapping per Destination (TB_M_PART_CANDIDATE_DEST)</t>
         </is>
       </c>
       <c r="BF29" s="961" t="n"/>
@@ -36291,7 +36295,7 @@
       <c r="BD30" s="959" t="n"/>
       <c r="BE30" s="963" t="inlineStr">
         <is>
-          <t>user must first reduce the mapping in the Mapping per</t>
+          <t>(e.g. mapped 100, new Max Case/Day 80 is rejected). The</t>
         </is>
       </c>
       <c r="BF30" s="961" t="n"/>
@@ -36399,56 +36403,56 @@
       <c r="AY31" s="941" t="n"/>
       <c r="AZ31" s="943" t="n"/>
       <c r="BA31" s="941" t="n"/>
-      <c r="BB31" s="969" t="n"/>
-      <c r="BC31" s="972" t="n"/>
-      <c r="BD31" s="970" t="n"/>
-      <c r="BE31" s="975" t="inlineStr">
-        <is>
-          <t>Destination sub-menu, then lower Max Case/Day in Part List.</t>
-        </is>
-      </c>
-      <c r="BF31" s="972" t="n"/>
-      <c r="BG31" s="972" t="n"/>
-      <c r="BH31" s="972" t="n"/>
-      <c r="BI31" s="972" t="n"/>
-      <c r="BJ31" s="972" t="n"/>
-      <c r="BK31" s="972" t="n"/>
-      <c r="BL31" s="972" t="n"/>
-      <c r="BM31" s="972" t="n"/>
-      <c r="BN31" s="972" t="n"/>
-      <c r="BO31" s="972" t="n"/>
-      <c r="BP31" s="972" t="n"/>
-      <c r="BQ31" s="972" t="n"/>
-      <c r="BR31" s="972" t="n"/>
-      <c r="BS31" s="972" t="n"/>
-      <c r="BT31" s="972" t="n"/>
-      <c r="BU31" s="972" t="n"/>
-      <c r="BV31" s="972" t="n"/>
-      <c r="BW31" s="972" t="n"/>
-      <c r="BX31" s="972" t="n"/>
-      <c r="BY31" s="972" t="n"/>
-      <c r="BZ31" s="972" t="n"/>
-      <c r="CA31" s="972" t="n"/>
-      <c r="CB31" s="972" t="n"/>
-      <c r="CC31" s="972" t="n"/>
-      <c r="CD31" s="972" t="n"/>
-      <c r="CE31" s="972" t="n"/>
-      <c r="CF31" s="972" t="n"/>
-      <c r="CG31" s="972" t="n"/>
-      <c r="CH31" s="972" t="n"/>
-      <c r="CI31" s="970" t="n"/>
-      <c r="CJ31" s="975" t="n"/>
-      <c r="CK31" s="972" t="n"/>
-      <c r="CL31" s="972" t="n"/>
-      <c r="CM31" s="972" t="n"/>
-      <c r="CN31" s="972" t="n"/>
-      <c r="CO31" s="972" t="n"/>
-      <c r="CP31" s="972" t="n"/>
-      <c r="CQ31" s="972" t="n"/>
-      <c r="CR31" s="972" t="n"/>
-      <c r="CS31" s="972" t="n"/>
-      <c r="CT31" s="972" t="n"/>
-      <c r="CU31" s="970" t="n"/>
+      <c r="BB31" s="962" t="n"/>
+      <c r="BC31" s="961" t="n"/>
+      <c r="BD31" s="959" t="n"/>
+      <c r="BE31" s="963" t="inlineStr">
+        <is>
+          <t>user must first reduce the mapping in the Mapping per</t>
+        </is>
+      </c>
+      <c r="BF31" s="961" t="n"/>
+      <c r="BG31" s="961" t="n"/>
+      <c r="BH31" s="961" t="n"/>
+      <c r="BI31" s="961" t="n"/>
+      <c r="BJ31" s="961" t="n"/>
+      <c r="BK31" s="961" t="n"/>
+      <c r="BL31" s="961" t="n"/>
+      <c r="BM31" s="961" t="n"/>
+      <c r="BN31" s="961" t="n"/>
+      <c r="BO31" s="961" t="n"/>
+      <c r="BP31" s="961" t="n"/>
+      <c r="BQ31" s="961" t="n"/>
+      <c r="BR31" s="961" t="n"/>
+      <c r="BS31" s="961" t="n"/>
+      <c r="BT31" s="961" t="n"/>
+      <c r="BU31" s="961" t="n"/>
+      <c r="BV31" s="961" t="n"/>
+      <c r="BW31" s="961" t="n"/>
+      <c r="BX31" s="961" t="n"/>
+      <c r="BY31" s="961" t="n"/>
+      <c r="BZ31" s="961" t="n"/>
+      <c r="CA31" s="961" t="n"/>
+      <c r="CB31" s="961" t="n"/>
+      <c r="CC31" s="961" t="n"/>
+      <c r="CD31" s="961" t="n"/>
+      <c r="CE31" s="961" t="n"/>
+      <c r="CF31" s="961" t="n"/>
+      <c r="CG31" s="961" t="n"/>
+      <c r="CH31" s="961" t="n"/>
+      <c r="CI31" s="959" t="n"/>
+      <c r="CJ31" s="963" t="n"/>
+      <c r="CK31" s="961" t="n"/>
+      <c r="CL31" s="961" t="n"/>
+      <c r="CM31" s="961" t="n"/>
+      <c r="CN31" s="961" t="n"/>
+      <c r="CO31" s="961" t="n"/>
+      <c r="CP31" s="961" t="n"/>
+      <c r="CQ31" s="961" t="n"/>
+      <c r="CR31" s="961" t="n"/>
+      <c r="CS31" s="961" t="n"/>
+      <c r="CT31" s="961" t="n"/>
+      <c r="CU31" s="959" t="n"/>
       <c r="CV31" s="941" t="n"/>
       <c r="CW31" s="941" t="n"/>
       <c r="CX31" s="944" t="n"/>
@@ -36516,52 +36520,56 @@
       <c r="AY32" s="941" t="n"/>
       <c r="AZ32" s="943" t="n"/>
       <c r="BA32" s="941" t="n"/>
-      <c r="BB32" s="941" t="n"/>
-      <c r="BC32" s="941" t="n"/>
-      <c r="BD32" s="941" t="n"/>
-      <c r="BE32" s="941" t="n"/>
-      <c r="BF32" s="941" t="n"/>
-      <c r="BG32" s="941" t="n"/>
-      <c r="BH32" s="941" t="n"/>
-      <c r="BI32" s="941" t="n"/>
-      <c r="BJ32" s="941" t="n"/>
-      <c r="BK32" s="941" t="n"/>
-      <c r="BL32" s="941" t="n"/>
-      <c r="BM32" s="941" t="n"/>
-      <c r="BN32" s="941" t="n"/>
-      <c r="BO32" s="941" t="n"/>
-      <c r="BP32" s="941" t="n"/>
-      <c r="BQ32" s="941" t="n"/>
-      <c r="BR32" s="941" t="n"/>
-      <c r="BS32" s="941" t="n"/>
-      <c r="BT32" s="941" t="n"/>
-      <c r="BU32" s="941" t="n"/>
-      <c r="BV32" s="941" t="n"/>
-      <c r="BW32" s="941" t="n"/>
-      <c r="BX32" s="941" t="n"/>
-      <c r="BY32" s="941" t="n"/>
-      <c r="BZ32" s="941" t="n"/>
-      <c r="CA32" s="941" t="n"/>
-      <c r="CB32" s="941" t="n"/>
-      <c r="CC32" s="941" t="n"/>
-      <c r="CD32" s="941" t="n"/>
-      <c r="CE32" s="941" t="n"/>
-      <c r="CF32" s="941" t="n"/>
-      <c r="CG32" s="941" t="n"/>
-      <c r="CH32" s="941" t="n"/>
-      <c r="CI32" s="941" t="n"/>
-      <c r="CJ32" s="941" t="n"/>
-      <c r="CK32" s="941" t="n"/>
-      <c r="CL32" s="941" t="n"/>
-      <c r="CM32" s="941" t="n"/>
-      <c r="CN32" s="941" t="n"/>
-      <c r="CO32" s="941" t="n"/>
-      <c r="CP32" s="941" t="n"/>
-      <c r="CQ32" s="941" t="n"/>
-      <c r="CR32" s="941" t="n"/>
-      <c r="CS32" s="941" t="n"/>
-      <c r="CT32" s="941" t="n"/>
-      <c r="CU32" s="941" t="n"/>
+      <c r="BB32" s="969" t="n"/>
+      <c r="BC32" s="972" t="n"/>
+      <c r="BD32" s="970" t="n"/>
+      <c r="BE32" s="975" t="inlineStr">
+        <is>
+          <t>Destination sub-menu, then lower Max Case/Day in Part List.</t>
+        </is>
+      </c>
+      <c r="BF32" s="972" t="n"/>
+      <c r="BG32" s="972" t="n"/>
+      <c r="BH32" s="972" t="n"/>
+      <c r="BI32" s="972" t="n"/>
+      <c r="BJ32" s="972" t="n"/>
+      <c r="BK32" s="972" t="n"/>
+      <c r="BL32" s="972" t="n"/>
+      <c r="BM32" s="972" t="n"/>
+      <c r="BN32" s="972" t="n"/>
+      <c r="BO32" s="972" t="n"/>
+      <c r="BP32" s="972" t="n"/>
+      <c r="BQ32" s="972" t="n"/>
+      <c r="BR32" s="972" t="n"/>
+      <c r="BS32" s="972" t="n"/>
+      <c r="BT32" s="972" t="n"/>
+      <c r="BU32" s="972" t="n"/>
+      <c r="BV32" s="972" t="n"/>
+      <c r="BW32" s="972" t="n"/>
+      <c r="BX32" s="972" t="n"/>
+      <c r="BY32" s="972" t="n"/>
+      <c r="BZ32" s="972" t="n"/>
+      <c r="CA32" s="972" t="n"/>
+      <c r="CB32" s="972" t="n"/>
+      <c r="CC32" s="972" t="n"/>
+      <c r="CD32" s="972" t="n"/>
+      <c r="CE32" s="972" t="n"/>
+      <c r="CF32" s="972" t="n"/>
+      <c r="CG32" s="972" t="n"/>
+      <c r="CH32" s="972" t="n"/>
+      <c r="CI32" s="970" t="n"/>
+      <c r="CJ32" s="975" t="n"/>
+      <c r="CK32" s="972" t="n"/>
+      <c r="CL32" s="972" t="n"/>
+      <c r="CM32" s="972" t="n"/>
+      <c r="CN32" s="972" t="n"/>
+      <c r="CO32" s="972" t="n"/>
+      <c r="CP32" s="972" t="n"/>
+      <c r="CQ32" s="972" t="n"/>
+      <c r="CR32" s="972" t="n"/>
+      <c r="CS32" s="972" t="n"/>
+      <c r="CT32" s="972" t="n"/>
+      <c r="CU32" s="970" t="n"/>
       <c r="CV32" s="941" t="n"/>
       <c r="CW32" s="941" t="n"/>
       <c r="CX32" s="944" t="n"/>
@@ -38272,7 +38280,7 @@
       <c r="CY48" s="941" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="98">
     <mergeCell ref="CJ8:CU8"/>
     <mergeCell ref="BE12:CI12"/>
     <mergeCell ref="CJ26:CU26"/>
@@ -38315,6 +38323,7 @@
     <mergeCell ref="BE29:CI29"/>
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="CC3:CJ3"/>
+    <mergeCell ref="BE32:CI32"/>
     <mergeCell ref="BB30:BD30"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BB29:BD29"/>
@@ -38359,6 +38368,8 @@
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="BE18:CI18"/>
     <mergeCell ref="CC4:CJ4"/>
+    <mergeCell ref="BB32:BD32"/>
+    <mergeCell ref="CJ32:CU32"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="CJ13:CU13"/>
     <mergeCell ref="BB16:BD16"/>
@@ -44492,7 +44503,7 @@
       <c r="B11" s="942" t="n"/>
       <c r="C11" s="956" t="inlineStr">
         <is>
-          <t>minimum_mad</t>
+          <t>mad</t>
         </is>
       </c>
       <c r="D11" s="957" t="n"/>
@@ -44512,7 +44523,7 @@
       <c r="R11" s="955" t="n"/>
       <c r="S11" s="956" t="inlineStr">
         <is>
-          <t>Minimum MAD</t>
+          <t>MAD (optional; filled later by the MAD calculation function)</t>
         </is>
       </c>
       <c r="T11" s="957" t="n"/>
@@ -46298,7 +46309,7 @@
       <c r="D27" s="941" t="n"/>
       <c r="E27" s="966" t="inlineStr">
         <is>
-          <t>MIN_MAD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="F27" s="957" t="n"/>
@@ -46337,7 +46348,7 @@
       <c r="AI27" s="955" t="n"/>
       <c r="AJ27" s="965" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AK27" s="957" t="n"/>
@@ -46345,7 +46356,7 @@
       <c r="AM27" s="955" t="n"/>
       <c r="AN27" s="956" t="inlineStr">
         <is>
-          <t>Minimum MAD</t>
+          <t>MAD; result of the MAD calculation function, optional on Add / Upload</t>
         </is>
       </c>
       <c r="AO27" s="957" t="n"/>
@@ -48987,7 +48998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="710" min="1" max="1"/>
@@ -49043,7 +49054,7 @@
       </c>
       <c r="C6" s="1052" t="inlineStr">
         <is>
-          <t>Min MAD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D6" s="1052" t="inlineStr">
@@ -49305,7 +49316,7 @@
       </c>
       <c r="D16" s="1052" t="inlineStr">
         <is>
-          <t>minimum_mad</t>
+          <t>mad</t>
         </is>
       </c>
       <c r="E16" s="1052" t="inlineStr">
@@ -49675,268 +49686,262 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1051" t="inlineStr">
-        <is>
-          <t>C. Error scenarios (whole file rejected, nothing saved)</t>
+    <row r="25">
+      <c r="A25" s="1053" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="B25" s="1053" t="inlineStr">
+        <is>
+          <t>Add a new part without MAD</t>
+        </is>
+      </c>
+      <c r="C25" s="1053" t="inlineStr">
+        <is>
+          <t>PART-M03</t>
+        </is>
+      </c>
+      <c r="D25" s="1053" t="n"/>
+      <c r="E25" s="1054" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="1054" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1053" t="n"/>
+      <c r="H25" s="1053" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I25" s="1053" t="inlineStr">
+        <is>
+          <t>15-Sep-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="1053" t="inlineStr">
+        <is>
+          <t>Inserted. MAD stays blank until the MAD calculation function fills it.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1052" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B27" s="1052" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C27" s="1052" t="inlineStr">
-        <is>
-          <t>part_no</t>
-        </is>
-      </c>
-      <c r="D27" s="1052" t="inlineStr">
-        <is>
-          <t>minimum_mad</t>
-        </is>
-      </c>
-      <c r="E27" s="1052" t="inlineStr">
-        <is>
-          <t>pcs_case</t>
-        </is>
-      </c>
-      <c r="F27" s="1052" t="inlineStr">
-        <is>
-          <t>max_case_day</t>
-        </is>
-      </c>
-      <c r="G27" s="1052" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="H27" s="1052" t="inlineStr">
-        <is>
-          <t>flag_add_edit</t>
-        </is>
-      </c>
-      <c r="I27" s="1052" t="inlineStr">
-        <is>
-          <t>effective_start_date</t>
-        </is>
-      </c>
-      <c r="J27" s="1052" t="inlineStr">
-        <is>
-          <t>Error (4.2 check no.)</t>
+      <c r="A27" s="1051" t="inlineStr">
+        <is>
+          <t>C. Error scenarios (whole file rejected, nothing saved)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1053" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B28" s="1053" t="inlineStr">
-        <is>
-          <t>Flag is not A or E</t>
-        </is>
-      </c>
-      <c r="C28" s="1053" t="inlineStr">
-        <is>
-          <t>PART-I</t>
-        </is>
-      </c>
-      <c r="D28" s="1054" t="n">
-        <v>300</v>
-      </c>
-      <c r="E28" s="1054" t="n">
-        <v>15</v>
-      </c>
-      <c r="F28" s="1054" t="n">
-        <v>18</v>
-      </c>
-      <c r="G28" s="1053" t="n"/>
-      <c r="H28" s="1053" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I28" s="1053" t="inlineStr">
-        <is>
-          <t>20-Sep-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="1053" t="inlineStr">
-        <is>
-          <t>Check 1: flag_add_edit must be A or E.</t>
+      <c r="A28" s="1052" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B28" s="1052" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C28" s="1052" t="inlineStr">
+        <is>
+          <t>part_no</t>
+        </is>
+      </c>
+      <c r="D28" s="1052" t="inlineStr">
+        <is>
+          <t>mad</t>
+        </is>
+      </c>
+      <c r="E28" s="1052" t="inlineStr">
+        <is>
+          <t>pcs_case</t>
+        </is>
+      </c>
+      <c r="F28" s="1052" t="inlineStr">
+        <is>
+          <t>max_case_day</t>
+        </is>
+      </c>
+      <c r="G28" s="1052" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H28" s="1052" t="inlineStr">
+        <is>
+          <t>flag_add_edit</t>
+        </is>
+      </c>
+      <c r="I28" s="1052" t="inlineStr">
+        <is>
+          <t>effective_start_date</t>
+        </is>
+      </c>
+      <c r="J28" s="1052" t="inlineStr">
+        <is>
+          <t>Error (4.2 check no.)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1053" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B29" s="1053" t="inlineStr">
         <is>
-          <t>Part not in part master</t>
+          <t>Flag is not A or E</t>
         </is>
       </c>
       <c r="C29" s="1053" t="inlineStr">
         <is>
-          <t>PART-Z99</t>
+          <t>PART-I</t>
         </is>
       </c>
       <c r="D29" s="1054" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E29" s="1054" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1054" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G29" s="1053" t="n"/>
       <c r="H29" s="1053" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="I29" s="1053" t="n"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" s="1053" t="inlineStr">
+        <is>
+          <t>20-Sep-2026</t>
+        </is>
+      </c>
       <c r="J29" s="1053" t="inlineStr">
         <is>
-          <t>Check 2: Part No not found in TB_M_PART_MASTER.</t>
+          <t>Check 1: flag_add_edit must be A or E.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1053" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B30" s="1053" t="inlineStr">
         <is>
-          <t>Add a part that is already registered</t>
+          <t>Part not in part master</t>
         </is>
       </c>
       <c r="C30" s="1053" t="inlineStr">
         <is>
-          <t>PART-A</t>
+          <t>PART-Z99</t>
         </is>
       </c>
       <c r="D30" s="1054" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E30" s="1054" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1054" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1053" t="n"/>
       <c r="H30" s="1053" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I30" s="1053" t="inlineStr">
-        <is>
-          <t>14-Sep-2026</t>
-        </is>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I30" s="1053" t="n"/>
       <c r="J30" s="1053" t="inlineStr">
         <is>
-          <t>Check 3: Part No already registered, use flag E.</t>
+          <t>Check 2: Part No not found in TB_M_PART_MASTER.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1053" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B31" s="1053" t="inlineStr">
         <is>
-          <t>Edit a part that is not registered</t>
+          <t>Add a part that is already registered</t>
         </is>
       </c>
       <c r="C31" s="1053" t="inlineStr">
         <is>
-          <t>PART-M03</t>
+          <t>PART-A</t>
         </is>
       </c>
       <c r="D31" s="1054" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E31" s="1054" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F31" s="1054" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G31" s="1053" t="n"/>
       <c r="H31" s="1053" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="I31" s="1053" t="n"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I31" s="1053" t="inlineStr">
+        <is>
+          <t>14-Sep-2026</t>
+        </is>
+      </c>
       <c r="J31" s="1053" t="inlineStr">
         <is>
-          <t>Check 3: Part No not registered, use flag A.</t>
+          <t>Check 3: Part No already registered, use flag E.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1053" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B32" s="1053" t="inlineStr">
         <is>
-          <t>Same part twice in the file (row 1)</t>
+          <t>Edit a part that is not registered</t>
         </is>
       </c>
       <c r="C32" s="1053" t="inlineStr">
         <is>
-          <t>PART-I</t>
+          <t>PART-M03</t>
         </is>
       </c>
       <c r="D32" s="1054" t="n">
         <v>300</v>
       </c>
       <c r="E32" s="1054" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="1054" t="n">
         <v>15</v>
       </c>
-      <c r="F32" s="1054" t="n">
-        <v>18</v>
-      </c>
-      <c r="G32" s="1053" t="inlineStr">
-        <is>
-          <t>Candidate</t>
-        </is>
-      </c>
+      <c r="G32" s="1053" t="n"/>
       <c r="H32" s="1053" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I32" s="1053" t="inlineStr">
-        <is>
-          <t>20-Sep-2026</t>
-        </is>
-      </c>
+      <c r="I32" s="1053" t="n"/>
       <c r="J32" s="1053" t="inlineStr">
         <is>
-          <t>Check 4: Part No appears more than once.</t>
+          <t>Check 3: Part No not registered, use flag A.</t>
         </is>
       </c>
     </row>
@@ -49948,7 +49953,7 @@
       </c>
       <c r="B33" s="1053" t="inlineStr">
         <is>
-          <t>Same part twice in the file (row 2)</t>
+          <t>Same part twice in the file (row 1)</t>
         </is>
       </c>
       <c r="C33" s="1053" t="inlineStr">
@@ -49963,7 +49968,7 @@
         <v>15</v>
       </c>
       <c r="F33" s="1054" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G33" s="1053" t="inlineStr">
         <is>
@@ -49989,119 +49994,119 @@
     <row r="34">
       <c r="A34" s="1053" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B34" s="1053" t="inlineStr">
         <is>
-          <t>Invalid number</t>
+          <t>Same part twice in the file (row 2)</t>
         </is>
       </c>
       <c r="C34" s="1053" t="inlineStr">
         <is>
-          <t>PART-M03</t>
+          <t>PART-I</t>
         </is>
       </c>
       <c r="D34" s="1054" t="n">
         <v>300</v>
       </c>
       <c r="E34" s="1054" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1054" t="n">
-        <v>15</v>
-      </c>
-      <c r="G34" s="1053" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="G34" s="1053" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
       <c r="H34" s="1053" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I34" s="1053" t="inlineStr">
         <is>
-          <t>14-Sep-2026</t>
+          <t>20-Sep-2026</t>
         </is>
       </c>
       <c r="J34" s="1053" t="inlineStr">
         <is>
-          <t>Check 5: pcs_case must be greater than 0. A blank cell in a required column is also an error.</t>
+          <t>Check 4: Part No appears more than once.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1053" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B35" s="1053" t="inlineStr">
         <is>
-          <t>Change the status of a Candidate part</t>
+          <t>Invalid number</t>
         </is>
       </c>
       <c r="C35" s="1053" t="inlineStr">
         <is>
-          <t>PART-I</t>
+          <t>PART-M03</t>
         </is>
       </c>
       <c r="D35" s="1054" t="n">
         <v>300</v>
       </c>
       <c r="E35" s="1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1054" t="n">
         <v>15</v>
       </c>
-      <c r="F35" s="1054" t="n">
-        <v>20</v>
-      </c>
-      <c r="G35" s="1053" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="G35" s="1053" t="n"/>
       <c r="H35" s="1053" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I35" s="1053" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>14-Sep-2026</t>
         </is>
       </c>
       <c r="J35" s="1053" t="inlineStr">
         <is>
-          <t>Check 6: the status of a Candidate part cannot be changed by upload. Change it in the Edit part data modal.</t>
+          <t>Check 5: pcs_case must be greater than 0. A blank pcs_case or max_case_day is also an error (a blank mad is allowed).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1053" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="B36" s="1053" t="inlineStr">
         <is>
-          <t>Change an Active part to Candidate</t>
+          <t>Change the status of a Candidate part</t>
         </is>
       </c>
       <c r="C36" s="1053" t="inlineStr">
         <is>
-          <t>PART-C</t>
+          <t>PART-I</t>
         </is>
       </c>
       <c r="D36" s="1054" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E36" s="1054" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1054" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G36" s="1053" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H36" s="1053" t="inlineStr">
@@ -50109,106 +50114,114 @@
           <t>E</t>
         </is>
       </c>
-      <c r="I36" s="1053" t="n"/>
+      <c r="I36" s="1053" t="inlineStr">
+        <is>
+          <t>15-Sep-2026</t>
+        </is>
+      </c>
       <c r="J36" s="1053" t="inlineStr">
         <is>
-          <t>Check 6: no part can be changed to Candidate.</t>
+          <t>Check 6: the status of a Candidate part cannot be changed by upload. Change it in the Edit part data modal.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1053" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="B37" s="1053" t="inlineStr">
         <is>
-          <t>Add with a status</t>
+          <t>Change an Active part to Candidate</t>
         </is>
       </c>
       <c r="C37" s="1053" t="inlineStr">
         <is>
-          <t>PART-M03</t>
+          <t>PART-C</t>
         </is>
       </c>
       <c r="D37" s="1054" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E37" s="1054" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F37" s="1054" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G37" s="1053" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="H37" s="1053" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I37" s="1053" t="inlineStr">
-        <is>
-          <t>14-Sep-2026</t>
-        </is>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I37" s="1053" t="n"/>
       <c r="J37" s="1053" t="inlineStr">
         <is>
-          <t>Check 6: status of a new part is always Candidate, leave it blank.</t>
+          <t>Check 6: no part can be changed to Candidate.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1053" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E9</t>
         </is>
       </c>
       <c r="B38" s="1053" t="inlineStr">
         <is>
-          <t>Add without effective date</t>
+          <t>Add with a status</t>
         </is>
       </c>
       <c r="C38" s="1053" t="inlineStr">
         <is>
-          <t>PART-M02</t>
+          <t>PART-M03</t>
         </is>
       </c>
       <c r="D38" s="1054" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E38" s="1054" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F38" s="1054" t="n">
-        <v>40</v>
-      </c>
-      <c r="G38" s="1053" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="G38" s="1053" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="H38" s="1053" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I38" s="1053" t="n"/>
+      <c r="I38" s="1053" t="inlineStr">
+        <is>
+          <t>14-Sep-2026</t>
+        </is>
+      </c>
       <c r="J38" s="1053" t="inlineStr">
         <is>
-          <t>Check 7: Effective Start Date is required for Candidate.</t>
+          <t>Check 6: status of a new part is always Candidate, leave it blank.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1053" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B39" s="1053" t="inlineStr">
         <is>
-          <t>Effective date in the past</t>
+          <t>Add without effective date</t>
         </is>
       </c>
       <c r="C39" s="1053" t="inlineStr">
@@ -50231,83 +50244,79 @@
           <t>A</t>
         </is>
       </c>
-      <c r="I39" s="1053" t="inlineStr">
-        <is>
-          <t>12-Sep-2026</t>
-        </is>
-      </c>
+      <c r="I39" s="1053" t="n"/>
       <c r="J39" s="1053" t="inlineStr">
         <is>
-          <t>Check 7: Effective Start Date must be today or later.</t>
+          <t>Check 7: Effective Start Date is required for Candidate.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1053" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B40" s="1053" t="inlineStr">
         <is>
-          <t>Change effective date of an Active part</t>
+          <t>Effective date in the past</t>
         </is>
       </c>
       <c r="C40" s="1053" t="inlineStr">
         <is>
-          <t>PART-C</t>
+          <t>PART-M02</t>
         </is>
       </c>
       <c r="D40" s="1054" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E40" s="1054" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1054" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1053" t="n"/>
       <c r="H40" s="1053" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I40" s="1053" t="inlineStr">
         <is>
-          <t>20-Sep-2026</t>
+          <t>12-Sep-2026</t>
         </is>
       </c>
       <c r="J40" s="1053" t="inlineStr">
         <is>
-          <t>Check 8: effective date can only change while the part is Candidate.</t>
+          <t>Check 7: Effective Start Date must be today or later.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1053" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B41" s="1053" t="inlineStr">
         <is>
-          <t>Max Case/Day below existing mapping</t>
+          <t>Change effective date of an Active part</t>
         </is>
       </c>
       <c r="C41" s="1053" t="inlineStr">
         <is>
-          <t>PART-A</t>
+          <t>PART-C</t>
         </is>
       </c>
       <c r="D41" s="1054" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E41" s="1054" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F41" s="1054" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G41" s="1053" t="n"/>
       <c r="H41" s="1053" t="inlineStr">
@@ -50315,52 +50324,52 @@
           <t>E</t>
         </is>
       </c>
-      <c r="I41" s="1053" t="n"/>
+      <c r="I41" s="1053" t="inlineStr">
+        <is>
+          <t>20-Sep-2026</t>
+        </is>
+      </c>
       <c r="J41" s="1053" t="inlineStr">
         <is>
-          <t>Check 9: Max Case/Day 20 is below mapped 24. Reduce the mapping first in Mapping per Destination.</t>
+          <t>Check 8: effective date can only change while the part is Candidate.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1053" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B42" s="1053" t="inlineStr">
         <is>
-          <t>Valid row (= N1) mixed with an error row (= E2), row 1</t>
+          <t>Max Case/Day below existing mapping</t>
         </is>
       </c>
       <c r="C42" s="1053" t="inlineStr">
         <is>
-          <t>PART-M01</t>
+          <t>PART-A</t>
         </is>
       </c>
       <c r="D42" s="1054" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E42" s="1054" t="n">
+        <v>60</v>
+      </c>
+      <c r="F42" s="1054" t="n">
         <v>20</v>
-      </c>
-      <c r="F42" s="1054" t="n">
-        <v>15</v>
       </c>
       <c r="G42" s="1053" t="n"/>
       <c r="H42" s="1053" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I42" s="1053" t="inlineStr">
-        <is>
-          <t>14-Sep-2026</t>
-        </is>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I42" s="1053" t="n"/>
       <c r="J42" s="1053" t="inlineStr">
         <is>
-          <t>Whole file rejected. The valid row is NOT saved.</t>
+          <t>Check 9: Max Case/Day 20 is below mapped 24. Reduce the mapping first in Mapping per Destination.</t>
         </is>
       </c>
     </row>
@@ -50372,140 +50381,182 @@
       </c>
       <c r="B43" s="1053" t="inlineStr">
         <is>
-          <t>Valid row mixed with an error row, row 2</t>
+          <t>Valid row (= N1) mixed with an error row (= E2), row 1</t>
         </is>
       </c>
       <c r="C43" s="1053" t="inlineStr">
         <is>
-          <t>PART-Z99</t>
+          <t>PART-M01</t>
         </is>
       </c>
       <c r="D43" s="1054" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E43" s="1054" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1054" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G43" s="1053" t="n"/>
       <c r="H43" s="1053" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I43" s="1053" t="inlineStr">
+        <is>
+          <t>14-Sep-2026</t>
+        </is>
+      </c>
+      <c r="J43" s="1053" t="inlineStr">
+        <is>
+          <t>Whole file rejected. The valid row is NOT saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1053" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B44" s="1053" t="inlineStr">
+        <is>
+          <t>Valid row mixed with an error row, row 2</t>
+        </is>
+      </c>
+      <c r="C44" s="1053" t="inlineStr">
+        <is>
+          <t>PART-Z99</t>
+        </is>
+      </c>
+      <c r="D44" s="1054" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" s="1054" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" s="1054" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1053" t="n"/>
+      <c r="H44" s="1053" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I43" s="1053" t="n"/>
-      <c r="J43" s="1053" t="inlineStr">
+      <c r="I44" s="1053" t="n"/>
+      <c r="J44" s="1053" t="inlineStr">
         <is>
           <t>Check 2 on this row. Result report sheet Re-upload lists the rows to correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1051" t="inlineStr">
-        <is>
-          <t>D. File-level errors (file check 4.1)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1052" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B46" s="1052" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C46" s="1052" t="inlineStr">
-        <is>
-          <t>Expected result</t>
+      <c r="A46" s="1051" t="inlineStr">
+        <is>
+          <t>D. File-level errors (file check 4.1)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1053" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B47" s="1053" t="inlineStr">
-        <is>
-          <t>File is .xls or .csv</t>
-        </is>
-      </c>
-      <c r="C47" s="1053" t="inlineStr">
-        <is>
-          <t>Rejected: file must be .xlsx.</t>
+      <c r="A47" s="1052" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B47" s="1052" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C47" s="1052" t="inlineStr">
+        <is>
+          <t>Expected result</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1053" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B48" s="1053" t="inlineStr">
         <is>
-          <t>File larger than 5 MB</t>
+          <t>File is .xls or .csv</t>
         </is>
       </c>
       <c r="C48" s="1053" t="inlineStr">
         <is>
-          <t>Rejected: file size exceeds 5 MB.</t>
+          <t>Rejected: file must be .xlsx.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1053" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B49" s="1053" t="inlineStr">
         <is>
-          <t>More than 5,000 data rows, or no data row</t>
+          <t>File larger than 5 MB</t>
         </is>
       </c>
       <c r="C49" s="1053" t="inlineStr">
         <is>
-          <t>Rejected: row count out of range.</t>
+          <t>Rejected: file size exceeds 5 MB.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1053" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B50" s="1053" t="inlineStr">
         <is>
-          <t>No sheet named Upload (e.g. only sheet Part List)</t>
+          <t>More than 5,000 data rows, or no data row</t>
         </is>
       </c>
       <c r="C50" s="1053" t="inlineStr">
         <is>
-          <t>Rejected: sheet Upload not found.</t>
+          <t>Rejected: row count out of range.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1053" t="inlineStr">
         <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B51" s="1053" t="inlineStr">
+        <is>
+          <t>No sheet named Upload (e.g. only sheet Part List)</t>
+        </is>
+      </c>
+      <c r="C51" s="1053" t="inlineStr">
+        <is>
+          <t>Rejected: sheet Upload not found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1053" t="inlineStr">
+        <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B51" s="1053" t="inlineStr">
+      <c r="B52" s="1053" t="inlineStr">
         <is>
           <t>A template column is missing (e.g. flag_add_edit deleted)</t>
         </is>
       </c>
-      <c r="C51" s="1053" t="inlineStr">
+      <c r="C52" s="1053" t="inlineStr">
         <is>
           <t>Rejected: required column not found.</t>
         </is>

--- a/UISS_Batch_PartListUpload_v2.xlsx
+++ b/UISS_Batch_PartListUpload_v2.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Logging Message'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Logging Message'!$A$1:$CX$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Appendix'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Appendix'!$A$1:$CX$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Appendix'!$A$1:$CX$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -55,7 +55,7 @@
     <numFmt numFmtId="178" formatCode="\\#,##0.00;[RED]&quot;\-&quot;#,##0.00"/>
     <numFmt numFmtId="179" formatCode="\\#,##0;[RED]&quot;\-&quot;#,##0"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -286,6 +286,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -384,7 +389,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="141">
+  <borders count="143">
     <border>
       <left/>
       <right/>
@@ -1312,6 +1317,18 @@
       <top/>
       <bottom/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1552,7 +1569,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1056">
+  <cellXfs count="1069">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -4596,19 +4613,58 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="66">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="66">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="66">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="14" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -30837,7 +30893,7 @@
       <c r="AN74" s="856" t="n"/>
       <c r="AO74" s="1015" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>HIST_ID</t>
         </is>
       </c>
       <c r="AP74" s="855" t="n"/>
@@ -30852,7 +30908,7 @@
       <c r="AY74" s="855" t="n"/>
       <c r="AZ74" s="1015" t="inlineStr">
         <is>
-          <t>Part of the event</t>
+          <t>Auto (identity)</t>
         </is>
       </c>
       <c r="BA74" s="855" t="n"/>
@@ -30949,7 +31005,7 @@
       <c r="AN75" s="856" t="n"/>
       <c r="AO75" s="1015" t="inlineStr">
         <is>
-          <t>PERIOD</t>
+          <t>PART_NO</t>
         </is>
       </c>
       <c r="AP75" s="855" t="n"/>
@@ -30964,7 +31020,7 @@
       <c r="AY75" s="855" t="n"/>
       <c r="AZ75" s="1015" t="inlineStr">
         <is>
-          <t>Blank (Part List has no period)</t>
+          <t>Part of the event</t>
         </is>
       </c>
       <c r="BA75" s="855" t="n"/>
@@ -31061,7 +31117,7 @@
       <c r="AN76" s="856" t="n"/>
       <c r="AO76" s="1015" t="inlineStr">
         <is>
-          <t>EVENT</t>
+          <t>PERIOD</t>
         </is>
       </c>
       <c r="AP76" s="855" t="n"/>
@@ -31076,7 +31132,7 @@
       <c r="AY76" s="855" t="n"/>
       <c r="AZ76" s="1015" t="inlineStr">
         <is>
-          <t>'ADD' (flag A) / 'EDIT' (flag E)</t>
+          <t>NULL (Part List has no period)</t>
         </is>
       </c>
       <c r="BA76" s="855" t="n"/>
@@ -31173,7 +31229,7 @@
       <c r="AN77" s="856" t="n"/>
       <c r="AO77" s="1015" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>EVENT_TYPE</t>
         </is>
       </c>
       <c r="AP77" s="855" t="n"/>
@@ -31188,7 +31244,7 @@
       <c r="AY77" s="855" t="n"/>
       <c r="AZ77" s="1015" t="inlineStr">
         <is>
-          <t>'UPLOAD'</t>
+          <t>'ADD' (flag A) / 'EDIT' (flag E)</t>
         </is>
       </c>
       <c r="BA77" s="855" t="n"/>
@@ -31285,7 +31341,7 @@
       <c r="AN78" s="856" t="n"/>
       <c r="AO78" s="1015" t="inlineStr">
         <is>
-          <t>FIELD_NAME</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="AP78" s="855" t="n"/>
@@ -31300,7 +31356,7 @@
       <c r="AY78" s="855" t="n"/>
       <c r="AZ78" s="1015" t="inlineStr">
         <is>
-          <t>Changed field, e.g. PCS_CASE, MAX_CASE_DAY,</t>
+          <t>'UPLOAD'</t>
         </is>
       </c>
       <c r="BA78" s="855" t="n"/>
@@ -31391,9 +31447,15 @@
       <c r="AJ79" s="771" t="n"/>
       <c r="AK79" s="771" t="n"/>
       <c r="AL79" s="771" t="n"/>
-      <c r="AM79" s="1014" t="n"/>
+      <c r="AM79" s="1014" t="n">
+        <v>6</v>
+      </c>
       <c r="AN79" s="856" t="n"/>
-      <c r="AO79" s="1015" t="n"/>
+      <c r="AO79" s="1015" t="inlineStr">
+        <is>
+          <t>UPLOAD_ID</t>
+        </is>
+      </c>
       <c r="AP79" s="855" t="n"/>
       <c r="AQ79" s="855" t="n"/>
       <c r="AR79" s="855" t="n"/>
@@ -31406,7 +31468,7 @@
       <c r="AY79" s="855" t="n"/>
       <c r="AZ79" s="1015" t="inlineStr">
         <is>
-          <t>PART_STATUS</t>
+          <t>UPLOAD_ID of this run</t>
         </is>
       </c>
       <c r="BA79" s="855" t="n"/>
@@ -31498,12 +31560,12 @@
       <c r="AK80" s="771" t="n"/>
       <c r="AL80" s="771" t="n"/>
       <c r="AM80" s="1014" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN80" s="856" t="n"/>
       <c r="AO80" s="1015" t="inlineStr">
         <is>
-          <t>OLD_VALUE</t>
+          <t>DEST_CODE</t>
         </is>
       </c>
       <c r="AP80" s="855" t="n"/>
@@ -31518,7 +31580,7 @@
       <c r="AY80" s="855" t="n"/>
       <c r="AZ80" s="1015" t="inlineStr">
         <is>
-          <t>Value before upload (blank for ADD)</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="BA80" s="855" t="n"/>
@@ -31610,12 +31672,12 @@
       <c r="AK81" s="771" t="n"/>
       <c r="AL81" s="771" t="n"/>
       <c r="AM81" s="1014" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN81" s="856" t="n"/>
       <c r="AO81" s="1015" t="inlineStr">
         <is>
-          <t>NEW_VALUE</t>
+          <t>FIELD_NAME</t>
         </is>
       </c>
       <c r="AP81" s="855" t="n"/>
@@ -31630,7 +31692,7 @@
       <c r="AY81" s="855" t="n"/>
       <c r="AZ81" s="1015" t="inlineStr">
         <is>
-          <t>Value from the file</t>
+          <t>Changed field, e.g. PCS_CASE, MAX_CASE_DAY,</t>
         </is>
       </c>
       <c r="BA81" s="855" t="n"/>
@@ -31721,15 +31783,9 @@
       <c r="AJ82" s="771" t="n"/>
       <c r="AK82" s="771" t="n"/>
       <c r="AL82" s="771" t="n"/>
-      <c r="AM82" s="1014" t="n">
-        <v>8</v>
-      </c>
+      <c r="AM82" s="1014" t="n"/>
       <c r="AN82" s="856" t="n"/>
-      <c r="AO82" s="1015" t="inlineStr">
-        <is>
-          <t>CHANGED_BY</t>
-        </is>
-      </c>
+      <c r="AO82" s="1015" t="n"/>
       <c r="AP82" s="855" t="n"/>
       <c r="AQ82" s="855" t="n"/>
       <c r="AR82" s="855" t="n"/>
@@ -31742,7 +31798,7 @@
       <c r="AY82" s="855" t="n"/>
       <c r="AZ82" s="1015" t="inlineStr">
         <is>
-          <t>Login name of the user who uploaded</t>
+          <t>PART_STATUS</t>
         </is>
       </c>
       <c r="BA82" s="855" t="n"/>
@@ -31839,7 +31895,7 @@
       <c r="AN83" s="856" t="n"/>
       <c r="AO83" s="1015" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>OLD_VALUE</t>
         </is>
       </c>
       <c r="AP83" s="855" t="n"/>
@@ -31854,7 +31910,7 @@
       <c r="AY83" s="855" t="n"/>
       <c r="AZ83" s="1015" t="inlineStr">
         <is>
-          <t>Server system date and time</t>
+          <t>Value before upload (NULL for ADD)</t>
         </is>
       </c>
       <c r="BA83" s="855" t="n"/>
@@ -31910,423 +31966,451 @@
       <c r="CY83" s="1022" t="n"/>
     </row>
     <row r="84" ht="11.1" customHeight="1" s="710">
-      <c r="A84" s="1022" t="n"/>
-      <c r="B84" s="1023" t="n"/>
-      <c r="C84" s="1022" t="n"/>
-      <c r="D84" s="1022" t="n"/>
-      <c r="E84" s="1022" t="n"/>
-      <c r="F84" s="1022" t="n"/>
-      <c r="G84" s="1022" t="n"/>
-      <c r="H84" s="1022" t="n"/>
-      <c r="I84" s="1022" t="n"/>
-      <c r="J84" s="1022" t="n"/>
-      <c r="K84" s="1022" t="n"/>
-      <c r="L84" s="1022" t="n"/>
-      <c r="M84" s="1022" t="n"/>
-      <c r="N84" s="1022" t="n"/>
-      <c r="O84" s="1022" t="n"/>
-      <c r="P84" s="1022" t="n"/>
-      <c r="Q84" s="1022" t="n"/>
-      <c r="R84" s="1022" t="n"/>
-      <c r="S84" s="1022" t="n"/>
-      <c r="T84" s="1022" t="n"/>
-      <c r="U84" s="1022" t="n"/>
-      <c r="V84" s="1022" t="n"/>
-      <c r="W84" s="1022" t="n"/>
-      <c r="X84" s="1022" t="n"/>
-      <c r="Y84" s="1022" t="n"/>
-      <c r="Z84" s="1022" t="n"/>
-      <c r="AA84" s="1022" t="n"/>
-      <c r="AB84" s="1022" t="n"/>
-      <c r="AC84" s="1022" t="n"/>
-      <c r="AD84" s="1022" t="n"/>
-      <c r="AE84" s="1022" t="n"/>
-      <c r="AF84" s="1022" t="n"/>
-      <c r="AG84" s="1022" t="n"/>
-      <c r="AH84" s="1022" t="n"/>
-      <c r="AI84" s="1022" t="n"/>
-      <c r="AJ84" s="1022" t="n"/>
-      <c r="AK84" s="1022" t="n"/>
-      <c r="AL84" s="1022" t="n"/>
-      <c r="AM84" s="1022" t="n"/>
-      <c r="AN84" s="1022" t="n"/>
-      <c r="AO84" s="1022" t="n"/>
-      <c r="AP84" s="1022" t="n"/>
-      <c r="AQ84" s="1022" t="n"/>
-      <c r="AR84" s="1022" t="n"/>
-      <c r="AS84" s="1022" t="n"/>
-      <c r="AT84" s="1022" t="n"/>
-      <c r="AU84" s="1022" t="n"/>
-      <c r="AV84" s="1022" t="n"/>
-      <c r="AW84" s="1022" t="n"/>
-      <c r="AX84" s="1022" t="n"/>
-      <c r="AY84" s="1022" t="n"/>
-      <c r="AZ84" s="1022" t="n"/>
-      <c r="BA84" s="1022" t="n"/>
-      <c r="BB84" s="1022" t="n"/>
-      <c r="BC84" s="1022" t="n"/>
-      <c r="BD84" s="1022" t="n"/>
-      <c r="BE84" s="1022" t="n"/>
-      <c r="BF84" s="1022" t="n"/>
-      <c r="BG84" s="1022" t="n"/>
-      <c r="BH84" s="1022" t="n"/>
-      <c r="BI84" s="1022" t="n"/>
-      <c r="BJ84" s="1022" t="n"/>
-      <c r="BK84" s="1022" t="n"/>
-      <c r="BL84" s="1022" t="n"/>
-      <c r="BM84" s="1022" t="n"/>
-      <c r="BN84" s="1022" t="n"/>
-      <c r="BO84" s="1022" t="n"/>
-      <c r="BP84" s="1022" t="n"/>
-      <c r="BQ84" s="1022" t="n"/>
-      <c r="BR84" s="1022" t="n"/>
-      <c r="BS84" s="1022" t="n"/>
-      <c r="BT84" s="1022" t="n"/>
-      <c r="BU84" s="1022" t="n"/>
-      <c r="BV84" s="1022" t="n"/>
-      <c r="BW84" s="1022" t="n"/>
-      <c r="BX84" s="1022" t="n"/>
-      <c r="BY84" s="1022" t="n"/>
-      <c r="BZ84" s="1022" t="n"/>
-      <c r="CA84" s="1022" t="n"/>
-      <c r="CB84" s="1022" t="n"/>
-      <c r="CC84" s="1022" t="n"/>
-      <c r="CD84" s="1022" t="n"/>
-      <c r="CE84" s="1022" t="n"/>
-      <c r="CF84" s="1022" t="n"/>
-      <c r="CG84" s="1022" t="n"/>
-      <c r="CH84" s="1022" t="n"/>
-      <c r="CI84" s="1022" t="n"/>
-      <c r="CJ84" s="1022" t="n"/>
-      <c r="CK84" s="1022" t="n"/>
-      <c r="CL84" s="1022" t="n"/>
-      <c r="CM84" s="1022" t="n"/>
-      <c r="CN84" s="1022" t="n"/>
-      <c r="CO84" s="1022" t="n"/>
-      <c r="CP84" s="1022" t="n"/>
-      <c r="CQ84" s="1022" t="n"/>
-      <c r="CR84" s="1022" t="n"/>
-      <c r="CS84" s="1022" t="n"/>
-      <c r="CT84" s="1022" t="n"/>
-      <c r="CU84" s="1022" t="n"/>
-      <c r="CV84" s="1022" t="n"/>
-      <c r="CW84" s="1022" t="n"/>
-      <c r="CX84" s="1024" t="n"/>
+      <c r="B84" s="1009" t="n"/>
+      <c r="C84" s="855" t="n"/>
+      <c r="D84" s="855" t="n"/>
+      <c r="E84" s="855" t="n"/>
+      <c r="F84" s="855" t="n"/>
+      <c r="G84" s="855" t="n"/>
+      <c r="H84" s="855" t="n"/>
+      <c r="I84" s="855" t="n"/>
+      <c r="J84" s="856" t="n"/>
+      <c r="K84" s="1010" t="n"/>
+      <c r="L84" s="732" t="n"/>
+      <c r="M84" s="732" t="n"/>
+      <c r="N84" s="732" t="n"/>
+      <c r="O84" s="732" t="n"/>
+      <c r="P84" s="732" t="n"/>
+      <c r="Q84" s="858" t="n"/>
+      <c r="R84" s="1011" t="n"/>
+      <c r="S84" s="856" t="n"/>
+      <c r="T84" s="1012" t="n"/>
+      <c r="U84" s="855" t="n"/>
+      <c r="V84" s="855" t="n"/>
+      <c r="W84" s="855" t="n"/>
+      <c r="X84" s="855" t="n"/>
+      <c r="Y84" s="855" t="n"/>
+      <c r="Z84" s="855" t="n"/>
+      <c r="AA84" s="855" t="n"/>
+      <c r="AB84" s="855" t="n"/>
+      <c r="AC84" s="855" t="n"/>
+      <c r="AD84" s="861" t="n"/>
+      <c r="AE84" s="771" t="n"/>
+      <c r="AF84" s="771" t="n"/>
+      <c r="AI84" s="771" t="n"/>
+      <c r="AJ84" s="771" t="n"/>
+      <c r="AK84" s="771" t="n"/>
+      <c r="AL84" s="771" t="n"/>
+      <c r="AM84" s="1014" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN84" s="856" t="n"/>
+      <c r="AO84" s="1015" t="inlineStr">
+        <is>
+          <t>NEW_VALUE</t>
+        </is>
+      </c>
+      <c r="AP84" s="855" t="n"/>
+      <c r="AQ84" s="855" t="n"/>
+      <c r="AR84" s="855" t="n"/>
+      <c r="AS84" s="855" t="n"/>
+      <c r="AT84" s="855" t="n"/>
+      <c r="AU84" s="855" t="n"/>
+      <c r="AV84" s="855" t="n"/>
+      <c r="AW84" s="855" t="n"/>
+      <c r="AX84" s="855" t="n"/>
+      <c r="AY84" s="855" t="n"/>
+      <c r="AZ84" s="1015" t="inlineStr">
+        <is>
+          <t>Value from the file</t>
+        </is>
+      </c>
+      <c r="BA84" s="855" t="n"/>
+      <c r="BB84" s="855" t="n"/>
+      <c r="BC84" s="855" t="n"/>
+      <c r="BD84" s="855" t="n"/>
+      <c r="BE84" s="855" t="n"/>
+      <c r="BF84" s="855" t="n"/>
+      <c r="BG84" s="855" t="n"/>
+      <c r="BH84" s="855" t="n"/>
+      <c r="BI84" s="855" t="n"/>
+      <c r="BJ84" s="855" t="n"/>
+      <c r="BK84" s="855" t="n"/>
+      <c r="BL84" s="855" t="n"/>
+      <c r="BM84" s="855" t="n"/>
+      <c r="BN84" s="855" t="n"/>
+      <c r="BO84" s="855" t="n"/>
+      <c r="BP84" s="855" t="n"/>
+      <c r="BQ84" s="855" t="n"/>
+      <c r="BR84" s="855" t="n"/>
+      <c r="BS84" s="855" t="n"/>
+      <c r="BT84" s="855" t="n"/>
+      <c r="BU84" s="855" t="n"/>
+      <c r="BV84" s="855" t="n"/>
+      <c r="BW84" s="855" t="n"/>
+      <c r="BX84" s="855" t="n"/>
+      <c r="BY84" s="855" t="n"/>
+      <c r="BZ84" s="855" t="n"/>
+      <c r="CA84" s="855" t="n"/>
+      <c r="CB84" s="855" t="n"/>
+      <c r="CC84" s="855" t="n"/>
+      <c r="CD84" s="855" t="n"/>
+      <c r="CE84" s="855" t="n"/>
+      <c r="CF84" s="855" t="n"/>
+      <c r="CG84" s="1016" t="n"/>
+      <c r="CH84" s="855" t="n"/>
+      <c r="CI84" s="855" t="n"/>
+      <c r="CJ84" s="855" t="n"/>
+      <c r="CK84" s="855" t="n"/>
+      <c r="CL84" s="855" t="n"/>
+      <c r="CM84" s="855" t="n"/>
+      <c r="CN84" s="855" t="n"/>
+      <c r="CO84" s="855" t="n"/>
+      <c r="CP84" s="855" t="n"/>
+      <c r="CQ84" s="856" t="n"/>
+      <c r="CR84" s="1017" t="n"/>
+      <c r="CS84" s="732" t="n"/>
+      <c r="CT84" s="732" t="n"/>
+      <c r="CU84" s="732" t="n"/>
+      <c r="CV84" s="732" t="n"/>
+      <c r="CW84" s="732" t="n"/>
+      <c r="CX84" s="733" t="n"/>
       <c r="CY84" s="1022" t="n"/>
     </row>
     <row r="85" ht="11.1" customHeight="1" s="710">
-      <c r="A85" s="1022" t="n"/>
-      <c r="B85" s="1023" t="n"/>
-      <c r="C85" s="1022" t="n"/>
-      <c r="D85" s="1022" t="n"/>
-      <c r="E85" s="1022" t="n"/>
-      <c r="F85" s="1022" t="n"/>
-      <c r="G85" s="1022" t="n"/>
-      <c r="H85" s="1022" t="n"/>
-      <c r="I85" s="1022" t="n"/>
-      <c r="J85" s="1022" t="n"/>
-      <c r="K85" s="1022" t="n"/>
-      <c r="L85" s="1022" t="n"/>
-      <c r="M85" s="1022" t="n"/>
-      <c r="N85" s="1022" t="n"/>
-      <c r="O85" s="1022" t="n"/>
-      <c r="P85" s="1022" t="n"/>
-      <c r="Q85" s="1022" t="n"/>
-      <c r="R85" s="1022" t="n"/>
-      <c r="S85" s="1022" t="n"/>
-      <c r="T85" s="1022" t="n"/>
-      <c r="U85" s="1022" t="n"/>
-      <c r="V85" s="1022" t="n"/>
-      <c r="W85" s="1022" t="n"/>
-      <c r="X85" s="1022" t="n"/>
-      <c r="Y85" s="1022" t="n"/>
-      <c r="Z85" s="1022" t="n"/>
-      <c r="AA85" s="1022" t="n"/>
-      <c r="AB85" s="1022" t="n"/>
-      <c r="AC85" s="1022" t="n"/>
-      <c r="AD85" s="1022" t="n"/>
-      <c r="AE85" s="1022" t="n"/>
-      <c r="AF85" s="1022" t="n"/>
-      <c r="AG85" s="1022" t="n"/>
-      <c r="AH85" s="1022" t="n"/>
-      <c r="AI85" s="1022" t="n"/>
-      <c r="AJ85" s="1022" t="n"/>
-      <c r="AK85" s="1022" t="n"/>
-      <c r="AL85" s="1022" t="n"/>
-      <c r="AM85" s="1022" t="n"/>
-      <c r="AN85" s="1022" t="n"/>
-      <c r="AO85" s="1022" t="n"/>
-      <c r="AP85" s="1022" t="n"/>
-      <c r="AQ85" s="1022" t="n"/>
-      <c r="AR85" s="1022" t="n"/>
-      <c r="AS85" s="1022" t="n"/>
-      <c r="AT85" s="1022" t="n"/>
-      <c r="AU85" s="1022" t="n"/>
-      <c r="AV85" s="1022" t="n"/>
-      <c r="AW85" s="1022" t="n"/>
-      <c r="AX85" s="1022" t="n"/>
-      <c r="AY85" s="1022" t="n"/>
-      <c r="AZ85" s="1022" t="n"/>
-      <c r="BA85" s="1022" t="n"/>
-      <c r="BB85" s="1022" t="n"/>
-      <c r="BC85" s="1022" t="n"/>
-      <c r="BD85" s="1022" t="n"/>
-      <c r="BE85" s="1022" t="n"/>
-      <c r="BF85" s="1022" t="n"/>
-      <c r="BG85" s="1022" t="n"/>
-      <c r="BH85" s="1022" t="n"/>
-      <c r="BI85" s="1022" t="n"/>
-      <c r="BJ85" s="1022" t="n"/>
-      <c r="BK85" s="1022" t="n"/>
-      <c r="BL85" s="1022" t="n"/>
-      <c r="BM85" s="1022" t="n"/>
-      <c r="BN85" s="1022" t="n"/>
-      <c r="BO85" s="1022" t="n"/>
-      <c r="BP85" s="1022" t="n"/>
-      <c r="BQ85" s="1022" t="n"/>
-      <c r="BR85" s="1022" t="n"/>
-      <c r="BS85" s="1022" t="n"/>
-      <c r="BT85" s="1022" t="n"/>
-      <c r="BU85" s="1022" t="n"/>
-      <c r="BV85" s="1022" t="n"/>
-      <c r="BW85" s="1022" t="n"/>
-      <c r="BX85" s="1022" t="n"/>
-      <c r="BY85" s="1022" t="n"/>
-      <c r="BZ85" s="1022" t="n"/>
-      <c r="CA85" s="1022" t="n"/>
-      <c r="CB85" s="1022" t="n"/>
-      <c r="CC85" s="1022" t="n"/>
-      <c r="CD85" s="1022" t="n"/>
-      <c r="CE85" s="1022" t="n"/>
-      <c r="CF85" s="1022" t="n"/>
-      <c r="CG85" s="1022" t="n"/>
-      <c r="CH85" s="1022" t="n"/>
-      <c r="CI85" s="1022" t="n"/>
-      <c r="CJ85" s="1022" t="n"/>
-      <c r="CK85" s="1022" t="n"/>
-      <c r="CL85" s="1022" t="n"/>
-      <c r="CM85" s="1022" t="n"/>
-      <c r="CN85" s="1022" t="n"/>
-      <c r="CO85" s="1022" t="n"/>
-      <c r="CP85" s="1022" t="n"/>
-      <c r="CQ85" s="1022" t="n"/>
-      <c r="CR85" s="1022" t="n"/>
-      <c r="CS85" s="1022" t="n"/>
-      <c r="CT85" s="1022" t="n"/>
-      <c r="CU85" s="1022" t="n"/>
-      <c r="CV85" s="1022" t="n"/>
-      <c r="CW85" s="1022" t="n"/>
-      <c r="CX85" s="1024" t="n"/>
+      <c r="B85" s="1009" t="n"/>
+      <c r="C85" s="855" t="n"/>
+      <c r="D85" s="855" t="n"/>
+      <c r="E85" s="855" t="n"/>
+      <c r="F85" s="855" t="n"/>
+      <c r="G85" s="855" t="n"/>
+      <c r="H85" s="855" t="n"/>
+      <c r="I85" s="855" t="n"/>
+      <c r="J85" s="856" t="n"/>
+      <c r="K85" s="1010" t="n"/>
+      <c r="L85" s="732" t="n"/>
+      <c r="M85" s="732" t="n"/>
+      <c r="N85" s="732" t="n"/>
+      <c r="O85" s="732" t="n"/>
+      <c r="P85" s="732" t="n"/>
+      <c r="Q85" s="858" t="n"/>
+      <c r="R85" s="1011" t="n"/>
+      <c r="S85" s="856" t="n"/>
+      <c r="T85" s="1012" t="n"/>
+      <c r="U85" s="855" t="n"/>
+      <c r="V85" s="855" t="n"/>
+      <c r="W85" s="855" t="n"/>
+      <c r="X85" s="855" t="n"/>
+      <c r="Y85" s="855" t="n"/>
+      <c r="Z85" s="855" t="n"/>
+      <c r="AA85" s="855" t="n"/>
+      <c r="AB85" s="855" t="n"/>
+      <c r="AC85" s="855" t="n"/>
+      <c r="AD85" s="861" t="n"/>
+      <c r="AE85" s="771" t="n"/>
+      <c r="AF85" s="771" t="n"/>
+      <c r="AI85" s="771" t="n"/>
+      <c r="AJ85" s="771" t="n"/>
+      <c r="AK85" s="771" t="n"/>
+      <c r="AL85" s="771" t="n"/>
+      <c r="AM85" s="1014" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN85" s="856" t="n"/>
+      <c r="AO85" s="1015" t="inlineStr">
+        <is>
+          <t>REMARK</t>
+        </is>
+      </c>
+      <c r="AP85" s="855" t="n"/>
+      <c r="AQ85" s="855" t="n"/>
+      <c r="AR85" s="855" t="n"/>
+      <c r="AS85" s="855" t="n"/>
+      <c r="AT85" s="855" t="n"/>
+      <c r="AU85" s="855" t="n"/>
+      <c r="AV85" s="855" t="n"/>
+      <c r="AW85" s="855" t="n"/>
+      <c r="AX85" s="855" t="n"/>
+      <c r="AY85" s="855" t="n"/>
+      <c r="AZ85" s="1015" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="BA85" s="855" t="n"/>
+      <c r="BB85" s="855" t="n"/>
+      <c r="BC85" s="855" t="n"/>
+      <c r="BD85" s="855" t="n"/>
+      <c r="BE85" s="855" t="n"/>
+      <c r="BF85" s="855" t="n"/>
+      <c r="BG85" s="855" t="n"/>
+      <c r="BH85" s="855" t="n"/>
+      <c r="BI85" s="855" t="n"/>
+      <c r="BJ85" s="855" t="n"/>
+      <c r="BK85" s="855" t="n"/>
+      <c r="BL85" s="855" t="n"/>
+      <c r="BM85" s="855" t="n"/>
+      <c r="BN85" s="855" t="n"/>
+      <c r="BO85" s="855" t="n"/>
+      <c r="BP85" s="855" t="n"/>
+      <c r="BQ85" s="855" t="n"/>
+      <c r="BR85" s="855" t="n"/>
+      <c r="BS85" s="855" t="n"/>
+      <c r="BT85" s="855" t="n"/>
+      <c r="BU85" s="855" t="n"/>
+      <c r="BV85" s="855" t="n"/>
+      <c r="BW85" s="855" t="n"/>
+      <c r="BX85" s="855" t="n"/>
+      <c r="BY85" s="855" t="n"/>
+      <c r="BZ85" s="855" t="n"/>
+      <c r="CA85" s="855" t="n"/>
+      <c r="CB85" s="855" t="n"/>
+      <c r="CC85" s="855" t="n"/>
+      <c r="CD85" s="855" t="n"/>
+      <c r="CE85" s="855" t="n"/>
+      <c r="CF85" s="855" t="n"/>
+      <c r="CG85" s="1016" t="n"/>
+      <c r="CH85" s="855" t="n"/>
+      <c r="CI85" s="855" t="n"/>
+      <c r="CJ85" s="855" t="n"/>
+      <c r="CK85" s="855" t="n"/>
+      <c r="CL85" s="855" t="n"/>
+      <c r="CM85" s="855" t="n"/>
+      <c r="CN85" s="855" t="n"/>
+      <c r="CO85" s="855" t="n"/>
+      <c r="CP85" s="855" t="n"/>
+      <c r="CQ85" s="856" t="n"/>
+      <c r="CR85" s="1017" t="n"/>
+      <c r="CS85" s="732" t="n"/>
+      <c r="CT85" s="732" t="n"/>
+      <c r="CU85" s="732" t="n"/>
+      <c r="CV85" s="732" t="n"/>
+      <c r="CW85" s="732" t="n"/>
+      <c r="CX85" s="733" t="n"/>
       <c r="CY85" s="1022" t="n"/>
     </row>
     <row r="86" ht="11.1" customHeight="1" s="710">
-      <c r="A86" s="1022" t="n"/>
-      <c r="B86" s="1023" t="n"/>
-      <c r="C86" s="1022" t="n"/>
-      <c r="D86" s="1022" t="n"/>
-      <c r="E86" s="1022" t="n"/>
-      <c r="F86" s="1022" t="n"/>
-      <c r="G86" s="1022" t="n"/>
-      <c r="H86" s="1022" t="n"/>
-      <c r="I86" s="1022" t="n"/>
-      <c r="J86" s="1022" t="n"/>
-      <c r="K86" s="1022" t="n"/>
-      <c r="L86" s="1022" t="n"/>
-      <c r="M86" s="1022" t="n"/>
-      <c r="N86" s="1022" t="n"/>
-      <c r="O86" s="1022" t="n"/>
-      <c r="P86" s="1022" t="n"/>
-      <c r="Q86" s="1022" t="n"/>
-      <c r="R86" s="1022" t="n"/>
-      <c r="S86" s="1022" t="n"/>
-      <c r="T86" s="1022" t="n"/>
-      <c r="U86" s="1022" t="n"/>
-      <c r="V86" s="1022" t="n"/>
-      <c r="W86" s="1022" t="n"/>
-      <c r="X86" s="1022" t="n"/>
-      <c r="Y86" s="1022" t="n"/>
-      <c r="Z86" s="1022" t="n"/>
-      <c r="AA86" s="1022" t="n"/>
-      <c r="AB86" s="1022" t="n"/>
-      <c r="AC86" s="1022" t="n"/>
-      <c r="AD86" s="1022" t="n"/>
-      <c r="AE86" s="1022" t="n"/>
-      <c r="AF86" s="1022" t="n"/>
-      <c r="AG86" s="1022" t="n"/>
-      <c r="AH86" s="1022" t="n"/>
-      <c r="AI86" s="1022" t="n"/>
-      <c r="AJ86" s="1022" t="n"/>
-      <c r="AK86" s="1022" t="n"/>
-      <c r="AL86" s="1022" t="n"/>
-      <c r="AM86" s="1022" t="n"/>
-      <c r="AN86" s="1022" t="n"/>
-      <c r="AO86" s="1022" t="n"/>
-      <c r="AP86" s="1022" t="n"/>
-      <c r="AQ86" s="1022" t="n"/>
-      <c r="AR86" s="1022" t="n"/>
-      <c r="AS86" s="1022" t="n"/>
-      <c r="AT86" s="1022" t="n"/>
-      <c r="AU86" s="1022" t="n"/>
-      <c r="AV86" s="1022" t="n"/>
-      <c r="AW86" s="1022" t="n"/>
-      <c r="AX86" s="1022" t="n"/>
-      <c r="AY86" s="1022" t="n"/>
-      <c r="AZ86" s="1022" t="n"/>
-      <c r="BA86" s="1022" t="n"/>
-      <c r="BB86" s="1022" t="n"/>
-      <c r="BC86" s="1022" t="n"/>
-      <c r="BD86" s="1022" t="n"/>
-      <c r="BE86" s="1022" t="n"/>
-      <c r="BF86" s="1022" t="n"/>
-      <c r="BG86" s="1022" t="n"/>
-      <c r="BH86" s="1022" t="n"/>
-      <c r="BI86" s="1022" t="n"/>
-      <c r="BJ86" s="1022" t="n"/>
-      <c r="BK86" s="1022" t="n"/>
-      <c r="BL86" s="1022" t="n"/>
-      <c r="BM86" s="1022" t="n"/>
-      <c r="BN86" s="1022" t="n"/>
-      <c r="BO86" s="1022" t="n"/>
-      <c r="BP86" s="1022" t="n"/>
-      <c r="BQ86" s="1022" t="n"/>
-      <c r="BR86" s="1022" t="n"/>
-      <c r="BS86" s="1022" t="n"/>
-      <c r="BT86" s="1022" t="n"/>
-      <c r="BU86" s="1022" t="n"/>
-      <c r="BV86" s="1022" t="n"/>
-      <c r="BW86" s="1022" t="n"/>
-      <c r="BX86" s="1022" t="n"/>
-      <c r="BY86" s="1022" t="n"/>
-      <c r="BZ86" s="1022" t="n"/>
-      <c r="CA86" s="1022" t="n"/>
-      <c r="CB86" s="1022" t="n"/>
-      <c r="CC86" s="1022" t="n"/>
-      <c r="CD86" s="1022" t="n"/>
-      <c r="CE86" s="1022" t="n"/>
-      <c r="CF86" s="1022" t="n"/>
-      <c r="CG86" s="1022" t="n"/>
-      <c r="CH86" s="1022" t="n"/>
-      <c r="CI86" s="1022" t="n"/>
-      <c r="CJ86" s="1022" t="n"/>
-      <c r="CK86" s="1022" t="n"/>
-      <c r="CL86" s="1022" t="n"/>
-      <c r="CM86" s="1022" t="n"/>
-      <c r="CN86" s="1022" t="n"/>
-      <c r="CO86" s="1022" t="n"/>
-      <c r="CP86" s="1022" t="n"/>
-      <c r="CQ86" s="1022" t="n"/>
-      <c r="CR86" s="1022" t="n"/>
-      <c r="CS86" s="1022" t="n"/>
-      <c r="CT86" s="1022" t="n"/>
-      <c r="CU86" s="1022" t="n"/>
-      <c r="CV86" s="1022" t="n"/>
-      <c r="CW86" s="1022" t="n"/>
-      <c r="CX86" s="1024" t="n"/>
+      <c r="B86" s="1009" t="n"/>
+      <c r="C86" s="855" t="n"/>
+      <c r="D86" s="855" t="n"/>
+      <c r="E86" s="855" t="n"/>
+      <c r="F86" s="855" t="n"/>
+      <c r="G86" s="855" t="n"/>
+      <c r="H86" s="855" t="n"/>
+      <c r="I86" s="855" t="n"/>
+      <c r="J86" s="856" t="n"/>
+      <c r="K86" s="1010" t="n"/>
+      <c r="L86" s="732" t="n"/>
+      <c r="M86" s="732" t="n"/>
+      <c r="N86" s="732" t="n"/>
+      <c r="O86" s="732" t="n"/>
+      <c r="P86" s="732" t="n"/>
+      <c r="Q86" s="858" t="n"/>
+      <c r="R86" s="1011" t="n"/>
+      <c r="S86" s="856" t="n"/>
+      <c r="T86" s="1012" t="n"/>
+      <c r="U86" s="855" t="n"/>
+      <c r="V86" s="855" t="n"/>
+      <c r="W86" s="855" t="n"/>
+      <c r="X86" s="855" t="n"/>
+      <c r="Y86" s="855" t="n"/>
+      <c r="Z86" s="855" t="n"/>
+      <c r="AA86" s="855" t="n"/>
+      <c r="AB86" s="855" t="n"/>
+      <c r="AC86" s="855" t="n"/>
+      <c r="AD86" s="861" t="n"/>
+      <c r="AE86" s="771" t="n"/>
+      <c r="AF86" s="771" t="n"/>
+      <c r="AI86" s="771" t="n"/>
+      <c r="AJ86" s="771" t="n"/>
+      <c r="AK86" s="771" t="n"/>
+      <c r="AL86" s="771" t="n"/>
+      <c r="AM86" s="1014" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN86" s="856" t="n"/>
+      <c r="AO86" s="1015" t="inlineStr">
+        <is>
+          <t>CREATED_BY</t>
+        </is>
+      </c>
+      <c r="AP86" s="855" t="n"/>
+      <c r="AQ86" s="855" t="n"/>
+      <c r="AR86" s="855" t="n"/>
+      <c r="AS86" s="855" t="n"/>
+      <c r="AT86" s="855" t="n"/>
+      <c r="AU86" s="855" t="n"/>
+      <c r="AV86" s="855" t="n"/>
+      <c r="AW86" s="855" t="n"/>
+      <c r="AX86" s="855" t="n"/>
+      <c r="AY86" s="855" t="n"/>
+      <c r="AZ86" s="1015" t="inlineStr">
+        <is>
+          <t>Login name of the user who uploaded</t>
+        </is>
+      </c>
+      <c r="BA86" s="855" t="n"/>
+      <c r="BB86" s="855" t="n"/>
+      <c r="BC86" s="855" t="n"/>
+      <c r="BD86" s="855" t="n"/>
+      <c r="BE86" s="855" t="n"/>
+      <c r="BF86" s="855" t="n"/>
+      <c r="BG86" s="855" t="n"/>
+      <c r="BH86" s="855" t="n"/>
+      <c r="BI86" s="855" t="n"/>
+      <c r="BJ86" s="855" t="n"/>
+      <c r="BK86" s="855" t="n"/>
+      <c r="BL86" s="855" t="n"/>
+      <c r="BM86" s="855" t="n"/>
+      <c r="BN86" s="855" t="n"/>
+      <c r="BO86" s="855" t="n"/>
+      <c r="BP86" s="855" t="n"/>
+      <c r="BQ86" s="855" t="n"/>
+      <c r="BR86" s="855" t="n"/>
+      <c r="BS86" s="855" t="n"/>
+      <c r="BT86" s="855" t="n"/>
+      <c r="BU86" s="855" t="n"/>
+      <c r="BV86" s="855" t="n"/>
+      <c r="BW86" s="855" t="n"/>
+      <c r="BX86" s="855" t="n"/>
+      <c r="BY86" s="855" t="n"/>
+      <c r="BZ86" s="855" t="n"/>
+      <c r="CA86" s="855" t="n"/>
+      <c r="CB86" s="855" t="n"/>
+      <c r="CC86" s="855" t="n"/>
+      <c r="CD86" s="855" t="n"/>
+      <c r="CE86" s="855" t="n"/>
+      <c r="CF86" s="855" t="n"/>
+      <c r="CG86" s="1016" t="n"/>
+      <c r="CH86" s="855" t="n"/>
+      <c r="CI86" s="855" t="n"/>
+      <c r="CJ86" s="855" t="n"/>
+      <c r="CK86" s="855" t="n"/>
+      <c r="CL86" s="855" t="n"/>
+      <c r="CM86" s="855" t="n"/>
+      <c r="CN86" s="855" t="n"/>
+      <c r="CO86" s="855" t="n"/>
+      <c r="CP86" s="855" t="n"/>
+      <c r="CQ86" s="856" t="n"/>
+      <c r="CR86" s="1017" t="n"/>
+      <c r="CS86" s="732" t="n"/>
+      <c r="CT86" s="732" t="n"/>
+      <c r="CU86" s="732" t="n"/>
+      <c r="CV86" s="732" t="n"/>
+      <c r="CW86" s="732" t="n"/>
+      <c r="CX86" s="733" t="n"/>
       <c r="CY86" s="1022" t="n"/>
     </row>
     <row r="87" ht="11.1" customHeight="1" s="710">
-      <c r="A87" s="1022" t="n"/>
-      <c r="B87" s="1023" t="n"/>
-      <c r="C87" s="1022" t="n"/>
-      <c r="D87" s="1022" t="n"/>
-      <c r="E87" s="1022" t="n"/>
-      <c r="F87" s="1022" t="n"/>
-      <c r="G87" s="1022" t="n"/>
-      <c r="H87" s="1022" t="n"/>
-      <c r="I87" s="1022" t="n"/>
-      <c r="J87" s="1022" t="n"/>
-      <c r="K87" s="1022" t="n"/>
-      <c r="L87" s="1022" t="n"/>
-      <c r="M87" s="1022" t="n"/>
-      <c r="N87" s="1022" t="n"/>
-      <c r="O87" s="1022" t="n"/>
-      <c r="P87" s="1022" t="n"/>
-      <c r="Q87" s="1022" t="n"/>
-      <c r="R87" s="1022" t="n"/>
-      <c r="S87" s="1022" t="n"/>
-      <c r="T87" s="1022" t="n"/>
-      <c r="U87" s="1022" t="n"/>
-      <c r="V87" s="1022" t="n"/>
-      <c r="W87" s="1022" t="n"/>
-      <c r="X87" s="1022" t="n"/>
-      <c r="Y87" s="1022" t="n"/>
-      <c r="Z87" s="1022" t="n"/>
-      <c r="AA87" s="1022" t="n"/>
-      <c r="AB87" s="1022" t="n"/>
-      <c r="AC87" s="1022" t="n"/>
-      <c r="AD87" s="1022" t="n"/>
-      <c r="AE87" s="1022" t="n"/>
-      <c r="AF87" s="1022" t="n"/>
-      <c r="AG87" s="1022" t="n"/>
-      <c r="AH87" s="1022" t="n"/>
-      <c r="AI87" s="1022" t="n"/>
-      <c r="AJ87" s="1022" t="n"/>
-      <c r="AK87" s="1022" t="n"/>
-      <c r="AL87" s="1022" t="n"/>
-      <c r="AM87" s="1022" t="n"/>
-      <c r="AN87" s="1022" t="n"/>
-      <c r="AO87" s="1022" t="n"/>
-      <c r="AP87" s="1022" t="n"/>
-      <c r="AQ87" s="1022" t="n"/>
-      <c r="AR87" s="1022" t="n"/>
-      <c r="AS87" s="1022" t="n"/>
-      <c r="AT87" s="1022" t="n"/>
-      <c r="AU87" s="1022" t="n"/>
-      <c r="AV87" s="1022" t="n"/>
-      <c r="AW87" s="1022" t="n"/>
-      <c r="AX87" s="1022" t="n"/>
-      <c r="AY87" s="1022" t="n"/>
-      <c r="AZ87" s="1022" t="n"/>
-      <c r="BA87" s="1022" t="n"/>
-      <c r="BB87" s="1022" t="n"/>
-      <c r="BC87" s="1022" t="n"/>
-      <c r="BD87" s="1022" t="n"/>
-      <c r="BE87" s="1022" t="n"/>
-      <c r="BF87" s="1022" t="n"/>
-      <c r="BG87" s="1022" t="n"/>
-      <c r="BH87" s="1022" t="n"/>
-      <c r="BI87" s="1022" t="n"/>
-      <c r="BJ87" s="1022" t="n"/>
-      <c r="BK87" s="1022" t="n"/>
-      <c r="BL87" s="1022" t="n"/>
-      <c r="BM87" s="1022" t="n"/>
-      <c r="BN87" s="1022" t="n"/>
-      <c r="BO87" s="1022" t="n"/>
-      <c r="BP87" s="1022" t="n"/>
-      <c r="BQ87" s="1022" t="n"/>
-      <c r="BR87" s="1022" t="n"/>
-      <c r="BS87" s="1022" t="n"/>
-      <c r="BT87" s="1022" t="n"/>
-      <c r="BU87" s="1022" t="n"/>
-      <c r="BV87" s="1022" t="n"/>
-      <c r="BW87" s="1022" t="n"/>
-      <c r="BX87" s="1022" t="n"/>
-      <c r="BY87" s="1022" t="n"/>
-      <c r="BZ87" s="1022" t="n"/>
-      <c r="CA87" s="1022" t="n"/>
-      <c r="CB87" s="1022" t="n"/>
-      <c r="CC87" s="1022" t="n"/>
-      <c r="CD87" s="1022" t="n"/>
-      <c r="CE87" s="1022" t="n"/>
-      <c r="CF87" s="1022" t="n"/>
-      <c r="CG87" s="1022" t="n"/>
-      <c r="CH87" s="1022" t="n"/>
-      <c r="CI87" s="1022" t="n"/>
-      <c r="CJ87" s="1022" t="n"/>
-      <c r="CK87" s="1022" t="n"/>
-      <c r="CL87" s="1022" t="n"/>
-      <c r="CM87" s="1022" t="n"/>
-      <c r="CN87" s="1022" t="n"/>
-      <c r="CO87" s="1022" t="n"/>
-      <c r="CP87" s="1022" t="n"/>
-      <c r="CQ87" s="1022" t="n"/>
-      <c r="CR87" s="1022" t="n"/>
-      <c r="CS87" s="1022" t="n"/>
-      <c r="CT87" s="1022" t="n"/>
-      <c r="CU87" s="1022" t="n"/>
-      <c r="CV87" s="1022" t="n"/>
-      <c r="CW87" s="1022" t="n"/>
-      <c r="CX87" s="1024" t="n"/>
+      <c r="B87" s="1009" t="n"/>
+      <c r="C87" s="855" t="n"/>
+      <c r="D87" s="855" t="n"/>
+      <c r="E87" s="855" t="n"/>
+      <c r="F87" s="855" t="n"/>
+      <c r="G87" s="855" t="n"/>
+      <c r="H87" s="855" t="n"/>
+      <c r="I87" s="855" t="n"/>
+      <c r="J87" s="856" t="n"/>
+      <c r="K87" s="1010" t="n"/>
+      <c r="L87" s="732" t="n"/>
+      <c r="M87" s="732" t="n"/>
+      <c r="N87" s="732" t="n"/>
+      <c r="O87" s="732" t="n"/>
+      <c r="P87" s="732" t="n"/>
+      <c r="Q87" s="858" t="n"/>
+      <c r="R87" s="1011" t="n"/>
+      <c r="S87" s="856" t="n"/>
+      <c r="T87" s="1012" t="n"/>
+      <c r="U87" s="855" t="n"/>
+      <c r="V87" s="855" t="n"/>
+      <c r="W87" s="855" t="n"/>
+      <c r="X87" s="855" t="n"/>
+      <c r="Y87" s="855" t="n"/>
+      <c r="Z87" s="855" t="n"/>
+      <c r="AA87" s="855" t="n"/>
+      <c r="AB87" s="855" t="n"/>
+      <c r="AC87" s="855" t="n"/>
+      <c r="AD87" s="861" t="n"/>
+      <c r="AE87" s="771" t="n"/>
+      <c r="AF87" s="771" t="n"/>
+      <c r="AI87" s="771" t="n"/>
+      <c r="AJ87" s="771" t="n"/>
+      <c r="AK87" s="771" t="n"/>
+      <c r="AL87" s="771" t="n"/>
+      <c r="AM87" s="1014" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN87" s="856" t="n"/>
+      <c r="AO87" s="1015" t="inlineStr">
+        <is>
+          <t>CREATED_DT</t>
+        </is>
+      </c>
+      <c r="AP87" s="855" t="n"/>
+      <c r="AQ87" s="855" t="n"/>
+      <c r="AR87" s="855" t="n"/>
+      <c r="AS87" s="855" t="n"/>
+      <c r="AT87" s="855" t="n"/>
+      <c r="AU87" s="855" t="n"/>
+      <c r="AV87" s="855" t="n"/>
+      <c r="AW87" s="855" t="n"/>
+      <c r="AX87" s="855" t="n"/>
+      <c r="AY87" s="855" t="n"/>
+      <c r="AZ87" s="1015" t="inlineStr">
+        <is>
+          <t>Server system date and time</t>
+        </is>
+      </c>
+      <c r="BA87" s="855" t="n"/>
+      <c r="BB87" s="855" t="n"/>
+      <c r="BC87" s="855" t="n"/>
+      <c r="BD87" s="855" t="n"/>
+      <c r="BE87" s="855" t="n"/>
+      <c r="BF87" s="855" t="n"/>
+      <c r="BG87" s="855" t="n"/>
+      <c r="BH87" s="855" t="n"/>
+      <c r="BI87" s="855" t="n"/>
+      <c r="BJ87" s="855" t="n"/>
+      <c r="BK87" s="855" t="n"/>
+      <c r="BL87" s="855" t="n"/>
+      <c r="BM87" s="855" t="n"/>
+      <c r="BN87" s="855" t="n"/>
+      <c r="BO87" s="855" t="n"/>
+      <c r="BP87" s="855" t="n"/>
+      <c r="BQ87" s="855" t="n"/>
+      <c r="BR87" s="855" t="n"/>
+      <c r="BS87" s="855" t="n"/>
+      <c r="BT87" s="855" t="n"/>
+      <c r="BU87" s="855" t="n"/>
+      <c r="BV87" s="855" t="n"/>
+      <c r="BW87" s="855" t="n"/>
+      <c r="BX87" s="855" t="n"/>
+      <c r="BY87" s="855" t="n"/>
+      <c r="BZ87" s="855" t="n"/>
+      <c r="CA87" s="855" t="n"/>
+      <c r="CB87" s="855" t="n"/>
+      <c r="CC87" s="855" t="n"/>
+      <c r="CD87" s="855" t="n"/>
+      <c r="CE87" s="855" t="n"/>
+      <c r="CF87" s="855" t="n"/>
+      <c r="CG87" s="1016" t="n"/>
+      <c r="CH87" s="855" t="n"/>
+      <c r="CI87" s="855" t="n"/>
+      <c r="CJ87" s="855" t="n"/>
+      <c r="CK87" s="855" t="n"/>
+      <c r="CL87" s="855" t="n"/>
+      <c r="CM87" s="855" t="n"/>
+      <c r="CN87" s="855" t="n"/>
+      <c r="CO87" s="855" t="n"/>
+      <c r="CP87" s="855" t="n"/>
+      <c r="CQ87" s="856" t="n"/>
+      <c r="CR87" s="1017" t="n"/>
+      <c r="CS87" s="732" t="n"/>
+      <c r="CT87" s="732" t="n"/>
+      <c r="CU87" s="732" t="n"/>
+      <c r="CV87" s="732" t="n"/>
+      <c r="CW87" s="732" t="n"/>
+      <c r="CX87" s="733" t="n"/>
       <c r="CY87" s="1022" t="n"/>
     </row>
     <row r="88" ht="11.1" customHeight="1" s="710">
@@ -36977,7 +37061,7 @@
       <c r="CY130" s="1022" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="600">
+  <mergeCells count="636">
     <mergeCell ref="B67:J67"/>
     <mergeCell ref="B61:J61"/>
     <mergeCell ref="R67:S67"/>
@@ -36991,9 +37075,11 @@
     <mergeCell ref="AM56:AN56"/>
     <mergeCell ref="R69:S69"/>
     <mergeCell ref="AZ54:CF54"/>
-    <mergeCell ref="BT90:BX90"/>
+    <mergeCell ref="B87:J87"/>
     <mergeCell ref="AO13:AY13"/>
     <mergeCell ref="CG53:CQ53"/>
+    <mergeCell ref="BT90:BX90"/>
+    <mergeCell ref="CR87:CX87"/>
     <mergeCell ref="CG96:CQ96"/>
     <mergeCell ref="K92:Q92"/>
     <mergeCell ref="CR62:CX62"/>
@@ -37074,16 +37160,21 @@
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="R20:S20"/>
     <mergeCell ref="AM78:AN78"/>
+    <mergeCell ref="B85:J85"/>
+    <mergeCell ref="R85:S85"/>
     <mergeCell ref="CR14:CX14"/>
     <mergeCell ref="AM72:AN73"/>
     <mergeCell ref="CF49:CX49"/>
     <mergeCell ref="CO4:CX4"/>
     <mergeCell ref="CG69:CQ69"/>
+    <mergeCell ref="T85:AD85"/>
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="CR78:CX78"/>
+    <mergeCell ref="T84:AD84"/>
     <mergeCell ref="T22:AD22"/>
     <mergeCell ref="K75:Q75"/>
     <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="T86:AD86"/>
     <mergeCell ref="B96:J96"/>
     <mergeCell ref="AM27:AN27"/>
     <mergeCell ref="CR96:CX96"/>
@@ -37105,6 +37196,7 @@
     <mergeCell ref="AZ12:CF12"/>
     <mergeCell ref="T91:AD92"/>
     <mergeCell ref="K63:Q63"/>
+    <mergeCell ref="AM84:AN84"/>
     <mergeCell ref="CR20:CX20"/>
     <mergeCell ref="AM75:AN75"/>
     <mergeCell ref="CR17:CX17"/>
@@ -37114,19 +37206,23 @@
     <mergeCell ref="AM15:AN15"/>
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="K58:Q58"/>
-    <mergeCell ref="B93:J93"/>
+    <mergeCell ref="AM86:AN86"/>
     <mergeCell ref="AZ13:CF13"/>
     <mergeCell ref="K52:Q52"/>
     <mergeCell ref="AM80:AN80"/>
     <mergeCell ref="CR22:CX22"/>
+    <mergeCell ref="CR84:CX84"/>
+    <mergeCell ref="AZ78:CF78"/>
+    <mergeCell ref="B93:J93"/>
     <mergeCell ref="R93:S93"/>
-    <mergeCell ref="AZ78:CF78"/>
     <mergeCell ref="AZ72:CF73"/>
     <mergeCell ref="AM79:AN79"/>
     <mergeCell ref="T9:AD10"/>
+    <mergeCell ref="B86:J86"/>
     <mergeCell ref="CR99:CX99"/>
     <mergeCell ref="AZ15:CF15"/>
     <mergeCell ref="AO52:AY52"/>
+    <mergeCell ref="CR86:CX86"/>
     <mergeCell ref="CR80:CX80"/>
     <mergeCell ref="AZ80:CF80"/>
     <mergeCell ref="B101:J101"/>
@@ -37159,9 +37255,12 @@
     <mergeCell ref="AZ68:CF68"/>
     <mergeCell ref="AM94:AN94"/>
     <mergeCell ref="CG20:CQ20"/>
+    <mergeCell ref="AZ84:CF84"/>
+    <mergeCell ref="CG85:CQ85"/>
     <mergeCell ref="T101:AD101"/>
     <mergeCell ref="AM14:AN14"/>
     <mergeCell ref="CR61:CX61"/>
+    <mergeCell ref="AZ86:CF86"/>
     <mergeCell ref="R59:S59"/>
     <mergeCell ref="CO3:CX3"/>
     <mergeCell ref="K66:Q66"/>
@@ -37237,6 +37336,7 @@
     <mergeCell ref="T97:AD97"/>
     <mergeCell ref="B82:J82"/>
     <mergeCell ref="T72:AD73"/>
+    <mergeCell ref="K87:Q87"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="CR57:CX57"/>
     <mergeCell ref="CR54:CX54"/>
@@ -37270,6 +37370,7 @@
     <mergeCell ref="B13:J13"/>
     <mergeCell ref="AO23:AY23"/>
     <mergeCell ref="B78:J78"/>
+    <mergeCell ref="R84:S84"/>
     <mergeCell ref="R78:S78"/>
     <mergeCell ref="AM58:AN58"/>
     <mergeCell ref="BY49:CE49"/>
@@ -37278,6 +37379,7 @@
     <mergeCell ref="CG62:CQ62"/>
     <mergeCell ref="T78:AD78"/>
     <mergeCell ref="CG56:CQ56"/>
+    <mergeCell ref="AO87:AY87"/>
     <mergeCell ref="T65:AD65"/>
     <mergeCell ref="AM24:AN24"/>
     <mergeCell ref="R80:S80"/>
@@ -37294,6 +37396,7 @@
     <mergeCell ref="K21:Q21"/>
     <mergeCell ref="AZ58:CF58"/>
     <mergeCell ref="B25:J25"/>
+    <mergeCell ref="CR85:CX85"/>
     <mergeCell ref="H2:N2"/>
     <mergeCell ref="K96:Q96"/>
     <mergeCell ref="AZ60:CF60"/>
@@ -37320,12 +37423,14 @@
     <mergeCell ref="CG52:CQ52"/>
     <mergeCell ref="T68:AD68"/>
     <mergeCell ref="K16:Q16"/>
+    <mergeCell ref="B84:J84"/>
     <mergeCell ref="T55:AD55"/>
     <mergeCell ref="R9:S10"/>
     <mergeCell ref="B72:Q72"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="AO14:AY14"/>
     <mergeCell ref="B80:J80"/>
+    <mergeCell ref="R86:S86"/>
     <mergeCell ref="CR15:CX15"/>
     <mergeCell ref="CG64:CQ64"/>
     <mergeCell ref="B79:J79"/>
@@ -37369,6 +37474,7 @@
     <mergeCell ref="CR67:CX67"/>
     <mergeCell ref="R76:S76"/>
     <mergeCell ref="AZ61:CF61"/>
+    <mergeCell ref="AM87:AN87"/>
     <mergeCell ref="B94:J94"/>
     <mergeCell ref="T76:AD76"/>
     <mergeCell ref="T100:AD100"/>
@@ -37387,8 +37493,10 @@
     <mergeCell ref="AZ74:CF74"/>
     <mergeCell ref="AO76:AY76"/>
     <mergeCell ref="CG25:CQ25"/>
+    <mergeCell ref="R87:S87"/>
     <mergeCell ref="AZ76:CF76"/>
     <mergeCell ref="K62:Q62"/>
+    <mergeCell ref="T87:AD87"/>
     <mergeCell ref="AM77:AN77"/>
     <mergeCell ref="R24:S24"/>
     <mergeCell ref="CR97:CX97"/>
@@ -37406,6 +37514,7 @@
     <mergeCell ref="B100:J100"/>
     <mergeCell ref="O3:AI3"/>
     <mergeCell ref="AZ23:CF23"/>
+    <mergeCell ref="CG84:CQ84"/>
     <mergeCell ref="CR94:CX94"/>
     <mergeCell ref="AZ69:CF69"/>
     <mergeCell ref="K67:Q67"/>
@@ -37413,8 +37522,10 @@
     <mergeCell ref="AO59:AY59"/>
     <mergeCell ref="CG72:CX72"/>
     <mergeCell ref="CG99:CQ99"/>
+    <mergeCell ref="AZ87:CF87"/>
     <mergeCell ref="B77:J77"/>
     <mergeCell ref="CG15:CQ15"/>
+    <mergeCell ref="CG86:CQ86"/>
     <mergeCell ref="AM26:AN26"/>
     <mergeCell ref="T77:AD77"/>
     <mergeCell ref="AM97:AN97"/>
@@ -37460,11 +37571,13 @@
     <mergeCell ref="AE15:AL15"/>
     <mergeCell ref="CF90:CX90"/>
     <mergeCell ref="B27:J27"/>
+    <mergeCell ref="AM85:AN85"/>
     <mergeCell ref="R98:S98"/>
     <mergeCell ref="T27:AD27"/>
-    <mergeCell ref="T98:AD98"/>
+    <mergeCell ref="AO85:AY85"/>
     <mergeCell ref="BY90:CE90"/>
     <mergeCell ref="CG76:CQ76"/>
+    <mergeCell ref="T98:AD98"/>
     <mergeCell ref="CA4:CH4"/>
     <mergeCell ref="K17:Q17"/>
     <mergeCell ref="R63:S63"/>
@@ -37491,6 +37604,7 @@
     <mergeCell ref="K60:Q60"/>
     <mergeCell ref="T11:AD11"/>
     <mergeCell ref="BK90:BS90"/>
+    <mergeCell ref="CG87:CQ87"/>
     <mergeCell ref="CR21:CX21"/>
     <mergeCell ref="T75:AD75"/>
     <mergeCell ref="CG24:CQ24"/>
@@ -37518,28 +37632,33 @@
     <mergeCell ref="K65:Q65"/>
     <mergeCell ref="AM93:AN93"/>
     <mergeCell ref="AZ20:CF20"/>
+    <mergeCell ref="AZ85:CF85"/>
     <mergeCell ref="AO75:AY75"/>
     <mergeCell ref="CO2:CX2"/>
     <mergeCell ref="AZ22:CF22"/>
     <mergeCell ref="CR93:CX93"/>
+    <mergeCell ref="AO86:AY86"/>
     <mergeCell ref="CG77:CQ77"/>
     <mergeCell ref="AZ96:CF96"/>
     <mergeCell ref="K20:Q20"/>
     <mergeCell ref="R17:S17"/>
     <mergeCell ref="R66:S66"/>
+    <mergeCell ref="K85:Q85"/>
     <mergeCell ref="CR55:CX55"/>
     <mergeCell ref="R53:S53"/>
     <mergeCell ref="T17:AD17"/>
     <mergeCell ref="AZ98:CF98"/>
     <mergeCell ref="B59:J59"/>
+    <mergeCell ref="K84:Q84"/>
     <mergeCell ref="AM12:AN12"/>
     <mergeCell ref="K22:Q22"/>
     <mergeCell ref="R68:S68"/>
     <mergeCell ref="T19:AD19"/>
     <mergeCell ref="T50:AD51"/>
     <mergeCell ref="CR25:CX25"/>
+    <mergeCell ref="K86:Q86"/>
+    <mergeCell ref="R61:S61"/>
     <mergeCell ref="CG95:CQ95"/>
-    <mergeCell ref="R61:S61"/>
     <mergeCell ref="CR12:CX12"/>
     <mergeCell ref="CG26:CQ26"/>
     <mergeCell ref="CG97:CQ97"/>
@@ -37577,6 +37696,7 @@
     <mergeCell ref="K81:Q81"/>
     <mergeCell ref="CR51:CX51"/>
     <mergeCell ref="K99:Q99"/>
+    <mergeCell ref="AO84:AY84"/>
     <mergeCell ref="B21:J21"/>
   </mergeCells>
   <dataValidations count="1">
@@ -41378,7 +41498,7 @@
       <c r="C35" s="941" t="n"/>
       <c r="D35" s="948" t="inlineStr">
         <is>
-          <t>TB_H_PART_CANDIDATE (event ADD / EDIT, source UPLOAD). Column names TBD.</t>
+          <t>TB_H_PART_CANDIDATE (event ADD / EDIT, source UPLOAD, UPLOAD_ID of this run; refer</t>
         </is>
       </c>
       <c r="E35" s="949" t="n"/>
@@ -41484,14 +41604,10 @@
     <row r="36" ht="11.1" customHeight="1" s="710">
       <c r="A36" s="941" t="n"/>
       <c r="B36" s="942" t="n"/>
-      <c r="C36" s="948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C36" s="941" t="n"/>
       <c r="D36" s="948" t="inlineStr">
         <is>
-          <t>Every saved record gets Sync Status = No Sync. It is sent to the global system by the RPA</t>
+          <t>Appendix).</t>
         </is>
       </c>
       <c r="E36" s="949" t="n"/>
@@ -41597,10 +41713,14 @@
     <row r="37" ht="11.1" customHeight="1" s="710">
       <c r="A37" s="941" t="n"/>
       <c r="B37" s="942" t="n"/>
-      <c r="C37" s="941" t="n"/>
+      <c r="C37" s="948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D37" s="948" t="inlineStr">
         <is>
-          <t>when D/S clicks [Sync] in Mapping per Destination.</t>
+          <t>Every saved record gets Sync Status = No Sync. It is sent to the global system by the RPA</t>
         </is>
       </c>
       <c r="E37" s="949" t="n"/>
@@ -41706,14 +41826,10 @@
     <row r="38" ht="11.1" customHeight="1" s="710">
       <c r="A38" s="941" t="n"/>
       <c r="B38" s="942" t="n"/>
-      <c r="C38" s="948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C38" s="941" t="n"/>
       <c r="D38" s="948" t="inlineStr">
         <is>
-          <t>A result report (.xlsx) is created for both cases.</t>
+          <t>when D/S clicks [Sync] in Mapping per Destination.</t>
         </is>
       </c>
       <c r="E38" s="949" t="n"/>
@@ -41819,8 +41935,16 @@
     <row r="39" ht="11.1" customHeight="1" s="710">
       <c r="A39" s="941" t="n"/>
       <c r="B39" s="942" t="n"/>
-      <c r="C39" s="941" t="n"/>
-      <c r="D39" s="941" t="n"/>
+      <c r="C39" s="948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="948" t="inlineStr">
+        <is>
+          <t>A result report (.xlsx) is created for both cases.</t>
+        </is>
+      </c>
       <c r="E39" s="949" t="n"/>
       <c r="F39" s="949" t="n"/>
       <c r="G39" s="949" t="n"/>
@@ -43742,7 +43866,7 @@
       <c r="AP9" s="955" t="n"/>
       <c r="AQ9" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG1</t>
         </is>
       </c>
       <c r="AR9" s="957" t="n"/>
@@ -43978,7 +44102,7 @@
       <c r="AP11" s="955" t="n"/>
       <c r="AQ11" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG2</t>
         </is>
       </c>
       <c r="AR11" s="957" t="n"/>
@@ -44539,7 +44663,7 @@
       <c r="AP16" s="955" t="n"/>
       <c r="AQ16" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG3</t>
         </is>
       </c>
       <c r="AR16" s="957" t="n"/>
@@ -44779,7 +44903,7 @@
       <c r="AP18" s="955" t="n"/>
       <c r="AQ18" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG4</t>
         </is>
       </c>
       <c r="AR18" s="957" t="n"/>
@@ -45233,7 +45357,7 @@
       <c r="AP22" s="955" t="n"/>
       <c r="AQ22" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG5</t>
         </is>
       </c>
       <c r="AR22" s="957" t="n"/>
@@ -45580,7 +45704,7 @@
       <c r="AP25" s="955" t="n"/>
       <c r="AQ25" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG6</t>
         </is>
       </c>
       <c r="AR25" s="957" t="n"/>
@@ -45824,7 +45948,7 @@
       <c r="AP27" s="955" t="n"/>
       <c r="AQ27" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG7</t>
         </is>
       </c>
       <c r="AR27" s="957" t="n"/>
@@ -46068,7 +46192,7 @@
       <c r="AP29" s="955" t="n"/>
       <c r="AQ29" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG8</t>
         </is>
       </c>
       <c r="AR29" s="957" t="n"/>
@@ -46308,7 +46432,7 @@
       <c r="AP31" s="955" t="n"/>
       <c r="AQ31" s="1035" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>LOG9</t>
         </is>
       </c>
       <c r="AR31" s="957" t="n"/>
@@ -48141,7 +48265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CY48"/>
+  <dimension ref="A1:CY90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="1.41796875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="0.7" customWidth="1" style="754" min="1" max="1"/>
@@ -50091,7 +50215,7 @@
       <c r="B20" s="942" t="n"/>
       <c r="C20" s="946" t="inlineStr">
         <is>
-          <t>Table definitions</t>
+          <t>Table definitions (proposed)</t>
         </is>
       </c>
       <c r="D20" s="941" t="n"/>
@@ -50199,7 +50323,11 @@
       <c r="A21" s="941" t="n"/>
       <c r="B21" s="942" t="n"/>
       <c r="C21" s="949" t="n"/>
-      <c r="D21" s="949" t="n"/>
+      <c r="D21" s="1049" t="inlineStr">
+        <is>
+          <t>Names/lengths marked proposed or TBD must be aligned with the project naming convention and master tables before development.</t>
+        </is>
+      </c>
       <c r="E21" s="941" t="n"/>
       <c r="F21" s="949" t="n"/>
       <c r="G21" s="941" t="n"/>
@@ -50304,11 +50432,7 @@
       <c r="A22" s="941" t="n"/>
       <c r="B22" s="942" t="n"/>
       <c r="C22" s="941" t="n"/>
-      <c r="D22" s="946" t="inlineStr">
-        <is>
-          <t>TB_M_PART_CANDIDATE</t>
-        </is>
-      </c>
+      <c r="D22" s="941" t="n"/>
       <c r="E22" s="949" t="n"/>
       <c r="F22" s="949" t="n"/>
       <c r="G22" s="949" t="n"/>
@@ -50413,12 +50537,12 @@
       <c r="A23" s="941" t="n"/>
       <c r="B23" s="942" t="n"/>
       <c r="C23" s="949" t="n"/>
-      <c r="D23" s="949" t="n"/>
-      <c r="E23" s="1029" t="inlineStr">
-        <is>
-          <t>Transaction table - Candidate part setting, one record per part (Part List data, no calculation period). Target of a successful upload.</t>
-        </is>
-      </c>
+      <c r="D23" s="945" t="inlineStr">
+        <is>
+          <t>TB_M_PART_CANDIDATE</t>
+        </is>
+      </c>
+      <c r="E23" s="949" t="n"/>
       <c r="F23" s="949" t="n"/>
       <c r="G23" s="949" t="n"/>
       <c r="H23" s="949" t="n"/>
@@ -50523,119 +50647,103 @@
       <c r="B24" s="942" t="n"/>
       <c r="C24" s="941" t="n"/>
       <c r="D24" s="941" t="n"/>
-      <c r="E24" s="953" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="F24" s="952" t="n"/>
-      <c r="G24" s="952" t="n"/>
-      <c r="H24" s="952" t="n"/>
-      <c r="I24" s="952" t="n"/>
-      <c r="J24" s="952" t="n"/>
-      <c r="K24" s="952" t="n"/>
-      <c r="L24" s="952" t="n"/>
-      <c r="M24" s="952" t="n"/>
-      <c r="N24" s="952" t="n"/>
-      <c r="O24" s="952" t="n"/>
-      <c r="P24" s="952" t="n"/>
-      <c r="Q24" s="952" t="n"/>
-      <c r="R24" s="952" t="n"/>
-      <c r="S24" s="952" t="n"/>
-      <c r="T24" s="951" t="n"/>
-      <c r="U24" s="950" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="V24" s="952" t="n"/>
-      <c r="W24" s="952" t="n"/>
-      <c r="X24" s="952" t="n"/>
-      <c r="Y24" s="952" t="n"/>
-      <c r="Z24" s="952" t="n"/>
-      <c r="AA24" s="952" t="n"/>
-      <c r="AB24" s="952" t="n"/>
-      <c r="AC24" s="952" t="n"/>
-      <c r="AD24" s="952" t="n"/>
-      <c r="AE24" s="952" t="n"/>
-      <c r="AF24" s="951" t="n"/>
-      <c r="AG24" s="950" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="AH24" s="952" t="n"/>
-      <c r="AI24" s="951" t="n"/>
-      <c r="AJ24" s="950" t="inlineStr">
-        <is>
-          <t>Null</t>
-        </is>
-      </c>
-      <c r="AK24" s="952" t="n"/>
-      <c r="AL24" s="952" t="n"/>
-      <c r="AM24" s="951" t="n"/>
-      <c r="AN24" s="950" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="AO24" s="952" t="n"/>
-      <c r="AP24" s="952" t="n"/>
-      <c r="AQ24" s="952" t="n"/>
-      <c r="AR24" s="952" t="n"/>
-      <c r="AS24" s="952" t="n"/>
-      <c r="AT24" s="952" t="n"/>
-      <c r="AU24" s="952" t="n"/>
-      <c r="AV24" s="952" t="n"/>
-      <c r="AW24" s="952" t="n"/>
-      <c r="AX24" s="952" t="n"/>
-      <c r="AY24" s="952" t="n"/>
-      <c r="AZ24" s="952" t="n"/>
-      <c r="BA24" s="952" t="n"/>
-      <c r="BB24" s="952" t="n"/>
-      <c r="BC24" s="952" t="n"/>
-      <c r="BD24" s="952" t="n"/>
-      <c r="BE24" s="952" t="n"/>
-      <c r="BF24" s="952" t="n"/>
-      <c r="BG24" s="952" t="n"/>
-      <c r="BH24" s="952" t="n"/>
-      <c r="BI24" s="952" t="n"/>
-      <c r="BJ24" s="952" t="n"/>
-      <c r="BK24" s="952" t="n"/>
-      <c r="BL24" s="952" t="n"/>
-      <c r="BM24" s="952" t="n"/>
-      <c r="BN24" s="952" t="n"/>
-      <c r="BO24" s="952" t="n"/>
-      <c r="BP24" s="952" t="n"/>
-      <c r="BQ24" s="952" t="n"/>
-      <c r="BR24" s="952" t="n"/>
-      <c r="BS24" s="952" t="n"/>
-      <c r="BT24" s="952" t="n"/>
-      <c r="BU24" s="952" t="n"/>
-      <c r="BV24" s="952" t="n"/>
-      <c r="BW24" s="952" t="n"/>
-      <c r="BX24" s="952" t="n"/>
-      <c r="BY24" s="952" t="n"/>
-      <c r="BZ24" s="952" t="n"/>
-      <c r="CA24" s="952" t="n"/>
-      <c r="CB24" s="952" t="n"/>
-      <c r="CC24" s="952" t="n"/>
-      <c r="CD24" s="952" t="n"/>
-      <c r="CE24" s="952" t="n"/>
-      <c r="CF24" s="952" t="n"/>
-      <c r="CG24" s="952" t="n"/>
-      <c r="CH24" s="952" t="n"/>
-      <c r="CI24" s="952" t="n"/>
-      <c r="CJ24" s="952" t="n"/>
-      <c r="CK24" s="952" t="n"/>
-      <c r="CL24" s="952" t="n"/>
-      <c r="CM24" s="952" t="n"/>
-      <c r="CN24" s="952" t="n"/>
-      <c r="CO24" s="952" t="n"/>
-      <c r="CP24" s="952" t="n"/>
-      <c r="CQ24" s="952" t="n"/>
-      <c r="CR24" s="952" t="n"/>
-      <c r="CS24" s="951" t="n"/>
+      <c r="E24" s="1029" t="inlineStr">
+        <is>
+          <t>Transaction table - Candidate part setting, one record per part (Part List data, no calculation period). Target of a successful upload.</t>
+        </is>
+      </c>
+      <c r="F24" s="949" t="n"/>
+      <c r="G24" s="949" t="n"/>
+      <c r="H24" s="949" t="n"/>
+      <c r="I24" s="949" t="n"/>
+      <c r="J24" s="949" t="n"/>
+      <c r="K24" s="949" t="n"/>
+      <c r="L24" s="949" t="n"/>
+      <c r="M24" s="949" t="n"/>
+      <c r="N24" s="949" t="n"/>
+      <c r="O24" s="949" t="n"/>
+      <c r="P24" s="949" t="n"/>
+      <c r="Q24" s="941" t="n"/>
+      <c r="R24" s="941" t="n"/>
+      <c r="S24" s="941" t="n"/>
+      <c r="T24" s="941" t="n"/>
+      <c r="U24" s="941" t="n"/>
+      <c r="V24" s="941" t="n"/>
+      <c r="W24" s="941" t="n"/>
+      <c r="X24" s="941" t="n"/>
+      <c r="Y24" s="949" t="n"/>
+      <c r="Z24" s="949" t="n"/>
+      <c r="AA24" s="941" t="n"/>
+      <c r="AB24" s="941" t="n"/>
+      <c r="AC24" s="941" t="n"/>
+      <c r="AD24" s="941" t="n"/>
+      <c r="AE24" s="941" t="n"/>
+      <c r="AF24" s="941" t="n"/>
+      <c r="AG24" s="941" t="n"/>
+      <c r="AH24" s="941" t="n"/>
+      <c r="AI24" s="941" t="n"/>
+      <c r="AJ24" s="941" t="n"/>
+      <c r="AK24" s="941" t="n"/>
+      <c r="AL24" s="941" t="n"/>
+      <c r="AM24" s="941" t="n"/>
+      <c r="AN24" s="941" t="n"/>
+      <c r="AO24" s="941" t="n"/>
+      <c r="AP24" s="941" t="n"/>
+      <c r="AQ24" s="941" t="n"/>
+      <c r="AR24" s="941" t="n"/>
+      <c r="AS24" s="941" t="n"/>
+      <c r="AT24" s="941" t="n"/>
+      <c r="AU24" s="941" t="n"/>
+      <c r="AV24" s="941" t="n"/>
+      <c r="AW24" s="941" t="n"/>
+      <c r="AX24" s="941" t="n"/>
+      <c r="AY24" s="941" t="n"/>
+      <c r="AZ24" s="943" t="n"/>
+      <c r="BA24" s="941" t="n"/>
+      <c r="BB24" s="941" t="n"/>
+      <c r="BC24" s="941" t="n"/>
+      <c r="BD24" s="941" t="n"/>
+      <c r="BE24" s="941" t="n"/>
+      <c r="BF24" s="941" t="n"/>
+      <c r="BG24" s="941" t="n"/>
+      <c r="BH24" s="941" t="n"/>
+      <c r="BI24" s="941" t="n"/>
+      <c r="BJ24" s="941" t="n"/>
+      <c r="BK24" s="941" t="n"/>
+      <c r="BL24" s="941" t="n"/>
+      <c r="BM24" s="941" t="n"/>
+      <c r="BN24" s="941" t="n"/>
+      <c r="BO24" s="941" t="n"/>
+      <c r="BP24" s="941" t="n"/>
+      <c r="BQ24" s="941" t="n"/>
+      <c r="BR24" s="941" t="n"/>
+      <c r="BS24" s="941" t="n"/>
+      <c r="BT24" s="941" t="n"/>
+      <c r="BU24" s="941" t="n"/>
+      <c r="BV24" s="941" t="n"/>
+      <c r="BW24" s="941" t="n"/>
+      <c r="BX24" s="941" t="n"/>
+      <c r="BY24" s="941" t="n"/>
+      <c r="BZ24" s="941" t="n"/>
+      <c r="CA24" s="941" t="n"/>
+      <c r="CB24" s="941" t="n"/>
+      <c r="CC24" s="941" t="n"/>
+      <c r="CD24" s="941" t="n"/>
+      <c r="CE24" s="941" t="n"/>
+      <c r="CF24" s="941" t="n"/>
+      <c r="CG24" s="941" t="n"/>
+      <c r="CH24" s="941" t="n"/>
+      <c r="CI24" s="941" t="n"/>
+      <c r="CJ24" s="941" t="n"/>
+      <c r="CK24" s="941" t="n"/>
+      <c r="CL24" s="941" t="n"/>
+      <c r="CM24" s="941" t="n"/>
+      <c r="CN24" s="941" t="n"/>
+      <c r="CO24" s="941" t="n"/>
+      <c r="CP24" s="941" t="n"/>
+      <c r="CQ24" s="941" t="n"/>
+      <c r="CR24" s="941" t="n"/>
+      <c r="CS24" s="941" t="n"/>
       <c r="CT24" s="941" t="n"/>
       <c r="CU24" s="941" t="n"/>
       <c r="CV24" s="941" t="n"/>
@@ -50648,119 +50756,119 @@
       <c r="B25" s="942" t="n"/>
       <c r="C25" s="941" t="n"/>
       <c r="D25" s="941" t="n"/>
-      <c r="E25" s="966" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F25" s="957" t="n"/>
-      <c r="G25" s="957" t="n"/>
-      <c r="H25" s="957" t="n"/>
-      <c r="I25" s="957" t="n"/>
-      <c r="J25" s="957" t="n"/>
-      <c r="K25" s="957" t="n"/>
-      <c r="L25" s="957" t="n"/>
-      <c r="M25" s="957" t="n"/>
-      <c r="N25" s="957" t="n"/>
-      <c r="O25" s="957" t="n"/>
-      <c r="P25" s="957" t="n"/>
-      <c r="Q25" s="957" t="n"/>
-      <c r="R25" s="957" t="n"/>
-      <c r="S25" s="957" t="n"/>
-      <c r="T25" s="955" t="n"/>
-      <c r="U25" s="956" t="inlineStr">
-        <is>
-          <t>VARCHAR(TBD)</t>
-        </is>
-      </c>
-      <c r="V25" s="957" t="n"/>
-      <c r="W25" s="957" t="n"/>
-      <c r="X25" s="957" t="n"/>
-      <c r="Y25" s="957" t="n"/>
-      <c r="Z25" s="957" t="n"/>
-      <c r="AA25" s="957" t="n"/>
-      <c r="AB25" s="957" t="n"/>
-      <c r="AC25" s="957" t="n"/>
-      <c r="AD25" s="957" t="n"/>
-      <c r="AE25" s="957" t="n"/>
-      <c r="AF25" s="955" t="n"/>
-      <c r="AG25" s="954" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AH25" s="957" t="n"/>
-      <c r="AI25" s="955" t="n"/>
-      <c r="AJ25" s="954" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AK25" s="957" t="n"/>
-      <c r="AL25" s="957" t="n"/>
-      <c r="AM25" s="955" t="n"/>
-      <c r="AN25" s="956" t="inlineStr">
-        <is>
-          <t>Part number; length follows TB_M_PART_MASTER</t>
-        </is>
-      </c>
-      <c r="AO25" s="957" t="n"/>
-      <c r="AP25" s="957" t="n"/>
-      <c r="AQ25" s="957" t="n"/>
-      <c r="AR25" s="957" t="n"/>
-      <c r="AS25" s="957" t="n"/>
-      <c r="AT25" s="957" t="n"/>
-      <c r="AU25" s="957" t="n"/>
-      <c r="AV25" s="957" t="n"/>
-      <c r="AW25" s="957" t="n"/>
-      <c r="AX25" s="957" t="n"/>
-      <c r="AY25" s="957" t="n"/>
-      <c r="AZ25" s="957" t="n"/>
-      <c r="BA25" s="957" t="n"/>
-      <c r="BB25" s="957" t="n"/>
-      <c r="BC25" s="957" t="n"/>
-      <c r="BD25" s="957" t="n"/>
-      <c r="BE25" s="957" t="n"/>
-      <c r="BF25" s="957" t="n"/>
-      <c r="BG25" s="957" t="n"/>
-      <c r="BH25" s="957" t="n"/>
-      <c r="BI25" s="957" t="n"/>
-      <c r="BJ25" s="957" t="n"/>
-      <c r="BK25" s="957" t="n"/>
-      <c r="BL25" s="957" t="n"/>
-      <c r="BM25" s="957" t="n"/>
-      <c r="BN25" s="957" t="n"/>
-      <c r="BO25" s="957" t="n"/>
-      <c r="BP25" s="957" t="n"/>
-      <c r="BQ25" s="957" t="n"/>
-      <c r="BR25" s="957" t="n"/>
-      <c r="BS25" s="957" t="n"/>
-      <c r="BT25" s="957" t="n"/>
-      <c r="BU25" s="957" t="n"/>
-      <c r="BV25" s="957" t="n"/>
-      <c r="BW25" s="957" t="n"/>
-      <c r="BX25" s="957" t="n"/>
-      <c r="BY25" s="957" t="n"/>
-      <c r="BZ25" s="957" t="n"/>
-      <c r="CA25" s="957" t="n"/>
-      <c r="CB25" s="957" t="n"/>
-      <c r="CC25" s="957" t="n"/>
-      <c r="CD25" s="957" t="n"/>
-      <c r="CE25" s="957" t="n"/>
-      <c r="CF25" s="957" t="n"/>
-      <c r="CG25" s="957" t="n"/>
-      <c r="CH25" s="957" t="n"/>
-      <c r="CI25" s="957" t="n"/>
-      <c r="CJ25" s="957" t="n"/>
-      <c r="CK25" s="957" t="n"/>
-      <c r="CL25" s="957" t="n"/>
-      <c r="CM25" s="957" t="n"/>
-      <c r="CN25" s="957" t="n"/>
-      <c r="CO25" s="957" t="n"/>
-      <c r="CP25" s="957" t="n"/>
-      <c r="CQ25" s="957" t="n"/>
-      <c r="CR25" s="957" t="n"/>
-      <c r="CS25" s="955" t="n"/>
+      <c r="E25" s="953" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="F25" s="952" t="n"/>
+      <c r="G25" s="952" t="n"/>
+      <c r="H25" s="952" t="n"/>
+      <c r="I25" s="952" t="n"/>
+      <c r="J25" s="952" t="n"/>
+      <c r="K25" s="952" t="n"/>
+      <c r="L25" s="952" t="n"/>
+      <c r="M25" s="952" t="n"/>
+      <c r="N25" s="952" t="n"/>
+      <c r="O25" s="952" t="n"/>
+      <c r="P25" s="952" t="n"/>
+      <c r="Q25" s="952" t="n"/>
+      <c r="R25" s="952" t="n"/>
+      <c r="S25" s="952" t="n"/>
+      <c r="T25" s="951" t="n"/>
+      <c r="U25" s="950" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="V25" s="952" t="n"/>
+      <c r="W25" s="952" t="n"/>
+      <c r="X25" s="952" t="n"/>
+      <c r="Y25" s="952" t="n"/>
+      <c r="Z25" s="952" t="n"/>
+      <c r="AA25" s="952" t="n"/>
+      <c r="AB25" s="952" t="n"/>
+      <c r="AC25" s="952" t="n"/>
+      <c r="AD25" s="952" t="n"/>
+      <c r="AE25" s="952" t="n"/>
+      <c r="AF25" s="951" t="n"/>
+      <c r="AG25" s="950" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="AH25" s="952" t="n"/>
+      <c r="AI25" s="951" t="n"/>
+      <c r="AJ25" s="950" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AK25" s="952" t="n"/>
+      <c r="AL25" s="952" t="n"/>
+      <c r="AM25" s="951" t="n"/>
+      <c r="AN25" s="950" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="AO25" s="952" t="n"/>
+      <c r="AP25" s="952" t="n"/>
+      <c r="AQ25" s="952" t="n"/>
+      <c r="AR25" s="952" t="n"/>
+      <c r="AS25" s="952" t="n"/>
+      <c r="AT25" s="952" t="n"/>
+      <c r="AU25" s="952" t="n"/>
+      <c r="AV25" s="952" t="n"/>
+      <c r="AW25" s="952" t="n"/>
+      <c r="AX25" s="952" t="n"/>
+      <c r="AY25" s="952" t="n"/>
+      <c r="AZ25" s="952" t="n"/>
+      <c r="BA25" s="952" t="n"/>
+      <c r="BB25" s="952" t="n"/>
+      <c r="BC25" s="952" t="n"/>
+      <c r="BD25" s="952" t="n"/>
+      <c r="BE25" s="952" t="n"/>
+      <c r="BF25" s="952" t="n"/>
+      <c r="BG25" s="952" t="n"/>
+      <c r="BH25" s="952" t="n"/>
+      <c r="BI25" s="952" t="n"/>
+      <c r="BJ25" s="952" t="n"/>
+      <c r="BK25" s="952" t="n"/>
+      <c r="BL25" s="952" t="n"/>
+      <c r="BM25" s="952" t="n"/>
+      <c r="BN25" s="952" t="n"/>
+      <c r="BO25" s="952" t="n"/>
+      <c r="BP25" s="952" t="n"/>
+      <c r="BQ25" s="952" t="n"/>
+      <c r="BR25" s="952" t="n"/>
+      <c r="BS25" s="952" t="n"/>
+      <c r="BT25" s="952" t="n"/>
+      <c r="BU25" s="952" t="n"/>
+      <c r="BV25" s="952" t="n"/>
+      <c r="BW25" s="952" t="n"/>
+      <c r="BX25" s="952" t="n"/>
+      <c r="BY25" s="952" t="n"/>
+      <c r="BZ25" s="952" t="n"/>
+      <c r="CA25" s="952" t="n"/>
+      <c r="CB25" s="952" t="n"/>
+      <c r="CC25" s="952" t="n"/>
+      <c r="CD25" s="952" t="n"/>
+      <c r="CE25" s="952" t="n"/>
+      <c r="CF25" s="952" t="n"/>
+      <c r="CG25" s="952" t="n"/>
+      <c r="CH25" s="952" t="n"/>
+      <c r="CI25" s="952" t="n"/>
+      <c r="CJ25" s="952" t="n"/>
+      <c r="CK25" s="952" t="n"/>
+      <c r="CL25" s="952" t="n"/>
+      <c r="CM25" s="952" t="n"/>
+      <c r="CN25" s="952" t="n"/>
+      <c r="CO25" s="952" t="n"/>
+      <c r="CP25" s="952" t="n"/>
+      <c r="CQ25" s="952" t="n"/>
+      <c r="CR25" s="952" t="n"/>
+      <c r="CS25" s="951" t="n"/>
       <c r="CT25" s="941" t="n"/>
       <c r="CU25" s="941" t="n"/>
       <c r="CV25" s="941" t="n"/>
@@ -50775,7 +50883,7 @@
       <c r="D26" s="941" t="n"/>
       <c r="E26" s="966" t="inlineStr">
         <is>
-          <t>PART_NAME</t>
+          <t>PART_NO</t>
         </is>
       </c>
       <c r="F26" s="957" t="n"/>
@@ -50809,7 +50917,11 @@
       <c r="AD26" s="957" t="n"/>
       <c r="AE26" s="957" t="n"/>
       <c r="AF26" s="955" t="n"/>
-      <c r="AG26" s="965" t="n"/>
+      <c r="AG26" s="965" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AH26" s="957" t="n"/>
       <c r="AI26" s="955" t="n"/>
       <c r="AJ26" s="965" t="inlineStr">
@@ -50822,7 +50934,7 @@
       <c r="AM26" s="955" t="n"/>
       <c r="AN26" s="956" t="inlineStr">
         <is>
-          <t>Retrieved from TB_M_PART_MASTER by PART_NO</t>
+          <t>Part number; length follows TB_M_PART_MASTER</t>
         </is>
       </c>
       <c r="AO26" s="957" t="n"/>
@@ -50896,7 +51008,7 @@
       <c r="D27" s="941" t="n"/>
       <c r="E27" s="966" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>PART_NAME</t>
         </is>
       </c>
       <c r="F27" s="957" t="n"/>
@@ -50916,7 +51028,7 @@
       <c r="T27" s="955" t="n"/>
       <c r="U27" s="966" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(TBD)</t>
         </is>
       </c>
       <c r="V27" s="957" t="n"/>
@@ -50935,7 +51047,7 @@
       <c r="AI27" s="955" t="n"/>
       <c r="AJ27" s="965" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK27" s="957" t="n"/>
@@ -50943,7 +51055,7 @@
       <c r="AM27" s="955" t="n"/>
       <c r="AN27" s="956" t="inlineStr">
         <is>
-          <t>MAD; result of the MAD calculation function, optional on Add / Upload</t>
+          <t>Retrieved from TB_M_PART_MASTER by PART_NO</t>
         </is>
       </c>
       <c r="AO27" s="957" t="n"/>
@@ -51017,7 +51129,7 @@
       <c r="D28" s="941" t="n"/>
       <c r="E28" s="966" t="inlineStr">
         <is>
-          <t>PCS_CASE</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="F28" s="957" t="n"/>
@@ -51056,7 +51168,7 @@
       <c r="AI28" s="955" t="n"/>
       <c r="AJ28" s="965" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AK28" s="957" t="n"/>
@@ -51064,7 +51176,7 @@
       <c r="AM28" s="955" t="n"/>
       <c r="AN28" s="956" t="inlineStr">
         <is>
-          <t>Pieces per case (&gt; 0)</t>
+          <t>MAD; result of the MAD calculation function, optional on Add / Upload</t>
         </is>
       </c>
       <c r="AO28" s="957" t="n"/>
@@ -51138,7 +51250,7 @@
       <c r="D29" s="941" t="n"/>
       <c r="E29" s="966" t="inlineStr">
         <is>
-          <t>MAX_CASE_DAY</t>
+          <t>PCS_CASE</t>
         </is>
       </c>
       <c r="F29" s="957" t="n"/>
@@ -51185,7 +51297,7 @@
       <c r="AM29" s="955" t="n"/>
       <c r="AN29" s="956" t="inlineStr">
         <is>
-          <t>Total Case/Day of the part (&gt; 0)</t>
+          <t>Pieces per case (&gt; 0)</t>
         </is>
       </c>
       <c r="AO29" s="957" t="n"/>
@@ -51259,7 +51371,7 @@
       <c r="D30" s="941" t="n"/>
       <c r="E30" s="966" t="inlineStr">
         <is>
-          <t>TOTAL_PCS_DAY</t>
+          <t>MAX_CASE_DAY</t>
         </is>
       </c>
       <c r="F30" s="957" t="n"/>
@@ -51306,7 +51418,7 @@
       <c r="AM30" s="955" t="n"/>
       <c r="AN30" s="956" t="inlineStr">
         <is>
-          <t>PCS_CASE x MAX_CASE_DAY</t>
+          <t>Total Case/Day of the part (&gt; 0)</t>
         </is>
       </c>
       <c r="AO30" s="957" t="n"/>
@@ -51380,7 +51492,7 @@
       <c r="D31" s="941" t="n"/>
       <c r="E31" s="966" t="inlineStr">
         <is>
-          <t>EFFECTIVE_START_DATE</t>
+          <t>TOTAL_PCS_DAY</t>
         </is>
       </c>
       <c r="F31" s="957" t="n"/>
@@ -51400,7 +51512,7 @@
       <c r="T31" s="955" t="n"/>
       <c r="U31" s="966" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="V31" s="957" t="n"/>
@@ -51419,7 +51531,7 @@
       <c r="AI31" s="955" t="n"/>
       <c r="AJ31" s="965" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK31" s="957" t="n"/>
@@ -51427,7 +51539,7 @@
       <c r="AM31" s="955" t="n"/>
       <c r="AN31" s="956" t="inlineStr">
         <is>
-          <t>Effective start date; required while the part is Candidate</t>
+          <t>PCS_CASE x MAX_CASE_DAY</t>
         </is>
       </c>
       <c r="AO31" s="957" t="n"/>
@@ -51501,7 +51613,7 @@
       <c r="D32" s="941" t="n"/>
       <c r="E32" s="966" t="inlineStr">
         <is>
-          <t>PART_STATUS</t>
+          <t>EFFECTIVE_START_DATE</t>
         </is>
       </c>
       <c r="F32" s="957" t="n"/>
@@ -51521,7 +51633,7 @@
       <c r="T32" s="955" t="n"/>
       <c r="U32" s="966" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="V32" s="957" t="n"/>
@@ -51540,7 +51652,7 @@
       <c r="AI32" s="955" t="n"/>
       <c r="AJ32" s="965" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AK32" s="957" t="n"/>
@@ -51548,7 +51660,7 @@
       <c r="AM32" s="955" t="n"/>
       <c r="AN32" s="956" t="inlineStr">
         <is>
-          <t>Candidate / Active / Inactive</t>
+          <t>Effective start date; required while the part is Candidate</t>
         </is>
       </c>
       <c r="AO32" s="957" t="n"/>
@@ -51622,7 +51734,7 @@
       <c r="D33" s="941" t="n"/>
       <c r="E33" s="966" t="inlineStr">
         <is>
-          <t>SYNC_STATUS</t>
+          <t>PART_STATUS</t>
         </is>
       </c>
       <c r="F33" s="957" t="n"/>
@@ -51642,7 +51754,7 @@
       <c r="T33" s="955" t="n"/>
       <c r="U33" s="966" t="inlineStr">
         <is>
-          <t>CHAR(1)</t>
+          <t>VARCHAR(TBD)</t>
         </is>
       </c>
       <c r="V33" s="957" t="n"/>
@@ -51669,7 +51781,7 @@
       <c r="AM33" s="955" t="n"/>
       <c r="AN33" s="956" t="inlineStr">
         <is>
-          <t>0 = No Sync, 3 = Waiting, 1 = Success, 2 = Failed</t>
+          <t>Candidate / Active / Inactive</t>
         </is>
       </c>
       <c r="AO33" s="957" t="n"/>
@@ -51743,7 +51855,7 @@
       <c r="D34" s="941" t="n"/>
       <c r="E34" s="966" t="inlineStr">
         <is>
-          <t>SYNC_DT</t>
+          <t>SYNC_STATUS</t>
         </is>
       </c>
       <c r="F34" s="957" t="n"/>
@@ -51763,7 +51875,7 @@
       <c r="T34" s="955" t="n"/>
       <c r="U34" s="966" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>CHAR(1)</t>
         </is>
       </c>
       <c r="V34" s="957" t="n"/>
@@ -51782,7 +51894,7 @@
       <c r="AI34" s="955" t="n"/>
       <c r="AJ34" s="965" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK34" s="957" t="n"/>
@@ -51790,7 +51902,7 @@
       <c r="AM34" s="955" t="n"/>
       <c r="AN34" s="956" t="inlineStr">
         <is>
-          <t>Date-time of the last RPA result</t>
+          <t>0 = No Sync, 3 = Waiting, 1 = Success, 2 = Failed</t>
         </is>
       </c>
       <c r="AO34" s="957" t="n"/>
@@ -51864,7 +51976,7 @@
       <c r="D35" s="941" t="n"/>
       <c r="E35" s="966" t="inlineStr">
         <is>
-          <t>SYNC_MESSAGE</t>
+          <t>SYNC_DT</t>
         </is>
       </c>
       <c r="F35" s="957" t="n"/>
@@ -51884,7 +51996,7 @@
       <c r="T35" s="955" t="n"/>
       <c r="U35" s="966" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="V35" s="957" t="n"/>
@@ -51911,7 +52023,7 @@
       <c r="AM35" s="955" t="n"/>
       <c r="AN35" s="966" t="inlineStr">
         <is>
-          <t>Reason of the last Failed sync</t>
+          <t>Date-time of the last RPA result</t>
         </is>
       </c>
       <c r="AO35" s="957" t="n"/>
@@ -51985,7 +52097,7 @@
       <c r="D36" s="941" t="n"/>
       <c r="E36" s="966" t="inlineStr">
         <is>
-          <t>LAST_SOURCE</t>
+          <t>SYNC_MESSAGE</t>
         </is>
       </c>
       <c r="F36" s="957" t="n"/>
@@ -52024,7 +52136,7 @@
       <c r="AI36" s="955" t="n"/>
       <c r="AJ36" s="965" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AK36" s="957" t="n"/>
@@ -52032,7 +52144,7 @@
       <c r="AM36" s="955" t="n"/>
       <c r="AN36" s="966" t="inlineStr">
         <is>
-          <t>CALC / SCREEN / UPLOAD</t>
+          <t>Reason of the last Failed sync</t>
         </is>
       </c>
       <c r="AO36" s="957" t="n"/>
@@ -52106,7 +52218,7 @@
       <c r="D37" s="941" t="n"/>
       <c r="E37" s="966" t="inlineStr">
         <is>
-          <t>LAST_UPLOAD_ID</t>
+          <t>LAST_SOURCE</t>
         </is>
       </c>
       <c r="F37" s="957" t="n"/>
@@ -52145,7 +52257,7 @@
       <c r="AI37" s="955" t="n"/>
       <c r="AJ37" s="965" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK37" s="957" t="n"/>
@@ -52153,7 +52265,7 @@
       <c r="AM37" s="955" t="n"/>
       <c r="AN37" s="956" t="inlineStr">
         <is>
-          <t>Upload that last changed the record</t>
+          <t>CALC / SCREEN / UPLOAD</t>
         </is>
       </c>
       <c r="AO37" s="957" t="n"/>
@@ -52227,7 +52339,7 @@
       <c r="D38" s="941" t="n"/>
       <c r="E38" s="966" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>LAST_UPLOAD_ID</t>
         </is>
       </c>
       <c r="F38" s="957" t="n"/>
@@ -52266,7 +52378,7 @@
       <c r="AI38" s="955" t="n"/>
       <c r="AJ38" s="965" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AK38" s="957" t="n"/>
@@ -52274,7 +52386,7 @@
       <c r="AM38" s="955" t="n"/>
       <c r="AN38" s="956" t="inlineStr">
         <is>
-          <t>User who created the record</t>
+          <t>Upload that last changed the record</t>
         </is>
       </c>
       <c r="AO38" s="957" t="n"/>
@@ -52348,7 +52460,7 @@
       <c r="D39" s="941" t="n"/>
       <c r="E39" s="966" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>CREATED_BY</t>
         </is>
       </c>
       <c r="F39" s="957" t="n"/>
@@ -52368,7 +52480,7 @@
       <c r="T39" s="955" t="n"/>
       <c r="U39" s="966" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(TBD)</t>
         </is>
       </c>
       <c r="V39" s="957" t="n"/>
@@ -52395,7 +52507,7 @@
       <c r="AM39" s="955" t="n"/>
       <c r="AN39" s="956" t="inlineStr">
         <is>
-          <t>Created date and time</t>
+          <t>User who created the record</t>
         </is>
       </c>
       <c r="AO39" s="957" t="n"/>
@@ -52469,7 +52581,7 @@
       <c r="D40" s="941" t="n"/>
       <c r="E40" s="956" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>CREATED_DT</t>
         </is>
       </c>
       <c r="F40" s="957" t="n"/>
@@ -52489,7 +52601,7 @@
       <c r="T40" s="955" t="n"/>
       <c r="U40" s="956" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="V40" s="957" t="n"/>
@@ -52516,7 +52628,7 @@
       <c r="AM40" s="955" t="n"/>
       <c r="AN40" s="956" t="inlineStr">
         <is>
-          <t>User who last changed the record</t>
+          <t>Created date and time</t>
         </is>
       </c>
       <c r="AO40" s="957" t="n"/>
@@ -52588,115 +52700,115 @@
       <c r="B41" s="942" t="n"/>
       <c r="C41" s="941" t="n"/>
       <c r="D41" s="941" t="n"/>
-      <c r="E41" s="985" t="inlineStr">
-        <is>
-          <t>CHANGED_DT</t>
-        </is>
-      </c>
-      <c r="F41" s="986" t="n"/>
-      <c r="G41" s="986" t="n"/>
-      <c r="H41" s="986" t="n"/>
-      <c r="I41" s="986" t="n"/>
-      <c r="J41" s="986" t="n"/>
-      <c r="K41" s="986" t="n"/>
-      <c r="L41" s="986" t="n"/>
-      <c r="M41" s="986" t="n"/>
-      <c r="N41" s="986" t="n"/>
-      <c r="O41" s="986" t="n"/>
-      <c r="P41" s="986" t="n"/>
-      <c r="Q41" s="986" t="n"/>
-      <c r="R41" s="986" t="n"/>
-      <c r="S41" s="986" t="n"/>
-      <c r="T41" s="987" t="n"/>
-      <c r="U41" s="985" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="V41" s="986" t="n"/>
-      <c r="W41" s="986" t="n"/>
-      <c r="X41" s="986" t="n"/>
-      <c r="Y41" s="986" t="n"/>
-      <c r="Z41" s="986" t="n"/>
-      <c r="AA41" s="986" t="n"/>
-      <c r="AB41" s="986" t="n"/>
-      <c r="AC41" s="986" t="n"/>
-      <c r="AD41" s="986" t="n"/>
-      <c r="AE41" s="986" t="n"/>
-      <c r="AF41" s="987" t="n"/>
-      <c r="AG41" s="1049" t="n"/>
-      <c r="AH41" s="986" t="n"/>
-      <c r="AI41" s="987" t="n"/>
-      <c r="AJ41" s="1049" t="inlineStr">
+      <c r="E41" s="956" t="inlineStr">
+        <is>
+          <t>CHANGED_BY</t>
+        </is>
+      </c>
+      <c r="F41" s="957" t="n"/>
+      <c r="G41" s="957" t="n"/>
+      <c r="H41" s="957" t="n"/>
+      <c r="I41" s="957" t="n"/>
+      <c r="J41" s="957" t="n"/>
+      <c r="K41" s="957" t="n"/>
+      <c r="L41" s="957" t="n"/>
+      <c r="M41" s="957" t="n"/>
+      <c r="N41" s="957" t="n"/>
+      <c r="O41" s="957" t="n"/>
+      <c r="P41" s="957" t="n"/>
+      <c r="Q41" s="957" t="n"/>
+      <c r="R41" s="957" t="n"/>
+      <c r="S41" s="957" t="n"/>
+      <c r="T41" s="955" t="n"/>
+      <c r="U41" s="956" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="V41" s="957" t="n"/>
+      <c r="W41" s="957" t="n"/>
+      <c r="X41" s="957" t="n"/>
+      <c r="Y41" s="957" t="n"/>
+      <c r="Z41" s="957" t="n"/>
+      <c r="AA41" s="957" t="n"/>
+      <c r="AB41" s="957" t="n"/>
+      <c r="AC41" s="957" t="n"/>
+      <c r="AD41" s="957" t="n"/>
+      <c r="AE41" s="957" t="n"/>
+      <c r="AF41" s="955" t="n"/>
+      <c r="AG41" s="954" t="n"/>
+      <c r="AH41" s="957" t="n"/>
+      <c r="AI41" s="955" t="n"/>
+      <c r="AJ41" s="954" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AK41" s="986" t="n"/>
-      <c r="AL41" s="986" t="n"/>
-      <c r="AM41" s="987" t="n"/>
-      <c r="AN41" s="985" t="inlineStr">
-        <is>
-          <t>Last changed date and time</t>
-        </is>
-      </c>
-      <c r="AO41" s="986" t="n"/>
-      <c r="AP41" s="986" t="n"/>
-      <c r="AQ41" s="986" t="n"/>
-      <c r="AR41" s="986" t="n"/>
-      <c r="AS41" s="986" t="n"/>
-      <c r="AT41" s="986" t="n"/>
-      <c r="AU41" s="986" t="n"/>
-      <c r="AV41" s="986" t="n"/>
-      <c r="AW41" s="986" t="n"/>
-      <c r="AX41" s="986" t="n"/>
-      <c r="AY41" s="986" t="n"/>
-      <c r="AZ41" s="986" t="n"/>
-      <c r="BA41" s="986" t="n"/>
-      <c r="BB41" s="986" t="n"/>
-      <c r="BC41" s="986" t="n"/>
-      <c r="BD41" s="986" t="n"/>
-      <c r="BE41" s="986" t="n"/>
-      <c r="BF41" s="986" t="n"/>
-      <c r="BG41" s="986" t="n"/>
-      <c r="BH41" s="986" t="n"/>
-      <c r="BI41" s="986" t="n"/>
-      <c r="BJ41" s="986" t="n"/>
-      <c r="BK41" s="986" t="n"/>
-      <c r="BL41" s="986" t="n"/>
-      <c r="BM41" s="986" t="n"/>
-      <c r="BN41" s="986" t="n"/>
-      <c r="BO41" s="986" t="n"/>
-      <c r="BP41" s="986" t="n"/>
-      <c r="BQ41" s="986" t="n"/>
-      <c r="BR41" s="986" t="n"/>
-      <c r="BS41" s="986" t="n"/>
-      <c r="BT41" s="986" t="n"/>
-      <c r="BU41" s="986" t="n"/>
-      <c r="BV41" s="986" t="n"/>
-      <c r="BW41" s="986" t="n"/>
-      <c r="BX41" s="986" t="n"/>
-      <c r="BY41" s="986" t="n"/>
-      <c r="BZ41" s="986" t="n"/>
-      <c r="CA41" s="986" t="n"/>
-      <c r="CB41" s="986" t="n"/>
-      <c r="CC41" s="986" t="n"/>
-      <c r="CD41" s="986" t="n"/>
-      <c r="CE41" s="986" t="n"/>
-      <c r="CF41" s="986" t="n"/>
-      <c r="CG41" s="986" t="n"/>
-      <c r="CH41" s="986" t="n"/>
-      <c r="CI41" s="986" t="n"/>
-      <c r="CJ41" s="986" t="n"/>
-      <c r="CK41" s="986" t="n"/>
-      <c r="CL41" s="986" t="n"/>
-      <c r="CM41" s="986" t="n"/>
-      <c r="CN41" s="986" t="n"/>
-      <c r="CO41" s="986" t="n"/>
-      <c r="CP41" s="986" t="n"/>
-      <c r="CQ41" s="986" t="n"/>
-      <c r="CR41" s="986" t="n"/>
-      <c r="CS41" s="987" t="n"/>
+      <c r="AK41" s="957" t="n"/>
+      <c r="AL41" s="957" t="n"/>
+      <c r="AM41" s="955" t="n"/>
+      <c r="AN41" s="956" t="inlineStr">
+        <is>
+          <t>User who last changed the record</t>
+        </is>
+      </c>
+      <c r="AO41" s="957" t="n"/>
+      <c r="AP41" s="957" t="n"/>
+      <c r="AQ41" s="957" t="n"/>
+      <c r="AR41" s="957" t="n"/>
+      <c r="AS41" s="957" t="n"/>
+      <c r="AT41" s="957" t="n"/>
+      <c r="AU41" s="957" t="n"/>
+      <c r="AV41" s="957" t="n"/>
+      <c r="AW41" s="957" t="n"/>
+      <c r="AX41" s="957" t="n"/>
+      <c r="AY41" s="957" t="n"/>
+      <c r="AZ41" s="957" t="n"/>
+      <c r="BA41" s="957" t="n"/>
+      <c r="BB41" s="957" t="n"/>
+      <c r="BC41" s="957" t="n"/>
+      <c r="BD41" s="957" t="n"/>
+      <c r="BE41" s="957" t="n"/>
+      <c r="BF41" s="957" t="n"/>
+      <c r="BG41" s="957" t="n"/>
+      <c r="BH41" s="957" t="n"/>
+      <c r="BI41" s="957" t="n"/>
+      <c r="BJ41" s="957" t="n"/>
+      <c r="BK41" s="957" t="n"/>
+      <c r="BL41" s="957" t="n"/>
+      <c r="BM41" s="957" t="n"/>
+      <c r="BN41" s="957" t="n"/>
+      <c r="BO41" s="957" t="n"/>
+      <c r="BP41" s="957" t="n"/>
+      <c r="BQ41" s="957" t="n"/>
+      <c r="BR41" s="957" t="n"/>
+      <c r="BS41" s="957" t="n"/>
+      <c r="BT41" s="957" t="n"/>
+      <c r="BU41" s="957" t="n"/>
+      <c r="BV41" s="957" t="n"/>
+      <c r="BW41" s="957" t="n"/>
+      <c r="BX41" s="957" t="n"/>
+      <c r="BY41" s="957" t="n"/>
+      <c r="BZ41" s="957" t="n"/>
+      <c r="CA41" s="957" t="n"/>
+      <c r="CB41" s="957" t="n"/>
+      <c r="CC41" s="957" t="n"/>
+      <c r="CD41" s="957" t="n"/>
+      <c r="CE41" s="957" t="n"/>
+      <c r="CF41" s="957" t="n"/>
+      <c r="CG41" s="957" t="n"/>
+      <c r="CH41" s="957" t="n"/>
+      <c r="CI41" s="957" t="n"/>
+      <c r="CJ41" s="957" t="n"/>
+      <c r="CK41" s="957" t="n"/>
+      <c r="CL41" s="957" t="n"/>
+      <c r="CM41" s="957" t="n"/>
+      <c r="CN41" s="957" t="n"/>
+      <c r="CO41" s="957" t="n"/>
+      <c r="CP41" s="957" t="n"/>
+      <c r="CQ41" s="957" t="n"/>
+      <c r="CR41" s="957" t="n"/>
+      <c r="CS41" s="955" t="n"/>
       <c r="CT41" s="941" t="n"/>
       <c r="CU41" s="941" t="n"/>
       <c r="CV41" s="941" t="n"/>
@@ -52709,99 +52821,115 @@
       <c r="B42" s="942" t="n"/>
       <c r="C42" s="941" t="n"/>
       <c r="D42" s="941" t="n"/>
-      <c r="E42" s="941" t="n"/>
-      <c r="F42" s="941" t="n"/>
-      <c r="G42" s="941" t="n"/>
-      <c r="H42" s="941" t="n"/>
-      <c r="I42" s="941" t="n"/>
-      <c r="J42" s="941" t="n"/>
-      <c r="K42" s="941" t="n"/>
-      <c r="L42" s="941" t="n"/>
-      <c r="M42" s="941" t="n"/>
-      <c r="N42" s="941" t="n"/>
-      <c r="O42" s="941" t="n"/>
-      <c r="P42" s="941" t="n"/>
-      <c r="Q42" s="941" t="n"/>
-      <c r="R42" s="941" t="n"/>
-      <c r="S42" s="941" t="n"/>
-      <c r="T42" s="941" t="n"/>
-      <c r="U42" s="941" t="n"/>
-      <c r="V42" s="941" t="n"/>
-      <c r="W42" s="941" t="n"/>
-      <c r="X42" s="941" t="n"/>
-      <c r="Y42" s="941" t="n"/>
-      <c r="Z42" s="941" t="n"/>
-      <c r="AA42" s="941" t="n"/>
-      <c r="AB42" s="941" t="n"/>
-      <c r="AC42" s="941" t="n"/>
-      <c r="AD42" s="941" t="n"/>
-      <c r="AE42" s="941" t="n"/>
-      <c r="AF42" s="941" t="n"/>
-      <c r="AG42" s="941" t="n"/>
-      <c r="AH42" s="941" t="n"/>
-      <c r="AI42" s="941" t="n"/>
-      <c r="AJ42" s="941" t="n"/>
-      <c r="AK42" s="941" t="n"/>
-      <c r="AL42" s="941" t="n"/>
-      <c r="AM42" s="941" t="n"/>
-      <c r="AN42" s="941" t="n"/>
-      <c r="AO42" s="941" t="n"/>
-      <c r="AP42" s="941" t="n"/>
-      <c r="AQ42" s="941" t="n"/>
-      <c r="AR42" s="941" t="n"/>
-      <c r="AS42" s="941" t="n"/>
-      <c r="AT42" s="941" t="n"/>
-      <c r="AU42" s="949" t="n"/>
-      <c r="AV42" s="949" t="n"/>
-      <c r="AW42" s="949" t="n"/>
-      <c r="AX42" s="949" t="n"/>
-      <c r="AY42" s="941" t="n"/>
-      <c r="AZ42" s="943" t="n"/>
-      <c r="BA42" s="941" t="n"/>
-      <c r="BB42" s="941" t="n"/>
-      <c r="BC42" s="941" t="n"/>
-      <c r="BD42" s="941" t="n"/>
-      <c r="BE42" s="941" t="n"/>
-      <c r="BF42" s="941" t="n"/>
-      <c r="BG42" s="941" t="n"/>
-      <c r="BH42" s="941" t="n"/>
-      <c r="BI42" s="941" t="n"/>
-      <c r="BJ42" s="941" t="n"/>
-      <c r="BK42" s="941" t="n"/>
-      <c r="BL42" s="941" t="n"/>
-      <c r="BM42" s="941" t="n"/>
-      <c r="BN42" s="941" t="n"/>
-      <c r="BO42" s="941" t="n"/>
-      <c r="BP42" s="941" t="n"/>
-      <c r="BQ42" s="941" t="n"/>
-      <c r="BR42" s="941" t="n"/>
-      <c r="BS42" s="941" t="n"/>
-      <c r="BT42" s="941" t="n"/>
-      <c r="BU42" s="941" t="n"/>
-      <c r="BV42" s="941" t="n"/>
-      <c r="BW42" s="941" t="n"/>
-      <c r="BX42" s="941" t="n"/>
-      <c r="BY42" s="941" t="n"/>
-      <c r="BZ42" s="941" t="n"/>
-      <c r="CA42" s="941" t="n"/>
-      <c r="CB42" s="941" t="n"/>
-      <c r="CC42" s="941" t="n"/>
-      <c r="CD42" s="941" t="n"/>
-      <c r="CE42" s="941" t="n"/>
-      <c r="CF42" s="941" t="n"/>
-      <c r="CG42" s="941" t="n"/>
-      <c r="CH42" s="941" t="n"/>
-      <c r="CI42" s="941" t="n"/>
-      <c r="CJ42" s="941" t="n"/>
-      <c r="CK42" s="941" t="n"/>
-      <c r="CL42" s="941" t="n"/>
-      <c r="CM42" s="941" t="n"/>
-      <c r="CN42" s="941" t="n"/>
-      <c r="CO42" s="941" t="n"/>
-      <c r="CP42" s="941" t="n"/>
-      <c r="CQ42" s="941" t="n"/>
-      <c r="CR42" s="941" t="n"/>
-      <c r="CS42" s="941" t="n"/>
+      <c r="E42" s="985" t="inlineStr">
+        <is>
+          <t>CHANGED_DT</t>
+        </is>
+      </c>
+      <c r="F42" s="986" t="n"/>
+      <c r="G42" s="986" t="n"/>
+      <c r="H42" s="986" t="n"/>
+      <c r="I42" s="986" t="n"/>
+      <c r="J42" s="986" t="n"/>
+      <c r="K42" s="986" t="n"/>
+      <c r="L42" s="986" t="n"/>
+      <c r="M42" s="986" t="n"/>
+      <c r="N42" s="986" t="n"/>
+      <c r="O42" s="986" t="n"/>
+      <c r="P42" s="986" t="n"/>
+      <c r="Q42" s="986" t="n"/>
+      <c r="R42" s="986" t="n"/>
+      <c r="S42" s="986" t="n"/>
+      <c r="T42" s="987" t="n"/>
+      <c r="U42" s="985" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="V42" s="986" t="n"/>
+      <c r="W42" s="986" t="n"/>
+      <c r="X42" s="986" t="n"/>
+      <c r="Y42" s="986" t="n"/>
+      <c r="Z42" s="986" t="n"/>
+      <c r="AA42" s="986" t="n"/>
+      <c r="AB42" s="986" t="n"/>
+      <c r="AC42" s="986" t="n"/>
+      <c r="AD42" s="986" t="n"/>
+      <c r="AE42" s="986" t="n"/>
+      <c r="AF42" s="987" t="n"/>
+      <c r="AG42" s="1050" t="n"/>
+      <c r="AH42" s="986" t="n"/>
+      <c r="AI42" s="987" t="n"/>
+      <c r="AJ42" s="1050" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK42" s="986" t="n"/>
+      <c r="AL42" s="986" t="n"/>
+      <c r="AM42" s="987" t="n"/>
+      <c r="AN42" s="985" t="inlineStr">
+        <is>
+          <t>Last changed date and time</t>
+        </is>
+      </c>
+      <c r="AO42" s="986" t="n"/>
+      <c r="AP42" s="986" t="n"/>
+      <c r="AQ42" s="986" t="n"/>
+      <c r="AR42" s="986" t="n"/>
+      <c r="AS42" s="986" t="n"/>
+      <c r="AT42" s="986" t="n"/>
+      <c r="AU42" s="986" t="n"/>
+      <c r="AV42" s="986" t="n"/>
+      <c r="AW42" s="986" t="n"/>
+      <c r="AX42" s="986" t="n"/>
+      <c r="AY42" s="986" t="n"/>
+      <c r="AZ42" s="986" t="n"/>
+      <c r="BA42" s="986" t="n"/>
+      <c r="BB42" s="986" t="n"/>
+      <c r="BC42" s="986" t="n"/>
+      <c r="BD42" s="986" t="n"/>
+      <c r="BE42" s="986" t="n"/>
+      <c r="BF42" s="986" t="n"/>
+      <c r="BG42" s="986" t="n"/>
+      <c r="BH42" s="986" t="n"/>
+      <c r="BI42" s="986" t="n"/>
+      <c r="BJ42" s="986" t="n"/>
+      <c r="BK42" s="986" t="n"/>
+      <c r="BL42" s="986" t="n"/>
+      <c r="BM42" s="986" t="n"/>
+      <c r="BN42" s="986" t="n"/>
+      <c r="BO42" s="986" t="n"/>
+      <c r="BP42" s="986" t="n"/>
+      <c r="BQ42" s="986" t="n"/>
+      <c r="BR42" s="986" t="n"/>
+      <c r="BS42" s="986" t="n"/>
+      <c r="BT42" s="986" t="n"/>
+      <c r="BU42" s="986" t="n"/>
+      <c r="BV42" s="986" t="n"/>
+      <c r="BW42" s="986" t="n"/>
+      <c r="BX42" s="986" t="n"/>
+      <c r="BY42" s="986" t="n"/>
+      <c r="BZ42" s="986" t="n"/>
+      <c r="CA42" s="986" t="n"/>
+      <c r="CB42" s="986" t="n"/>
+      <c r="CC42" s="986" t="n"/>
+      <c r="CD42" s="986" t="n"/>
+      <c r="CE42" s="986" t="n"/>
+      <c r="CF42" s="986" t="n"/>
+      <c r="CG42" s="986" t="n"/>
+      <c r="CH42" s="986" t="n"/>
+      <c r="CI42" s="986" t="n"/>
+      <c r="CJ42" s="986" t="n"/>
+      <c r="CK42" s="986" t="n"/>
+      <c r="CL42" s="986" t="n"/>
+      <c r="CM42" s="986" t="n"/>
+      <c r="CN42" s="986" t="n"/>
+      <c r="CO42" s="986" t="n"/>
+      <c r="CP42" s="986" t="n"/>
+      <c r="CQ42" s="986" t="n"/>
+      <c r="CR42" s="986" t="n"/>
+      <c r="CS42" s="987" t="n"/>
       <c r="CT42" s="941" t="n"/>
       <c r="CU42" s="941" t="n"/>
       <c r="CV42" s="941" t="n"/>
@@ -53336,137 +53464,4808 @@
     </row>
     <row r="48" ht="11.1" customFormat="1" customHeight="1" s="761">
       <c r="A48" s="941" t="n"/>
-      <c r="B48" s="990" t="n"/>
-      <c r="C48" s="991" t="n"/>
-      <c r="D48" s="991" t="n"/>
-      <c r="E48" s="991" t="n"/>
-      <c r="F48" s="991" t="n"/>
-      <c r="G48" s="991" t="n"/>
-      <c r="H48" s="991" t="n"/>
-      <c r="I48" s="991" t="n"/>
-      <c r="J48" s="991" t="n"/>
-      <c r="K48" s="991" t="n"/>
-      <c r="L48" s="991" t="n"/>
-      <c r="M48" s="991" t="n"/>
-      <c r="N48" s="991" t="n"/>
-      <c r="O48" s="991" t="n"/>
-      <c r="P48" s="991" t="n"/>
-      <c r="Q48" s="991" t="n"/>
-      <c r="R48" s="991" t="n"/>
-      <c r="S48" s="991" t="n"/>
-      <c r="T48" s="991" t="n"/>
-      <c r="U48" s="991" t="n"/>
-      <c r="V48" s="991" t="n"/>
-      <c r="W48" s="991" t="n"/>
-      <c r="X48" s="991" t="n"/>
-      <c r="Y48" s="991" t="n"/>
-      <c r="Z48" s="991" t="n"/>
-      <c r="AA48" s="991" t="n"/>
-      <c r="AB48" s="991" t="n"/>
-      <c r="AC48" s="991" t="n"/>
-      <c r="AD48" s="991" t="n"/>
-      <c r="AE48" s="991" t="n"/>
-      <c r="AF48" s="991" t="n"/>
-      <c r="AG48" s="991" t="n"/>
-      <c r="AH48" s="991" t="n"/>
-      <c r="AI48" s="991" t="n"/>
-      <c r="AJ48" s="991" t="n"/>
-      <c r="AK48" s="991" t="n"/>
-      <c r="AL48" s="991" t="n"/>
-      <c r="AM48" s="991" t="n"/>
-      <c r="AN48" s="991" t="n"/>
-      <c r="AO48" s="991" t="n"/>
-      <c r="AP48" s="991" t="n"/>
-      <c r="AQ48" s="991" t="n"/>
-      <c r="AR48" s="991" t="n"/>
-      <c r="AS48" s="991" t="n"/>
-      <c r="AT48" s="991" t="n"/>
-      <c r="AU48" s="991" t="n"/>
-      <c r="AV48" s="991" t="n"/>
-      <c r="AW48" s="991" t="n"/>
-      <c r="AX48" s="991" t="n"/>
-      <c r="AY48" s="991" t="n"/>
-      <c r="AZ48" s="991" t="n"/>
-      <c r="BA48" s="991" t="n"/>
-      <c r="BB48" s="991" t="n"/>
-      <c r="BC48" s="991" t="n"/>
-      <c r="BD48" s="991" t="n"/>
-      <c r="BE48" s="991" t="n"/>
-      <c r="BF48" s="991" t="n"/>
-      <c r="BG48" s="991" t="n"/>
-      <c r="BH48" s="991" t="n"/>
-      <c r="BI48" s="991" t="n"/>
-      <c r="BJ48" s="991" t="n"/>
-      <c r="BK48" s="991" t="n"/>
-      <c r="BL48" s="991" t="n"/>
-      <c r="BM48" s="991" t="n"/>
-      <c r="BN48" s="991" t="n"/>
-      <c r="BO48" s="991" t="n"/>
-      <c r="BP48" s="991" t="n"/>
-      <c r="BQ48" s="991" t="n"/>
-      <c r="BR48" s="991" t="n"/>
-      <c r="BS48" s="991" t="n"/>
-      <c r="BT48" s="991" t="n"/>
-      <c r="BU48" s="991" t="n"/>
-      <c r="BV48" s="991" t="n"/>
-      <c r="BW48" s="991" t="n"/>
-      <c r="BX48" s="991" t="n"/>
-      <c r="BY48" s="991" t="n"/>
-      <c r="BZ48" s="991" t="n"/>
-      <c r="CA48" s="991" t="n"/>
-      <c r="CB48" s="991" t="n"/>
-      <c r="CC48" s="991" t="n"/>
-      <c r="CD48" s="991" t="n"/>
-      <c r="CE48" s="991" t="n"/>
-      <c r="CF48" s="991" t="n"/>
-      <c r="CG48" s="991" t="n"/>
-      <c r="CH48" s="991" t="n"/>
-      <c r="CI48" s="991" t="n"/>
-      <c r="CJ48" s="991" t="n"/>
-      <c r="CK48" s="991" t="n"/>
-      <c r="CL48" s="991" t="n"/>
-      <c r="CM48" s="991" t="n"/>
-      <c r="CN48" s="991" t="n"/>
-      <c r="CO48" s="991" t="n"/>
-      <c r="CP48" s="991" t="n"/>
-      <c r="CQ48" s="991" t="n"/>
-      <c r="CR48" s="991" t="n"/>
-      <c r="CS48" s="991" t="n"/>
-      <c r="CT48" s="991" t="n"/>
-      <c r="CU48" s="991" t="n"/>
-      <c r="CV48" s="991" t="n"/>
-      <c r="CW48" s="991" t="n"/>
-      <c r="CX48" s="992" t="n"/>
+      <c r="B48" s="1051" t="n"/>
+      <c r="C48" s="1052" t="n"/>
+      <c r="D48" s="1052" t="n"/>
+      <c r="E48" s="1052" t="n"/>
+      <c r="F48" s="1052" t="n"/>
+      <c r="G48" s="1052" t="n"/>
+      <c r="H48" s="1052" t="n"/>
+      <c r="I48" s="1052" t="n"/>
+      <c r="J48" s="1052" t="n"/>
+      <c r="K48" s="1052" t="n"/>
+      <c r="L48" s="1052" t="n"/>
+      <c r="M48" s="1052" t="n"/>
+      <c r="N48" s="1052" t="n"/>
+      <c r="O48" s="1052" t="n"/>
+      <c r="P48" s="1052" t="n"/>
+      <c r="Q48" s="1052" t="n"/>
+      <c r="R48" s="1052" t="n"/>
+      <c r="S48" s="1052" t="n"/>
+      <c r="T48" s="1052" t="n"/>
+      <c r="U48" s="1052" t="n"/>
+      <c r="V48" s="1052" t="n"/>
+      <c r="W48" s="1052" t="n"/>
+      <c r="X48" s="1052" t="n"/>
+      <c r="Y48" s="1052" t="n"/>
+      <c r="Z48" s="1052" t="n"/>
+      <c r="AA48" s="1052" t="n"/>
+      <c r="AB48" s="1052" t="n"/>
+      <c r="AC48" s="1052" t="n"/>
+      <c r="AD48" s="1052" t="n"/>
+      <c r="AE48" s="1052" t="n"/>
+      <c r="AF48" s="1052" t="n"/>
+      <c r="AG48" s="1052" t="n"/>
+      <c r="AH48" s="1052" t="n"/>
+      <c r="AI48" s="1052" t="n"/>
+      <c r="AJ48" s="1052" t="n"/>
+      <c r="AK48" s="1052" t="n"/>
+      <c r="AL48" s="1052" t="n"/>
+      <c r="AM48" s="1052" t="n"/>
+      <c r="AN48" s="1052" t="n"/>
+      <c r="AO48" s="1052" t="n"/>
+      <c r="AP48" s="1052" t="n"/>
+      <c r="AQ48" s="1052" t="n"/>
+      <c r="AR48" s="1052" t="n"/>
+      <c r="AS48" s="1052" t="n"/>
+      <c r="AT48" s="1052" t="n"/>
+      <c r="AU48" s="1052" t="n"/>
+      <c r="AV48" s="1052" t="n"/>
+      <c r="AW48" s="1052" t="n"/>
+      <c r="AX48" s="1052" t="n"/>
+      <c r="AY48" s="1052" t="n"/>
+      <c r="AZ48" s="1052" t="n"/>
+      <c r="BA48" s="1052" t="n"/>
+      <c r="BB48" s="1052" t="n"/>
+      <c r="BC48" s="1052" t="n"/>
+      <c r="BD48" s="1052" t="n"/>
+      <c r="BE48" s="1052" t="n"/>
+      <c r="BF48" s="1052" t="n"/>
+      <c r="BG48" s="1052" t="n"/>
+      <c r="BH48" s="1052" t="n"/>
+      <c r="BI48" s="1052" t="n"/>
+      <c r="BJ48" s="1052" t="n"/>
+      <c r="BK48" s="1052" t="n"/>
+      <c r="BL48" s="1052" t="n"/>
+      <c r="BM48" s="1052" t="n"/>
+      <c r="BN48" s="1052" t="n"/>
+      <c r="BO48" s="1052" t="n"/>
+      <c r="BP48" s="1052" t="n"/>
+      <c r="BQ48" s="1052" t="n"/>
+      <c r="BR48" s="1052" t="n"/>
+      <c r="BS48" s="1052" t="n"/>
+      <c r="BT48" s="1052" t="n"/>
+      <c r="BU48" s="1052" t="n"/>
+      <c r="BV48" s="1052" t="n"/>
+      <c r="BW48" s="1052" t="n"/>
+      <c r="BX48" s="1052" t="n"/>
+      <c r="BY48" s="1052" t="n"/>
+      <c r="BZ48" s="1052" t="n"/>
+      <c r="CA48" s="1052" t="n"/>
+      <c r="CB48" s="1052" t="n"/>
+      <c r="CC48" s="1052" t="n"/>
+      <c r="CD48" s="1052" t="n"/>
+      <c r="CE48" s="1052" t="n"/>
+      <c r="CF48" s="1052" t="n"/>
+      <c r="CG48" s="1052" t="n"/>
+      <c r="CH48" s="1052" t="n"/>
+      <c r="CI48" s="1052" t="n"/>
+      <c r="CJ48" s="1052" t="n"/>
+      <c r="CK48" s="1052" t="n"/>
+      <c r="CL48" s="1052" t="n"/>
+      <c r="CM48" s="1052" t="n"/>
+      <c r="CN48" s="1052" t="n"/>
+      <c r="CO48" s="1052" t="n"/>
+      <c r="CP48" s="1052" t="n"/>
+      <c r="CQ48" s="1052" t="n"/>
+      <c r="CR48" s="1052" t="n"/>
+      <c r="CS48" s="1052" t="n"/>
+      <c r="CT48" s="1052" t="n"/>
+      <c r="CU48" s="1052" t="n"/>
+      <c r="CV48" s="1052" t="n"/>
+      <c r="CW48" s="1052" t="n"/>
+      <c r="CX48" s="1053" t="n"/>
       <c r="CY48" s="941" t="n"/>
     </row>
+    <row r="49" ht="11.1" customHeight="1" s="710">
+      <c r="A49" s="1022" t="n"/>
+      <c r="B49" s="1023" t="n"/>
+      <c r="C49" s="1022" t="n"/>
+      <c r="D49" s="1022" t="n"/>
+      <c r="E49" s="1022" t="n"/>
+      <c r="F49" s="1022" t="n"/>
+      <c r="G49" s="1022" t="n"/>
+      <c r="H49" s="1022" t="n"/>
+      <c r="I49" s="1022" t="n"/>
+      <c r="J49" s="1022" t="n"/>
+      <c r="K49" s="1022" t="n"/>
+      <c r="L49" s="1022" t="n"/>
+      <c r="M49" s="1022" t="n"/>
+      <c r="N49" s="1022" t="n"/>
+      <c r="O49" s="1022" t="n"/>
+      <c r="P49" s="1022" t="n"/>
+      <c r="Q49" s="1022" t="n"/>
+      <c r="R49" s="1022" t="n"/>
+      <c r="S49" s="1022" t="n"/>
+      <c r="T49" s="1022" t="n"/>
+      <c r="U49" s="1022" t="n"/>
+      <c r="V49" s="1022" t="n"/>
+      <c r="W49" s="1022" t="n"/>
+      <c r="X49" s="1022" t="n"/>
+      <c r="Y49" s="1022" t="n"/>
+      <c r="Z49" s="1022" t="n"/>
+      <c r="AA49" s="1022" t="n"/>
+      <c r="AB49" s="1022" t="n"/>
+      <c r="AC49" s="1022" t="n"/>
+      <c r="AD49" s="1022" t="n"/>
+      <c r="AE49" s="1022" t="n"/>
+      <c r="AF49" s="1022" t="n"/>
+      <c r="AG49" s="1022" t="n"/>
+      <c r="AH49" s="1022" t="n"/>
+      <c r="AI49" s="1022" t="n"/>
+      <c r="AJ49" s="1022" t="n"/>
+      <c r="AK49" s="1022" t="n"/>
+      <c r="AL49" s="1022" t="n"/>
+      <c r="AM49" s="1022" t="n"/>
+      <c r="AN49" s="1022" t="n"/>
+      <c r="AO49" s="1022" t="n"/>
+      <c r="AP49" s="1022" t="n"/>
+      <c r="AQ49" s="1022" t="n"/>
+      <c r="AR49" s="1022" t="n"/>
+      <c r="AS49" s="1022" t="n"/>
+      <c r="AT49" s="1022" t="n"/>
+      <c r="AU49" s="1022" t="n"/>
+      <c r="AV49" s="1022" t="n"/>
+      <c r="AW49" s="1022" t="n"/>
+      <c r="AX49" s="1022" t="n"/>
+      <c r="AY49" s="1022" t="n"/>
+      <c r="AZ49" s="1022" t="n"/>
+      <c r="BA49" s="1022" t="n"/>
+      <c r="BB49" s="1022" t="n"/>
+      <c r="BC49" s="1022" t="n"/>
+      <c r="BD49" s="1022" t="n"/>
+      <c r="BE49" s="1022" t="n"/>
+      <c r="BF49" s="1022" t="n"/>
+      <c r="BG49" s="1022" t="n"/>
+      <c r="BH49" s="1022" t="n"/>
+      <c r="BI49" s="1022" t="n"/>
+      <c r="BJ49" s="1022" t="n"/>
+      <c r="BK49" s="1022" t="n"/>
+      <c r="BL49" s="1022" t="n"/>
+      <c r="BM49" s="1022" t="n"/>
+      <c r="BN49" s="1022" t="n"/>
+      <c r="BO49" s="1022" t="n"/>
+      <c r="BP49" s="1022" t="n"/>
+      <c r="BQ49" s="1022" t="n"/>
+      <c r="BR49" s="1022" t="n"/>
+      <c r="BS49" s="1022" t="n"/>
+      <c r="BT49" s="1022" t="n"/>
+      <c r="BU49" s="1022" t="n"/>
+      <c r="BV49" s="1022" t="n"/>
+      <c r="BW49" s="1022" t="n"/>
+      <c r="BX49" s="1022" t="n"/>
+      <c r="BY49" s="1022" t="n"/>
+      <c r="BZ49" s="1022" t="n"/>
+      <c r="CA49" s="1022" t="n"/>
+      <c r="CB49" s="1022" t="n"/>
+      <c r="CC49" s="1022" t="n"/>
+      <c r="CD49" s="1022" t="n"/>
+      <c r="CE49" s="1022" t="n"/>
+      <c r="CF49" s="1022" t="n"/>
+      <c r="CG49" s="1022" t="n"/>
+      <c r="CH49" s="1022" t="n"/>
+      <c r="CI49" s="1022" t="n"/>
+      <c r="CJ49" s="1022" t="n"/>
+      <c r="CK49" s="1022" t="n"/>
+      <c r="CL49" s="1022" t="n"/>
+      <c r="CM49" s="1022" t="n"/>
+      <c r="CN49" s="1022" t="n"/>
+      <c r="CO49" s="1022" t="n"/>
+      <c r="CP49" s="1022" t="n"/>
+      <c r="CQ49" s="1022" t="n"/>
+      <c r="CR49" s="1022" t="n"/>
+      <c r="CS49" s="1022" t="n"/>
+      <c r="CT49" s="1022" t="n"/>
+      <c r="CU49" s="1022" t="n"/>
+      <c r="CV49" s="1022" t="n"/>
+      <c r="CW49" s="1022" t="n"/>
+      <c r="CX49" s="1024" t="n"/>
+      <c r="CY49" s="1022" t="n"/>
+    </row>
+    <row r="50" ht="11.1" customHeight="1" s="710">
+      <c r="A50" s="1022" t="n"/>
+      <c r="B50" s="1023" t="n"/>
+      <c r="C50" s="1022" t="n"/>
+      <c r="D50" s="1054" t="inlineStr">
+        <is>
+          <t>TB_H_PART_CANDIDATE (proposed)</t>
+        </is>
+      </c>
+      <c r="E50" s="1022" t="n"/>
+      <c r="F50" s="1022" t="n"/>
+      <c r="G50" s="1022" t="n"/>
+      <c r="H50" s="1022" t="n"/>
+      <c r="I50" s="1022" t="n"/>
+      <c r="J50" s="1022" t="n"/>
+      <c r="K50" s="1022" t="n"/>
+      <c r="L50" s="1022" t="n"/>
+      <c r="M50" s="1022" t="n"/>
+      <c r="N50" s="1022" t="n"/>
+      <c r="O50" s="1022" t="n"/>
+      <c r="P50" s="1022" t="n"/>
+      <c r="Q50" s="1022" t="n"/>
+      <c r="R50" s="1022" t="n"/>
+      <c r="S50" s="1022" t="n"/>
+      <c r="T50" s="1022" t="n"/>
+      <c r="U50" s="1022" t="n"/>
+      <c r="V50" s="1022" t="n"/>
+      <c r="W50" s="1022" t="n"/>
+      <c r="X50" s="1022" t="n"/>
+      <c r="Y50" s="1022" t="n"/>
+      <c r="Z50" s="1022" t="n"/>
+      <c r="AA50" s="1022" t="n"/>
+      <c r="AB50" s="1022" t="n"/>
+      <c r="AC50" s="1022" t="n"/>
+      <c r="AD50" s="1022" t="n"/>
+      <c r="AE50" s="1022" t="n"/>
+      <c r="AF50" s="1022" t="n"/>
+      <c r="AG50" s="1022" t="n"/>
+      <c r="AH50" s="1022" t="n"/>
+      <c r="AI50" s="1022" t="n"/>
+      <c r="AJ50" s="1022" t="n"/>
+      <c r="AK50" s="1022" t="n"/>
+      <c r="AL50" s="1022" t="n"/>
+      <c r="AM50" s="1022" t="n"/>
+      <c r="AN50" s="1022" t="n"/>
+      <c r="AO50" s="1022" t="n"/>
+      <c r="AP50" s="1022" t="n"/>
+      <c r="AQ50" s="1022" t="n"/>
+      <c r="AR50" s="1022" t="n"/>
+      <c r="AS50" s="1022" t="n"/>
+      <c r="AT50" s="1022" t="n"/>
+      <c r="AU50" s="1022" t="n"/>
+      <c r="AV50" s="1022" t="n"/>
+      <c r="AW50" s="1022" t="n"/>
+      <c r="AX50" s="1022" t="n"/>
+      <c r="AY50" s="1022" t="n"/>
+      <c r="AZ50" s="1022" t="n"/>
+      <c r="BA50" s="1022" t="n"/>
+      <c r="BB50" s="1022" t="n"/>
+      <c r="BC50" s="1022" t="n"/>
+      <c r="BD50" s="1022" t="n"/>
+      <c r="BE50" s="1022" t="n"/>
+      <c r="BF50" s="1022" t="n"/>
+      <c r="BG50" s="1022" t="n"/>
+      <c r="BH50" s="1022" t="n"/>
+      <c r="BI50" s="1022" t="n"/>
+      <c r="BJ50" s="1022" t="n"/>
+      <c r="BK50" s="1022" t="n"/>
+      <c r="BL50" s="1022" t="n"/>
+      <c r="BM50" s="1022" t="n"/>
+      <c r="BN50" s="1022" t="n"/>
+      <c r="BO50" s="1022" t="n"/>
+      <c r="BP50" s="1022" t="n"/>
+      <c r="BQ50" s="1022" t="n"/>
+      <c r="BR50" s="1022" t="n"/>
+      <c r="BS50" s="1022" t="n"/>
+      <c r="BT50" s="1022" t="n"/>
+      <c r="BU50" s="1022" t="n"/>
+      <c r="BV50" s="1022" t="n"/>
+      <c r="BW50" s="1022" t="n"/>
+      <c r="BX50" s="1022" t="n"/>
+      <c r="BY50" s="1022" t="n"/>
+      <c r="BZ50" s="1022" t="n"/>
+      <c r="CA50" s="1022" t="n"/>
+      <c r="CB50" s="1022" t="n"/>
+      <c r="CC50" s="1022" t="n"/>
+      <c r="CD50" s="1022" t="n"/>
+      <c r="CE50" s="1022" t="n"/>
+      <c r="CF50" s="1022" t="n"/>
+      <c r="CG50" s="1022" t="n"/>
+      <c r="CH50" s="1022" t="n"/>
+      <c r="CI50" s="1022" t="n"/>
+      <c r="CJ50" s="1022" t="n"/>
+      <c r="CK50" s="1022" t="n"/>
+      <c r="CL50" s="1022" t="n"/>
+      <c r="CM50" s="1022" t="n"/>
+      <c r="CN50" s="1022" t="n"/>
+      <c r="CO50" s="1022" t="n"/>
+      <c r="CP50" s="1022" t="n"/>
+      <c r="CQ50" s="1022" t="n"/>
+      <c r="CR50" s="1022" t="n"/>
+      <c r="CS50" s="1022" t="n"/>
+      <c r="CT50" s="1022" t="n"/>
+      <c r="CU50" s="1022" t="n"/>
+      <c r="CV50" s="1022" t="n"/>
+      <c r="CW50" s="1022" t="n"/>
+      <c r="CX50" s="1024" t="n"/>
+      <c r="CY50" s="1022" t="n"/>
+    </row>
+    <row r="51" ht="11.1" customHeight="1" s="710">
+      <c r="A51" s="1022" t="n"/>
+      <c r="B51" s="1023" t="n"/>
+      <c r="C51" s="1022" t="n"/>
+      <c r="D51" s="1022" t="n"/>
+      <c r="E51" s="1055" t="inlineStr">
+        <is>
+          <t>History table - History of every change of a crossdock part (Add / Edit by screen or upload, mapping changes, Sync results). Read by the History setting modal of Part List (index PART_NO,</t>
+        </is>
+      </c>
+      <c r="F51" s="1022" t="n"/>
+      <c r="G51" s="1022" t="n"/>
+      <c r="H51" s="1022" t="n"/>
+      <c r="I51" s="1022" t="n"/>
+      <c r="J51" s="1022" t="n"/>
+      <c r="K51" s="1022" t="n"/>
+      <c r="L51" s="1022" t="n"/>
+      <c r="M51" s="1022" t="n"/>
+      <c r="N51" s="1022" t="n"/>
+      <c r="O51" s="1022" t="n"/>
+      <c r="P51" s="1022" t="n"/>
+      <c r="Q51" s="1022" t="n"/>
+      <c r="R51" s="1022" t="n"/>
+      <c r="S51" s="1022" t="n"/>
+      <c r="T51" s="1022" t="n"/>
+      <c r="U51" s="1022" t="n"/>
+      <c r="V51" s="1022" t="n"/>
+      <c r="W51" s="1022" t="n"/>
+      <c r="X51" s="1022" t="n"/>
+      <c r="Y51" s="1022" t="n"/>
+      <c r="Z51" s="1022" t="n"/>
+      <c r="AA51" s="1022" t="n"/>
+      <c r="AB51" s="1022" t="n"/>
+      <c r="AC51" s="1022" t="n"/>
+      <c r="AD51" s="1022" t="n"/>
+      <c r="AE51" s="1022" t="n"/>
+      <c r="AF51" s="1022" t="n"/>
+      <c r="AG51" s="1022" t="n"/>
+      <c r="AH51" s="1022" t="n"/>
+      <c r="AI51" s="1022" t="n"/>
+      <c r="AJ51" s="1022" t="n"/>
+      <c r="AK51" s="1022" t="n"/>
+      <c r="AL51" s="1022" t="n"/>
+      <c r="AM51" s="1022" t="n"/>
+      <c r="AN51" s="1022" t="n"/>
+      <c r="AO51" s="1022" t="n"/>
+      <c r="AP51" s="1022" t="n"/>
+      <c r="AQ51" s="1022" t="n"/>
+      <c r="AR51" s="1022" t="n"/>
+      <c r="AS51" s="1022" t="n"/>
+      <c r="AT51" s="1022" t="n"/>
+      <c r="AU51" s="1022" t="n"/>
+      <c r="AV51" s="1022" t="n"/>
+      <c r="AW51" s="1022" t="n"/>
+      <c r="AX51" s="1022" t="n"/>
+      <c r="AY51" s="1022" t="n"/>
+      <c r="AZ51" s="1022" t="n"/>
+      <c r="BA51" s="1022" t="n"/>
+      <c r="BB51" s="1022" t="n"/>
+      <c r="BC51" s="1022" t="n"/>
+      <c r="BD51" s="1022" t="n"/>
+      <c r="BE51" s="1022" t="n"/>
+      <c r="BF51" s="1022" t="n"/>
+      <c r="BG51" s="1022" t="n"/>
+      <c r="BH51" s="1022" t="n"/>
+      <c r="BI51" s="1022" t="n"/>
+      <c r="BJ51" s="1022" t="n"/>
+      <c r="BK51" s="1022" t="n"/>
+      <c r="BL51" s="1022" t="n"/>
+      <c r="BM51" s="1022" t="n"/>
+      <c r="BN51" s="1022" t="n"/>
+      <c r="BO51" s="1022" t="n"/>
+      <c r="BP51" s="1022" t="n"/>
+      <c r="BQ51" s="1022" t="n"/>
+      <c r="BR51" s="1022" t="n"/>
+      <c r="BS51" s="1022" t="n"/>
+      <c r="BT51" s="1022" t="n"/>
+      <c r="BU51" s="1022" t="n"/>
+      <c r="BV51" s="1022" t="n"/>
+      <c r="BW51" s="1022" t="n"/>
+      <c r="BX51" s="1022" t="n"/>
+      <c r="BY51" s="1022" t="n"/>
+      <c r="BZ51" s="1022" t="n"/>
+      <c r="CA51" s="1022" t="n"/>
+      <c r="CB51" s="1022" t="n"/>
+      <c r="CC51" s="1022" t="n"/>
+      <c r="CD51" s="1022" t="n"/>
+      <c r="CE51" s="1022" t="n"/>
+      <c r="CF51" s="1022" t="n"/>
+      <c r="CG51" s="1022" t="n"/>
+      <c r="CH51" s="1022" t="n"/>
+      <c r="CI51" s="1022" t="n"/>
+      <c r="CJ51" s="1022" t="n"/>
+      <c r="CK51" s="1022" t="n"/>
+      <c r="CL51" s="1022" t="n"/>
+      <c r="CM51" s="1022" t="n"/>
+      <c r="CN51" s="1022" t="n"/>
+      <c r="CO51" s="1022" t="n"/>
+      <c r="CP51" s="1022" t="n"/>
+      <c r="CQ51" s="1022" t="n"/>
+      <c r="CR51" s="1022" t="n"/>
+      <c r="CS51" s="1022" t="n"/>
+      <c r="CT51" s="1022" t="n"/>
+      <c r="CU51" s="1022" t="n"/>
+      <c r="CV51" s="1022" t="n"/>
+      <c r="CW51" s="1022" t="n"/>
+      <c r="CX51" s="1024" t="n"/>
+      <c r="CY51" s="1022" t="n"/>
+    </row>
+    <row r="52" ht="11.1" customHeight="1" s="710">
+      <c r="A52" s="1022" t="n"/>
+      <c r="B52" s="1023" t="n"/>
+      <c r="C52" s="1022" t="n"/>
+      <c r="D52" s="1022" t="n"/>
+      <c r="E52" s="1055" t="inlineStr">
+        <is>
+          <t>CREATED_DT). Proposed retention: 24 months online by CREATED_DT; a monthly housekeeping job deletes older records (period configurable in system master). To be confirmed.</t>
+        </is>
+      </c>
+      <c r="F52" s="1022" t="n"/>
+      <c r="G52" s="1022" t="n"/>
+      <c r="H52" s="1022" t="n"/>
+      <c r="I52" s="1022" t="n"/>
+      <c r="J52" s="1022" t="n"/>
+      <c r="K52" s="1022" t="n"/>
+      <c r="L52" s="1022" t="n"/>
+      <c r="M52" s="1022" t="n"/>
+      <c r="N52" s="1022" t="n"/>
+      <c r="O52" s="1022" t="n"/>
+      <c r="P52" s="1022" t="n"/>
+      <c r="Q52" s="1022" t="n"/>
+      <c r="R52" s="1022" t="n"/>
+      <c r="S52" s="1022" t="n"/>
+      <c r="T52" s="1022" t="n"/>
+      <c r="U52" s="1022" t="n"/>
+      <c r="V52" s="1022" t="n"/>
+      <c r="W52" s="1022" t="n"/>
+      <c r="X52" s="1022" t="n"/>
+      <c r="Y52" s="1022" t="n"/>
+      <c r="Z52" s="1022" t="n"/>
+      <c r="AA52" s="1022" t="n"/>
+      <c r="AB52" s="1022" t="n"/>
+      <c r="AC52" s="1022" t="n"/>
+      <c r="AD52" s="1022" t="n"/>
+      <c r="AE52" s="1022" t="n"/>
+      <c r="AF52" s="1022" t="n"/>
+      <c r="AG52" s="1022" t="n"/>
+      <c r="AH52" s="1022" t="n"/>
+      <c r="AI52" s="1022" t="n"/>
+      <c r="AJ52" s="1022" t="n"/>
+      <c r="AK52" s="1022" t="n"/>
+      <c r="AL52" s="1022" t="n"/>
+      <c r="AM52" s="1022" t="n"/>
+      <c r="AN52" s="1022" t="n"/>
+      <c r="AO52" s="1022" t="n"/>
+      <c r="AP52" s="1022" t="n"/>
+      <c r="AQ52" s="1022" t="n"/>
+      <c r="AR52" s="1022" t="n"/>
+      <c r="AS52" s="1022" t="n"/>
+      <c r="AT52" s="1022" t="n"/>
+      <c r="AU52" s="1022" t="n"/>
+      <c r="AV52" s="1022" t="n"/>
+      <c r="AW52" s="1022" t="n"/>
+      <c r="AX52" s="1022" t="n"/>
+      <c r="AY52" s="1022" t="n"/>
+      <c r="AZ52" s="1022" t="n"/>
+      <c r="BA52" s="1022" t="n"/>
+      <c r="BB52" s="1022" t="n"/>
+      <c r="BC52" s="1022" t="n"/>
+      <c r="BD52" s="1022" t="n"/>
+      <c r="BE52" s="1022" t="n"/>
+      <c r="BF52" s="1022" t="n"/>
+      <c r="BG52" s="1022" t="n"/>
+      <c r="BH52" s="1022" t="n"/>
+      <c r="BI52" s="1022" t="n"/>
+      <c r="BJ52" s="1022" t="n"/>
+      <c r="BK52" s="1022" t="n"/>
+      <c r="BL52" s="1022" t="n"/>
+      <c r="BM52" s="1022" t="n"/>
+      <c r="BN52" s="1022" t="n"/>
+      <c r="BO52" s="1022" t="n"/>
+      <c r="BP52" s="1022" t="n"/>
+      <c r="BQ52" s="1022" t="n"/>
+      <c r="BR52" s="1022" t="n"/>
+      <c r="BS52" s="1022" t="n"/>
+      <c r="BT52" s="1022" t="n"/>
+      <c r="BU52" s="1022" t="n"/>
+      <c r="BV52" s="1022" t="n"/>
+      <c r="BW52" s="1022" t="n"/>
+      <c r="BX52" s="1022" t="n"/>
+      <c r="BY52" s="1022" t="n"/>
+      <c r="BZ52" s="1022" t="n"/>
+      <c r="CA52" s="1022" t="n"/>
+      <c r="CB52" s="1022" t="n"/>
+      <c r="CC52" s="1022" t="n"/>
+      <c r="CD52" s="1022" t="n"/>
+      <c r="CE52" s="1022" t="n"/>
+      <c r="CF52" s="1022" t="n"/>
+      <c r="CG52" s="1022" t="n"/>
+      <c r="CH52" s="1022" t="n"/>
+      <c r="CI52" s="1022" t="n"/>
+      <c r="CJ52" s="1022" t="n"/>
+      <c r="CK52" s="1022" t="n"/>
+      <c r="CL52" s="1022" t="n"/>
+      <c r="CM52" s="1022" t="n"/>
+      <c r="CN52" s="1022" t="n"/>
+      <c r="CO52" s="1022" t="n"/>
+      <c r="CP52" s="1022" t="n"/>
+      <c r="CQ52" s="1022" t="n"/>
+      <c r="CR52" s="1022" t="n"/>
+      <c r="CS52" s="1022" t="n"/>
+      <c r="CT52" s="1022" t="n"/>
+      <c r="CU52" s="1022" t="n"/>
+      <c r="CV52" s="1022" t="n"/>
+      <c r="CW52" s="1022" t="n"/>
+      <c r="CX52" s="1024" t="n"/>
+      <c r="CY52" s="1022" t="n"/>
+    </row>
+    <row r="53" ht="11.1" customHeight="1" s="710">
+      <c r="A53" s="1022" t="n"/>
+      <c r="B53" s="1023" t="n"/>
+      <c r="C53" s="1022" t="n"/>
+      <c r="D53" s="1022" t="n"/>
+      <c r="E53" s="1056" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="F53" s="952" t="n"/>
+      <c r="G53" s="952" t="n"/>
+      <c r="H53" s="952" t="n"/>
+      <c r="I53" s="952" t="n"/>
+      <c r="J53" s="952" t="n"/>
+      <c r="K53" s="952" t="n"/>
+      <c r="L53" s="952" t="n"/>
+      <c r="M53" s="952" t="n"/>
+      <c r="N53" s="952" t="n"/>
+      <c r="O53" s="952" t="n"/>
+      <c r="P53" s="952" t="n"/>
+      <c r="Q53" s="952" t="n"/>
+      <c r="R53" s="952" t="n"/>
+      <c r="S53" s="952" t="n"/>
+      <c r="T53" s="951" t="n"/>
+      <c r="U53" s="1056" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="V53" s="952" t="n"/>
+      <c r="W53" s="952" t="n"/>
+      <c r="X53" s="952" t="n"/>
+      <c r="Y53" s="952" t="n"/>
+      <c r="Z53" s="952" t="n"/>
+      <c r="AA53" s="952" t="n"/>
+      <c r="AB53" s="952" t="n"/>
+      <c r="AC53" s="952" t="n"/>
+      <c r="AD53" s="952" t="n"/>
+      <c r="AE53" s="952" t="n"/>
+      <c r="AF53" s="951" t="n"/>
+      <c r="AG53" s="1056" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="AH53" s="952" t="n"/>
+      <c r="AI53" s="951" t="n"/>
+      <c r="AJ53" s="1056" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AK53" s="952" t="n"/>
+      <c r="AL53" s="952" t="n"/>
+      <c r="AM53" s="951" t="n"/>
+      <c r="AN53" s="1056" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="AO53" s="952" t="n"/>
+      <c r="AP53" s="952" t="n"/>
+      <c r="AQ53" s="952" t="n"/>
+      <c r="AR53" s="952" t="n"/>
+      <c r="AS53" s="952" t="n"/>
+      <c r="AT53" s="952" t="n"/>
+      <c r="AU53" s="952" t="n"/>
+      <c r="AV53" s="952" t="n"/>
+      <c r="AW53" s="952" t="n"/>
+      <c r="AX53" s="952" t="n"/>
+      <c r="AY53" s="952" t="n"/>
+      <c r="AZ53" s="952" t="n"/>
+      <c r="BA53" s="952" t="n"/>
+      <c r="BB53" s="952" t="n"/>
+      <c r="BC53" s="952" t="n"/>
+      <c r="BD53" s="952" t="n"/>
+      <c r="BE53" s="952" t="n"/>
+      <c r="BF53" s="952" t="n"/>
+      <c r="BG53" s="952" t="n"/>
+      <c r="BH53" s="952" t="n"/>
+      <c r="BI53" s="952" t="n"/>
+      <c r="BJ53" s="952" t="n"/>
+      <c r="BK53" s="952" t="n"/>
+      <c r="BL53" s="952" t="n"/>
+      <c r="BM53" s="952" t="n"/>
+      <c r="BN53" s="952" t="n"/>
+      <c r="BO53" s="952" t="n"/>
+      <c r="BP53" s="952" t="n"/>
+      <c r="BQ53" s="952" t="n"/>
+      <c r="BR53" s="952" t="n"/>
+      <c r="BS53" s="952" t="n"/>
+      <c r="BT53" s="952" t="n"/>
+      <c r="BU53" s="952" t="n"/>
+      <c r="BV53" s="952" t="n"/>
+      <c r="BW53" s="952" t="n"/>
+      <c r="BX53" s="952" t="n"/>
+      <c r="BY53" s="952" t="n"/>
+      <c r="BZ53" s="952" t="n"/>
+      <c r="CA53" s="952" t="n"/>
+      <c r="CB53" s="952" t="n"/>
+      <c r="CC53" s="952" t="n"/>
+      <c r="CD53" s="952" t="n"/>
+      <c r="CE53" s="952" t="n"/>
+      <c r="CF53" s="952" t="n"/>
+      <c r="CG53" s="952" t="n"/>
+      <c r="CH53" s="952" t="n"/>
+      <c r="CI53" s="952" t="n"/>
+      <c r="CJ53" s="952" t="n"/>
+      <c r="CK53" s="952" t="n"/>
+      <c r="CL53" s="952" t="n"/>
+      <c r="CM53" s="952" t="n"/>
+      <c r="CN53" s="952" t="n"/>
+      <c r="CO53" s="952" t="n"/>
+      <c r="CP53" s="952" t="n"/>
+      <c r="CQ53" s="952" t="n"/>
+      <c r="CR53" s="952" t="n"/>
+      <c r="CS53" s="951" t="n"/>
+      <c r="CT53" s="1022" t="n"/>
+      <c r="CU53" s="1022" t="n"/>
+      <c r="CV53" s="1022" t="n"/>
+      <c r="CW53" s="1022" t="n"/>
+      <c r="CX53" s="1024" t="n"/>
+      <c r="CY53" s="1022" t="n"/>
+    </row>
+    <row r="54" ht="11.1" customHeight="1" s="710">
+      <c r="A54" s="1022" t="n"/>
+      <c r="B54" s="1023" t="n"/>
+      <c r="C54" s="1022" t="n"/>
+      <c r="D54" s="1022" t="n"/>
+      <c r="E54" s="1057" t="inlineStr">
+        <is>
+          <t>HIST_ID</t>
+        </is>
+      </c>
+      <c r="F54" s="957" t="n"/>
+      <c r="G54" s="957" t="n"/>
+      <c r="H54" s="957" t="n"/>
+      <c r="I54" s="957" t="n"/>
+      <c r="J54" s="957" t="n"/>
+      <c r="K54" s="957" t="n"/>
+      <c r="L54" s="957" t="n"/>
+      <c r="M54" s="957" t="n"/>
+      <c r="N54" s="957" t="n"/>
+      <c r="O54" s="957" t="n"/>
+      <c r="P54" s="957" t="n"/>
+      <c r="Q54" s="957" t="n"/>
+      <c r="R54" s="957" t="n"/>
+      <c r="S54" s="957" t="n"/>
+      <c r="T54" s="955" t="n"/>
+      <c r="U54" s="1057" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="V54" s="957" t="n"/>
+      <c r="W54" s="957" t="n"/>
+      <c r="X54" s="957" t="n"/>
+      <c r="Y54" s="957" t="n"/>
+      <c r="Z54" s="957" t="n"/>
+      <c r="AA54" s="957" t="n"/>
+      <c r="AB54" s="957" t="n"/>
+      <c r="AC54" s="957" t="n"/>
+      <c r="AD54" s="957" t="n"/>
+      <c r="AE54" s="957" t="n"/>
+      <c r="AF54" s="955" t="n"/>
+      <c r="AG54" s="1058" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AH54" s="957" t="n"/>
+      <c r="AI54" s="955" t="n"/>
+      <c r="AJ54" s="1058" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK54" s="957" t="n"/>
+      <c r="AL54" s="957" t="n"/>
+      <c r="AM54" s="955" t="n"/>
+      <c r="AN54" s="1057" t="inlineStr">
+        <is>
+          <t>Running number (identity)</t>
+        </is>
+      </c>
+      <c r="AO54" s="957" t="n"/>
+      <c r="AP54" s="957" t="n"/>
+      <c r="AQ54" s="957" t="n"/>
+      <c r="AR54" s="957" t="n"/>
+      <c r="AS54" s="957" t="n"/>
+      <c r="AT54" s="957" t="n"/>
+      <c r="AU54" s="957" t="n"/>
+      <c r="AV54" s="957" t="n"/>
+      <c r="AW54" s="957" t="n"/>
+      <c r="AX54" s="957" t="n"/>
+      <c r="AY54" s="957" t="n"/>
+      <c r="AZ54" s="957" t="n"/>
+      <c r="BA54" s="957" t="n"/>
+      <c r="BB54" s="957" t="n"/>
+      <c r="BC54" s="957" t="n"/>
+      <c r="BD54" s="957" t="n"/>
+      <c r="BE54" s="957" t="n"/>
+      <c r="BF54" s="957" t="n"/>
+      <c r="BG54" s="957" t="n"/>
+      <c r="BH54" s="957" t="n"/>
+      <c r="BI54" s="957" t="n"/>
+      <c r="BJ54" s="957" t="n"/>
+      <c r="BK54" s="957" t="n"/>
+      <c r="BL54" s="957" t="n"/>
+      <c r="BM54" s="957" t="n"/>
+      <c r="BN54" s="957" t="n"/>
+      <c r="BO54" s="957" t="n"/>
+      <c r="BP54" s="957" t="n"/>
+      <c r="BQ54" s="957" t="n"/>
+      <c r="BR54" s="957" t="n"/>
+      <c r="BS54" s="957" t="n"/>
+      <c r="BT54" s="957" t="n"/>
+      <c r="BU54" s="957" t="n"/>
+      <c r="BV54" s="957" t="n"/>
+      <c r="BW54" s="957" t="n"/>
+      <c r="BX54" s="957" t="n"/>
+      <c r="BY54" s="957" t="n"/>
+      <c r="BZ54" s="957" t="n"/>
+      <c r="CA54" s="957" t="n"/>
+      <c r="CB54" s="957" t="n"/>
+      <c r="CC54" s="957" t="n"/>
+      <c r="CD54" s="957" t="n"/>
+      <c r="CE54" s="957" t="n"/>
+      <c r="CF54" s="957" t="n"/>
+      <c r="CG54" s="957" t="n"/>
+      <c r="CH54" s="957" t="n"/>
+      <c r="CI54" s="957" t="n"/>
+      <c r="CJ54" s="957" t="n"/>
+      <c r="CK54" s="957" t="n"/>
+      <c r="CL54" s="957" t="n"/>
+      <c r="CM54" s="957" t="n"/>
+      <c r="CN54" s="957" t="n"/>
+      <c r="CO54" s="957" t="n"/>
+      <c r="CP54" s="957" t="n"/>
+      <c r="CQ54" s="957" t="n"/>
+      <c r="CR54" s="957" t="n"/>
+      <c r="CS54" s="955" t="n"/>
+      <c r="CT54" s="1022" t="n"/>
+      <c r="CU54" s="1022" t="n"/>
+      <c r="CV54" s="1022" t="n"/>
+      <c r="CW54" s="1022" t="n"/>
+      <c r="CX54" s="1024" t="n"/>
+      <c r="CY54" s="1022" t="n"/>
+    </row>
+    <row r="55" ht="11.1" customHeight="1" s="710">
+      <c r="A55" s="1022" t="n"/>
+      <c r="B55" s="1023" t="n"/>
+      <c r="C55" s="1022" t="n"/>
+      <c r="D55" s="1022" t="n"/>
+      <c r="E55" s="1057" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F55" s="957" t="n"/>
+      <c r="G55" s="957" t="n"/>
+      <c r="H55" s="957" t="n"/>
+      <c r="I55" s="957" t="n"/>
+      <c r="J55" s="957" t="n"/>
+      <c r="K55" s="957" t="n"/>
+      <c r="L55" s="957" t="n"/>
+      <c r="M55" s="957" t="n"/>
+      <c r="N55" s="957" t="n"/>
+      <c r="O55" s="957" t="n"/>
+      <c r="P55" s="957" t="n"/>
+      <c r="Q55" s="957" t="n"/>
+      <c r="R55" s="957" t="n"/>
+      <c r="S55" s="957" t="n"/>
+      <c r="T55" s="955" t="n"/>
+      <c r="U55" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="V55" s="957" t="n"/>
+      <c r="W55" s="957" t="n"/>
+      <c r="X55" s="957" t="n"/>
+      <c r="Y55" s="957" t="n"/>
+      <c r="Z55" s="957" t="n"/>
+      <c r="AA55" s="957" t="n"/>
+      <c r="AB55" s="957" t="n"/>
+      <c r="AC55" s="957" t="n"/>
+      <c r="AD55" s="957" t="n"/>
+      <c r="AE55" s="957" t="n"/>
+      <c r="AF55" s="955" t="n"/>
+      <c r="AG55" s="1058" t="n"/>
+      <c r="AH55" s="957" t="n"/>
+      <c r="AI55" s="955" t="n"/>
+      <c r="AJ55" s="1058" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK55" s="957" t="n"/>
+      <c r="AL55" s="957" t="n"/>
+      <c r="AM55" s="955" t="n"/>
+      <c r="AN55" s="1057" t="inlineStr">
+        <is>
+          <t>Part number; length follows TB_M_PART_MASTER</t>
+        </is>
+      </c>
+      <c r="AO55" s="957" t="n"/>
+      <c r="AP55" s="957" t="n"/>
+      <c r="AQ55" s="957" t="n"/>
+      <c r="AR55" s="957" t="n"/>
+      <c r="AS55" s="957" t="n"/>
+      <c r="AT55" s="957" t="n"/>
+      <c r="AU55" s="957" t="n"/>
+      <c r="AV55" s="957" t="n"/>
+      <c r="AW55" s="957" t="n"/>
+      <c r="AX55" s="957" t="n"/>
+      <c r="AY55" s="957" t="n"/>
+      <c r="AZ55" s="957" t="n"/>
+      <c r="BA55" s="957" t="n"/>
+      <c r="BB55" s="957" t="n"/>
+      <c r="BC55" s="957" t="n"/>
+      <c r="BD55" s="957" t="n"/>
+      <c r="BE55" s="957" t="n"/>
+      <c r="BF55" s="957" t="n"/>
+      <c r="BG55" s="957" t="n"/>
+      <c r="BH55" s="957" t="n"/>
+      <c r="BI55" s="957" t="n"/>
+      <c r="BJ55" s="957" t="n"/>
+      <c r="BK55" s="957" t="n"/>
+      <c r="BL55" s="957" t="n"/>
+      <c r="BM55" s="957" t="n"/>
+      <c r="BN55" s="957" t="n"/>
+      <c r="BO55" s="957" t="n"/>
+      <c r="BP55" s="957" t="n"/>
+      <c r="BQ55" s="957" t="n"/>
+      <c r="BR55" s="957" t="n"/>
+      <c r="BS55" s="957" t="n"/>
+      <c r="BT55" s="957" t="n"/>
+      <c r="BU55" s="957" t="n"/>
+      <c r="BV55" s="957" t="n"/>
+      <c r="BW55" s="957" t="n"/>
+      <c r="BX55" s="957" t="n"/>
+      <c r="BY55" s="957" t="n"/>
+      <c r="BZ55" s="957" t="n"/>
+      <c r="CA55" s="957" t="n"/>
+      <c r="CB55" s="957" t="n"/>
+      <c r="CC55" s="957" t="n"/>
+      <c r="CD55" s="957" t="n"/>
+      <c r="CE55" s="957" t="n"/>
+      <c r="CF55" s="957" t="n"/>
+      <c r="CG55" s="957" t="n"/>
+      <c r="CH55" s="957" t="n"/>
+      <c r="CI55" s="957" t="n"/>
+      <c r="CJ55" s="957" t="n"/>
+      <c r="CK55" s="957" t="n"/>
+      <c r="CL55" s="957" t="n"/>
+      <c r="CM55" s="957" t="n"/>
+      <c r="CN55" s="957" t="n"/>
+      <c r="CO55" s="957" t="n"/>
+      <c r="CP55" s="957" t="n"/>
+      <c r="CQ55" s="957" t="n"/>
+      <c r="CR55" s="957" t="n"/>
+      <c r="CS55" s="955" t="n"/>
+      <c r="CT55" s="1022" t="n"/>
+      <c r="CU55" s="1022" t="n"/>
+      <c r="CV55" s="1022" t="n"/>
+      <c r="CW55" s="1022" t="n"/>
+      <c r="CX55" s="1024" t="n"/>
+      <c r="CY55" s="1022" t="n"/>
+    </row>
+    <row r="56" ht="11.1" customHeight="1" s="710">
+      <c r="A56" s="1022" t="n"/>
+      <c r="B56" s="1023" t="n"/>
+      <c r="C56" s="1022" t="n"/>
+      <c r="D56" s="1022" t="n"/>
+      <c r="E56" s="1057" t="inlineStr">
+        <is>
+          <t>PERIOD</t>
+        </is>
+      </c>
+      <c r="F56" s="957" t="n"/>
+      <c r="G56" s="957" t="n"/>
+      <c r="H56" s="957" t="n"/>
+      <c r="I56" s="957" t="n"/>
+      <c r="J56" s="957" t="n"/>
+      <c r="K56" s="957" t="n"/>
+      <c r="L56" s="957" t="n"/>
+      <c r="M56" s="957" t="n"/>
+      <c r="N56" s="957" t="n"/>
+      <c r="O56" s="957" t="n"/>
+      <c r="P56" s="957" t="n"/>
+      <c r="Q56" s="957" t="n"/>
+      <c r="R56" s="957" t="n"/>
+      <c r="S56" s="957" t="n"/>
+      <c r="T56" s="955" t="n"/>
+      <c r="U56" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="V56" s="957" t="n"/>
+      <c r="W56" s="957" t="n"/>
+      <c r="X56" s="957" t="n"/>
+      <c r="Y56" s="957" t="n"/>
+      <c r="Z56" s="957" t="n"/>
+      <c r="AA56" s="957" t="n"/>
+      <c r="AB56" s="957" t="n"/>
+      <c r="AC56" s="957" t="n"/>
+      <c r="AD56" s="957" t="n"/>
+      <c r="AE56" s="957" t="n"/>
+      <c r="AF56" s="955" t="n"/>
+      <c r="AG56" s="1058" t="n"/>
+      <c r="AH56" s="957" t="n"/>
+      <c r="AI56" s="955" t="n"/>
+      <c r="AJ56" s="1058" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AK56" s="957" t="n"/>
+      <c r="AL56" s="957" t="n"/>
+      <c r="AM56" s="955" t="n"/>
+      <c r="AN56" s="1057" t="inlineStr">
+        <is>
+          <t>Calculation period for MAPPING / SYNC; NULL for ADD / EDIT (Part List has no period)</t>
+        </is>
+      </c>
+      <c r="AO56" s="957" t="n"/>
+      <c r="AP56" s="957" t="n"/>
+      <c r="AQ56" s="957" t="n"/>
+      <c r="AR56" s="957" t="n"/>
+      <c r="AS56" s="957" t="n"/>
+      <c r="AT56" s="957" t="n"/>
+      <c r="AU56" s="957" t="n"/>
+      <c r="AV56" s="957" t="n"/>
+      <c r="AW56" s="957" t="n"/>
+      <c r="AX56" s="957" t="n"/>
+      <c r="AY56" s="957" t="n"/>
+      <c r="AZ56" s="957" t="n"/>
+      <c r="BA56" s="957" t="n"/>
+      <c r="BB56" s="957" t="n"/>
+      <c r="BC56" s="957" t="n"/>
+      <c r="BD56" s="957" t="n"/>
+      <c r="BE56" s="957" t="n"/>
+      <c r="BF56" s="957" t="n"/>
+      <c r="BG56" s="957" t="n"/>
+      <c r="BH56" s="957" t="n"/>
+      <c r="BI56" s="957" t="n"/>
+      <c r="BJ56" s="957" t="n"/>
+      <c r="BK56" s="957" t="n"/>
+      <c r="BL56" s="957" t="n"/>
+      <c r="BM56" s="957" t="n"/>
+      <c r="BN56" s="957" t="n"/>
+      <c r="BO56" s="957" t="n"/>
+      <c r="BP56" s="957" t="n"/>
+      <c r="BQ56" s="957" t="n"/>
+      <c r="BR56" s="957" t="n"/>
+      <c r="BS56" s="957" t="n"/>
+      <c r="BT56" s="957" t="n"/>
+      <c r="BU56" s="957" t="n"/>
+      <c r="BV56" s="957" t="n"/>
+      <c r="BW56" s="957" t="n"/>
+      <c r="BX56" s="957" t="n"/>
+      <c r="BY56" s="957" t="n"/>
+      <c r="BZ56" s="957" t="n"/>
+      <c r="CA56" s="957" t="n"/>
+      <c r="CB56" s="957" t="n"/>
+      <c r="CC56" s="957" t="n"/>
+      <c r="CD56" s="957" t="n"/>
+      <c r="CE56" s="957" t="n"/>
+      <c r="CF56" s="957" t="n"/>
+      <c r="CG56" s="957" t="n"/>
+      <c r="CH56" s="957" t="n"/>
+      <c r="CI56" s="957" t="n"/>
+      <c r="CJ56" s="957" t="n"/>
+      <c r="CK56" s="957" t="n"/>
+      <c r="CL56" s="957" t="n"/>
+      <c r="CM56" s="957" t="n"/>
+      <c r="CN56" s="957" t="n"/>
+      <c r="CO56" s="957" t="n"/>
+      <c r="CP56" s="957" t="n"/>
+      <c r="CQ56" s="957" t="n"/>
+      <c r="CR56" s="957" t="n"/>
+      <c r="CS56" s="955" t="n"/>
+      <c r="CT56" s="1022" t="n"/>
+      <c r="CU56" s="1022" t="n"/>
+      <c r="CV56" s="1022" t="n"/>
+      <c r="CW56" s="1022" t="n"/>
+      <c r="CX56" s="1024" t="n"/>
+      <c r="CY56" s="1022" t="n"/>
+    </row>
+    <row r="57" ht="11.1" customHeight="1" s="710">
+      <c r="A57" s="1022" t="n"/>
+      <c r="B57" s="1023" t="n"/>
+      <c r="C57" s="1022" t="n"/>
+      <c r="D57" s="1022" t="n"/>
+      <c r="E57" s="1057" t="inlineStr">
+        <is>
+          <t>EVENT_TYPE</t>
+        </is>
+      </c>
+      <c r="F57" s="957" t="n"/>
+      <c r="G57" s="957" t="n"/>
+      <c r="H57" s="957" t="n"/>
+      <c r="I57" s="957" t="n"/>
+      <c r="J57" s="957" t="n"/>
+      <c r="K57" s="957" t="n"/>
+      <c r="L57" s="957" t="n"/>
+      <c r="M57" s="957" t="n"/>
+      <c r="N57" s="957" t="n"/>
+      <c r="O57" s="957" t="n"/>
+      <c r="P57" s="957" t="n"/>
+      <c r="Q57" s="957" t="n"/>
+      <c r="R57" s="957" t="n"/>
+      <c r="S57" s="957" t="n"/>
+      <c r="T57" s="955" t="n"/>
+      <c r="U57" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="V57" s="957" t="n"/>
+      <c r="W57" s="957" t="n"/>
+      <c r="X57" s="957" t="n"/>
+      <c r="Y57" s="957" t="n"/>
+      <c r="Z57" s="957" t="n"/>
+      <c r="AA57" s="957" t="n"/>
+      <c r="AB57" s="957" t="n"/>
+      <c r="AC57" s="957" t="n"/>
+      <c r="AD57" s="957" t="n"/>
+      <c r="AE57" s="957" t="n"/>
+      <c r="AF57" s="955" t="n"/>
+      <c r="AG57" s="1058" t="n"/>
+      <c r="AH57" s="957" t="n"/>
+      <c r="AI57" s="955" t="n"/>
+      <c r="AJ57" s="1058" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK57" s="957" t="n"/>
+      <c r="AL57" s="957" t="n"/>
+      <c r="AM57" s="955" t="n"/>
+      <c r="AN57" s="1057" t="inlineStr">
+        <is>
+          <t>ADD / EDIT / MAPPING / SYNC</t>
+        </is>
+      </c>
+      <c r="AO57" s="957" t="n"/>
+      <c r="AP57" s="957" t="n"/>
+      <c r="AQ57" s="957" t="n"/>
+      <c r="AR57" s="957" t="n"/>
+      <c r="AS57" s="957" t="n"/>
+      <c r="AT57" s="957" t="n"/>
+      <c r="AU57" s="957" t="n"/>
+      <c r="AV57" s="957" t="n"/>
+      <c r="AW57" s="957" t="n"/>
+      <c r="AX57" s="957" t="n"/>
+      <c r="AY57" s="957" t="n"/>
+      <c r="AZ57" s="957" t="n"/>
+      <c r="BA57" s="957" t="n"/>
+      <c r="BB57" s="957" t="n"/>
+      <c r="BC57" s="957" t="n"/>
+      <c r="BD57" s="957" t="n"/>
+      <c r="BE57" s="957" t="n"/>
+      <c r="BF57" s="957" t="n"/>
+      <c r="BG57" s="957" t="n"/>
+      <c r="BH57" s="957" t="n"/>
+      <c r="BI57" s="957" t="n"/>
+      <c r="BJ57" s="957" t="n"/>
+      <c r="BK57" s="957" t="n"/>
+      <c r="BL57" s="957" t="n"/>
+      <c r="BM57" s="957" t="n"/>
+      <c r="BN57" s="957" t="n"/>
+      <c r="BO57" s="957" t="n"/>
+      <c r="BP57" s="957" t="n"/>
+      <c r="BQ57" s="957" t="n"/>
+      <c r="BR57" s="957" t="n"/>
+      <c r="BS57" s="957" t="n"/>
+      <c r="BT57" s="957" t="n"/>
+      <c r="BU57" s="957" t="n"/>
+      <c r="BV57" s="957" t="n"/>
+      <c r="BW57" s="957" t="n"/>
+      <c r="BX57" s="957" t="n"/>
+      <c r="BY57" s="957" t="n"/>
+      <c r="BZ57" s="957" t="n"/>
+      <c r="CA57" s="957" t="n"/>
+      <c r="CB57" s="957" t="n"/>
+      <c r="CC57" s="957" t="n"/>
+      <c r="CD57" s="957" t="n"/>
+      <c r="CE57" s="957" t="n"/>
+      <c r="CF57" s="957" t="n"/>
+      <c r="CG57" s="957" t="n"/>
+      <c r="CH57" s="957" t="n"/>
+      <c r="CI57" s="957" t="n"/>
+      <c r="CJ57" s="957" t="n"/>
+      <c r="CK57" s="957" t="n"/>
+      <c r="CL57" s="957" t="n"/>
+      <c r="CM57" s="957" t="n"/>
+      <c r="CN57" s="957" t="n"/>
+      <c r="CO57" s="957" t="n"/>
+      <c r="CP57" s="957" t="n"/>
+      <c r="CQ57" s="957" t="n"/>
+      <c r="CR57" s="957" t="n"/>
+      <c r="CS57" s="955" t="n"/>
+      <c r="CT57" s="1022" t="n"/>
+      <c r="CU57" s="1022" t="n"/>
+      <c r="CV57" s="1022" t="n"/>
+      <c r="CW57" s="1022" t="n"/>
+      <c r="CX57" s="1024" t="n"/>
+      <c r="CY57" s="1022" t="n"/>
+    </row>
+    <row r="58" ht="11.1" customHeight="1" s="710">
+      <c r="A58" s="1022" t="n"/>
+      <c r="B58" s="1023" t="n"/>
+      <c r="C58" s="1022" t="n"/>
+      <c r="D58" s="1022" t="n"/>
+      <c r="E58" s="1057" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="F58" s="957" t="n"/>
+      <c r="G58" s="957" t="n"/>
+      <c r="H58" s="957" t="n"/>
+      <c r="I58" s="957" t="n"/>
+      <c r="J58" s="957" t="n"/>
+      <c r="K58" s="957" t="n"/>
+      <c r="L58" s="957" t="n"/>
+      <c r="M58" s="957" t="n"/>
+      <c r="N58" s="957" t="n"/>
+      <c r="O58" s="957" t="n"/>
+      <c r="P58" s="957" t="n"/>
+      <c r="Q58" s="957" t="n"/>
+      <c r="R58" s="957" t="n"/>
+      <c r="S58" s="957" t="n"/>
+      <c r="T58" s="955" t="n"/>
+      <c r="U58" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="V58" s="957" t="n"/>
+      <c r="W58" s="957" t="n"/>
+      <c r="X58" s="957" t="n"/>
+      <c r="Y58" s="957" t="n"/>
+      <c r="Z58" s="957" t="n"/>
+      <c r="AA58" s="957" t="n"/>
+      <c r="AB58" s="957" t="n"/>
+      <c r="AC58" s="957" t="n"/>
+      <c r="AD58" s="957" t="n"/>
+      <c r="AE58" s="957" t="n"/>
+      <c r="AF58" s="955" t="n"/>
+      <c r="AG58" s="1058" t="n"/>
+      <c r="AH58" s="957" t="n"/>
+      <c r="AI58" s="955" t="n"/>
+      <c r="AJ58" s="1058" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK58" s="957" t="n"/>
+      <c r="AL58" s="957" t="n"/>
+      <c r="AM58" s="955" t="n"/>
+      <c r="AN58" s="1057" t="inlineStr">
+        <is>
+          <t>SCREEN / UPLOAD / RPA</t>
+        </is>
+      </c>
+      <c r="AO58" s="957" t="n"/>
+      <c r="AP58" s="957" t="n"/>
+      <c r="AQ58" s="957" t="n"/>
+      <c r="AR58" s="957" t="n"/>
+      <c r="AS58" s="957" t="n"/>
+      <c r="AT58" s="957" t="n"/>
+      <c r="AU58" s="957" t="n"/>
+      <c r="AV58" s="957" t="n"/>
+      <c r="AW58" s="957" t="n"/>
+      <c r="AX58" s="957" t="n"/>
+      <c r="AY58" s="957" t="n"/>
+      <c r="AZ58" s="957" t="n"/>
+      <c r="BA58" s="957" t="n"/>
+      <c r="BB58" s="957" t="n"/>
+      <c r="BC58" s="957" t="n"/>
+      <c r="BD58" s="957" t="n"/>
+      <c r="BE58" s="957" t="n"/>
+      <c r="BF58" s="957" t="n"/>
+      <c r="BG58" s="957" t="n"/>
+      <c r="BH58" s="957" t="n"/>
+      <c r="BI58" s="957" t="n"/>
+      <c r="BJ58" s="957" t="n"/>
+      <c r="BK58" s="957" t="n"/>
+      <c r="BL58" s="957" t="n"/>
+      <c r="BM58" s="957" t="n"/>
+      <c r="BN58" s="957" t="n"/>
+      <c r="BO58" s="957" t="n"/>
+      <c r="BP58" s="957" t="n"/>
+      <c r="BQ58" s="957" t="n"/>
+      <c r="BR58" s="957" t="n"/>
+      <c r="BS58" s="957" t="n"/>
+      <c r="BT58" s="957" t="n"/>
+      <c r="BU58" s="957" t="n"/>
+      <c r="BV58" s="957" t="n"/>
+      <c r="BW58" s="957" t="n"/>
+      <c r="BX58" s="957" t="n"/>
+      <c r="BY58" s="957" t="n"/>
+      <c r="BZ58" s="957" t="n"/>
+      <c r="CA58" s="957" t="n"/>
+      <c r="CB58" s="957" t="n"/>
+      <c r="CC58" s="957" t="n"/>
+      <c r="CD58" s="957" t="n"/>
+      <c r="CE58" s="957" t="n"/>
+      <c r="CF58" s="957" t="n"/>
+      <c r="CG58" s="957" t="n"/>
+      <c r="CH58" s="957" t="n"/>
+      <c r="CI58" s="957" t="n"/>
+      <c r="CJ58" s="957" t="n"/>
+      <c r="CK58" s="957" t="n"/>
+      <c r="CL58" s="957" t="n"/>
+      <c r="CM58" s="957" t="n"/>
+      <c r="CN58" s="957" t="n"/>
+      <c r="CO58" s="957" t="n"/>
+      <c r="CP58" s="957" t="n"/>
+      <c r="CQ58" s="957" t="n"/>
+      <c r="CR58" s="957" t="n"/>
+      <c r="CS58" s="955" t="n"/>
+      <c r="CT58" s="1022" t="n"/>
+      <c r="CU58" s="1022" t="n"/>
+      <c r="CV58" s="1022" t="n"/>
+      <c r="CW58" s="1022" t="n"/>
+      <c r="CX58" s="1024" t="n"/>
+      <c r="CY58" s="1022" t="n"/>
+    </row>
+    <row r="59" ht="11.1" customHeight="1" s="710">
+      <c r="A59" s="1022" t="n"/>
+      <c r="B59" s="1023" t="n"/>
+      <c r="C59" s="1022" t="n"/>
+      <c r="D59" s="1022" t="n"/>
+      <c r="E59" s="1057" t="inlineStr">
+        <is>
+          <t>UPLOAD_ID</t>
+        </is>
+      </c>
+      <c r="F59" s="957" t="n"/>
+      <c r="G59" s="957" t="n"/>
+      <c r="H59" s="957" t="n"/>
+      <c r="I59" s="957" t="n"/>
+      <c r="J59" s="957" t="n"/>
+      <c r="K59" s="957" t="n"/>
+      <c r="L59" s="957" t="n"/>
+      <c r="M59" s="957" t="n"/>
+      <c r="N59" s="957" t="n"/>
+      <c r="O59" s="957" t="n"/>
+      <c r="P59" s="957" t="n"/>
+      <c r="Q59" s="957" t="n"/>
+      <c r="R59" s="957" t="n"/>
+      <c r="S59" s="957" t="n"/>
+      <c r="T59" s="955" t="n"/>
+      <c r="U59" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="V59" s="957" t="n"/>
+      <c r="W59" s="957" t="n"/>
+      <c r="X59" s="957" t="n"/>
+      <c r="Y59" s="957" t="n"/>
+      <c r="Z59" s="957" t="n"/>
+      <c r="AA59" s="957" t="n"/>
+      <c r="AB59" s="957" t="n"/>
+      <c r="AC59" s="957" t="n"/>
+      <c r="AD59" s="957" t="n"/>
+      <c r="AE59" s="957" t="n"/>
+      <c r="AF59" s="955" t="n"/>
+      <c r="AG59" s="1058" t="n"/>
+      <c r="AH59" s="957" t="n"/>
+      <c r="AI59" s="955" t="n"/>
+      <c r="AJ59" s="1058" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AK59" s="957" t="n"/>
+      <c r="AL59" s="957" t="n"/>
+      <c r="AM59" s="955" t="n"/>
+      <c r="AN59" s="1057" t="inlineStr">
+        <is>
+          <t>Upload of the change (Log); NULL when not from an upload</t>
+        </is>
+      </c>
+      <c r="AO59" s="957" t="n"/>
+      <c r="AP59" s="957" t="n"/>
+      <c r="AQ59" s="957" t="n"/>
+      <c r="AR59" s="957" t="n"/>
+      <c r="AS59" s="957" t="n"/>
+      <c r="AT59" s="957" t="n"/>
+      <c r="AU59" s="957" t="n"/>
+      <c r="AV59" s="957" t="n"/>
+      <c r="AW59" s="957" t="n"/>
+      <c r="AX59" s="957" t="n"/>
+      <c r="AY59" s="957" t="n"/>
+      <c r="AZ59" s="957" t="n"/>
+      <c r="BA59" s="957" t="n"/>
+      <c r="BB59" s="957" t="n"/>
+      <c r="BC59" s="957" t="n"/>
+      <c r="BD59" s="957" t="n"/>
+      <c r="BE59" s="957" t="n"/>
+      <c r="BF59" s="957" t="n"/>
+      <c r="BG59" s="957" t="n"/>
+      <c r="BH59" s="957" t="n"/>
+      <c r="BI59" s="957" t="n"/>
+      <c r="BJ59" s="957" t="n"/>
+      <c r="BK59" s="957" t="n"/>
+      <c r="BL59" s="957" t="n"/>
+      <c r="BM59" s="957" t="n"/>
+      <c r="BN59" s="957" t="n"/>
+      <c r="BO59" s="957" t="n"/>
+      <c r="BP59" s="957" t="n"/>
+      <c r="BQ59" s="957" t="n"/>
+      <c r="BR59" s="957" t="n"/>
+      <c r="BS59" s="957" t="n"/>
+      <c r="BT59" s="957" t="n"/>
+      <c r="BU59" s="957" t="n"/>
+      <c r="BV59" s="957" t="n"/>
+      <c r="BW59" s="957" t="n"/>
+      <c r="BX59" s="957" t="n"/>
+      <c r="BY59" s="957" t="n"/>
+      <c r="BZ59" s="957" t="n"/>
+      <c r="CA59" s="957" t="n"/>
+      <c r="CB59" s="957" t="n"/>
+      <c r="CC59" s="957" t="n"/>
+      <c r="CD59" s="957" t="n"/>
+      <c r="CE59" s="957" t="n"/>
+      <c r="CF59" s="957" t="n"/>
+      <c r="CG59" s="957" t="n"/>
+      <c r="CH59" s="957" t="n"/>
+      <c r="CI59" s="957" t="n"/>
+      <c r="CJ59" s="957" t="n"/>
+      <c r="CK59" s="957" t="n"/>
+      <c r="CL59" s="957" t="n"/>
+      <c r="CM59" s="957" t="n"/>
+      <c r="CN59" s="957" t="n"/>
+      <c r="CO59" s="957" t="n"/>
+      <c r="CP59" s="957" t="n"/>
+      <c r="CQ59" s="957" t="n"/>
+      <c r="CR59" s="957" t="n"/>
+      <c r="CS59" s="955" t="n"/>
+      <c r="CT59" s="1022" t="n"/>
+      <c r="CU59" s="1022" t="n"/>
+      <c r="CV59" s="1022" t="n"/>
+      <c r="CW59" s="1022" t="n"/>
+      <c r="CX59" s="1024" t="n"/>
+      <c r="CY59" s="1022" t="n"/>
+    </row>
+    <row r="60" ht="11.1" customHeight="1" s="710">
+      <c r="A60" s="1022" t="n"/>
+      <c r="B60" s="1023" t="n"/>
+      <c r="C60" s="1022" t="n"/>
+      <c r="D60" s="1022" t="n"/>
+      <c r="E60" s="1057" t="inlineStr">
+        <is>
+          <t>DEST_CODE</t>
+        </is>
+      </c>
+      <c r="F60" s="957" t="n"/>
+      <c r="G60" s="957" t="n"/>
+      <c r="H60" s="957" t="n"/>
+      <c r="I60" s="957" t="n"/>
+      <c r="J60" s="957" t="n"/>
+      <c r="K60" s="957" t="n"/>
+      <c r="L60" s="957" t="n"/>
+      <c r="M60" s="957" t="n"/>
+      <c r="N60" s="957" t="n"/>
+      <c r="O60" s="957" t="n"/>
+      <c r="P60" s="957" t="n"/>
+      <c r="Q60" s="957" t="n"/>
+      <c r="R60" s="957" t="n"/>
+      <c r="S60" s="957" t="n"/>
+      <c r="T60" s="955" t="n"/>
+      <c r="U60" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="V60" s="957" t="n"/>
+      <c r="W60" s="957" t="n"/>
+      <c r="X60" s="957" t="n"/>
+      <c r="Y60" s="957" t="n"/>
+      <c r="Z60" s="957" t="n"/>
+      <c r="AA60" s="957" t="n"/>
+      <c r="AB60" s="957" t="n"/>
+      <c r="AC60" s="957" t="n"/>
+      <c r="AD60" s="957" t="n"/>
+      <c r="AE60" s="957" t="n"/>
+      <c r="AF60" s="955" t="n"/>
+      <c r="AG60" s="1058" t="n"/>
+      <c r="AH60" s="957" t="n"/>
+      <c r="AI60" s="955" t="n"/>
+      <c r="AJ60" s="1058" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AK60" s="957" t="n"/>
+      <c r="AL60" s="957" t="n"/>
+      <c r="AM60" s="955" t="n"/>
+      <c r="AN60" s="1057" t="inlineStr">
+        <is>
+          <t>Destination code for MAPPING; NULL for other events</t>
+        </is>
+      </c>
+      <c r="AO60" s="957" t="n"/>
+      <c r="AP60" s="957" t="n"/>
+      <c r="AQ60" s="957" t="n"/>
+      <c r="AR60" s="957" t="n"/>
+      <c r="AS60" s="957" t="n"/>
+      <c r="AT60" s="957" t="n"/>
+      <c r="AU60" s="957" t="n"/>
+      <c r="AV60" s="957" t="n"/>
+      <c r="AW60" s="957" t="n"/>
+      <c r="AX60" s="957" t="n"/>
+      <c r="AY60" s="957" t="n"/>
+      <c r="AZ60" s="957" t="n"/>
+      <c r="BA60" s="957" t="n"/>
+      <c r="BB60" s="957" t="n"/>
+      <c r="BC60" s="957" t="n"/>
+      <c r="BD60" s="957" t="n"/>
+      <c r="BE60" s="957" t="n"/>
+      <c r="BF60" s="957" t="n"/>
+      <c r="BG60" s="957" t="n"/>
+      <c r="BH60" s="957" t="n"/>
+      <c r="BI60" s="957" t="n"/>
+      <c r="BJ60" s="957" t="n"/>
+      <c r="BK60" s="957" t="n"/>
+      <c r="BL60" s="957" t="n"/>
+      <c r="BM60" s="957" t="n"/>
+      <c r="BN60" s="957" t="n"/>
+      <c r="BO60" s="957" t="n"/>
+      <c r="BP60" s="957" t="n"/>
+      <c r="BQ60" s="957" t="n"/>
+      <c r="BR60" s="957" t="n"/>
+      <c r="BS60" s="957" t="n"/>
+      <c r="BT60" s="957" t="n"/>
+      <c r="BU60" s="957" t="n"/>
+      <c r="BV60" s="957" t="n"/>
+      <c r="BW60" s="957" t="n"/>
+      <c r="BX60" s="957" t="n"/>
+      <c r="BY60" s="957" t="n"/>
+      <c r="BZ60" s="957" t="n"/>
+      <c r="CA60" s="957" t="n"/>
+      <c r="CB60" s="957" t="n"/>
+      <c r="CC60" s="957" t="n"/>
+      <c r="CD60" s="957" t="n"/>
+      <c r="CE60" s="957" t="n"/>
+      <c r="CF60" s="957" t="n"/>
+      <c r="CG60" s="957" t="n"/>
+      <c r="CH60" s="957" t="n"/>
+      <c r="CI60" s="957" t="n"/>
+      <c r="CJ60" s="957" t="n"/>
+      <c r="CK60" s="957" t="n"/>
+      <c r="CL60" s="957" t="n"/>
+      <c r="CM60" s="957" t="n"/>
+      <c r="CN60" s="957" t="n"/>
+      <c r="CO60" s="957" t="n"/>
+      <c r="CP60" s="957" t="n"/>
+      <c r="CQ60" s="957" t="n"/>
+      <c r="CR60" s="957" t="n"/>
+      <c r="CS60" s="955" t="n"/>
+      <c r="CT60" s="1022" t="n"/>
+      <c r="CU60" s="1022" t="n"/>
+      <c r="CV60" s="1022" t="n"/>
+      <c r="CW60" s="1022" t="n"/>
+      <c r="CX60" s="1024" t="n"/>
+      <c r="CY60" s="1022" t="n"/>
+    </row>
+    <row r="61" ht="11.1" customHeight="1" s="710">
+      <c r="A61" s="1022" t="n"/>
+      <c r="B61" s="1023" t="n"/>
+      <c r="C61" s="1022" t="n"/>
+      <c r="D61" s="1022" t="n"/>
+      <c r="E61" s="1057" t="inlineStr">
+        <is>
+          <t>FIELD_NAME</t>
+        </is>
+      </c>
+      <c r="F61" s="957" t="n"/>
+      <c r="G61" s="957" t="n"/>
+      <c r="H61" s="957" t="n"/>
+      <c r="I61" s="957" t="n"/>
+      <c r="J61" s="957" t="n"/>
+      <c r="K61" s="957" t="n"/>
+      <c r="L61" s="957" t="n"/>
+      <c r="M61" s="957" t="n"/>
+      <c r="N61" s="957" t="n"/>
+      <c r="O61" s="957" t="n"/>
+      <c r="P61" s="957" t="n"/>
+      <c r="Q61" s="957" t="n"/>
+      <c r="R61" s="957" t="n"/>
+      <c r="S61" s="957" t="n"/>
+      <c r="T61" s="955" t="n"/>
+      <c r="U61" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="V61" s="957" t="n"/>
+      <c r="W61" s="957" t="n"/>
+      <c r="X61" s="957" t="n"/>
+      <c r="Y61" s="957" t="n"/>
+      <c r="Z61" s="957" t="n"/>
+      <c r="AA61" s="957" t="n"/>
+      <c r="AB61" s="957" t="n"/>
+      <c r="AC61" s="957" t="n"/>
+      <c r="AD61" s="957" t="n"/>
+      <c r="AE61" s="957" t="n"/>
+      <c r="AF61" s="955" t="n"/>
+      <c r="AG61" s="1058" t="n"/>
+      <c r="AH61" s="957" t="n"/>
+      <c r="AI61" s="955" t="n"/>
+      <c r="AJ61" s="1058" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK61" s="957" t="n"/>
+      <c r="AL61" s="957" t="n"/>
+      <c r="AM61" s="955" t="n"/>
+      <c r="AN61" s="1057" t="inlineStr">
+        <is>
+          <t>Changed field: PCS_CASE, MAX_CASE_DAY, MAD, PART_STATUS, EFFECTIVE_START_DATE, CASE_DAY,</t>
+        </is>
+      </c>
+      <c r="AO61" s="957" t="n"/>
+      <c r="AP61" s="957" t="n"/>
+      <c r="AQ61" s="957" t="n"/>
+      <c r="AR61" s="957" t="n"/>
+      <c r="AS61" s="957" t="n"/>
+      <c r="AT61" s="957" t="n"/>
+      <c r="AU61" s="957" t="n"/>
+      <c r="AV61" s="957" t="n"/>
+      <c r="AW61" s="957" t="n"/>
+      <c r="AX61" s="957" t="n"/>
+      <c r="AY61" s="957" t="n"/>
+      <c r="AZ61" s="957" t="n"/>
+      <c r="BA61" s="957" t="n"/>
+      <c r="BB61" s="957" t="n"/>
+      <c r="BC61" s="957" t="n"/>
+      <c r="BD61" s="957" t="n"/>
+      <c r="BE61" s="957" t="n"/>
+      <c r="BF61" s="957" t="n"/>
+      <c r="BG61" s="957" t="n"/>
+      <c r="BH61" s="957" t="n"/>
+      <c r="BI61" s="957" t="n"/>
+      <c r="BJ61" s="957" t="n"/>
+      <c r="BK61" s="957" t="n"/>
+      <c r="BL61" s="957" t="n"/>
+      <c r="BM61" s="957" t="n"/>
+      <c r="BN61" s="957" t="n"/>
+      <c r="BO61" s="957" t="n"/>
+      <c r="BP61" s="957" t="n"/>
+      <c r="BQ61" s="957" t="n"/>
+      <c r="BR61" s="957" t="n"/>
+      <c r="BS61" s="957" t="n"/>
+      <c r="BT61" s="957" t="n"/>
+      <c r="BU61" s="957" t="n"/>
+      <c r="BV61" s="957" t="n"/>
+      <c r="BW61" s="957" t="n"/>
+      <c r="BX61" s="957" t="n"/>
+      <c r="BY61" s="957" t="n"/>
+      <c r="BZ61" s="957" t="n"/>
+      <c r="CA61" s="957" t="n"/>
+      <c r="CB61" s="957" t="n"/>
+      <c r="CC61" s="957" t="n"/>
+      <c r="CD61" s="957" t="n"/>
+      <c r="CE61" s="957" t="n"/>
+      <c r="CF61" s="957" t="n"/>
+      <c r="CG61" s="957" t="n"/>
+      <c r="CH61" s="957" t="n"/>
+      <c r="CI61" s="957" t="n"/>
+      <c r="CJ61" s="957" t="n"/>
+      <c r="CK61" s="957" t="n"/>
+      <c r="CL61" s="957" t="n"/>
+      <c r="CM61" s="957" t="n"/>
+      <c r="CN61" s="957" t="n"/>
+      <c r="CO61" s="957" t="n"/>
+      <c r="CP61" s="957" t="n"/>
+      <c r="CQ61" s="957" t="n"/>
+      <c r="CR61" s="957" t="n"/>
+      <c r="CS61" s="955" t="n"/>
+      <c r="CT61" s="1022" t="n"/>
+      <c r="CU61" s="1022" t="n"/>
+      <c r="CV61" s="1022" t="n"/>
+      <c r="CW61" s="1022" t="n"/>
+      <c r="CX61" s="1024" t="n"/>
+      <c r="CY61" s="1022" t="n"/>
+    </row>
+    <row r="62" ht="11.1" customHeight="1" s="710">
+      <c r="A62" s="1022" t="n"/>
+      <c r="B62" s="1023" t="n"/>
+      <c r="C62" s="1022" t="n"/>
+      <c r="D62" s="1022" t="n"/>
+      <c r="E62" s="1059" t="n"/>
+      <c r="F62" s="961" t="n"/>
+      <c r="G62" s="961" t="n"/>
+      <c r="H62" s="961" t="n"/>
+      <c r="I62" s="961" t="n"/>
+      <c r="J62" s="961" t="n"/>
+      <c r="K62" s="961" t="n"/>
+      <c r="L62" s="961" t="n"/>
+      <c r="M62" s="961" t="n"/>
+      <c r="N62" s="961" t="n"/>
+      <c r="O62" s="961" t="n"/>
+      <c r="P62" s="961" t="n"/>
+      <c r="Q62" s="961" t="n"/>
+      <c r="R62" s="961" t="n"/>
+      <c r="S62" s="961" t="n"/>
+      <c r="T62" s="959" t="n"/>
+      <c r="U62" s="1059" t="n"/>
+      <c r="V62" s="961" t="n"/>
+      <c r="W62" s="961" t="n"/>
+      <c r="X62" s="961" t="n"/>
+      <c r="Y62" s="961" t="n"/>
+      <c r="Z62" s="961" t="n"/>
+      <c r="AA62" s="961" t="n"/>
+      <c r="AB62" s="961" t="n"/>
+      <c r="AC62" s="961" t="n"/>
+      <c r="AD62" s="961" t="n"/>
+      <c r="AE62" s="961" t="n"/>
+      <c r="AF62" s="959" t="n"/>
+      <c r="AG62" s="1060" t="n"/>
+      <c r="AH62" s="961" t="n"/>
+      <c r="AI62" s="959" t="n"/>
+      <c r="AJ62" s="1060" t="n"/>
+      <c r="AK62" s="961" t="n"/>
+      <c r="AL62" s="961" t="n"/>
+      <c r="AM62" s="959" t="n"/>
+      <c r="AN62" s="1059" t="inlineStr">
+        <is>
+          <t>SYNC_STATUS</t>
+        </is>
+      </c>
+      <c r="AO62" s="961" t="n"/>
+      <c r="AP62" s="961" t="n"/>
+      <c r="AQ62" s="961" t="n"/>
+      <c r="AR62" s="961" t="n"/>
+      <c r="AS62" s="961" t="n"/>
+      <c r="AT62" s="961" t="n"/>
+      <c r="AU62" s="961" t="n"/>
+      <c r="AV62" s="961" t="n"/>
+      <c r="AW62" s="961" t="n"/>
+      <c r="AX62" s="961" t="n"/>
+      <c r="AY62" s="961" t="n"/>
+      <c r="AZ62" s="961" t="n"/>
+      <c r="BA62" s="961" t="n"/>
+      <c r="BB62" s="961" t="n"/>
+      <c r="BC62" s="961" t="n"/>
+      <c r="BD62" s="961" t="n"/>
+      <c r="BE62" s="961" t="n"/>
+      <c r="BF62" s="961" t="n"/>
+      <c r="BG62" s="961" t="n"/>
+      <c r="BH62" s="961" t="n"/>
+      <c r="BI62" s="961" t="n"/>
+      <c r="BJ62" s="961" t="n"/>
+      <c r="BK62" s="961" t="n"/>
+      <c r="BL62" s="961" t="n"/>
+      <c r="BM62" s="961" t="n"/>
+      <c r="BN62" s="961" t="n"/>
+      <c r="BO62" s="961" t="n"/>
+      <c r="BP62" s="961" t="n"/>
+      <c r="BQ62" s="961" t="n"/>
+      <c r="BR62" s="961" t="n"/>
+      <c r="BS62" s="961" t="n"/>
+      <c r="BT62" s="961" t="n"/>
+      <c r="BU62" s="961" t="n"/>
+      <c r="BV62" s="961" t="n"/>
+      <c r="BW62" s="961" t="n"/>
+      <c r="BX62" s="961" t="n"/>
+      <c r="BY62" s="961" t="n"/>
+      <c r="BZ62" s="961" t="n"/>
+      <c r="CA62" s="961" t="n"/>
+      <c r="CB62" s="961" t="n"/>
+      <c r="CC62" s="961" t="n"/>
+      <c r="CD62" s="961" t="n"/>
+      <c r="CE62" s="961" t="n"/>
+      <c r="CF62" s="961" t="n"/>
+      <c r="CG62" s="961" t="n"/>
+      <c r="CH62" s="961" t="n"/>
+      <c r="CI62" s="961" t="n"/>
+      <c r="CJ62" s="961" t="n"/>
+      <c r="CK62" s="961" t="n"/>
+      <c r="CL62" s="961" t="n"/>
+      <c r="CM62" s="961" t="n"/>
+      <c r="CN62" s="961" t="n"/>
+      <c r="CO62" s="961" t="n"/>
+      <c r="CP62" s="961" t="n"/>
+      <c r="CQ62" s="961" t="n"/>
+      <c r="CR62" s="961" t="n"/>
+      <c r="CS62" s="959" t="n"/>
+      <c r="CT62" s="1022" t="n"/>
+      <c r="CU62" s="1022" t="n"/>
+      <c r="CV62" s="1022" t="n"/>
+      <c r="CW62" s="1022" t="n"/>
+      <c r="CX62" s="1024" t="n"/>
+      <c r="CY62" s="1022" t="n"/>
+    </row>
+    <row r="63" ht="11.1" customHeight="1" s="710">
+      <c r="A63" s="1022" t="n"/>
+      <c r="B63" s="1023" t="n"/>
+      <c r="C63" s="1022" t="n"/>
+      <c r="D63" s="1022" t="n"/>
+      <c r="E63" s="1057" t="inlineStr">
+        <is>
+          <t>OLD_VALUE</t>
+        </is>
+      </c>
+      <c r="F63" s="957" t="n"/>
+      <c r="G63" s="957" t="n"/>
+      <c r="H63" s="957" t="n"/>
+      <c r="I63" s="957" t="n"/>
+      <c r="J63" s="957" t="n"/>
+      <c r="K63" s="957" t="n"/>
+      <c r="L63" s="957" t="n"/>
+      <c r="M63" s="957" t="n"/>
+      <c r="N63" s="957" t="n"/>
+      <c r="O63" s="957" t="n"/>
+      <c r="P63" s="957" t="n"/>
+      <c r="Q63" s="957" t="n"/>
+      <c r="R63" s="957" t="n"/>
+      <c r="S63" s="957" t="n"/>
+      <c r="T63" s="955" t="n"/>
+      <c r="U63" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="V63" s="957" t="n"/>
+      <c r="W63" s="957" t="n"/>
+      <c r="X63" s="957" t="n"/>
+      <c r="Y63" s="957" t="n"/>
+      <c r="Z63" s="957" t="n"/>
+      <c r="AA63" s="957" t="n"/>
+      <c r="AB63" s="957" t="n"/>
+      <c r="AC63" s="957" t="n"/>
+      <c r="AD63" s="957" t="n"/>
+      <c r="AE63" s="957" t="n"/>
+      <c r="AF63" s="955" t="n"/>
+      <c r="AG63" s="1058" t="n"/>
+      <c r="AH63" s="957" t="n"/>
+      <c r="AI63" s="955" t="n"/>
+      <c r="AJ63" s="1058" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AK63" s="957" t="n"/>
+      <c r="AL63" s="957" t="n"/>
+      <c r="AM63" s="955" t="n"/>
+      <c r="AN63" s="1057" t="inlineStr">
+        <is>
+          <t>Value before the change; NULL for ADD or an added destination</t>
+        </is>
+      </c>
+      <c r="AO63" s="957" t="n"/>
+      <c r="AP63" s="957" t="n"/>
+      <c r="AQ63" s="957" t="n"/>
+      <c r="AR63" s="957" t="n"/>
+      <c r="AS63" s="957" t="n"/>
+      <c r="AT63" s="957" t="n"/>
+      <c r="AU63" s="957" t="n"/>
+      <c r="AV63" s="957" t="n"/>
+      <c r="AW63" s="957" t="n"/>
+      <c r="AX63" s="957" t="n"/>
+      <c r="AY63" s="957" t="n"/>
+      <c r="AZ63" s="957" t="n"/>
+      <c r="BA63" s="957" t="n"/>
+      <c r="BB63" s="957" t="n"/>
+      <c r="BC63" s="957" t="n"/>
+      <c r="BD63" s="957" t="n"/>
+      <c r="BE63" s="957" t="n"/>
+      <c r="BF63" s="957" t="n"/>
+      <c r="BG63" s="957" t="n"/>
+      <c r="BH63" s="957" t="n"/>
+      <c r="BI63" s="957" t="n"/>
+      <c r="BJ63" s="957" t="n"/>
+      <c r="BK63" s="957" t="n"/>
+      <c r="BL63" s="957" t="n"/>
+      <c r="BM63" s="957" t="n"/>
+      <c r="BN63" s="957" t="n"/>
+      <c r="BO63" s="957" t="n"/>
+      <c r="BP63" s="957" t="n"/>
+      <c r="BQ63" s="957" t="n"/>
+      <c r="BR63" s="957" t="n"/>
+      <c r="BS63" s="957" t="n"/>
+      <c r="BT63" s="957" t="n"/>
+      <c r="BU63" s="957" t="n"/>
+      <c r="BV63" s="957" t="n"/>
+      <c r="BW63" s="957" t="n"/>
+      <c r="BX63" s="957" t="n"/>
+      <c r="BY63" s="957" t="n"/>
+      <c r="BZ63" s="957" t="n"/>
+      <c r="CA63" s="957" t="n"/>
+      <c r="CB63" s="957" t="n"/>
+      <c r="CC63" s="957" t="n"/>
+      <c r="CD63" s="957" t="n"/>
+      <c r="CE63" s="957" t="n"/>
+      <c r="CF63" s="957" t="n"/>
+      <c r="CG63" s="957" t="n"/>
+      <c r="CH63" s="957" t="n"/>
+      <c r="CI63" s="957" t="n"/>
+      <c r="CJ63" s="957" t="n"/>
+      <c r="CK63" s="957" t="n"/>
+      <c r="CL63" s="957" t="n"/>
+      <c r="CM63" s="957" t="n"/>
+      <c r="CN63" s="957" t="n"/>
+      <c r="CO63" s="957" t="n"/>
+      <c r="CP63" s="957" t="n"/>
+      <c r="CQ63" s="957" t="n"/>
+      <c r="CR63" s="957" t="n"/>
+      <c r="CS63" s="955" t="n"/>
+      <c r="CT63" s="1022" t="n"/>
+      <c r="CU63" s="1022" t="n"/>
+      <c r="CV63" s="1022" t="n"/>
+      <c r="CW63" s="1022" t="n"/>
+      <c r="CX63" s="1024" t="n"/>
+      <c r="CY63" s="1022" t="n"/>
+    </row>
+    <row r="64" ht="11.1" customHeight="1" s="710">
+      <c r="A64" s="1022" t="n"/>
+      <c r="B64" s="1023" t="n"/>
+      <c r="C64" s="1022" t="n"/>
+      <c r="D64" s="1022" t="n"/>
+      <c r="E64" s="1057" t="inlineStr">
+        <is>
+          <t>NEW_VALUE</t>
+        </is>
+      </c>
+      <c r="F64" s="957" t="n"/>
+      <c r="G64" s="957" t="n"/>
+      <c r="H64" s="957" t="n"/>
+      <c r="I64" s="957" t="n"/>
+      <c r="J64" s="957" t="n"/>
+      <c r="K64" s="957" t="n"/>
+      <c r="L64" s="957" t="n"/>
+      <c r="M64" s="957" t="n"/>
+      <c r="N64" s="957" t="n"/>
+      <c r="O64" s="957" t="n"/>
+      <c r="P64" s="957" t="n"/>
+      <c r="Q64" s="957" t="n"/>
+      <c r="R64" s="957" t="n"/>
+      <c r="S64" s="957" t="n"/>
+      <c r="T64" s="955" t="n"/>
+      <c r="U64" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="V64" s="957" t="n"/>
+      <c r="W64" s="957" t="n"/>
+      <c r="X64" s="957" t="n"/>
+      <c r="Y64" s="957" t="n"/>
+      <c r="Z64" s="957" t="n"/>
+      <c r="AA64" s="957" t="n"/>
+      <c r="AB64" s="957" t="n"/>
+      <c r="AC64" s="957" t="n"/>
+      <c r="AD64" s="957" t="n"/>
+      <c r="AE64" s="957" t="n"/>
+      <c r="AF64" s="955" t="n"/>
+      <c r="AG64" s="1058" t="n"/>
+      <c r="AH64" s="957" t="n"/>
+      <c r="AI64" s="955" t="n"/>
+      <c r="AJ64" s="1058" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AK64" s="957" t="n"/>
+      <c r="AL64" s="957" t="n"/>
+      <c r="AM64" s="955" t="n"/>
+      <c r="AN64" s="1057" t="inlineStr">
+        <is>
+          <t>Value after the change; NULL for a removed destination</t>
+        </is>
+      </c>
+      <c r="AO64" s="957" t="n"/>
+      <c r="AP64" s="957" t="n"/>
+      <c r="AQ64" s="957" t="n"/>
+      <c r="AR64" s="957" t="n"/>
+      <c r="AS64" s="957" t="n"/>
+      <c r="AT64" s="957" t="n"/>
+      <c r="AU64" s="957" t="n"/>
+      <c r="AV64" s="957" t="n"/>
+      <c r="AW64" s="957" t="n"/>
+      <c r="AX64" s="957" t="n"/>
+      <c r="AY64" s="957" t="n"/>
+      <c r="AZ64" s="957" t="n"/>
+      <c r="BA64" s="957" t="n"/>
+      <c r="BB64" s="957" t="n"/>
+      <c r="BC64" s="957" t="n"/>
+      <c r="BD64" s="957" t="n"/>
+      <c r="BE64" s="957" t="n"/>
+      <c r="BF64" s="957" t="n"/>
+      <c r="BG64" s="957" t="n"/>
+      <c r="BH64" s="957" t="n"/>
+      <c r="BI64" s="957" t="n"/>
+      <c r="BJ64" s="957" t="n"/>
+      <c r="BK64" s="957" t="n"/>
+      <c r="BL64" s="957" t="n"/>
+      <c r="BM64" s="957" t="n"/>
+      <c r="BN64" s="957" t="n"/>
+      <c r="BO64" s="957" t="n"/>
+      <c r="BP64" s="957" t="n"/>
+      <c r="BQ64" s="957" t="n"/>
+      <c r="BR64" s="957" t="n"/>
+      <c r="BS64" s="957" t="n"/>
+      <c r="BT64" s="957" t="n"/>
+      <c r="BU64" s="957" t="n"/>
+      <c r="BV64" s="957" t="n"/>
+      <c r="BW64" s="957" t="n"/>
+      <c r="BX64" s="957" t="n"/>
+      <c r="BY64" s="957" t="n"/>
+      <c r="BZ64" s="957" t="n"/>
+      <c r="CA64" s="957" t="n"/>
+      <c r="CB64" s="957" t="n"/>
+      <c r="CC64" s="957" t="n"/>
+      <c r="CD64" s="957" t="n"/>
+      <c r="CE64" s="957" t="n"/>
+      <c r="CF64" s="957" t="n"/>
+      <c r="CG64" s="957" t="n"/>
+      <c r="CH64" s="957" t="n"/>
+      <c r="CI64" s="957" t="n"/>
+      <c r="CJ64" s="957" t="n"/>
+      <c r="CK64" s="957" t="n"/>
+      <c r="CL64" s="957" t="n"/>
+      <c r="CM64" s="957" t="n"/>
+      <c r="CN64" s="957" t="n"/>
+      <c r="CO64" s="957" t="n"/>
+      <c r="CP64" s="957" t="n"/>
+      <c r="CQ64" s="957" t="n"/>
+      <c r="CR64" s="957" t="n"/>
+      <c r="CS64" s="955" t="n"/>
+      <c r="CT64" s="1022" t="n"/>
+      <c r="CU64" s="1022" t="n"/>
+      <c r="CV64" s="1022" t="n"/>
+      <c r="CW64" s="1022" t="n"/>
+      <c r="CX64" s="1024" t="n"/>
+      <c r="CY64" s="1022" t="n"/>
+    </row>
+    <row r="65" ht="11.1" customHeight="1" s="710">
+      <c r="A65" s="1022" t="n"/>
+      <c r="B65" s="1023" t="n"/>
+      <c r="C65" s="1022" t="n"/>
+      <c r="D65" s="1022" t="n"/>
+      <c r="E65" s="1057" t="inlineStr">
+        <is>
+          <t>REMARK</t>
+        </is>
+      </c>
+      <c r="F65" s="957" t="n"/>
+      <c r="G65" s="957" t="n"/>
+      <c r="H65" s="957" t="n"/>
+      <c r="I65" s="957" t="n"/>
+      <c r="J65" s="957" t="n"/>
+      <c r="K65" s="957" t="n"/>
+      <c r="L65" s="957" t="n"/>
+      <c r="M65" s="957" t="n"/>
+      <c r="N65" s="957" t="n"/>
+      <c r="O65" s="957" t="n"/>
+      <c r="P65" s="957" t="n"/>
+      <c r="Q65" s="957" t="n"/>
+      <c r="R65" s="957" t="n"/>
+      <c r="S65" s="957" t="n"/>
+      <c r="T65" s="955" t="n"/>
+      <c r="U65" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="V65" s="957" t="n"/>
+      <c r="W65" s="957" t="n"/>
+      <c r="X65" s="957" t="n"/>
+      <c r="Y65" s="957" t="n"/>
+      <c r="Z65" s="957" t="n"/>
+      <c r="AA65" s="957" t="n"/>
+      <c r="AB65" s="957" t="n"/>
+      <c r="AC65" s="957" t="n"/>
+      <c r="AD65" s="957" t="n"/>
+      <c r="AE65" s="957" t="n"/>
+      <c r="AF65" s="955" t="n"/>
+      <c r="AG65" s="1058" t="n"/>
+      <c r="AH65" s="957" t="n"/>
+      <c r="AI65" s="955" t="n"/>
+      <c r="AJ65" s="1058" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AK65" s="957" t="n"/>
+      <c r="AL65" s="957" t="n"/>
+      <c r="AM65" s="955" t="n"/>
+      <c r="AN65" s="1057" t="inlineStr">
+        <is>
+          <t>Free text, e.g. SYNC_MESSAGE of a Failed sync</t>
+        </is>
+      </c>
+      <c r="AO65" s="957" t="n"/>
+      <c r="AP65" s="957" t="n"/>
+      <c r="AQ65" s="957" t="n"/>
+      <c r="AR65" s="957" t="n"/>
+      <c r="AS65" s="957" t="n"/>
+      <c r="AT65" s="957" t="n"/>
+      <c r="AU65" s="957" t="n"/>
+      <c r="AV65" s="957" t="n"/>
+      <c r="AW65" s="957" t="n"/>
+      <c r="AX65" s="957" t="n"/>
+      <c r="AY65" s="957" t="n"/>
+      <c r="AZ65" s="957" t="n"/>
+      <c r="BA65" s="957" t="n"/>
+      <c r="BB65" s="957" t="n"/>
+      <c r="BC65" s="957" t="n"/>
+      <c r="BD65" s="957" t="n"/>
+      <c r="BE65" s="957" t="n"/>
+      <c r="BF65" s="957" t="n"/>
+      <c r="BG65" s="957" t="n"/>
+      <c r="BH65" s="957" t="n"/>
+      <c r="BI65" s="957" t="n"/>
+      <c r="BJ65" s="957" t="n"/>
+      <c r="BK65" s="957" t="n"/>
+      <c r="BL65" s="957" t="n"/>
+      <c r="BM65" s="957" t="n"/>
+      <c r="BN65" s="957" t="n"/>
+      <c r="BO65" s="957" t="n"/>
+      <c r="BP65" s="957" t="n"/>
+      <c r="BQ65" s="957" t="n"/>
+      <c r="BR65" s="957" t="n"/>
+      <c r="BS65" s="957" t="n"/>
+      <c r="BT65" s="957" t="n"/>
+      <c r="BU65" s="957" t="n"/>
+      <c r="BV65" s="957" t="n"/>
+      <c r="BW65" s="957" t="n"/>
+      <c r="BX65" s="957" t="n"/>
+      <c r="BY65" s="957" t="n"/>
+      <c r="BZ65" s="957" t="n"/>
+      <c r="CA65" s="957" t="n"/>
+      <c r="CB65" s="957" t="n"/>
+      <c r="CC65" s="957" t="n"/>
+      <c r="CD65" s="957" t="n"/>
+      <c r="CE65" s="957" t="n"/>
+      <c r="CF65" s="957" t="n"/>
+      <c r="CG65" s="957" t="n"/>
+      <c r="CH65" s="957" t="n"/>
+      <c r="CI65" s="957" t="n"/>
+      <c r="CJ65" s="957" t="n"/>
+      <c r="CK65" s="957" t="n"/>
+      <c r="CL65" s="957" t="n"/>
+      <c r="CM65" s="957" t="n"/>
+      <c r="CN65" s="957" t="n"/>
+      <c r="CO65" s="957" t="n"/>
+      <c r="CP65" s="957" t="n"/>
+      <c r="CQ65" s="957" t="n"/>
+      <c r="CR65" s="957" t="n"/>
+      <c r="CS65" s="955" t="n"/>
+      <c r="CT65" s="1022" t="n"/>
+      <c r="CU65" s="1022" t="n"/>
+      <c r="CV65" s="1022" t="n"/>
+      <c r="CW65" s="1022" t="n"/>
+      <c r="CX65" s="1024" t="n"/>
+      <c r="CY65" s="1022" t="n"/>
+    </row>
+    <row r="66" ht="11.1" customHeight="1" s="710">
+      <c r="A66" s="1022" t="n"/>
+      <c r="B66" s="1023" t="n"/>
+      <c r="C66" s="1022" t="n"/>
+      <c r="D66" s="1022" t="n"/>
+      <c r="E66" s="1057" t="inlineStr">
+        <is>
+          <t>CREATED_BY</t>
+        </is>
+      </c>
+      <c r="F66" s="957" t="n"/>
+      <c r="G66" s="957" t="n"/>
+      <c r="H66" s="957" t="n"/>
+      <c r="I66" s="957" t="n"/>
+      <c r="J66" s="957" t="n"/>
+      <c r="K66" s="957" t="n"/>
+      <c r="L66" s="957" t="n"/>
+      <c r="M66" s="957" t="n"/>
+      <c r="N66" s="957" t="n"/>
+      <c r="O66" s="957" t="n"/>
+      <c r="P66" s="957" t="n"/>
+      <c r="Q66" s="957" t="n"/>
+      <c r="R66" s="957" t="n"/>
+      <c r="S66" s="957" t="n"/>
+      <c r="T66" s="955" t="n"/>
+      <c r="U66" s="1057" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="V66" s="957" t="n"/>
+      <c r="W66" s="957" t="n"/>
+      <c r="X66" s="957" t="n"/>
+      <c r="Y66" s="957" t="n"/>
+      <c r="Z66" s="957" t="n"/>
+      <c r="AA66" s="957" t="n"/>
+      <c r="AB66" s="957" t="n"/>
+      <c r="AC66" s="957" t="n"/>
+      <c r="AD66" s="957" t="n"/>
+      <c r="AE66" s="957" t="n"/>
+      <c r="AF66" s="955" t="n"/>
+      <c r="AG66" s="1058" t="n"/>
+      <c r="AH66" s="957" t="n"/>
+      <c r="AI66" s="955" t="n"/>
+      <c r="AJ66" s="1058" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK66" s="957" t="n"/>
+      <c r="AL66" s="957" t="n"/>
+      <c r="AM66" s="955" t="n"/>
+      <c r="AN66" s="1057" t="inlineStr">
+        <is>
+          <t>User who made the change (RPA user ID for SYNC)</t>
+        </is>
+      </c>
+      <c r="AO66" s="957" t="n"/>
+      <c r="AP66" s="957" t="n"/>
+      <c r="AQ66" s="957" t="n"/>
+      <c r="AR66" s="957" t="n"/>
+      <c r="AS66" s="957" t="n"/>
+      <c r="AT66" s="957" t="n"/>
+      <c r="AU66" s="957" t="n"/>
+      <c r="AV66" s="957" t="n"/>
+      <c r="AW66" s="957" t="n"/>
+      <c r="AX66" s="957" t="n"/>
+      <c r="AY66" s="957" t="n"/>
+      <c r="AZ66" s="957" t="n"/>
+      <c r="BA66" s="957" t="n"/>
+      <c r="BB66" s="957" t="n"/>
+      <c r="BC66" s="957" t="n"/>
+      <c r="BD66" s="957" t="n"/>
+      <c r="BE66" s="957" t="n"/>
+      <c r="BF66" s="957" t="n"/>
+      <c r="BG66" s="957" t="n"/>
+      <c r="BH66" s="957" t="n"/>
+      <c r="BI66" s="957" t="n"/>
+      <c r="BJ66" s="957" t="n"/>
+      <c r="BK66" s="957" t="n"/>
+      <c r="BL66" s="957" t="n"/>
+      <c r="BM66" s="957" t="n"/>
+      <c r="BN66" s="957" t="n"/>
+      <c r="BO66" s="957" t="n"/>
+      <c r="BP66" s="957" t="n"/>
+      <c r="BQ66" s="957" t="n"/>
+      <c r="BR66" s="957" t="n"/>
+      <c r="BS66" s="957" t="n"/>
+      <c r="BT66" s="957" t="n"/>
+      <c r="BU66" s="957" t="n"/>
+      <c r="BV66" s="957" t="n"/>
+      <c r="BW66" s="957" t="n"/>
+      <c r="BX66" s="957" t="n"/>
+      <c r="BY66" s="957" t="n"/>
+      <c r="BZ66" s="957" t="n"/>
+      <c r="CA66" s="957" t="n"/>
+      <c r="CB66" s="957" t="n"/>
+      <c r="CC66" s="957" t="n"/>
+      <c r="CD66" s="957" t="n"/>
+      <c r="CE66" s="957" t="n"/>
+      <c r="CF66" s="957" t="n"/>
+      <c r="CG66" s="957" t="n"/>
+      <c r="CH66" s="957" t="n"/>
+      <c r="CI66" s="957" t="n"/>
+      <c r="CJ66" s="957" t="n"/>
+      <c r="CK66" s="957" t="n"/>
+      <c r="CL66" s="957" t="n"/>
+      <c r="CM66" s="957" t="n"/>
+      <c r="CN66" s="957" t="n"/>
+      <c r="CO66" s="957" t="n"/>
+      <c r="CP66" s="957" t="n"/>
+      <c r="CQ66" s="957" t="n"/>
+      <c r="CR66" s="957" t="n"/>
+      <c r="CS66" s="955" t="n"/>
+      <c r="CT66" s="1022" t="n"/>
+      <c r="CU66" s="1022" t="n"/>
+      <c r="CV66" s="1022" t="n"/>
+      <c r="CW66" s="1022" t="n"/>
+      <c r="CX66" s="1024" t="n"/>
+      <c r="CY66" s="1022" t="n"/>
+    </row>
+    <row r="67" ht="11.1" customHeight="1" s="710">
+      <c r="A67" s="1022" t="n"/>
+      <c r="B67" s="1023" t="n"/>
+      <c r="C67" s="1022" t="n"/>
+      <c r="D67" s="1022" t="n"/>
+      <c r="E67" s="1061" t="inlineStr">
+        <is>
+          <t>CREATED_DT</t>
+        </is>
+      </c>
+      <c r="F67" s="986" t="n"/>
+      <c r="G67" s="986" t="n"/>
+      <c r="H67" s="986" t="n"/>
+      <c r="I67" s="986" t="n"/>
+      <c r="J67" s="986" t="n"/>
+      <c r="K67" s="986" t="n"/>
+      <c r="L67" s="986" t="n"/>
+      <c r="M67" s="986" t="n"/>
+      <c r="N67" s="986" t="n"/>
+      <c r="O67" s="986" t="n"/>
+      <c r="P67" s="986" t="n"/>
+      <c r="Q67" s="986" t="n"/>
+      <c r="R67" s="986" t="n"/>
+      <c r="S67" s="986" t="n"/>
+      <c r="T67" s="987" t="n"/>
+      <c r="U67" s="1061" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="V67" s="986" t="n"/>
+      <c r="W67" s="986" t="n"/>
+      <c r="X67" s="986" t="n"/>
+      <c r="Y67" s="986" t="n"/>
+      <c r="Z67" s="986" t="n"/>
+      <c r="AA67" s="986" t="n"/>
+      <c r="AB67" s="986" t="n"/>
+      <c r="AC67" s="986" t="n"/>
+      <c r="AD67" s="986" t="n"/>
+      <c r="AE67" s="986" t="n"/>
+      <c r="AF67" s="987" t="n"/>
+      <c r="AG67" s="1062" t="n"/>
+      <c r="AH67" s="986" t="n"/>
+      <c r="AI67" s="987" t="n"/>
+      <c r="AJ67" s="1062" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK67" s="986" t="n"/>
+      <c r="AL67" s="986" t="n"/>
+      <c r="AM67" s="987" t="n"/>
+      <c r="AN67" s="1061" t="inlineStr">
+        <is>
+          <t>Date and time of the change</t>
+        </is>
+      </c>
+      <c r="AO67" s="986" t="n"/>
+      <c r="AP67" s="986" t="n"/>
+      <c r="AQ67" s="986" t="n"/>
+      <c r="AR67" s="986" t="n"/>
+      <c r="AS67" s="986" t="n"/>
+      <c r="AT67" s="986" t="n"/>
+      <c r="AU67" s="986" t="n"/>
+      <c r="AV67" s="986" t="n"/>
+      <c r="AW67" s="986" t="n"/>
+      <c r="AX67" s="986" t="n"/>
+      <c r="AY67" s="986" t="n"/>
+      <c r="AZ67" s="986" t="n"/>
+      <c r="BA67" s="986" t="n"/>
+      <c r="BB67" s="986" t="n"/>
+      <c r="BC67" s="986" t="n"/>
+      <c r="BD67" s="986" t="n"/>
+      <c r="BE67" s="986" t="n"/>
+      <c r="BF67" s="986" t="n"/>
+      <c r="BG67" s="986" t="n"/>
+      <c r="BH67" s="986" t="n"/>
+      <c r="BI67" s="986" t="n"/>
+      <c r="BJ67" s="986" t="n"/>
+      <c r="BK67" s="986" t="n"/>
+      <c r="BL67" s="986" t="n"/>
+      <c r="BM67" s="986" t="n"/>
+      <c r="BN67" s="986" t="n"/>
+      <c r="BO67" s="986" t="n"/>
+      <c r="BP67" s="986" t="n"/>
+      <c r="BQ67" s="986" t="n"/>
+      <c r="BR67" s="986" t="n"/>
+      <c r="BS67" s="986" t="n"/>
+      <c r="BT67" s="986" t="n"/>
+      <c r="BU67" s="986" t="n"/>
+      <c r="BV67" s="986" t="n"/>
+      <c r="BW67" s="986" t="n"/>
+      <c r="BX67" s="986" t="n"/>
+      <c r="BY67" s="986" t="n"/>
+      <c r="BZ67" s="986" t="n"/>
+      <c r="CA67" s="986" t="n"/>
+      <c r="CB67" s="986" t="n"/>
+      <c r="CC67" s="986" t="n"/>
+      <c r="CD67" s="986" t="n"/>
+      <c r="CE67" s="986" t="n"/>
+      <c r="CF67" s="986" t="n"/>
+      <c r="CG67" s="986" t="n"/>
+      <c r="CH67" s="986" t="n"/>
+      <c r="CI67" s="986" t="n"/>
+      <c r="CJ67" s="986" t="n"/>
+      <c r="CK67" s="986" t="n"/>
+      <c r="CL67" s="986" t="n"/>
+      <c r="CM67" s="986" t="n"/>
+      <c r="CN67" s="986" t="n"/>
+      <c r="CO67" s="986" t="n"/>
+      <c r="CP67" s="986" t="n"/>
+      <c r="CQ67" s="986" t="n"/>
+      <c r="CR67" s="986" t="n"/>
+      <c r="CS67" s="987" t="n"/>
+      <c r="CT67" s="1022" t="n"/>
+      <c r="CU67" s="1022" t="n"/>
+      <c r="CV67" s="1022" t="n"/>
+      <c r="CW67" s="1022" t="n"/>
+      <c r="CX67" s="1024" t="n"/>
+      <c r="CY67" s="1022" t="n"/>
+    </row>
+    <row r="68" ht="11.1" customHeight="1" s="710">
+      <c r="A68" s="1022" t="n"/>
+      <c r="B68" s="1023" t="n"/>
+      <c r="C68" s="1022" t="n"/>
+      <c r="D68" s="1022" t="n"/>
+      <c r="E68" s="1022" t="n"/>
+      <c r="F68" s="1022" t="n"/>
+      <c r="G68" s="1022" t="n"/>
+      <c r="H68" s="1022" t="n"/>
+      <c r="I68" s="1022" t="n"/>
+      <c r="J68" s="1022" t="n"/>
+      <c r="K68" s="1022" t="n"/>
+      <c r="L68" s="1022" t="n"/>
+      <c r="M68" s="1022" t="n"/>
+      <c r="N68" s="1022" t="n"/>
+      <c r="O68" s="1022" t="n"/>
+      <c r="P68" s="1022" t="n"/>
+      <c r="Q68" s="1022" t="n"/>
+      <c r="R68" s="1022" t="n"/>
+      <c r="S68" s="1022" t="n"/>
+      <c r="T68" s="1022" t="n"/>
+      <c r="U68" s="1022" t="n"/>
+      <c r="V68" s="1022" t="n"/>
+      <c r="W68" s="1022" t="n"/>
+      <c r="X68" s="1022" t="n"/>
+      <c r="Y68" s="1022" t="n"/>
+      <c r="Z68" s="1022" t="n"/>
+      <c r="AA68" s="1022" t="n"/>
+      <c r="AB68" s="1022" t="n"/>
+      <c r="AC68" s="1022" t="n"/>
+      <c r="AD68" s="1022" t="n"/>
+      <c r="AE68" s="1022" t="n"/>
+      <c r="AF68" s="1022" t="n"/>
+      <c r="AG68" s="1022" t="n"/>
+      <c r="AH68" s="1022" t="n"/>
+      <c r="AI68" s="1022" t="n"/>
+      <c r="AJ68" s="1022" t="n"/>
+      <c r="AK68" s="1022" t="n"/>
+      <c r="AL68" s="1022" t="n"/>
+      <c r="AM68" s="1022" t="n"/>
+      <c r="AN68" s="1022" t="n"/>
+      <c r="AO68" s="1022" t="n"/>
+      <c r="AP68" s="1022" t="n"/>
+      <c r="AQ68" s="1022" t="n"/>
+      <c r="AR68" s="1022" t="n"/>
+      <c r="AS68" s="1022" t="n"/>
+      <c r="AT68" s="1022" t="n"/>
+      <c r="AU68" s="1022" t="n"/>
+      <c r="AV68" s="1022" t="n"/>
+      <c r="AW68" s="1022" t="n"/>
+      <c r="AX68" s="1022" t="n"/>
+      <c r="AY68" s="1022" t="n"/>
+      <c r="AZ68" s="1022" t="n"/>
+      <c r="BA68" s="1022" t="n"/>
+      <c r="BB68" s="1022" t="n"/>
+      <c r="BC68" s="1022" t="n"/>
+      <c r="BD68" s="1022" t="n"/>
+      <c r="BE68" s="1022" t="n"/>
+      <c r="BF68" s="1022" t="n"/>
+      <c r="BG68" s="1022" t="n"/>
+      <c r="BH68" s="1022" t="n"/>
+      <c r="BI68" s="1022" t="n"/>
+      <c r="BJ68" s="1022" t="n"/>
+      <c r="BK68" s="1022" t="n"/>
+      <c r="BL68" s="1022" t="n"/>
+      <c r="BM68" s="1022" t="n"/>
+      <c r="BN68" s="1022" t="n"/>
+      <c r="BO68" s="1022" t="n"/>
+      <c r="BP68" s="1022" t="n"/>
+      <c r="BQ68" s="1022" t="n"/>
+      <c r="BR68" s="1022" t="n"/>
+      <c r="BS68" s="1022" t="n"/>
+      <c r="BT68" s="1022" t="n"/>
+      <c r="BU68" s="1022" t="n"/>
+      <c r="BV68" s="1022" t="n"/>
+      <c r="BW68" s="1022" t="n"/>
+      <c r="BX68" s="1022" t="n"/>
+      <c r="BY68" s="1022" t="n"/>
+      <c r="BZ68" s="1022" t="n"/>
+      <c r="CA68" s="1022" t="n"/>
+      <c r="CB68" s="1022" t="n"/>
+      <c r="CC68" s="1022" t="n"/>
+      <c r="CD68" s="1022" t="n"/>
+      <c r="CE68" s="1022" t="n"/>
+      <c r="CF68" s="1022" t="n"/>
+      <c r="CG68" s="1022" t="n"/>
+      <c r="CH68" s="1022" t="n"/>
+      <c r="CI68" s="1022" t="n"/>
+      <c r="CJ68" s="1022" t="n"/>
+      <c r="CK68" s="1022" t="n"/>
+      <c r="CL68" s="1022" t="n"/>
+      <c r="CM68" s="1022" t="n"/>
+      <c r="CN68" s="1022" t="n"/>
+      <c r="CO68" s="1022" t="n"/>
+      <c r="CP68" s="1022" t="n"/>
+      <c r="CQ68" s="1022" t="n"/>
+      <c r="CR68" s="1022" t="n"/>
+      <c r="CS68" s="1022" t="n"/>
+      <c r="CT68" s="1022" t="n"/>
+      <c r="CU68" s="1022" t="n"/>
+      <c r="CV68" s="1022" t="n"/>
+      <c r="CW68" s="1022" t="n"/>
+      <c r="CX68" s="1024" t="n"/>
+      <c r="CY68" s="1022" t="n"/>
+    </row>
+    <row r="69" ht="11.1" customHeight="1" s="710">
+      <c r="A69" s="1022" t="n"/>
+      <c r="B69" s="1023" t="n"/>
+      <c r="C69" s="1022" t="n"/>
+      <c r="D69" s="1022" t="n"/>
+      <c r="E69" s="1022" t="n"/>
+      <c r="F69" s="1022" t="n"/>
+      <c r="G69" s="1022" t="n"/>
+      <c r="H69" s="1022" t="n"/>
+      <c r="I69" s="1022" t="n"/>
+      <c r="J69" s="1022" t="n"/>
+      <c r="K69" s="1022" t="n"/>
+      <c r="L69" s="1022" t="n"/>
+      <c r="M69" s="1022" t="n"/>
+      <c r="N69" s="1022" t="n"/>
+      <c r="O69" s="1022" t="n"/>
+      <c r="P69" s="1022" t="n"/>
+      <c r="Q69" s="1022" t="n"/>
+      <c r="R69" s="1022" t="n"/>
+      <c r="S69" s="1022" t="n"/>
+      <c r="T69" s="1022" t="n"/>
+      <c r="U69" s="1022" t="n"/>
+      <c r="V69" s="1022" t="n"/>
+      <c r="W69" s="1022" t="n"/>
+      <c r="X69" s="1022" t="n"/>
+      <c r="Y69" s="1022" t="n"/>
+      <c r="Z69" s="1022" t="n"/>
+      <c r="AA69" s="1022" t="n"/>
+      <c r="AB69" s="1022" t="n"/>
+      <c r="AC69" s="1022" t="n"/>
+      <c r="AD69" s="1022" t="n"/>
+      <c r="AE69" s="1022" t="n"/>
+      <c r="AF69" s="1022" t="n"/>
+      <c r="AG69" s="1022" t="n"/>
+      <c r="AH69" s="1022" t="n"/>
+      <c r="AI69" s="1022" t="n"/>
+      <c r="AJ69" s="1022" t="n"/>
+      <c r="AK69" s="1022" t="n"/>
+      <c r="AL69" s="1022" t="n"/>
+      <c r="AM69" s="1022" t="n"/>
+      <c r="AN69" s="1022" t="n"/>
+      <c r="AO69" s="1022" t="n"/>
+      <c r="AP69" s="1022" t="n"/>
+      <c r="AQ69" s="1022" t="n"/>
+      <c r="AR69" s="1022" t="n"/>
+      <c r="AS69" s="1022" t="n"/>
+      <c r="AT69" s="1022" t="n"/>
+      <c r="AU69" s="1022" t="n"/>
+      <c r="AV69" s="1022" t="n"/>
+      <c r="AW69" s="1022" t="n"/>
+      <c r="AX69" s="1022" t="n"/>
+      <c r="AY69" s="1022" t="n"/>
+      <c r="AZ69" s="1022" t="n"/>
+      <c r="BA69" s="1022" t="n"/>
+      <c r="BB69" s="1022" t="n"/>
+      <c r="BC69" s="1022" t="n"/>
+      <c r="BD69" s="1022" t="n"/>
+      <c r="BE69" s="1022" t="n"/>
+      <c r="BF69" s="1022" t="n"/>
+      <c r="BG69" s="1022" t="n"/>
+      <c r="BH69" s="1022" t="n"/>
+      <c r="BI69" s="1022" t="n"/>
+      <c r="BJ69" s="1022" t="n"/>
+      <c r="BK69" s="1022" t="n"/>
+      <c r="BL69" s="1022" t="n"/>
+      <c r="BM69" s="1022" t="n"/>
+      <c r="BN69" s="1022" t="n"/>
+      <c r="BO69" s="1022" t="n"/>
+      <c r="BP69" s="1022" t="n"/>
+      <c r="BQ69" s="1022" t="n"/>
+      <c r="BR69" s="1022" t="n"/>
+      <c r="BS69" s="1022" t="n"/>
+      <c r="BT69" s="1022" t="n"/>
+      <c r="BU69" s="1022" t="n"/>
+      <c r="BV69" s="1022" t="n"/>
+      <c r="BW69" s="1022" t="n"/>
+      <c r="BX69" s="1022" t="n"/>
+      <c r="BY69" s="1022" t="n"/>
+      <c r="BZ69" s="1022" t="n"/>
+      <c r="CA69" s="1022" t="n"/>
+      <c r="CB69" s="1022" t="n"/>
+      <c r="CC69" s="1022" t="n"/>
+      <c r="CD69" s="1022" t="n"/>
+      <c r="CE69" s="1022" t="n"/>
+      <c r="CF69" s="1022" t="n"/>
+      <c r="CG69" s="1022" t="n"/>
+      <c r="CH69" s="1022" t="n"/>
+      <c r="CI69" s="1022" t="n"/>
+      <c r="CJ69" s="1022" t="n"/>
+      <c r="CK69" s="1022" t="n"/>
+      <c r="CL69" s="1022" t="n"/>
+      <c r="CM69" s="1022" t="n"/>
+      <c r="CN69" s="1022" t="n"/>
+      <c r="CO69" s="1022" t="n"/>
+      <c r="CP69" s="1022" t="n"/>
+      <c r="CQ69" s="1022" t="n"/>
+      <c r="CR69" s="1022" t="n"/>
+      <c r="CS69" s="1022" t="n"/>
+      <c r="CT69" s="1022" t="n"/>
+      <c r="CU69" s="1022" t="n"/>
+      <c r="CV69" s="1022" t="n"/>
+      <c r="CW69" s="1022" t="n"/>
+      <c r="CX69" s="1024" t="n"/>
+      <c r="CY69" s="1022" t="n"/>
+    </row>
+    <row r="70" ht="11.1" customHeight="1" s="710">
+      <c r="A70" s="1022" t="n"/>
+      <c r="B70" s="1023" t="n"/>
+      <c r="C70" s="1022" t="n"/>
+      <c r="D70" s="1022" t="n"/>
+      <c r="E70" s="1022" t="n"/>
+      <c r="F70" s="1022" t="n"/>
+      <c r="G70" s="1022" t="n"/>
+      <c r="H70" s="1022" t="n"/>
+      <c r="I70" s="1022" t="n"/>
+      <c r="J70" s="1022" t="n"/>
+      <c r="K70" s="1022" t="n"/>
+      <c r="L70" s="1022" t="n"/>
+      <c r="M70" s="1022" t="n"/>
+      <c r="N70" s="1022" t="n"/>
+      <c r="O70" s="1022" t="n"/>
+      <c r="P70" s="1022" t="n"/>
+      <c r="Q70" s="1022" t="n"/>
+      <c r="R70" s="1022" t="n"/>
+      <c r="S70" s="1022" t="n"/>
+      <c r="T70" s="1022" t="n"/>
+      <c r="U70" s="1022" t="n"/>
+      <c r="V70" s="1022" t="n"/>
+      <c r="W70" s="1022" t="n"/>
+      <c r="X70" s="1022" t="n"/>
+      <c r="Y70" s="1022" t="n"/>
+      <c r="Z70" s="1022" t="n"/>
+      <c r="AA70" s="1022" t="n"/>
+      <c r="AB70" s="1022" t="n"/>
+      <c r="AC70" s="1022" t="n"/>
+      <c r="AD70" s="1022" t="n"/>
+      <c r="AE70" s="1022" t="n"/>
+      <c r="AF70" s="1022" t="n"/>
+      <c r="AG70" s="1022" t="n"/>
+      <c r="AH70" s="1022" t="n"/>
+      <c r="AI70" s="1022" t="n"/>
+      <c r="AJ70" s="1022" t="n"/>
+      <c r="AK70" s="1022" t="n"/>
+      <c r="AL70" s="1022" t="n"/>
+      <c r="AM70" s="1022" t="n"/>
+      <c r="AN70" s="1022" t="n"/>
+      <c r="AO70" s="1022" t="n"/>
+      <c r="AP70" s="1022" t="n"/>
+      <c r="AQ70" s="1022" t="n"/>
+      <c r="AR70" s="1022" t="n"/>
+      <c r="AS70" s="1022" t="n"/>
+      <c r="AT70" s="1022" t="n"/>
+      <c r="AU70" s="1022" t="n"/>
+      <c r="AV70" s="1022" t="n"/>
+      <c r="AW70" s="1022" t="n"/>
+      <c r="AX70" s="1022" t="n"/>
+      <c r="AY70" s="1022" t="n"/>
+      <c r="AZ70" s="1022" t="n"/>
+      <c r="BA70" s="1022" t="n"/>
+      <c r="BB70" s="1022" t="n"/>
+      <c r="BC70" s="1022" t="n"/>
+      <c r="BD70" s="1022" t="n"/>
+      <c r="BE70" s="1022" t="n"/>
+      <c r="BF70" s="1022" t="n"/>
+      <c r="BG70" s="1022" t="n"/>
+      <c r="BH70" s="1022" t="n"/>
+      <c r="BI70" s="1022" t="n"/>
+      <c r="BJ70" s="1022" t="n"/>
+      <c r="BK70" s="1022" t="n"/>
+      <c r="BL70" s="1022" t="n"/>
+      <c r="BM70" s="1022" t="n"/>
+      <c r="BN70" s="1022" t="n"/>
+      <c r="BO70" s="1022" t="n"/>
+      <c r="BP70" s="1022" t="n"/>
+      <c r="BQ70" s="1022" t="n"/>
+      <c r="BR70" s="1022" t="n"/>
+      <c r="BS70" s="1022" t="n"/>
+      <c r="BT70" s="1022" t="n"/>
+      <c r="BU70" s="1022" t="n"/>
+      <c r="BV70" s="1022" t="n"/>
+      <c r="BW70" s="1022" t="n"/>
+      <c r="BX70" s="1022" t="n"/>
+      <c r="BY70" s="1022" t="n"/>
+      <c r="BZ70" s="1022" t="n"/>
+      <c r="CA70" s="1022" t="n"/>
+      <c r="CB70" s="1022" t="n"/>
+      <c r="CC70" s="1022" t="n"/>
+      <c r="CD70" s="1022" t="n"/>
+      <c r="CE70" s="1022" t="n"/>
+      <c r="CF70" s="1022" t="n"/>
+      <c r="CG70" s="1022" t="n"/>
+      <c r="CH70" s="1022" t="n"/>
+      <c r="CI70" s="1022" t="n"/>
+      <c r="CJ70" s="1022" t="n"/>
+      <c r="CK70" s="1022" t="n"/>
+      <c r="CL70" s="1022" t="n"/>
+      <c r="CM70" s="1022" t="n"/>
+      <c r="CN70" s="1022" t="n"/>
+      <c r="CO70" s="1022" t="n"/>
+      <c r="CP70" s="1022" t="n"/>
+      <c r="CQ70" s="1022" t="n"/>
+      <c r="CR70" s="1022" t="n"/>
+      <c r="CS70" s="1022" t="n"/>
+      <c r="CT70" s="1022" t="n"/>
+      <c r="CU70" s="1022" t="n"/>
+      <c r="CV70" s="1022" t="n"/>
+      <c r="CW70" s="1022" t="n"/>
+      <c r="CX70" s="1024" t="n"/>
+      <c r="CY70" s="1022" t="n"/>
+    </row>
+    <row r="71" ht="11.1" customHeight="1" s="710">
+      <c r="A71" s="1022" t="n"/>
+      <c r="B71" s="1023" t="n"/>
+      <c r="C71" s="1022" t="n"/>
+      <c r="D71" s="1022" t="n"/>
+      <c r="E71" s="1022" t="n"/>
+      <c r="F71" s="1022" t="n"/>
+      <c r="G71" s="1022" t="n"/>
+      <c r="H71" s="1022" t="n"/>
+      <c r="I71" s="1022" t="n"/>
+      <c r="J71" s="1022" t="n"/>
+      <c r="K71" s="1022" t="n"/>
+      <c r="L71" s="1022" t="n"/>
+      <c r="M71" s="1022" t="n"/>
+      <c r="N71" s="1022" t="n"/>
+      <c r="O71" s="1022" t="n"/>
+      <c r="P71" s="1022" t="n"/>
+      <c r="Q71" s="1022" t="n"/>
+      <c r="R71" s="1022" t="n"/>
+      <c r="S71" s="1022" t="n"/>
+      <c r="T71" s="1022" t="n"/>
+      <c r="U71" s="1022" t="n"/>
+      <c r="V71" s="1022" t="n"/>
+      <c r="W71" s="1022" t="n"/>
+      <c r="X71" s="1022" t="n"/>
+      <c r="Y71" s="1022" t="n"/>
+      <c r="Z71" s="1022" t="n"/>
+      <c r="AA71" s="1022" t="n"/>
+      <c r="AB71" s="1022" t="n"/>
+      <c r="AC71" s="1022" t="n"/>
+      <c r="AD71" s="1022" t="n"/>
+      <c r="AE71" s="1022" t="n"/>
+      <c r="AF71" s="1022" t="n"/>
+      <c r="AG71" s="1022" t="n"/>
+      <c r="AH71" s="1022" t="n"/>
+      <c r="AI71" s="1022" t="n"/>
+      <c r="AJ71" s="1022" t="n"/>
+      <c r="AK71" s="1022" t="n"/>
+      <c r="AL71" s="1022" t="n"/>
+      <c r="AM71" s="1022" t="n"/>
+      <c r="AN71" s="1022" t="n"/>
+      <c r="AO71" s="1022" t="n"/>
+      <c r="AP71" s="1022" t="n"/>
+      <c r="AQ71" s="1022" t="n"/>
+      <c r="AR71" s="1022" t="n"/>
+      <c r="AS71" s="1022" t="n"/>
+      <c r="AT71" s="1022" t="n"/>
+      <c r="AU71" s="1022" t="n"/>
+      <c r="AV71" s="1022" t="n"/>
+      <c r="AW71" s="1022" t="n"/>
+      <c r="AX71" s="1022" t="n"/>
+      <c r="AY71" s="1022" t="n"/>
+      <c r="AZ71" s="1022" t="n"/>
+      <c r="BA71" s="1022" t="n"/>
+      <c r="BB71" s="1022" t="n"/>
+      <c r="BC71" s="1022" t="n"/>
+      <c r="BD71" s="1022" t="n"/>
+      <c r="BE71" s="1022" t="n"/>
+      <c r="BF71" s="1022" t="n"/>
+      <c r="BG71" s="1022" t="n"/>
+      <c r="BH71" s="1022" t="n"/>
+      <c r="BI71" s="1022" t="n"/>
+      <c r="BJ71" s="1022" t="n"/>
+      <c r="BK71" s="1022" t="n"/>
+      <c r="BL71" s="1022" t="n"/>
+      <c r="BM71" s="1022" t="n"/>
+      <c r="BN71" s="1022" t="n"/>
+      <c r="BO71" s="1022" t="n"/>
+      <c r="BP71" s="1022" t="n"/>
+      <c r="BQ71" s="1022" t="n"/>
+      <c r="BR71" s="1022" t="n"/>
+      <c r="BS71" s="1022" t="n"/>
+      <c r="BT71" s="1022" t="n"/>
+      <c r="BU71" s="1022" t="n"/>
+      <c r="BV71" s="1022" t="n"/>
+      <c r="BW71" s="1022" t="n"/>
+      <c r="BX71" s="1022" t="n"/>
+      <c r="BY71" s="1022" t="n"/>
+      <c r="BZ71" s="1022" t="n"/>
+      <c r="CA71" s="1022" t="n"/>
+      <c r="CB71" s="1022" t="n"/>
+      <c r="CC71" s="1022" t="n"/>
+      <c r="CD71" s="1022" t="n"/>
+      <c r="CE71" s="1022" t="n"/>
+      <c r="CF71" s="1022" t="n"/>
+      <c r="CG71" s="1022" t="n"/>
+      <c r="CH71" s="1022" t="n"/>
+      <c r="CI71" s="1022" t="n"/>
+      <c r="CJ71" s="1022" t="n"/>
+      <c r="CK71" s="1022" t="n"/>
+      <c r="CL71" s="1022" t="n"/>
+      <c r="CM71" s="1022" t="n"/>
+      <c r="CN71" s="1022" t="n"/>
+      <c r="CO71" s="1022" t="n"/>
+      <c r="CP71" s="1022" t="n"/>
+      <c r="CQ71" s="1022" t="n"/>
+      <c r="CR71" s="1022" t="n"/>
+      <c r="CS71" s="1022" t="n"/>
+      <c r="CT71" s="1022" t="n"/>
+      <c r="CU71" s="1022" t="n"/>
+      <c r="CV71" s="1022" t="n"/>
+      <c r="CW71" s="1022" t="n"/>
+      <c r="CX71" s="1024" t="n"/>
+      <c r="CY71" s="1022" t="n"/>
+    </row>
+    <row r="72" ht="11.1" customHeight="1" s="710">
+      <c r="A72" s="1022" t="n"/>
+      <c r="B72" s="1023" t="n"/>
+      <c r="C72" s="1022" t="n"/>
+      <c r="D72" s="1022" t="n"/>
+      <c r="E72" s="1022" t="n"/>
+      <c r="F72" s="1022" t="n"/>
+      <c r="G72" s="1022" t="n"/>
+      <c r="H72" s="1022" t="n"/>
+      <c r="I72" s="1022" t="n"/>
+      <c r="J72" s="1022" t="n"/>
+      <c r="K72" s="1022" t="n"/>
+      <c r="L72" s="1022" t="n"/>
+      <c r="M72" s="1022" t="n"/>
+      <c r="N72" s="1022" t="n"/>
+      <c r="O72" s="1022" t="n"/>
+      <c r="P72" s="1022" t="n"/>
+      <c r="Q72" s="1022" t="n"/>
+      <c r="R72" s="1022" t="n"/>
+      <c r="S72" s="1022" t="n"/>
+      <c r="T72" s="1022" t="n"/>
+      <c r="U72" s="1022" t="n"/>
+      <c r="V72" s="1022" t="n"/>
+      <c r="W72" s="1022" t="n"/>
+      <c r="X72" s="1022" t="n"/>
+      <c r="Y72" s="1022" t="n"/>
+      <c r="Z72" s="1022" t="n"/>
+      <c r="AA72" s="1022" t="n"/>
+      <c r="AB72" s="1022" t="n"/>
+      <c r="AC72" s="1022" t="n"/>
+      <c r="AD72" s="1022" t="n"/>
+      <c r="AE72" s="1022" t="n"/>
+      <c r="AF72" s="1022" t="n"/>
+      <c r="AG72" s="1022" t="n"/>
+      <c r="AH72" s="1022" t="n"/>
+      <c r="AI72" s="1022" t="n"/>
+      <c r="AJ72" s="1022" t="n"/>
+      <c r="AK72" s="1022" t="n"/>
+      <c r="AL72" s="1022" t="n"/>
+      <c r="AM72" s="1022" t="n"/>
+      <c r="AN72" s="1022" t="n"/>
+      <c r="AO72" s="1022" t="n"/>
+      <c r="AP72" s="1022" t="n"/>
+      <c r="AQ72" s="1022" t="n"/>
+      <c r="AR72" s="1022" t="n"/>
+      <c r="AS72" s="1022" t="n"/>
+      <c r="AT72" s="1022" t="n"/>
+      <c r="AU72" s="1022" t="n"/>
+      <c r="AV72" s="1022" t="n"/>
+      <c r="AW72" s="1022" t="n"/>
+      <c r="AX72" s="1022" t="n"/>
+      <c r="AY72" s="1022" t="n"/>
+      <c r="AZ72" s="1022" t="n"/>
+      <c r="BA72" s="1022" t="n"/>
+      <c r="BB72" s="1022" t="n"/>
+      <c r="BC72" s="1022" t="n"/>
+      <c r="BD72" s="1022" t="n"/>
+      <c r="BE72" s="1022" t="n"/>
+      <c r="BF72" s="1022" t="n"/>
+      <c r="BG72" s="1022" t="n"/>
+      <c r="BH72" s="1022" t="n"/>
+      <c r="BI72" s="1022" t="n"/>
+      <c r="BJ72" s="1022" t="n"/>
+      <c r="BK72" s="1022" t="n"/>
+      <c r="BL72" s="1022" t="n"/>
+      <c r="BM72" s="1022" t="n"/>
+      <c r="BN72" s="1022" t="n"/>
+      <c r="BO72" s="1022" t="n"/>
+      <c r="BP72" s="1022" t="n"/>
+      <c r="BQ72" s="1022" t="n"/>
+      <c r="BR72" s="1022" t="n"/>
+      <c r="BS72" s="1022" t="n"/>
+      <c r="BT72" s="1022" t="n"/>
+      <c r="BU72" s="1022" t="n"/>
+      <c r="BV72" s="1022" t="n"/>
+      <c r="BW72" s="1022" t="n"/>
+      <c r="BX72" s="1022" t="n"/>
+      <c r="BY72" s="1022" t="n"/>
+      <c r="BZ72" s="1022" t="n"/>
+      <c r="CA72" s="1022" t="n"/>
+      <c r="CB72" s="1022" t="n"/>
+      <c r="CC72" s="1022" t="n"/>
+      <c r="CD72" s="1022" t="n"/>
+      <c r="CE72" s="1022" t="n"/>
+      <c r="CF72" s="1022" t="n"/>
+      <c r="CG72" s="1022" t="n"/>
+      <c r="CH72" s="1022" t="n"/>
+      <c r="CI72" s="1022" t="n"/>
+      <c r="CJ72" s="1022" t="n"/>
+      <c r="CK72" s="1022" t="n"/>
+      <c r="CL72" s="1022" t="n"/>
+      <c r="CM72" s="1022" t="n"/>
+      <c r="CN72" s="1022" t="n"/>
+      <c r="CO72" s="1022" t="n"/>
+      <c r="CP72" s="1022" t="n"/>
+      <c r="CQ72" s="1022" t="n"/>
+      <c r="CR72" s="1022" t="n"/>
+      <c r="CS72" s="1022" t="n"/>
+      <c r="CT72" s="1022" t="n"/>
+      <c r="CU72" s="1022" t="n"/>
+      <c r="CV72" s="1022" t="n"/>
+      <c r="CW72" s="1022" t="n"/>
+      <c r="CX72" s="1024" t="n"/>
+      <c r="CY72" s="1022" t="n"/>
+    </row>
+    <row r="73" ht="11.1" customHeight="1" s="710">
+      <c r="A73" s="1022" t="n"/>
+      <c r="B73" s="1023" t="n"/>
+      <c r="C73" s="1022" t="n"/>
+      <c r="D73" s="1022" t="n"/>
+      <c r="E73" s="1022" t="n"/>
+      <c r="F73" s="1022" t="n"/>
+      <c r="G73" s="1022" t="n"/>
+      <c r="H73" s="1022" t="n"/>
+      <c r="I73" s="1022" t="n"/>
+      <c r="J73" s="1022" t="n"/>
+      <c r="K73" s="1022" t="n"/>
+      <c r="L73" s="1022" t="n"/>
+      <c r="M73" s="1022" t="n"/>
+      <c r="N73" s="1022" t="n"/>
+      <c r="O73" s="1022" t="n"/>
+      <c r="P73" s="1022" t="n"/>
+      <c r="Q73" s="1022" t="n"/>
+      <c r="R73" s="1022" t="n"/>
+      <c r="S73" s="1022" t="n"/>
+      <c r="T73" s="1022" t="n"/>
+      <c r="U73" s="1022" t="n"/>
+      <c r="V73" s="1022" t="n"/>
+      <c r="W73" s="1022" t="n"/>
+      <c r="X73" s="1022" t="n"/>
+      <c r="Y73" s="1022" t="n"/>
+      <c r="Z73" s="1022" t="n"/>
+      <c r="AA73" s="1022" t="n"/>
+      <c r="AB73" s="1022" t="n"/>
+      <c r="AC73" s="1022" t="n"/>
+      <c r="AD73" s="1022" t="n"/>
+      <c r="AE73" s="1022" t="n"/>
+      <c r="AF73" s="1022" t="n"/>
+      <c r="AG73" s="1022" t="n"/>
+      <c r="AH73" s="1022" t="n"/>
+      <c r="AI73" s="1022" t="n"/>
+      <c r="AJ73" s="1022" t="n"/>
+      <c r="AK73" s="1022" t="n"/>
+      <c r="AL73" s="1022" t="n"/>
+      <c r="AM73" s="1022" t="n"/>
+      <c r="AN73" s="1022" t="n"/>
+      <c r="AO73" s="1022" t="n"/>
+      <c r="AP73" s="1022" t="n"/>
+      <c r="AQ73" s="1022" t="n"/>
+      <c r="AR73" s="1022" t="n"/>
+      <c r="AS73" s="1022" t="n"/>
+      <c r="AT73" s="1022" t="n"/>
+      <c r="AU73" s="1022" t="n"/>
+      <c r="AV73" s="1022" t="n"/>
+      <c r="AW73" s="1022" t="n"/>
+      <c r="AX73" s="1022" t="n"/>
+      <c r="AY73" s="1022" t="n"/>
+      <c r="AZ73" s="1022" t="n"/>
+      <c r="BA73" s="1022" t="n"/>
+      <c r="BB73" s="1022" t="n"/>
+      <c r="BC73" s="1022" t="n"/>
+      <c r="BD73" s="1022" t="n"/>
+      <c r="BE73" s="1022" t="n"/>
+      <c r="BF73" s="1022" t="n"/>
+      <c r="BG73" s="1022" t="n"/>
+      <c r="BH73" s="1022" t="n"/>
+      <c r="BI73" s="1022" t="n"/>
+      <c r="BJ73" s="1022" t="n"/>
+      <c r="BK73" s="1022" t="n"/>
+      <c r="BL73" s="1022" t="n"/>
+      <c r="BM73" s="1022" t="n"/>
+      <c r="BN73" s="1022" t="n"/>
+      <c r="BO73" s="1022" t="n"/>
+      <c r="BP73" s="1022" t="n"/>
+      <c r="BQ73" s="1022" t="n"/>
+      <c r="BR73" s="1022" t="n"/>
+      <c r="BS73" s="1022" t="n"/>
+      <c r="BT73" s="1022" t="n"/>
+      <c r="BU73" s="1022" t="n"/>
+      <c r="BV73" s="1022" t="n"/>
+      <c r="BW73" s="1022" t="n"/>
+      <c r="BX73" s="1022" t="n"/>
+      <c r="BY73" s="1022" t="n"/>
+      <c r="BZ73" s="1022" t="n"/>
+      <c r="CA73" s="1022" t="n"/>
+      <c r="CB73" s="1022" t="n"/>
+      <c r="CC73" s="1022" t="n"/>
+      <c r="CD73" s="1022" t="n"/>
+      <c r="CE73" s="1022" t="n"/>
+      <c r="CF73" s="1022" t="n"/>
+      <c r="CG73" s="1022" t="n"/>
+      <c r="CH73" s="1022" t="n"/>
+      <c r="CI73" s="1022" t="n"/>
+      <c r="CJ73" s="1022" t="n"/>
+      <c r="CK73" s="1022" t="n"/>
+      <c r="CL73" s="1022" t="n"/>
+      <c r="CM73" s="1022" t="n"/>
+      <c r="CN73" s="1022" t="n"/>
+      <c r="CO73" s="1022" t="n"/>
+      <c r="CP73" s="1022" t="n"/>
+      <c r="CQ73" s="1022" t="n"/>
+      <c r="CR73" s="1022" t="n"/>
+      <c r="CS73" s="1022" t="n"/>
+      <c r="CT73" s="1022" t="n"/>
+      <c r="CU73" s="1022" t="n"/>
+      <c r="CV73" s="1022" t="n"/>
+      <c r="CW73" s="1022" t="n"/>
+      <c r="CX73" s="1024" t="n"/>
+      <c r="CY73" s="1022" t="n"/>
+    </row>
+    <row r="74" ht="11.1" customHeight="1" s="710">
+      <c r="A74" s="1022" t="n"/>
+      <c r="B74" s="1023" t="n"/>
+      <c r="C74" s="1022" t="n"/>
+      <c r="D74" s="1022" t="n"/>
+      <c r="E74" s="1022" t="n"/>
+      <c r="F74" s="1022" t="n"/>
+      <c r="G74" s="1022" t="n"/>
+      <c r="H74" s="1022" t="n"/>
+      <c r="I74" s="1022" t="n"/>
+      <c r="J74" s="1022" t="n"/>
+      <c r="K74" s="1022" t="n"/>
+      <c r="L74" s="1022" t="n"/>
+      <c r="M74" s="1022" t="n"/>
+      <c r="N74" s="1022" t="n"/>
+      <c r="O74" s="1022" t="n"/>
+      <c r="P74" s="1022" t="n"/>
+      <c r="Q74" s="1022" t="n"/>
+      <c r="R74" s="1022" t="n"/>
+      <c r="S74" s="1022" t="n"/>
+      <c r="T74" s="1022" t="n"/>
+      <c r="U74" s="1022" t="n"/>
+      <c r="V74" s="1022" t="n"/>
+      <c r="W74" s="1022" t="n"/>
+      <c r="X74" s="1022" t="n"/>
+      <c r="Y74" s="1022" t="n"/>
+      <c r="Z74" s="1022" t="n"/>
+      <c r="AA74" s="1022" t="n"/>
+      <c r="AB74" s="1022" t="n"/>
+      <c r="AC74" s="1022" t="n"/>
+      <c r="AD74" s="1022" t="n"/>
+      <c r="AE74" s="1022" t="n"/>
+      <c r="AF74" s="1022" t="n"/>
+      <c r="AG74" s="1022" t="n"/>
+      <c r="AH74" s="1022" t="n"/>
+      <c r="AI74" s="1022" t="n"/>
+      <c r="AJ74" s="1022" t="n"/>
+      <c r="AK74" s="1022" t="n"/>
+      <c r="AL74" s="1022" t="n"/>
+      <c r="AM74" s="1022" t="n"/>
+      <c r="AN74" s="1022" t="n"/>
+      <c r="AO74" s="1022" t="n"/>
+      <c r="AP74" s="1022" t="n"/>
+      <c r="AQ74" s="1022" t="n"/>
+      <c r="AR74" s="1022" t="n"/>
+      <c r="AS74" s="1022" t="n"/>
+      <c r="AT74" s="1022" t="n"/>
+      <c r="AU74" s="1022" t="n"/>
+      <c r="AV74" s="1022" t="n"/>
+      <c r="AW74" s="1022" t="n"/>
+      <c r="AX74" s="1022" t="n"/>
+      <c r="AY74" s="1022" t="n"/>
+      <c r="AZ74" s="1022" t="n"/>
+      <c r="BA74" s="1022" t="n"/>
+      <c r="BB74" s="1022" t="n"/>
+      <c r="BC74" s="1022" t="n"/>
+      <c r="BD74" s="1022" t="n"/>
+      <c r="BE74" s="1022" t="n"/>
+      <c r="BF74" s="1022" t="n"/>
+      <c r="BG74" s="1022" t="n"/>
+      <c r="BH74" s="1022" t="n"/>
+      <c r="BI74" s="1022" t="n"/>
+      <c r="BJ74" s="1022" t="n"/>
+      <c r="BK74" s="1022" t="n"/>
+      <c r="BL74" s="1022" t="n"/>
+      <c r="BM74" s="1022" t="n"/>
+      <c r="BN74" s="1022" t="n"/>
+      <c r="BO74" s="1022" t="n"/>
+      <c r="BP74" s="1022" t="n"/>
+      <c r="BQ74" s="1022" t="n"/>
+      <c r="BR74" s="1022" t="n"/>
+      <c r="BS74" s="1022" t="n"/>
+      <c r="BT74" s="1022" t="n"/>
+      <c r="BU74" s="1022" t="n"/>
+      <c r="BV74" s="1022" t="n"/>
+      <c r="BW74" s="1022" t="n"/>
+      <c r="BX74" s="1022" t="n"/>
+      <c r="BY74" s="1022" t="n"/>
+      <c r="BZ74" s="1022" t="n"/>
+      <c r="CA74" s="1022" t="n"/>
+      <c r="CB74" s="1022" t="n"/>
+      <c r="CC74" s="1022" t="n"/>
+      <c r="CD74" s="1022" t="n"/>
+      <c r="CE74" s="1022" t="n"/>
+      <c r="CF74" s="1022" t="n"/>
+      <c r="CG74" s="1022" t="n"/>
+      <c r="CH74" s="1022" t="n"/>
+      <c r="CI74" s="1022" t="n"/>
+      <c r="CJ74" s="1022" t="n"/>
+      <c r="CK74" s="1022" t="n"/>
+      <c r="CL74" s="1022" t="n"/>
+      <c r="CM74" s="1022" t="n"/>
+      <c r="CN74" s="1022" t="n"/>
+      <c r="CO74" s="1022" t="n"/>
+      <c r="CP74" s="1022" t="n"/>
+      <c r="CQ74" s="1022" t="n"/>
+      <c r="CR74" s="1022" t="n"/>
+      <c r="CS74" s="1022" t="n"/>
+      <c r="CT74" s="1022" t="n"/>
+      <c r="CU74" s="1022" t="n"/>
+      <c r="CV74" s="1022" t="n"/>
+      <c r="CW74" s="1022" t="n"/>
+      <c r="CX74" s="1024" t="n"/>
+      <c r="CY74" s="1022" t="n"/>
+    </row>
+    <row r="75" ht="11.1" customHeight="1" s="710">
+      <c r="A75" s="1022" t="n"/>
+      <c r="B75" s="1023" t="n"/>
+      <c r="C75" s="1022" t="n"/>
+      <c r="D75" s="1022" t="n"/>
+      <c r="E75" s="1022" t="n"/>
+      <c r="F75" s="1022" t="n"/>
+      <c r="G75" s="1022" t="n"/>
+      <c r="H75" s="1022" t="n"/>
+      <c r="I75" s="1022" t="n"/>
+      <c r="J75" s="1022" t="n"/>
+      <c r="K75" s="1022" t="n"/>
+      <c r="L75" s="1022" t="n"/>
+      <c r="M75" s="1022" t="n"/>
+      <c r="N75" s="1022" t="n"/>
+      <c r="O75" s="1022" t="n"/>
+      <c r="P75" s="1022" t="n"/>
+      <c r="Q75" s="1022" t="n"/>
+      <c r="R75" s="1022" t="n"/>
+      <c r="S75" s="1022" t="n"/>
+      <c r="T75" s="1022" t="n"/>
+      <c r="U75" s="1022" t="n"/>
+      <c r="V75" s="1022" t="n"/>
+      <c r="W75" s="1022" t="n"/>
+      <c r="X75" s="1022" t="n"/>
+      <c r="Y75" s="1022" t="n"/>
+      <c r="Z75" s="1022" t="n"/>
+      <c r="AA75" s="1022" t="n"/>
+      <c r="AB75" s="1022" t="n"/>
+      <c r="AC75" s="1022" t="n"/>
+      <c r="AD75" s="1022" t="n"/>
+      <c r="AE75" s="1022" t="n"/>
+      <c r="AF75" s="1022" t="n"/>
+      <c r="AG75" s="1022" t="n"/>
+      <c r="AH75" s="1022" t="n"/>
+      <c r="AI75" s="1022" t="n"/>
+      <c r="AJ75" s="1022" t="n"/>
+      <c r="AK75" s="1022" t="n"/>
+      <c r="AL75" s="1022" t="n"/>
+      <c r="AM75" s="1022" t="n"/>
+      <c r="AN75" s="1022" t="n"/>
+      <c r="AO75" s="1022" t="n"/>
+      <c r="AP75" s="1022" t="n"/>
+      <c r="AQ75" s="1022" t="n"/>
+      <c r="AR75" s="1022" t="n"/>
+      <c r="AS75" s="1022" t="n"/>
+      <c r="AT75" s="1022" t="n"/>
+      <c r="AU75" s="1022" t="n"/>
+      <c r="AV75" s="1022" t="n"/>
+      <c r="AW75" s="1022" t="n"/>
+      <c r="AX75" s="1022" t="n"/>
+      <c r="AY75" s="1022" t="n"/>
+      <c r="AZ75" s="1022" t="n"/>
+      <c r="BA75" s="1022" t="n"/>
+      <c r="BB75" s="1022" t="n"/>
+      <c r="BC75" s="1022" t="n"/>
+      <c r="BD75" s="1022" t="n"/>
+      <c r="BE75" s="1022" t="n"/>
+      <c r="BF75" s="1022" t="n"/>
+      <c r="BG75" s="1022" t="n"/>
+      <c r="BH75" s="1022" t="n"/>
+      <c r="BI75" s="1022" t="n"/>
+      <c r="BJ75" s="1022" t="n"/>
+      <c r="BK75" s="1022" t="n"/>
+      <c r="BL75" s="1022" t="n"/>
+      <c r="BM75" s="1022" t="n"/>
+      <c r="BN75" s="1022" t="n"/>
+      <c r="BO75" s="1022" t="n"/>
+      <c r="BP75" s="1022" t="n"/>
+      <c r="BQ75" s="1022" t="n"/>
+      <c r="BR75" s="1022" t="n"/>
+      <c r="BS75" s="1022" t="n"/>
+      <c r="BT75" s="1022" t="n"/>
+      <c r="BU75" s="1022" t="n"/>
+      <c r="BV75" s="1022" t="n"/>
+      <c r="BW75" s="1022" t="n"/>
+      <c r="BX75" s="1022" t="n"/>
+      <c r="BY75" s="1022" t="n"/>
+      <c r="BZ75" s="1022" t="n"/>
+      <c r="CA75" s="1022" t="n"/>
+      <c r="CB75" s="1022" t="n"/>
+      <c r="CC75" s="1022" t="n"/>
+      <c r="CD75" s="1022" t="n"/>
+      <c r="CE75" s="1022" t="n"/>
+      <c r="CF75" s="1022" t="n"/>
+      <c r="CG75" s="1022" t="n"/>
+      <c r="CH75" s="1022" t="n"/>
+      <c r="CI75" s="1022" t="n"/>
+      <c r="CJ75" s="1022" t="n"/>
+      <c r="CK75" s="1022" t="n"/>
+      <c r="CL75" s="1022" t="n"/>
+      <c r="CM75" s="1022" t="n"/>
+      <c r="CN75" s="1022" t="n"/>
+      <c r="CO75" s="1022" t="n"/>
+      <c r="CP75" s="1022" t="n"/>
+      <c r="CQ75" s="1022" t="n"/>
+      <c r="CR75" s="1022" t="n"/>
+      <c r="CS75" s="1022" t="n"/>
+      <c r="CT75" s="1022" t="n"/>
+      <c r="CU75" s="1022" t="n"/>
+      <c r="CV75" s="1022" t="n"/>
+      <c r="CW75" s="1022" t="n"/>
+      <c r="CX75" s="1024" t="n"/>
+      <c r="CY75" s="1022" t="n"/>
+    </row>
+    <row r="76" ht="11.1" customHeight="1" s="710">
+      <c r="A76" s="1022" t="n"/>
+      <c r="B76" s="1023" t="n"/>
+      <c r="C76" s="1022" t="n"/>
+      <c r="D76" s="1022" t="n"/>
+      <c r="E76" s="1022" t="n"/>
+      <c r="F76" s="1022" t="n"/>
+      <c r="G76" s="1022" t="n"/>
+      <c r="H76" s="1022" t="n"/>
+      <c r="I76" s="1022" t="n"/>
+      <c r="J76" s="1022" t="n"/>
+      <c r="K76" s="1022" t="n"/>
+      <c r="L76" s="1022" t="n"/>
+      <c r="M76" s="1022" t="n"/>
+      <c r="N76" s="1022" t="n"/>
+      <c r="O76" s="1022" t="n"/>
+      <c r="P76" s="1022" t="n"/>
+      <c r="Q76" s="1022" t="n"/>
+      <c r="R76" s="1022" t="n"/>
+      <c r="S76" s="1022" t="n"/>
+      <c r="T76" s="1022" t="n"/>
+      <c r="U76" s="1022" t="n"/>
+      <c r="V76" s="1022" t="n"/>
+      <c r="W76" s="1022" t="n"/>
+      <c r="X76" s="1022" t="n"/>
+      <c r="Y76" s="1022" t="n"/>
+      <c r="Z76" s="1022" t="n"/>
+      <c r="AA76" s="1022" t="n"/>
+      <c r="AB76" s="1022" t="n"/>
+      <c r="AC76" s="1022" t="n"/>
+      <c r="AD76" s="1022" t="n"/>
+      <c r="AE76" s="1022" t="n"/>
+      <c r="AF76" s="1022" t="n"/>
+      <c r="AG76" s="1022" t="n"/>
+      <c r="AH76" s="1022" t="n"/>
+      <c r="AI76" s="1022" t="n"/>
+      <c r="AJ76" s="1022" t="n"/>
+      <c r="AK76" s="1022" t="n"/>
+      <c r="AL76" s="1022" t="n"/>
+      <c r="AM76" s="1022" t="n"/>
+      <c r="AN76" s="1022" t="n"/>
+      <c r="AO76" s="1022" t="n"/>
+      <c r="AP76" s="1022" t="n"/>
+      <c r="AQ76" s="1022" t="n"/>
+      <c r="AR76" s="1022" t="n"/>
+      <c r="AS76" s="1022" t="n"/>
+      <c r="AT76" s="1022" t="n"/>
+      <c r="AU76" s="1022" t="n"/>
+      <c r="AV76" s="1022" t="n"/>
+      <c r="AW76" s="1022" t="n"/>
+      <c r="AX76" s="1022" t="n"/>
+      <c r="AY76" s="1022" t="n"/>
+      <c r="AZ76" s="1022" t="n"/>
+      <c r="BA76" s="1022" t="n"/>
+      <c r="BB76" s="1022" t="n"/>
+      <c r="BC76" s="1022" t="n"/>
+      <c r="BD76" s="1022" t="n"/>
+      <c r="BE76" s="1022" t="n"/>
+      <c r="BF76" s="1022" t="n"/>
+      <c r="BG76" s="1022" t="n"/>
+      <c r="BH76" s="1022" t="n"/>
+      <c r="BI76" s="1022" t="n"/>
+      <c r="BJ76" s="1022" t="n"/>
+      <c r="BK76" s="1022" t="n"/>
+      <c r="BL76" s="1022" t="n"/>
+      <c r="BM76" s="1022" t="n"/>
+      <c r="BN76" s="1022" t="n"/>
+      <c r="BO76" s="1022" t="n"/>
+      <c r="BP76" s="1022" t="n"/>
+      <c r="BQ76" s="1022" t="n"/>
+      <c r="BR76" s="1022" t="n"/>
+      <c r="BS76" s="1022" t="n"/>
+      <c r="BT76" s="1022" t="n"/>
+      <c r="BU76" s="1022" t="n"/>
+      <c r="BV76" s="1022" t="n"/>
+      <c r="BW76" s="1022" t="n"/>
+      <c r="BX76" s="1022" t="n"/>
+      <c r="BY76" s="1022" t="n"/>
+      <c r="BZ76" s="1022" t="n"/>
+      <c r="CA76" s="1022" t="n"/>
+      <c r="CB76" s="1022" t="n"/>
+      <c r="CC76" s="1022" t="n"/>
+      <c r="CD76" s="1022" t="n"/>
+      <c r="CE76" s="1022" t="n"/>
+      <c r="CF76" s="1022" t="n"/>
+      <c r="CG76" s="1022" t="n"/>
+      <c r="CH76" s="1022" t="n"/>
+      <c r="CI76" s="1022" t="n"/>
+      <c r="CJ76" s="1022" t="n"/>
+      <c r="CK76" s="1022" t="n"/>
+      <c r="CL76" s="1022" t="n"/>
+      <c r="CM76" s="1022" t="n"/>
+      <c r="CN76" s="1022" t="n"/>
+      <c r="CO76" s="1022" t="n"/>
+      <c r="CP76" s="1022" t="n"/>
+      <c r="CQ76" s="1022" t="n"/>
+      <c r="CR76" s="1022" t="n"/>
+      <c r="CS76" s="1022" t="n"/>
+      <c r="CT76" s="1022" t="n"/>
+      <c r="CU76" s="1022" t="n"/>
+      <c r="CV76" s="1022" t="n"/>
+      <c r="CW76" s="1022" t="n"/>
+      <c r="CX76" s="1024" t="n"/>
+      <c r="CY76" s="1022" t="n"/>
+    </row>
+    <row r="77" ht="11.1" customHeight="1" s="710">
+      <c r="A77" s="1022" t="n"/>
+      <c r="B77" s="1023" t="n"/>
+      <c r="C77" s="1022" t="n"/>
+      <c r="D77" s="1022" t="n"/>
+      <c r="E77" s="1022" t="n"/>
+      <c r="F77" s="1022" t="n"/>
+      <c r="G77" s="1022" t="n"/>
+      <c r="H77" s="1022" t="n"/>
+      <c r="I77" s="1022" t="n"/>
+      <c r="J77" s="1022" t="n"/>
+      <c r="K77" s="1022" t="n"/>
+      <c r="L77" s="1022" t="n"/>
+      <c r="M77" s="1022" t="n"/>
+      <c r="N77" s="1022" t="n"/>
+      <c r="O77" s="1022" t="n"/>
+      <c r="P77" s="1022" t="n"/>
+      <c r="Q77" s="1022" t="n"/>
+      <c r="R77" s="1022" t="n"/>
+      <c r="S77" s="1022" t="n"/>
+      <c r="T77" s="1022" t="n"/>
+      <c r="U77" s="1022" t="n"/>
+      <c r="V77" s="1022" t="n"/>
+      <c r="W77" s="1022" t="n"/>
+      <c r="X77" s="1022" t="n"/>
+      <c r="Y77" s="1022" t="n"/>
+      <c r="Z77" s="1022" t="n"/>
+      <c r="AA77" s="1022" t="n"/>
+      <c r="AB77" s="1022" t="n"/>
+      <c r="AC77" s="1022" t="n"/>
+      <c r="AD77" s="1022" t="n"/>
+      <c r="AE77" s="1022" t="n"/>
+      <c r="AF77" s="1022" t="n"/>
+      <c r="AG77" s="1022" t="n"/>
+      <c r="AH77" s="1022" t="n"/>
+      <c r="AI77" s="1022" t="n"/>
+      <c r="AJ77" s="1022" t="n"/>
+      <c r="AK77" s="1022" t="n"/>
+      <c r="AL77" s="1022" t="n"/>
+      <c r="AM77" s="1022" t="n"/>
+      <c r="AN77" s="1022" t="n"/>
+      <c r="AO77" s="1022" t="n"/>
+      <c r="AP77" s="1022" t="n"/>
+      <c r="AQ77" s="1022" t="n"/>
+      <c r="AR77" s="1022" t="n"/>
+      <c r="AS77" s="1022" t="n"/>
+      <c r="AT77" s="1022" t="n"/>
+      <c r="AU77" s="1022" t="n"/>
+      <c r="AV77" s="1022" t="n"/>
+      <c r="AW77" s="1022" t="n"/>
+      <c r="AX77" s="1022" t="n"/>
+      <c r="AY77" s="1022" t="n"/>
+      <c r="AZ77" s="1022" t="n"/>
+      <c r="BA77" s="1022" t="n"/>
+      <c r="BB77" s="1022" t="n"/>
+      <c r="BC77" s="1022" t="n"/>
+      <c r="BD77" s="1022" t="n"/>
+      <c r="BE77" s="1022" t="n"/>
+      <c r="BF77" s="1022" t="n"/>
+      <c r="BG77" s="1022" t="n"/>
+      <c r="BH77" s="1022" t="n"/>
+      <c r="BI77" s="1022" t="n"/>
+      <c r="BJ77" s="1022" t="n"/>
+      <c r="BK77" s="1022" t="n"/>
+      <c r="BL77" s="1022" t="n"/>
+      <c r="BM77" s="1022" t="n"/>
+      <c r="BN77" s="1022" t="n"/>
+      <c r="BO77" s="1022" t="n"/>
+      <c r="BP77" s="1022" t="n"/>
+      <c r="BQ77" s="1022" t="n"/>
+      <c r="BR77" s="1022" t="n"/>
+      <c r="BS77" s="1022" t="n"/>
+      <c r="BT77" s="1022" t="n"/>
+      <c r="BU77" s="1022" t="n"/>
+      <c r="BV77" s="1022" t="n"/>
+      <c r="BW77" s="1022" t="n"/>
+      <c r="BX77" s="1022" t="n"/>
+      <c r="BY77" s="1022" t="n"/>
+      <c r="BZ77" s="1022" t="n"/>
+      <c r="CA77" s="1022" t="n"/>
+      <c r="CB77" s="1022" t="n"/>
+      <c r="CC77" s="1022" t="n"/>
+      <c r="CD77" s="1022" t="n"/>
+      <c r="CE77" s="1022" t="n"/>
+      <c r="CF77" s="1022" t="n"/>
+      <c r="CG77" s="1022" t="n"/>
+      <c r="CH77" s="1022" t="n"/>
+      <c r="CI77" s="1022" t="n"/>
+      <c r="CJ77" s="1022" t="n"/>
+      <c r="CK77" s="1022" t="n"/>
+      <c r="CL77" s="1022" t="n"/>
+      <c r="CM77" s="1022" t="n"/>
+      <c r="CN77" s="1022" t="n"/>
+      <c r="CO77" s="1022" t="n"/>
+      <c r="CP77" s="1022" t="n"/>
+      <c r="CQ77" s="1022" t="n"/>
+      <c r="CR77" s="1022" t="n"/>
+      <c r="CS77" s="1022" t="n"/>
+      <c r="CT77" s="1022" t="n"/>
+      <c r="CU77" s="1022" t="n"/>
+      <c r="CV77" s="1022" t="n"/>
+      <c r="CW77" s="1022" t="n"/>
+      <c r="CX77" s="1024" t="n"/>
+      <c r="CY77" s="1022" t="n"/>
+    </row>
+    <row r="78" ht="11.1" customHeight="1" s="710">
+      <c r="A78" s="1022" t="n"/>
+      <c r="B78" s="1023" t="n"/>
+      <c r="C78" s="1022" t="n"/>
+      <c r="D78" s="1022" t="n"/>
+      <c r="E78" s="1022" t="n"/>
+      <c r="F78" s="1022" t="n"/>
+      <c r="G78" s="1022" t="n"/>
+      <c r="H78" s="1022" t="n"/>
+      <c r="I78" s="1022" t="n"/>
+      <c r="J78" s="1022" t="n"/>
+      <c r="K78" s="1022" t="n"/>
+      <c r="L78" s="1022" t="n"/>
+      <c r="M78" s="1022" t="n"/>
+      <c r="N78" s="1022" t="n"/>
+      <c r="O78" s="1022" t="n"/>
+      <c r="P78" s="1022" t="n"/>
+      <c r="Q78" s="1022" t="n"/>
+      <c r="R78" s="1022" t="n"/>
+      <c r="S78" s="1022" t="n"/>
+      <c r="T78" s="1022" t="n"/>
+      <c r="U78" s="1022" t="n"/>
+      <c r="V78" s="1022" t="n"/>
+      <c r="W78" s="1022" t="n"/>
+      <c r="X78" s="1022" t="n"/>
+      <c r="Y78" s="1022" t="n"/>
+      <c r="Z78" s="1022" t="n"/>
+      <c r="AA78" s="1022" t="n"/>
+      <c r="AB78" s="1022" t="n"/>
+      <c r="AC78" s="1022" t="n"/>
+      <c r="AD78" s="1022" t="n"/>
+      <c r="AE78" s="1022" t="n"/>
+      <c r="AF78" s="1022" t="n"/>
+      <c r="AG78" s="1022" t="n"/>
+      <c r="AH78" s="1022" t="n"/>
+      <c r="AI78" s="1022" t="n"/>
+      <c r="AJ78" s="1022" t="n"/>
+      <c r="AK78" s="1022" t="n"/>
+      <c r="AL78" s="1022" t="n"/>
+      <c r="AM78" s="1022" t="n"/>
+      <c r="AN78" s="1022" t="n"/>
+      <c r="AO78" s="1022" t="n"/>
+      <c r="AP78" s="1022" t="n"/>
+      <c r="AQ78" s="1022" t="n"/>
+      <c r="AR78" s="1022" t="n"/>
+      <c r="AS78" s="1022" t="n"/>
+      <c r="AT78" s="1022" t="n"/>
+      <c r="AU78" s="1022" t="n"/>
+      <c r="AV78" s="1022" t="n"/>
+      <c r="AW78" s="1022" t="n"/>
+      <c r="AX78" s="1022" t="n"/>
+      <c r="AY78" s="1022" t="n"/>
+      <c r="AZ78" s="1022" t="n"/>
+      <c r="BA78" s="1022" t="n"/>
+      <c r="BB78" s="1022" t="n"/>
+      <c r="BC78" s="1022" t="n"/>
+      <c r="BD78" s="1022" t="n"/>
+      <c r="BE78" s="1022" t="n"/>
+      <c r="BF78" s="1022" t="n"/>
+      <c r="BG78" s="1022" t="n"/>
+      <c r="BH78" s="1022" t="n"/>
+      <c r="BI78" s="1022" t="n"/>
+      <c r="BJ78" s="1022" t="n"/>
+      <c r="BK78" s="1022" t="n"/>
+      <c r="BL78" s="1022" t="n"/>
+      <c r="BM78" s="1022" t="n"/>
+      <c r="BN78" s="1022" t="n"/>
+      <c r="BO78" s="1022" t="n"/>
+      <c r="BP78" s="1022" t="n"/>
+      <c r="BQ78" s="1022" t="n"/>
+      <c r="BR78" s="1022" t="n"/>
+      <c r="BS78" s="1022" t="n"/>
+      <c r="BT78" s="1022" t="n"/>
+      <c r="BU78" s="1022" t="n"/>
+      <c r="BV78" s="1022" t="n"/>
+      <c r="BW78" s="1022" t="n"/>
+      <c r="BX78" s="1022" t="n"/>
+      <c r="BY78" s="1022" t="n"/>
+      <c r="BZ78" s="1022" t="n"/>
+      <c r="CA78" s="1022" t="n"/>
+      <c r="CB78" s="1022" t="n"/>
+      <c r="CC78" s="1022" t="n"/>
+      <c r="CD78" s="1022" t="n"/>
+      <c r="CE78" s="1022" t="n"/>
+      <c r="CF78" s="1022" t="n"/>
+      <c r="CG78" s="1022" t="n"/>
+      <c r="CH78" s="1022" t="n"/>
+      <c r="CI78" s="1022" t="n"/>
+      <c r="CJ78" s="1022" t="n"/>
+      <c r="CK78" s="1022" t="n"/>
+      <c r="CL78" s="1022" t="n"/>
+      <c r="CM78" s="1022" t="n"/>
+      <c r="CN78" s="1022" t="n"/>
+      <c r="CO78" s="1022" t="n"/>
+      <c r="CP78" s="1022" t="n"/>
+      <c r="CQ78" s="1022" t="n"/>
+      <c r="CR78" s="1022" t="n"/>
+      <c r="CS78" s="1022" t="n"/>
+      <c r="CT78" s="1022" t="n"/>
+      <c r="CU78" s="1022" t="n"/>
+      <c r="CV78" s="1022" t="n"/>
+      <c r="CW78" s="1022" t="n"/>
+      <c r="CX78" s="1024" t="n"/>
+      <c r="CY78" s="1022" t="n"/>
+    </row>
+    <row r="79" ht="11.1" customHeight="1" s="710">
+      <c r="A79" s="1022" t="n"/>
+      <c r="B79" s="1023" t="n"/>
+      <c r="C79" s="1022" t="n"/>
+      <c r="D79" s="1022" t="n"/>
+      <c r="E79" s="1022" t="n"/>
+      <c r="F79" s="1022" t="n"/>
+      <c r="G79" s="1022" t="n"/>
+      <c r="H79" s="1022" t="n"/>
+      <c r="I79" s="1022" t="n"/>
+      <c r="J79" s="1022" t="n"/>
+      <c r="K79" s="1022" t="n"/>
+      <c r="L79" s="1022" t="n"/>
+      <c r="M79" s="1022" t="n"/>
+      <c r="N79" s="1022" t="n"/>
+      <c r="O79" s="1022" t="n"/>
+      <c r="P79" s="1022" t="n"/>
+      <c r="Q79" s="1022" t="n"/>
+      <c r="R79" s="1022" t="n"/>
+      <c r="S79" s="1022" t="n"/>
+      <c r="T79" s="1022" t="n"/>
+      <c r="U79" s="1022" t="n"/>
+      <c r="V79" s="1022" t="n"/>
+      <c r="W79" s="1022" t="n"/>
+      <c r="X79" s="1022" t="n"/>
+      <c r="Y79" s="1022" t="n"/>
+      <c r="Z79" s="1022" t="n"/>
+      <c r="AA79" s="1022" t="n"/>
+      <c r="AB79" s="1022" t="n"/>
+      <c r="AC79" s="1022" t="n"/>
+      <c r="AD79" s="1022" t="n"/>
+      <c r="AE79" s="1022" t="n"/>
+      <c r="AF79" s="1022" t="n"/>
+      <c r="AG79" s="1022" t="n"/>
+      <c r="AH79" s="1022" t="n"/>
+      <c r="AI79" s="1022" t="n"/>
+      <c r="AJ79" s="1022" t="n"/>
+      <c r="AK79" s="1022" t="n"/>
+      <c r="AL79" s="1022" t="n"/>
+      <c r="AM79" s="1022" t="n"/>
+      <c r="AN79" s="1022" t="n"/>
+      <c r="AO79" s="1022" t="n"/>
+      <c r="AP79" s="1022" t="n"/>
+      <c r="AQ79" s="1022" t="n"/>
+      <c r="AR79" s="1022" t="n"/>
+      <c r="AS79" s="1022" t="n"/>
+      <c r="AT79" s="1022" t="n"/>
+      <c r="AU79" s="1022" t="n"/>
+      <c r="AV79" s="1022" t="n"/>
+      <c r="AW79" s="1022" t="n"/>
+      <c r="AX79" s="1022" t="n"/>
+      <c r="AY79" s="1022" t="n"/>
+      <c r="AZ79" s="1022" t="n"/>
+      <c r="BA79" s="1022" t="n"/>
+      <c r="BB79" s="1022" t="n"/>
+      <c r="BC79" s="1022" t="n"/>
+      <c r="BD79" s="1022" t="n"/>
+      <c r="BE79" s="1022" t="n"/>
+      <c r="BF79" s="1022" t="n"/>
+      <c r="BG79" s="1022" t="n"/>
+      <c r="BH79" s="1022" t="n"/>
+      <c r="BI79" s="1022" t="n"/>
+      <c r="BJ79" s="1022" t="n"/>
+      <c r="BK79" s="1022" t="n"/>
+      <c r="BL79" s="1022" t="n"/>
+      <c r="BM79" s="1022" t="n"/>
+      <c r="BN79" s="1022" t="n"/>
+      <c r="BO79" s="1022" t="n"/>
+      <c r="BP79" s="1022" t="n"/>
+      <c r="BQ79" s="1022" t="n"/>
+      <c r="BR79" s="1022" t="n"/>
+      <c r="BS79" s="1022" t="n"/>
+      <c r="BT79" s="1022" t="n"/>
+      <c r="BU79" s="1022" t="n"/>
+      <c r="BV79" s="1022" t="n"/>
+      <c r="BW79" s="1022" t="n"/>
+      <c r="BX79" s="1022" t="n"/>
+      <c r="BY79" s="1022" t="n"/>
+      <c r="BZ79" s="1022" t="n"/>
+      <c r="CA79" s="1022" t="n"/>
+      <c r="CB79" s="1022" t="n"/>
+      <c r="CC79" s="1022" t="n"/>
+      <c r="CD79" s="1022" t="n"/>
+      <c r="CE79" s="1022" t="n"/>
+      <c r="CF79" s="1022" t="n"/>
+      <c r="CG79" s="1022" t="n"/>
+      <c r="CH79" s="1022" t="n"/>
+      <c r="CI79" s="1022" t="n"/>
+      <c r="CJ79" s="1022" t="n"/>
+      <c r="CK79" s="1022" t="n"/>
+      <c r="CL79" s="1022" t="n"/>
+      <c r="CM79" s="1022" t="n"/>
+      <c r="CN79" s="1022" t="n"/>
+      <c r="CO79" s="1022" t="n"/>
+      <c r="CP79" s="1022" t="n"/>
+      <c r="CQ79" s="1022" t="n"/>
+      <c r="CR79" s="1022" t="n"/>
+      <c r="CS79" s="1022" t="n"/>
+      <c r="CT79" s="1022" t="n"/>
+      <c r="CU79" s="1022" t="n"/>
+      <c r="CV79" s="1022" t="n"/>
+      <c r="CW79" s="1022" t="n"/>
+      <c r="CX79" s="1024" t="n"/>
+      <c r="CY79" s="1022" t="n"/>
+    </row>
+    <row r="80" ht="11.1" customHeight="1" s="710">
+      <c r="A80" s="1022" t="n"/>
+      <c r="B80" s="1023" t="n"/>
+      <c r="C80" s="1022" t="n"/>
+      <c r="D80" s="1022" t="n"/>
+      <c r="E80" s="1022" t="n"/>
+      <c r="F80" s="1022" t="n"/>
+      <c r="G80" s="1022" t="n"/>
+      <c r="H80" s="1022" t="n"/>
+      <c r="I80" s="1022" t="n"/>
+      <c r="J80" s="1022" t="n"/>
+      <c r="K80" s="1022" t="n"/>
+      <c r="L80" s="1022" t="n"/>
+      <c r="M80" s="1022" t="n"/>
+      <c r="N80" s="1022" t="n"/>
+      <c r="O80" s="1022" t="n"/>
+      <c r="P80" s="1022" t="n"/>
+      <c r="Q80" s="1022" t="n"/>
+      <c r="R80" s="1022" t="n"/>
+      <c r="S80" s="1022" t="n"/>
+      <c r="T80" s="1022" t="n"/>
+      <c r="U80" s="1022" t="n"/>
+      <c r="V80" s="1022" t="n"/>
+      <c r="W80" s="1022" t="n"/>
+      <c r="X80" s="1022" t="n"/>
+      <c r="Y80" s="1022" t="n"/>
+      <c r="Z80" s="1022" t="n"/>
+      <c r="AA80" s="1022" t="n"/>
+      <c r="AB80" s="1022" t="n"/>
+      <c r="AC80" s="1022" t="n"/>
+      <c r="AD80" s="1022" t="n"/>
+      <c r="AE80" s="1022" t="n"/>
+      <c r="AF80" s="1022" t="n"/>
+      <c r="AG80" s="1022" t="n"/>
+      <c r="AH80" s="1022" t="n"/>
+      <c r="AI80" s="1022" t="n"/>
+      <c r="AJ80" s="1022" t="n"/>
+      <c r="AK80" s="1022" t="n"/>
+      <c r="AL80" s="1022" t="n"/>
+      <c r="AM80" s="1022" t="n"/>
+      <c r="AN80" s="1022" t="n"/>
+      <c r="AO80" s="1022" t="n"/>
+      <c r="AP80" s="1022" t="n"/>
+      <c r="AQ80" s="1022" t="n"/>
+      <c r="AR80" s="1022" t="n"/>
+      <c r="AS80" s="1022" t="n"/>
+      <c r="AT80" s="1022" t="n"/>
+      <c r="AU80" s="1022" t="n"/>
+      <c r="AV80" s="1022" t="n"/>
+      <c r="AW80" s="1022" t="n"/>
+      <c r="AX80" s="1022" t="n"/>
+      <c r="AY80" s="1022" t="n"/>
+      <c r="AZ80" s="1022" t="n"/>
+      <c r="BA80" s="1022" t="n"/>
+      <c r="BB80" s="1022" t="n"/>
+      <c r="BC80" s="1022" t="n"/>
+      <c r="BD80" s="1022" t="n"/>
+      <c r="BE80" s="1022" t="n"/>
+      <c r="BF80" s="1022" t="n"/>
+      <c r="BG80" s="1022" t="n"/>
+      <c r="BH80" s="1022" t="n"/>
+      <c r="BI80" s="1022" t="n"/>
+      <c r="BJ80" s="1022" t="n"/>
+      <c r="BK80" s="1022" t="n"/>
+      <c r="BL80" s="1022" t="n"/>
+      <c r="BM80" s="1022" t="n"/>
+      <c r="BN80" s="1022" t="n"/>
+      <c r="BO80" s="1022" t="n"/>
+      <c r="BP80" s="1022" t="n"/>
+      <c r="BQ80" s="1022" t="n"/>
+      <c r="BR80" s="1022" t="n"/>
+      <c r="BS80" s="1022" t="n"/>
+      <c r="BT80" s="1022" t="n"/>
+      <c r="BU80" s="1022" t="n"/>
+      <c r="BV80" s="1022" t="n"/>
+      <c r="BW80" s="1022" t="n"/>
+      <c r="BX80" s="1022" t="n"/>
+      <c r="BY80" s="1022" t="n"/>
+      <c r="BZ80" s="1022" t="n"/>
+      <c r="CA80" s="1022" t="n"/>
+      <c r="CB80" s="1022" t="n"/>
+      <c r="CC80" s="1022" t="n"/>
+      <c r="CD80" s="1022" t="n"/>
+      <c r="CE80" s="1022" t="n"/>
+      <c r="CF80" s="1022" t="n"/>
+      <c r="CG80" s="1022" t="n"/>
+      <c r="CH80" s="1022" t="n"/>
+      <c r="CI80" s="1022" t="n"/>
+      <c r="CJ80" s="1022" t="n"/>
+      <c r="CK80" s="1022" t="n"/>
+      <c r="CL80" s="1022" t="n"/>
+      <c r="CM80" s="1022" t="n"/>
+      <c r="CN80" s="1022" t="n"/>
+      <c r="CO80" s="1022" t="n"/>
+      <c r="CP80" s="1022" t="n"/>
+      <c r="CQ80" s="1022" t="n"/>
+      <c r="CR80" s="1022" t="n"/>
+      <c r="CS80" s="1022" t="n"/>
+      <c r="CT80" s="1022" t="n"/>
+      <c r="CU80" s="1022" t="n"/>
+      <c r="CV80" s="1022" t="n"/>
+      <c r="CW80" s="1022" t="n"/>
+      <c r="CX80" s="1024" t="n"/>
+      <c r="CY80" s="1022" t="n"/>
+    </row>
+    <row r="81" ht="11.1" customHeight="1" s="710">
+      <c r="A81" s="1022" t="n"/>
+      <c r="B81" s="1023" t="n"/>
+      <c r="C81" s="1022" t="n"/>
+      <c r="D81" s="1022" t="n"/>
+      <c r="E81" s="1022" t="n"/>
+      <c r="F81" s="1022" t="n"/>
+      <c r="G81" s="1022" t="n"/>
+      <c r="H81" s="1022" t="n"/>
+      <c r="I81" s="1022" t="n"/>
+      <c r="J81" s="1022" t="n"/>
+      <c r="K81" s="1022" t="n"/>
+      <c r="L81" s="1022" t="n"/>
+      <c r="M81" s="1022" t="n"/>
+      <c r="N81" s="1022" t="n"/>
+      <c r="O81" s="1022" t="n"/>
+      <c r="P81" s="1022" t="n"/>
+      <c r="Q81" s="1022" t="n"/>
+      <c r="R81" s="1022" t="n"/>
+      <c r="S81" s="1022" t="n"/>
+      <c r="T81" s="1022" t="n"/>
+      <c r="U81" s="1022" t="n"/>
+      <c r="V81" s="1022" t="n"/>
+      <c r="W81" s="1022" t="n"/>
+      <c r="X81" s="1022" t="n"/>
+      <c r="Y81" s="1022" t="n"/>
+      <c r="Z81" s="1022" t="n"/>
+      <c r="AA81" s="1022" t="n"/>
+      <c r="AB81" s="1022" t="n"/>
+      <c r="AC81" s="1022" t="n"/>
+      <c r="AD81" s="1022" t="n"/>
+      <c r="AE81" s="1022" t="n"/>
+      <c r="AF81" s="1022" t="n"/>
+      <c r="AG81" s="1022" t="n"/>
+      <c r="AH81" s="1022" t="n"/>
+      <c r="AI81" s="1022" t="n"/>
+      <c r="AJ81" s="1022" t="n"/>
+      <c r="AK81" s="1022" t="n"/>
+      <c r="AL81" s="1022" t="n"/>
+      <c r="AM81" s="1022" t="n"/>
+      <c r="AN81" s="1022" t="n"/>
+      <c r="AO81" s="1022" t="n"/>
+      <c r="AP81" s="1022" t="n"/>
+      <c r="AQ81" s="1022" t="n"/>
+      <c r="AR81" s="1022" t="n"/>
+      <c r="AS81" s="1022" t="n"/>
+      <c r="AT81" s="1022" t="n"/>
+      <c r="AU81" s="1022" t="n"/>
+      <c r="AV81" s="1022" t="n"/>
+      <c r="AW81" s="1022" t="n"/>
+      <c r="AX81" s="1022" t="n"/>
+      <c r="AY81" s="1022" t="n"/>
+      <c r="AZ81" s="1022" t="n"/>
+      <c r="BA81" s="1022" t="n"/>
+      <c r="BB81" s="1022" t="n"/>
+      <c r="BC81" s="1022" t="n"/>
+      <c r="BD81" s="1022" t="n"/>
+      <c r="BE81" s="1022" t="n"/>
+      <c r="BF81" s="1022" t="n"/>
+      <c r="BG81" s="1022" t="n"/>
+      <c r="BH81" s="1022" t="n"/>
+      <c r="BI81" s="1022" t="n"/>
+      <c r="BJ81" s="1022" t="n"/>
+      <c r="BK81" s="1022" t="n"/>
+      <c r="BL81" s="1022" t="n"/>
+      <c r="BM81" s="1022" t="n"/>
+      <c r="BN81" s="1022" t="n"/>
+      <c r="BO81" s="1022" t="n"/>
+      <c r="BP81" s="1022" t="n"/>
+      <c r="BQ81" s="1022" t="n"/>
+      <c r="BR81" s="1022" t="n"/>
+      <c r="BS81" s="1022" t="n"/>
+      <c r="BT81" s="1022" t="n"/>
+      <c r="BU81" s="1022" t="n"/>
+      <c r="BV81" s="1022" t="n"/>
+      <c r="BW81" s="1022" t="n"/>
+      <c r="BX81" s="1022" t="n"/>
+      <c r="BY81" s="1022" t="n"/>
+      <c r="BZ81" s="1022" t="n"/>
+      <c r="CA81" s="1022" t="n"/>
+      <c r="CB81" s="1022" t="n"/>
+      <c r="CC81" s="1022" t="n"/>
+      <c r="CD81" s="1022" t="n"/>
+      <c r="CE81" s="1022" t="n"/>
+      <c r="CF81" s="1022" t="n"/>
+      <c r="CG81" s="1022" t="n"/>
+      <c r="CH81" s="1022" t="n"/>
+      <c r="CI81" s="1022" t="n"/>
+      <c r="CJ81" s="1022" t="n"/>
+      <c r="CK81" s="1022" t="n"/>
+      <c r="CL81" s="1022" t="n"/>
+      <c r="CM81" s="1022" t="n"/>
+      <c r="CN81" s="1022" t="n"/>
+      <c r="CO81" s="1022" t="n"/>
+      <c r="CP81" s="1022" t="n"/>
+      <c r="CQ81" s="1022" t="n"/>
+      <c r="CR81" s="1022" t="n"/>
+      <c r="CS81" s="1022" t="n"/>
+      <c r="CT81" s="1022" t="n"/>
+      <c r="CU81" s="1022" t="n"/>
+      <c r="CV81" s="1022" t="n"/>
+      <c r="CW81" s="1022" t="n"/>
+      <c r="CX81" s="1024" t="n"/>
+      <c r="CY81" s="1022" t="n"/>
+    </row>
+    <row r="82" ht="11.1" customHeight="1" s="710">
+      <c r="A82" s="1022" t="n"/>
+      <c r="B82" s="1023" t="n"/>
+      <c r="C82" s="1022" t="n"/>
+      <c r="D82" s="1022" t="n"/>
+      <c r="E82" s="1022" t="n"/>
+      <c r="F82" s="1022" t="n"/>
+      <c r="G82" s="1022" t="n"/>
+      <c r="H82" s="1022" t="n"/>
+      <c r="I82" s="1022" t="n"/>
+      <c r="J82" s="1022" t="n"/>
+      <c r="K82" s="1022" t="n"/>
+      <c r="L82" s="1022" t="n"/>
+      <c r="M82" s="1022" t="n"/>
+      <c r="N82" s="1022" t="n"/>
+      <c r="O82" s="1022" t="n"/>
+      <c r="P82" s="1022" t="n"/>
+      <c r="Q82" s="1022" t="n"/>
+      <c r="R82" s="1022" t="n"/>
+      <c r="S82" s="1022" t="n"/>
+      <c r="T82" s="1022" t="n"/>
+      <c r="U82" s="1022" t="n"/>
+      <c r="V82" s="1022" t="n"/>
+      <c r="W82" s="1022" t="n"/>
+      <c r="X82" s="1022" t="n"/>
+      <c r="Y82" s="1022" t="n"/>
+      <c r="Z82" s="1022" t="n"/>
+      <c r="AA82" s="1022" t="n"/>
+      <c r="AB82" s="1022" t="n"/>
+      <c r="AC82" s="1022" t="n"/>
+      <c r="AD82" s="1022" t="n"/>
+      <c r="AE82" s="1022" t="n"/>
+      <c r="AF82" s="1022" t="n"/>
+      <c r="AG82" s="1022" t="n"/>
+      <c r="AH82" s="1022" t="n"/>
+      <c r="AI82" s="1022" t="n"/>
+      <c r="AJ82" s="1022" t="n"/>
+      <c r="AK82" s="1022" t="n"/>
+      <c r="AL82" s="1022" t="n"/>
+      <c r="AM82" s="1022" t="n"/>
+      <c r="AN82" s="1022" t="n"/>
+      <c r="AO82" s="1022" t="n"/>
+      <c r="AP82" s="1022" t="n"/>
+      <c r="AQ82" s="1022" t="n"/>
+      <c r="AR82" s="1022" t="n"/>
+      <c r="AS82" s="1022" t="n"/>
+      <c r="AT82" s="1022" t="n"/>
+      <c r="AU82" s="1022" t="n"/>
+      <c r="AV82" s="1022" t="n"/>
+      <c r="AW82" s="1022" t="n"/>
+      <c r="AX82" s="1022" t="n"/>
+      <c r="AY82" s="1022" t="n"/>
+      <c r="AZ82" s="1022" t="n"/>
+      <c r="BA82" s="1022" t="n"/>
+      <c r="BB82" s="1022" t="n"/>
+      <c r="BC82" s="1022" t="n"/>
+      <c r="BD82" s="1022" t="n"/>
+      <c r="BE82" s="1022" t="n"/>
+      <c r="BF82" s="1022" t="n"/>
+      <c r="BG82" s="1022" t="n"/>
+      <c r="BH82" s="1022" t="n"/>
+      <c r="BI82" s="1022" t="n"/>
+      <c r="BJ82" s="1022" t="n"/>
+      <c r="BK82" s="1022" t="n"/>
+      <c r="BL82" s="1022" t="n"/>
+      <c r="BM82" s="1022" t="n"/>
+      <c r="BN82" s="1022" t="n"/>
+      <c r="BO82" s="1022" t="n"/>
+      <c r="BP82" s="1022" t="n"/>
+      <c r="BQ82" s="1022" t="n"/>
+      <c r="BR82" s="1022" t="n"/>
+      <c r="BS82" s="1022" t="n"/>
+      <c r="BT82" s="1022" t="n"/>
+      <c r="BU82" s="1022" t="n"/>
+      <c r="BV82" s="1022" t="n"/>
+      <c r="BW82" s="1022" t="n"/>
+      <c r="BX82" s="1022" t="n"/>
+      <c r="BY82" s="1022" t="n"/>
+      <c r="BZ82" s="1022" t="n"/>
+      <c r="CA82" s="1022" t="n"/>
+      <c r="CB82" s="1022" t="n"/>
+      <c r="CC82" s="1022" t="n"/>
+      <c r="CD82" s="1022" t="n"/>
+      <c r="CE82" s="1022" t="n"/>
+      <c r="CF82" s="1022" t="n"/>
+      <c r="CG82" s="1022" t="n"/>
+      <c r="CH82" s="1022" t="n"/>
+      <c r="CI82" s="1022" t="n"/>
+      <c r="CJ82" s="1022" t="n"/>
+      <c r="CK82" s="1022" t="n"/>
+      <c r="CL82" s="1022" t="n"/>
+      <c r="CM82" s="1022" t="n"/>
+      <c r="CN82" s="1022" t="n"/>
+      <c r="CO82" s="1022" t="n"/>
+      <c r="CP82" s="1022" t="n"/>
+      <c r="CQ82" s="1022" t="n"/>
+      <c r="CR82" s="1022" t="n"/>
+      <c r="CS82" s="1022" t="n"/>
+      <c r="CT82" s="1022" t="n"/>
+      <c r="CU82" s="1022" t="n"/>
+      <c r="CV82" s="1022" t="n"/>
+      <c r="CW82" s="1022" t="n"/>
+      <c r="CX82" s="1024" t="n"/>
+      <c r="CY82" s="1022" t="n"/>
+    </row>
+    <row r="83" ht="11.1" customHeight="1" s="710">
+      <c r="A83" s="1022" t="n"/>
+      <c r="B83" s="1023" t="n"/>
+      <c r="C83" s="1022" t="n"/>
+      <c r="D83" s="1022" t="n"/>
+      <c r="E83" s="1022" t="n"/>
+      <c r="F83" s="1022" t="n"/>
+      <c r="G83" s="1022" t="n"/>
+      <c r="H83" s="1022" t="n"/>
+      <c r="I83" s="1022" t="n"/>
+      <c r="J83" s="1022" t="n"/>
+      <c r="K83" s="1022" t="n"/>
+      <c r="L83" s="1022" t="n"/>
+      <c r="M83" s="1022" t="n"/>
+      <c r="N83" s="1022" t="n"/>
+      <c r="O83" s="1022" t="n"/>
+      <c r="P83" s="1022" t="n"/>
+      <c r="Q83" s="1022" t="n"/>
+      <c r="R83" s="1022" t="n"/>
+      <c r="S83" s="1022" t="n"/>
+      <c r="T83" s="1022" t="n"/>
+      <c r="U83" s="1022" t="n"/>
+      <c r="V83" s="1022" t="n"/>
+      <c r="W83" s="1022" t="n"/>
+      <c r="X83" s="1022" t="n"/>
+      <c r="Y83" s="1022" t="n"/>
+      <c r="Z83" s="1022" t="n"/>
+      <c r="AA83" s="1022" t="n"/>
+      <c r="AB83" s="1022" t="n"/>
+      <c r="AC83" s="1022" t="n"/>
+      <c r="AD83" s="1022" t="n"/>
+      <c r="AE83" s="1022" t="n"/>
+      <c r="AF83" s="1022" t="n"/>
+      <c r="AG83" s="1022" t="n"/>
+      <c r="AH83" s="1022" t="n"/>
+      <c r="AI83" s="1022" t="n"/>
+      <c r="AJ83" s="1022" t="n"/>
+      <c r="AK83" s="1022" t="n"/>
+      <c r="AL83" s="1022" t="n"/>
+      <c r="AM83" s="1022" t="n"/>
+      <c r="AN83" s="1022" t="n"/>
+      <c r="AO83" s="1022" t="n"/>
+      <c r="AP83" s="1022" t="n"/>
+      <c r="AQ83" s="1022" t="n"/>
+      <c r="AR83" s="1022" t="n"/>
+      <c r="AS83" s="1022" t="n"/>
+      <c r="AT83" s="1022" t="n"/>
+      <c r="AU83" s="1022" t="n"/>
+      <c r="AV83" s="1022" t="n"/>
+      <c r="AW83" s="1022" t="n"/>
+      <c r="AX83" s="1022" t="n"/>
+      <c r="AY83" s="1022" t="n"/>
+      <c r="AZ83" s="1022" t="n"/>
+      <c r="BA83" s="1022" t="n"/>
+      <c r="BB83" s="1022" t="n"/>
+      <c r="BC83" s="1022" t="n"/>
+      <c r="BD83" s="1022" t="n"/>
+      <c r="BE83" s="1022" t="n"/>
+      <c r="BF83" s="1022" t="n"/>
+      <c r="BG83" s="1022" t="n"/>
+      <c r="BH83" s="1022" t="n"/>
+      <c r="BI83" s="1022" t="n"/>
+      <c r="BJ83" s="1022" t="n"/>
+      <c r="BK83" s="1022" t="n"/>
+      <c r="BL83" s="1022" t="n"/>
+      <c r="BM83" s="1022" t="n"/>
+      <c r="BN83" s="1022" t="n"/>
+      <c r="BO83" s="1022" t="n"/>
+      <c r="BP83" s="1022" t="n"/>
+      <c r="BQ83" s="1022" t="n"/>
+      <c r="BR83" s="1022" t="n"/>
+      <c r="BS83" s="1022" t="n"/>
+      <c r="BT83" s="1022" t="n"/>
+      <c r="BU83" s="1022" t="n"/>
+      <c r="BV83" s="1022" t="n"/>
+      <c r="BW83" s="1022" t="n"/>
+      <c r="BX83" s="1022" t="n"/>
+      <c r="BY83" s="1022" t="n"/>
+      <c r="BZ83" s="1022" t="n"/>
+      <c r="CA83" s="1022" t="n"/>
+      <c r="CB83" s="1022" t="n"/>
+      <c r="CC83" s="1022" t="n"/>
+      <c r="CD83" s="1022" t="n"/>
+      <c r="CE83" s="1022" t="n"/>
+      <c r="CF83" s="1022" t="n"/>
+      <c r="CG83" s="1022" t="n"/>
+      <c r="CH83" s="1022" t="n"/>
+      <c r="CI83" s="1022" t="n"/>
+      <c r="CJ83" s="1022" t="n"/>
+      <c r="CK83" s="1022" t="n"/>
+      <c r="CL83" s="1022" t="n"/>
+      <c r="CM83" s="1022" t="n"/>
+      <c r="CN83" s="1022" t="n"/>
+      <c r="CO83" s="1022" t="n"/>
+      <c r="CP83" s="1022" t="n"/>
+      <c r="CQ83" s="1022" t="n"/>
+      <c r="CR83" s="1022" t="n"/>
+      <c r="CS83" s="1022" t="n"/>
+      <c r="CT83" s="1022" t="n"/>
+      <c r="CU83" s="1022" t="n"/>
+      <c r="CV83" s="1022" t="n"/>
+      <c r="CW83" s="1022" t="n"/>
+      <c r="CX83" s="1024" t="n"/>
+      <c r="CY83" s="1022" t="n"/>
+    </row>
+    <row r="84" ht="11.1" customHeight="1" s="710">
+      <c r="A84" s="1022" t="n"/>
+      <c r="B84" s="1023" t="n"/>
+      <c r="C84" s="1022" t="n"/>
+      <c r="D84" s="1022" t="n"/>
+      <c r="E84" s="1022" t="n"/>
+      <c r="F84" s="1022" t="n"/>
+      <c r="G84" s="1022" t="n"/>
+      <c r="H84" s="1022" t="n"/>
+      <c r="I84" s="1022" t="n"/>
+      <c r="J84" s="1022" t="n"/>
+      <c r="K84" s="1022" t="n"/>
+      <c r="L84" s="1022" t="n"/>
+      <c r="M84" s="1022" t="n"/>
+      <c r="N84" s="1022" t="n"/>
+      <c r="O84" s="1022" t="n"/>
+      <c r="P84" s="1022" t="n"/>
+      <c r="Q84" s="1022" t="n"/>
+      <c r="R84" s="1022" t="n"/>
+      <c r="S84" s="1022" t="n"/>
+      <c r="T84" s="1022" t="n"/>
+      <c r="U84" s="1022" t="n"/>
+      <c r="V84" s="1022" t="n"/>
+      <c r="W84" s="1022" t="n"/>
+      <c r="X84" s="1022" t="n"/>
+      <c r="Y84" s="1022" t="n"/>
+      <c r="Z84" s="1022" t="n"/>
+      <c r="AA84" s="1022" t="n"/>
+      <c r="AB84" s="1022" t="n"/>
+      <c r="AC84" s="1022" t="n"/>
+      <c r="AD84" s="1022" t="n"/>
+      <c r="AE84" s="1022" t="n"/>
+      <c r="AF84" s="1022" t="n"/>
+      <c r="AG84" s="1022" t="n"/>
+      <c r="AH84" s="1022" t="n"/>
+      <c r="AI84" s="1022" t="n"/>
+      <c r="AJ84" s="1022" t="n"/>
+      <c r="AK84" s="1022" t="n"/>
+      <c r="AL84" s="1022" t="n"/>
+      <c r="AM84" s="1022" t="n"/>
+      <c r="AN84" s="1022" t="n"/>
+      <c r="AO84" s="1022" t="n"/>
+      <c r="AP84" s="1022" t="n"/>
+      <c r="AQ84" s="1022" t="n"/>
+      <c r="AR84" s="1022" t="n"/>
+      <c r="AS84" s="1022" t="n"/>
+      <c r="AT84" s="1022" t="n"/>
+      <c r="AU84" s="1022" t="n"/>
+      <c r="AV84" s="1022" t="n"/>
+      <c r="AW84" s="1022" t="n"/>
+      <c r="AX84" s="1022" t="n"/>
+      <c r="AY84" s="1022" t="n"/>
+      <c r="AZ84" s="1022" t="n"/>
+      <c r="BA84" s="1022" t="n"/>
+      <c r="BB84" s="1022" t="n"/>
+      <c r="BC84" s="1022" t="n"/>
+      <c r="BD84" s="1022" t="n"/>
+      <c r="BE84" s="1022" t="n"/>
+      <c r="BF84" s="1022" t="n"/>
+      <c r="BG84" s="1022" t="n"/>
+      <c r="BH84" s="1022" t="n"/>
+      <c r="BI84" s="1022" t="n"/>
+      <c r="BJ84" s="1022" t="n"/>
+      <c r="BK84" s="1022" t="n"/>
+      <c r="BL84" s="1022" t="n"/>
+      <c r="BM84" s="1022" t="n"/>
+      <c r="BN84" s="1022" t="n"/>
+      <c r="BO84" s="1022" t="n"/>
+      <c r="BP84" s="1022" t="n"/>
+      <c r="BQ84" s="1022" t="n"/>
+      <c r="BR84" s="1022" t="n"/>
+      <c r="BS84" s="1022" t="n"/>
+      <c r="BT84" s="1022" t="n"/>
+      <c r="BU84" s="1022" t="n"/>
+      <c r="BV84" s="1022" t="n"/>
+      <c r="BW84" s="1022" t="n"/>
+      <c r="BX84" s="1022" t="n"/>
+      <c r="BY84" s="1022" t="n"/>
+      <c r="BZ84" s="1022" t="n"/>
+      <c r="CA84" s="1022" t="n"/>
+      <c r="CB84" s="1022" t="n"/>
+      <c r="CC84" s="1022" t="n"/>
+      <c r="CD84" s="1022" t="n"/>
+      <c r="CE84" s="1022" t="n"/>
+      <c r="CF84" s="1022" t="n"/>
+      <c r="CG84" s="1022" t="n"/>
+      <c r="CH84" s="1022" t="n"/>
+      <c r="CI84" s="1022" t="n"/>
+      <c r="CJ84" s="1022" t="n"/>
+      <c r="CK84" s="1022" t="n"/>
+      <c r="CL84" s="1022" t="n"/>
+      <c r="CM84" s="1022" t="n"/>
+      <c r="CN84" s="1022" t="n"/>
+      <c r="CO84" s="1022" t="n"/>
+      <c r="CP84" s="1022" t="n"/>
+      <c r="CQ84" s="1022" t="n"/>
+      <c r="CR84" s="1022" t="n"/>
+      <c r="CS84" s="1022" t="n"/>
+      <c r="CT84" s="1022" t="n"/>
+      <c r="CU84" s="1022" t="n"/>
+      <c r="CV84" s="1022" t="n"/>
+      <c r="CW84" s="1022" t="n"/>
+      <c r="CX84" s="1024" t="n"/>
+      <c r="CY84" s="1022" t="n"/>
+    </row>
+    <row r="85" ht="11.1" customHeight="1" s="710">
+      <c r="A85" s="1022" t="n"/>
+      <c r="B85" s="1023" t="n"/>
+      <c r="C85" s="1022" t="n"/>
+      <c r="D85" s="1022" t="n"/>
+      <c r="E85" s="1022" t="n"/>
+      <c r="F85" s="1022" t="n"/>
+      <c r="G85" s="1022" t="n"/>
+      <c r="H85" s="1022" t="n"/>
+      <c r="I85" s="1022" t="n"/>
+      <c r="J85" s="1022" t="n"/>
+      <c r="K85" s="1022" t="n"/>
+      <c r="L85" s="1022" t="n"/>
+      <c r="M85" s="1022" t="n"/>
+      <c r="N85" s="1022" t="n"/>
+      <c r="O85" s="1022" t="n"/>
+      <c r="P85" s="1022" t="n"/>
+      <c r="Q85" s="1022" t="n"/>
+      <c r="R85" s="1022" t="n"/>
+      <c r="S85" s="1022" t="n"/>
+      <c r="T85" s="1022" t="n"/>
+      <c r="U85" s="1022" t="n"/>
+      <c r="V85" s="1022" t="n"/>
+      <c r="W85" s="1022" t="n"/>
+      <c r="X85" s="1022" t="n"/>
+      <c r="Y85" s="1022" t="n"/>
+      <c r="Z85" s="1022" t="n"/>
+      <c r="AA85" s="1022" t="n"/>
+      <c r="AB85" s="1022" t="n"/>
+      <c r="AC85" s="1022" t="n"/>
+      <c r="AD85" s="1022" t="n"/>
+      <c r="AE85" s="1022" t="n"/>
+      <c r="AF85" s="1022" t="n"/>
+      <c r="AG85" s="1022" t="n"/>
+      <c r="AH85" s="1022" t="n"/>
+      <c r="AI85" s="1022" t="n"/>
+      <c r="AJ85" s="1022" t="n"/>
+      <c r="AK85" s="1022" t="n"/>
+      <c r="AL85" s="1022" t="n"/>
+      <c r="AM85" s="1022" t="n"/>
+      <c r="AN85" s="1022" t="n"/>
+      <c r="AO85" s="1022" t="n"/>
+      <c r="AP85" s="1022" t="n"/>
+      <c r="AQ85" s="1022" t="n"/>
+      <c r="AR85" s="1022" t="n"/>
+      <c r="AS85" s="1022" t="n"/>
+      <c r="AT85" s="1022" t="n"/>
+      <c r="AU85" s="1022" t="n"/>
+      <c r="AV85" s="1022" t="n"/>
+      <c r="AW85" s="1022" t="n"/>
+      <c r="AX85" s="1022" t="n"/>
+      <c r="AY85" s="1022" t="n"/>
+      <c r="AZ85" s="1022" t="n"/>
+      <c r="BA85" s="1022" t="n"/>
+      <c r="BB85" s="1022" t="n"/>
+      <c r="BC85" s="1022" t="n"/>
+      <c r="BD85" s="1022" t="n"/>
+      <c r="BE85" s="1022" t="n"/>
+      <c r="BF85" s="1022" t="n"/>
+      <c r="BG85" s="1022" t="n"/>
+      <c r="BH85" s="1022" t="n"/>
+      <c r="BI85" s="1022" t="n"/>
+      <c r="BJ85" s="1022" t="n"/>
+      <c r="BK85" s="1022" t="n"/>
+      <c r="BL85" s="1022" t="n"/>
+      <c r="BM85" s="1022" t="n"/>
+      <c r="BN85" s="1022" t="n"/>
+      <c r="BO85" s="1022" t="n"/>
+      <c r="BP85" s="1022" t="n"/>
+      <c r="BQ85" s="1022" t="n"/>
+      <c r="BR85" s="1022" t="n"/>
+      <c r="BS85" s="1022" t="n"/>
+      <c r="BT85" s="1022" t="n"/>
+      <c r="BU85" s="1022" t="n"/>
+      <c r="BV85" s="1022" t="n"/>
+      <c r="BW85" s="1022" t="n"/>
+      <c r="BX85" s="1022" t="n"/>
+      <c r="BY85" s="1022" t="n"/>
+      <c r="BZ85" s="1022" t="n"/>
+      <c r="CA85" s="1022" t="n"/>
+      <c r="CB85" s="1022" t="n"/>
+      <c r="CC85" s="1022" t="n"/>
+      <c r="CD85" s="1022" t="n"/>
+      <c r="CE85" s="1022" t="n"/>
+      <c r="CF85" s="1022" t="n"/>
+      <c r="CG85" s="1022" t="n"/>
+      <c r="CH85" s="1022" t="n"/>
+      <c r="CI85" s="1022" t="n"/>
+      <c r="CJ85" s="1022" t="n"/>
+      <c r="CK85" s="1022" t="n"/>
+      <c r="CL85" s="1022" t="n"/>
+      <c r="CM85" s="1022" t="n"/>
+      <c r="CN85" s="1022" t="n"/>
+      <c r="CO85" s="1022" t="n"/>
+      <c r="CP85" s="1022" t="n"/>
+      <c r="CQ85" s="1022" t="n"/>
+      <c r="CR85" s="1022" t="n"/>
+      <c r="CS85" s="1022" t="n"/>
+      <c r="CT85" s="1022" t="n"/>
+      <c r="CU85" s="1022" t="n"/>
+      <c r="CV85" s="1022" t="n"/>
+      <c r="CW85" s="1022" t="n"/>
+      <c r="CX85" s="1024" t="n"/>
+      <c r="CY85" s="1022" t="n"/>
+    </row>
+    <row r="86" ht="11.1" customHeight="1" s="710">
+      <c r="A86" s="1022" t="n"/>
+      <c r="B86" s="1023" t="n"/>
+      <c r="C86" s="1022" t="n"/>
+      <c r="D86" s="1022" t="n"/>
+      <c r="E86" s="1022" t="n"/>
+      <c r="F86" s="1022" t="n"/>
+      <c r="G86" s="1022" t="n"/>
+      <c r="H86" s="1022" t="n"/>
+      <c r="I86" s="1022" t="n"/>
+      <c r="J86" s="1022" t="n"/>
+      <c r="K86" s="1022" t="n"/>
+      <c r="L86" s="1022" t="n"/>
+      <c r="M86" s="1022" t="n"/>
+      <c r="N86" s="1022" t="n"/>
+      <c r="O86" s="1022" t="n"/>
+      <c r="P86" s="1022" t="n"/>
+      <c r="Q86" s="1022" t="n"/>
+      <c r="R86" s="1022" t="n"/>
+      <c r="S86" s="1022" t="n"/>
+      <c r="T86" s="1022" t="n"/>
+      <c r="U86" s="1022" t="n"/>
+      <c r="V86" s="1022" t="n"/>
+      <c r="W86" s="1022" t="n"/>
+      <c r="X86" s="1022" t="n"/>
+      <c r="Y86" s="1022" t="n"/>
+      <c r="Z86" s="1022" t="n"/>
+      <c r="AA86" s="1022" t="n"/>
+      <c r="AB86" s="1022" t="n"/>
+      <c r="AC86" s="1022" t="n"/>
+      <c r="AD86" s="1022" t="n"/>
+      <c r="AE86" s="1022" t="n"/>
+      <c r="AF86" s="1022" t="n"/>
+      <c r="AG86" s="1022" t="n"/>
+      <c r="AH86" s="1022" t="n"/>
+      <c r="AI86" s="1022" t="n"/>
+      <c r="AJ86" s="1022" t="n"/>
+      <c r="AK86" s="1022" t="n"/>
+      <c r="AL86" s="1022" t="n"/>
+      <c r="AM86" s="1022" t="n"/>
+      <c r="AN86" s="1022" t="n"/>
+      <c r="AO86" s="1022" t="n"/>
+      <c r="AP86" s="1022" t="n"/>
+      <c r="AQ86" s="1022" t="n"/>
+      <c r="AR86" s="1022" t="n"/>
+      <c r="AS86" s="1022" t="n"/>
+      <c r="AT86" s="1022" t="n"/>
+      <c r="AU86" s="1022" t="n"/>
+      <c r="AV86" s="1022" t="n"/>
+      <c r="AW86" s="1022" t="n"/>
+      <c r="AX86" s="1022" t="n"/>
+      <c r="AY86" s="1022" t="n"/>
+      <c r="AZ86" s="1022" t="n"/>
+      <c r="BA86" s="1022" t="n"/>
+      <c r="BB86" s="1022" t="n"/>
+      <c r="BC86" s="1022" t="n"/>
+      <c r="BD86" s="1022" t="n"/>
+      <c r="BE86" s="1022" t="n"/>
+      <c r="BF86" s="1022" t="n"/>
+      <c r="BG86" s="1022" t="n"/>
+      <c r="BH86" s="1022" t="n"/>
+      <c r="BI86" s="1022" t="n"/>
+      <c r="BJ86" s="1022" t="n"/>
+      <c r="BK86" s="1022" t="n"/>
+      <c r="BL86" s="1022" t="n"/>
+      <c r="BM86" s="1022" t="n"/>
+      <c r="BN86" s="1022" t="n"/>
+      <c r="BO86" s="1022" t="n"/>
+      <c r="BP86" s="1022" t="n"/>
+      <c r="BQ86" s="1022" t="n"/>
+      <c r="BR86" s="1022" t="n"/>
+      <c r="BS86" s="1022" t="n"/>
+      <c r="BT86" s="1022" t="n"/>
+      <c r="BU86" s="1022" t="n"/>
+      <c r="BV86" s="1022" t="n"/>
+      <c r="BW86" s="1022" t="n"/>
+      <c r="BX86" s="1022" t="n"/>
+      <c r="BY86" s="1022" t="n"/>
+      <c r="BZ86" s="1022" t="n"/>
+      <c r="CA86" s="1022" t="n"/>
+      <c r="CB86" s="1022" t="n"/>
+      <c r="CC86" s="1022" t="n"/>
+      <c r="CD86" s="1022" t="n"/>
+      <c r="CE86" s="1022" t="n"/>
+      <c r="CF86" s="1022" t="n"/>
+      <c r="CG86" s="1022" t="n"/>
+      <c r="CH86" s="1022" t="n"/>
+      <c r="CI86" s="1022" t="n"/>
+      <c r="CJ86" s="1022" t="n"/>
+      <c r="CK86" s="1022" t="n"/>
+      <c r="CL86" s="1022" t="n"/>
+      <c r="CM86" s="1022" t="n"/>
+      <c r="CN86" s="1022" t="n"/>
+      <c r="CO86" s="1022" t="n"/>
+      <c r="CP86" s="1022" t="n"/>
+      <c r="CQ86" s="1022" t="n"/>
+      <c r="CR86" s="1022" t="n"/>
+      <c r="CS86" s="1022" t="n"/>
+      <c r="CT86" s="1022" t="n"/>
+      <c r="CU86" s="1022" t="n"/>
+      <c r="CV86" s="1022" t="n"/>
+      <c r="CW86" s="1022" t="n"/>
+      <c r="CX86" s="1024" t="n"/>
+      <c r="CY86" s="1022" t="n"/>
+    </row>
+    <row r="87" ht="11.1" customHeight="1" s="710">
+      <c r="A87" s="1022" t="n"/>
+      <c r="B87" s="1023" t="n"/>
+      <c r="C87" s="1022" t="n"/>
+      <c r="D87" s="1022" t="n"/>
+      <c r="E87" s="1022" t="n"/>
+      <c r="F87" s="1022" t="n"/>
+      <c r="G87" s="1022" t="n"/>
+      <c r="H87" s="1022" t="n"/>
+      <c r="I87" s="1022" t="n"/>
+      <c r="J87" s="1022" t="n"/>
+      <c r="K87" s="1022" t="n"/>
+      <c r="L87" s="1022" t="n"/>
+      <c r="M87" s="1022" t="n"/>
+      <c r="N87" s="1022" t="n"/>
+      <c r="O87" s="1022" t="n"/>
+      <c r="P87" s="1022" t="n"/>
+      <c r="Q87" s="1022" t="n"/>
+      <c r="R87" s="1022" t="n"/>
+      <c r="S87" s="1022" t="n"/>
+      <c r="T87" s="1022" t="n"/>
+      <c r="U87" s="1022" t="n"/>
+      <c r="V87" s="1022" t="n"/>
+      <c r="W87" s="1022" t="n"/>
+      <c r="X87" s="1022" t="n"/>
+      <c r="Y87" s="1022" t="n"/>
+      <c r="Z87" s="1022" t="n"/>
+      <c r="AA87" s="1022" t="n"/>
+      <c r="AB87" s="1022" t="n"/>
+      <c r="AC87" s="1022" t="n"/>
+      <c r="AD87" s="1022" t="n"/>
+      <c r="AE87" s="1022" t="n"/>
+      <c r="AF87" s="1022" t="n"/>
+      <c r="AG87" s="1022" t="n"/>
+      <c r="AH87" s="1022" t="n"/>
+      <c r="AI87" s="1022" t="n"/>
+      <c r="AJ87" s="1022" t="n"/>
+      <c r="AK87" s="1022" t="n"/>
+      <c r="AL87" s="1022" t="n"/>
+      <c r="AM87" s="1022" t="n"/>
+      <c r="AN87" s="1022" t="n"/>
+      <c r="AO87" s="1022" t="n"/>
+      <c r="AP87" s="1022" t="n"/>
+      <c r="AQ87" s="1022" t="n"/>
+      <c r="AR87" s="1022" t="n"/>
+      <c r="AS87" s="1022" t="n"/>
+      <c r="AT87" s="1022" t="n"/>
+      <c r="AU87" s="1022" t="n"/>
+      <c r="AV87" s="1022" t="n"/>
+      <c r="AW87" s="1022" t="n"/>
+      <c r="AX87" s="1022" t="n"/>
+      <c r="AY87" s="1022" t="n"/>
+      <c r="AZ87" s="1022" t="n"/>
+      <c r="BA87" s="1022" t="n"/>
+      <c r="BB87" s="1022" t="n"/>
+      <c r="BC87" s="1022" t="n"/>
+      <c r="BD87" s="1022" t="n"/>
+      <c r="BE87" s="1022" t="n"/>
+      <c r="BF87" s="1022" t="n"/>
+      <c r="BG87" s="1022" t="n"/>
+      <c r="BH87" s="1022" t="n"/>
+      <c r="BI87" s="1022" t="n"/>
+      <c r="BJ87" s="1022" t="n"/>
+      <c r="BK87" s="1022" t="n"/>
+      <c r="BL87" s="1022" t="n"/>
+      <c r="BM87" s="1022" t="n"/>
+      <c r="BN87" s="1022" t="n"/>
+      <c r="BO87" s="1022" t="n"/>
+      <c r="BP87" s="1022" t="n"/>
+      <c r="BQ87" s="1022" t="n"/>
+      <c r="BR87" s="1022" t="n"/>
+      <c r="BS87" s="1022" t="n"/>
+      <c r="BT87" s="1022" t="n"/>
+      <c r="BU87" s="1022" t="n"/>
+      <c r="BV87" s="1022" t="n"/>
+      <c r="BW87" s="1022" t="n"/>
+      <c r="BX87" s="1022" t="n"/>
+      <c r="BY87" s="1022" t="n"/>
+      <c r="BZ87" s="1022" t="n"/>
+      <c r="CA87" s="1022" t="n"/>
+      <c r="CB87" s="1022" t="n"/>
+      <c r="CC87" s="1022" t="n"/>
+      <c r="CD87" s="1022" t="n"/>
+      <c r="CE87" s="1022" t="n"/>
+      <c r="CF87" s="1022" t="n"/>
+      <c r="CG87" s="1022" t="n"/>
+      <c r="CH87" s="1022" t="n"/>
+      <c r="CI87" s="1022" t="n"/>
+      <c r="CJ87" s="1022" t="n"/>
+      <c r="CK87" s="1022" t="n"/>
+      <c r="CL87" s="1022" t="n"/>
+      <c r="CM87" s="1022" t="n"/>
+      <c r="CN87" s="1022" t="n"/>
+      <c r="CO87" s="1022" t="n"/>
+      <c r="CP87" s="1022" t="n"/>
+      <c r="CQ87" s="1022" t="n"/>
+      <c r="CR87" s="1022" t="n"/>
+      <c r="CS87" s="1022" t="n"/>
+      <c r="CT87" s="1022" t="n"/>
+      <c r="CU87" s="1022" t="n"/>
+      <c r="CV87" s="1022" t="n"/>
+      <c r="CW87" s="1022" t="n"/>
+      <c r="CX87" s="1024" t="n"/>
+      <c r="CY87" s="1022" t="n"/>
+    </row>
+    <row r="88" ht="11.1" customHeight="1" s="710">
+      <c r="A88" s="1022" t="n"/>
+      <c r="B88" s="1023" t="n"/>
+      <c r="C88" s="1022" t="n"/>
+      <c r="D88" s="1022" t="n"/>
+      <c r="E88" s="1022" t="n"/>
+      <c r="F88" s="1022" t="n"/>
+      <c r="G88" s="1022" t="n"/>
+      <c r="H88" s="1022" t="n"/>
+      <c r="I88" s="1022" t="n"/>
+      <c r="J88" s="1022" t="n"/>
+      <c r="K88" s="1022" t="n"/>
+      <c r="L88" s="1022" t="n"/>
+      <c r="M88" s="1022" t="n"/>
+      <c r="N88" s="1022" t="n"/>
+      <c r="O88" s="1022" t="n"/>
+      <c r="P88" s="1022" t="n"/>
+      <c r="Q88" s="1022" t="n"/>
+      <c r="R88" s="1022" t="n"/>
+      <c r="S88" s="1022" t="n"/>
+      <c r="T88" s="1022" t="n"/>
+      <c r="U88" s="1022" t="n"/>
+      <c r="V88" s="1022" t="n"/>
+      <c r="W88" s="1022" t="n"/>
+      <c r="X88" s="1022" t="n"/>
+      <c r="Y88" s="1022" t="n"/>
+      <c r="Z88" s="1022" t="n"/>
+      <c r="AA88" s="1022" t="n"/>
+      <c r="AB88" s="1022" t="n"/>
+      <c r="AC88" s="1022" t="n"/>
+      <c r="AD88" s="1022" t="n"/>
+      <c r="AE88" s="1022" t="n"/>
+      <c r="AF88" s="1022" t="n"/>
+      <c r="AG88" s="1022" t="n"/>
+      <c r="AH88" s="1022" t="n"/>
+      <c r="AI88" s="1022" t="n"/>
+      <c r="AJ88" s="1022" t="n"/>
+      <c r="AK88" s="1022" t="n"/>
+      <c r="AL88" s="1022" t="n"/>
+      <c r="AM88" s="1022" t="n"/>
+      <c r="AN88" s="1022" t="n"/>
+      <c r="AO88" s="1022" t="n"/>
+      <c r="AP88" s="1022" t="n"/>
+      <c r="AQ88" s="1022" t="n"/>
+      <c r="AR88" s="1022" t="n"/>
+      <c r="AS88" s="1022" t="n"/>
+      <c r="AT88" s="1022" t="n"/>
+      <c r="AU88" s="1022" t="n"/>
+      <c r="AV88" s="1022" t="n"/>
+      <c r="AW88" s="1022" t="n"/>
+      <c r="AX88" s="1022" t="n"/>
+      <c r="AY88" s="1022" t="n"/>
+      <c r="AZ88" s="1022" t="n"/>
+      <c r="BA88" s="1022" t="n"/>
+      <c r="BB88" s="1022" t="n"/>
+      <c r="BC88" s="1022" t="n"/>
+      <c r="BD88" s="1022" t="n"/>
+      <c r="BE88" s="1022" t="n"/>
+      <c r="BF88" s="1022" t="n"/>
+      <c r="BG88" s="1022" t="n"/>
+      <c r="BH88" s="1022" t="n"/>
+      <c r="BI88" s="1022" t="n"/>
+      <c r="BJ88" s="1022" t="n"/>
+      <c r="BK88" s="1022" t="n"/>
+      <c r="BL88" s="1022" t="n"/>
+      <c r="BM88" s="1022" t="n"/>
+      <c r="BN88" s="1022" t="n"/>
+      <c r="BO88" s="1022" t="n"/>
+      <c r="BP88" s="1022" t="n"/>
+      <c r="BQ88" s="1022" t="n"/>
+      <c r="BR88" s="1022" t="n"/>
+      <c r="BS88" s="1022" t="n"/>
+      <c r="BT88" s="1022" t="n"/>
+      <c r="BU88" s="1022" t="n"/>
+      <c r="BV88" s="1022" t="n"/>
+      <c r="BW88" s="1022" t="n"/>
+      <c r="BX88" s="1022" t="n"/>
+      <c r="BY88" s="1022" t="n"/>
+      <c r="BZ88" s="1022" t="n"/>
+      <c r="CA88" s="1022" t="n"/>
+      <c r="CB88" s="1022" t="n"/>
+      <c r="CC88" s="1022" t="n"/>
+      <c r="CD88" s="1022" t="n"/>
+      <c r="CE88" s="1022" t="n"/>
+      <c r="CF88" s="1022" t="n"/>
+      <c r="CG88" s="1022" t="n"/>
+      <c r="CH88" s="1022" t="n"/>
+      <c r="CI88" s="1022" t="n"/>
+      <c r="CJ88" s="1022" t="n"/>
+      <c r="CK88" s="1022" t="n"/>
+      <c r="CL88" s="1022" t="n"/>
+      <c r="CM88" s="1022" t="n"/>
+      <c r="CN88" s="1022" t="n"/>
+      <c r="CO88" s="1022" t="n"/>
+      <c r="CP88" s="1022" t="n"/>
+      <c r="CQ88" s="1022" t="n"/>
+      <c r="CR88" s="1022" t="n"/>
+      <c r="CS88" s="1022" t="n"/>
+      <c r="CT88" s="1022" t="n"/>
+      <c r="CU88" s="1022" t="n"/>
+      <c r="CV88" s="1022" t="n"/>
+      <c r="CW88" s="1022" t="n"/>
+      <c r="CX88" s="1024" t="n"/>
+      <c r="CY88" s="1022" t="n"/>
+    </row>
+    <row r="89" ht="11.1" customHeight="1" s="710">
+      <c r="A89" s="1022" t="n"/>
+      <c r="B89" s="1023" t="n"/>
+      <c r="C89" s="1022" t="n"/>
+      <c r="D89" s="1022" t="n"/>
+      <c r="E89" s="1022" t="n"/>
+      <c r="F89" s="1022" t="n"/>
+      <c r="G89" s="1022" t="n"/>
+      <c r="H89" s="1022" t="n"/>
+      <c r="I89" s="1022" t="n"/>
+      <c r="J89" s="1022" t="n"/>
+      <c r="K89" s="1022" t="n"/>
+      <c r="L89" s="1022" t="n"/>
+      <c r="M89" s="1022" t="n"/>
+      <c r="N89" s="1022" t="n"/>
+      <c r="O89" s="1022" t="n"/>
+      <c r="P89" s="1022" t="n"/>
+      <c r="Q89" s="1022" t="n"/>
+      <c r="R89" s="1022" t="n"/>
+      <c r="S89" s="1022" t="n"/>
+      <c r="T89" s="1022" t="n"/>
+      <c r="U89" s="1022" t="n"/>
+      <c r="V89" s="1022" t="n"/>
+      <c r="W89" s="1022" t="n"/>
+      <c r="X89" s="1022" t="n"/>
+      <c r="Y89" s="1022" t="n"/>
+      <c r="Z89" s="1022" t="n"/>
+      <c r="AA89" s="1022" t="n"/>
+      <c r="AB89" s="1022" t="n"/>
+      <c r="AC89" s="1022" t="n"/>
+      <c r="AD89" s="1022" t="n"/>
+      <c r="AE89" s="1022" t="n"/>
+      <c r="AF89" s="1022" t="n"/>
+      <c r="AG89" s="1022" t="n"/>
+      <c r="AH89" s="1022" t="n"/>
+      <c r="AI89" s="1022" t="n"/>
+      <c r="AJ89" s="1022" t="n"/>
+      <c r="AK89" s="1022" t="n"/>
+      <c r="AL89" s="1022" t="n"/>
+      <c r="AM89" s="1022" t="n"/>
+      <c r="AN89" s="1022" t="n"/>
+      <c r="AO89" s="1022" t="n"/>
+      <c r="AP89" s="1022" t="n"/>
+      <c r="AQ89" s="1022" t="n"/>
+      <c r="AR89" s="1022" t="n"/>
+      <c r="AS89" s="1022" t="n"/>
+      <c r="AT89" s="1022" t="n"/>
+      <c r="AU89" s="1022" t="n"/>
+      <c r="AV89" s="1022" t="n"/>
+      <c r="AW89" s="1022" t="n"/>
+      <c r="AX89" s="1022" t="n"/>
+      <c r="AY89" s="1022" t="n"/>
+      <c r="AZ89" s="1022" t="n"/>
+      <c r="BA89" s="1022" t="n"/>
+      <c r="BB89" s="1022" t="n"/>
+      <c r="BC89" s="1022" t="n"/>
+      <c r="BD89" s="1022" t="n"/>
+      <c r="BE89" s="1022" t="n"/>
+      <c r="BF89" s="1022" t="n"/>
+      <c r="BG89" s="1022" t="n"/>
+      <c r="BH89" s="1022" t="n"/>
+      <c r="BI89" s="1022" t="n"/>
+      <c r="BJ89" s="1022" t="n"/>
+      <c r="BK89" s="1022" t="n"/>
+      <c r="BL89" s="1022" t="n"/>
+      <c r="BM89" s="1022" t="n"/>
+      <c r="BN89" s="1022" t="n"/>
+      <c r="BO89" s="1022" t="n"/>
+      <c r="BP89" s="1022" t="n"/>
+      <c r="BQ89" s="1022" t="n"/>
+      <c r="BR89" s="1022" t="n"/>
+      <c r="BS89" s="1022" t="n"/>
+      <c r="BT89" s="1022" t="n"/>
+      <c r="BU89" s="1022" t="n"/>
+      <c r="BV89" s="1022" t="n"/>
+      <c r="BW89" s="1022" t="n"/>
+      <c r="BX89" s="1022" t="n"/>
+      <c r="BY89" s="1022" t="n"/>
+      <c r="BZ89" s="1022" t="n"/>
+      <c r="CA89" s="1022" t="n"/>
+      <c r="CB89" s="1022" t="n"/>
+      <c r="CC89" s="1022" t="n"/>
+      <c r="CD89" s="1022" t="n"/>
+      <c r="CE89" s="1022" t="n"/>
+      <c r="CF89" s="1022" t="n"/>
+      <c r="CG89" s="1022" t="n"/>
+      <c r="CH89" s="1022" t="n"/>
+      <c r="CI89" s="1022" t="n"/>
+      <c r="CJ89" s="1022" t="n"/>
+      <c r="CK89" s="1022" t="n"/>
+      <c r="CL89" s="1022" t="n"/>
+      <c r="CM89" s="1022" t="n"/>
+      <c r="CN89" s="1022" t="n"/>
+      <c r="CO89" s="1022" t="n"/>
+      <c r="CP89" s="1022" t="n"/>
+      <c r="CQ89" s="1022" t="n"/>
+      <c r="CR89" s="1022" t="n"/>
+      <c r="CS89" s="1022" t="n"/>
+      <c r="CT89" s="1022" t="n"/>
+      <c r="CU89" s="1022" t="n"/>
+      <c r="CV89" s="1022" t="n"/>
+      <c r="CW89" s="1022" t="n"/>
+      <c r="CX89" s="1024" t="n"/>
+      <c r="CY89" s="1022" t="n"/>
+    </row>
+    <row r="90" ht="11.1" customHeight="1" s="710">
+      <c r="A90" s="1022" t="n"/>
+      <c r="B90" s="1026" t="n"/>
+      <c r="C90" s="1027" t="n"/>
+      <c r="D90" s="1027" t="n"/>
+      <c r="E90" s="1027" t="n"/>
+      <c r="F90" s="1027" t="n"/>
+      <c r="G90" s="1027" t="n"/>
+      <c r="H90" s="1027" t="n"/>
+      <c r="I90" s="1027" t="n"/>
+      <c r="J90" s="1027" t="n"/>
+      <c r="K90" s="1027" t="n"/>
+      <c r="L90" s="1027" t="n"/>
+      <c r="M90" s="1027" t="n"/>
+      <c r="N90" s="1027" t="n"/>
+      <c r="O90" s="1027" t="n"/>
+      <c r="P90" s="1027" t="n"/>
+      <c r="Q90" s="1027" t="n"/>
+      <c r="R90" s="1027" t="n"/>
+      <c r="S90" s="1027" t="n"/>
+      <c r="T90" s="1027" t="n"/>
+      <c r="U90" s="1027" t="n"/>
+      <c r="V90" s="1027" t="n"/>
+      <c r="W90" s="1027" t="n"/>
+      <c r="X90" s="1027" t="n"/>
+      <c r="Y90" s="1027" t="n"/>
+      <c r="Z90" s="1027" t="n"/>
+      <c r="AA90" s="1027" t="n"/>
+      <c r="AB90" s="1027" t="n"/>
+      <c r="AC90" s="1027" t="n"/>
+      <c r="AD90" s="1027" t="n"/>
+      <c r="AE90" s="1027" t="n"/>
+      <c r="AF90" s="1027" t="n"/>
+      <c r="AG90" s="1027" t="n"/>
+      <c r="AH90" s="1027" t="n"/>
+      <c r="AI90" s="1027" t="n"/>
+      <c r="AJ90" s="1027" t="n"/>
+      <c r="AK90" s="1027" t="n"/>
+      <c r="AL90" s="1027" t="n"/>
+      <c r="AM90" s="1027" t="n"/>
+      <c r="AN90" s="1027" t="n"/>
+      <c r="AO90" s="1027" t="n"/>
+      <c r="AP90" s="1027" t="n"/>
+      <c r="AQ90" s="1027" t="n"/>
+      <c r="AR90" s="1027" t="n"/>
+      <c r="AS90" s="1027" t="n"/>
+      <c r="AT90" s="1027" t="n"/>
+      <c r="AU90" s="1027" t="n"/>
+      <c r="AV90" s="1027" t="n"/>
+      <c r="AW90" s="1027" t="n"/>
+      <c r="AX90" s="1027" t="n"/>
+      <c r="AY90" s="1027" t="n"/>
+      <c r="AZ90" s="1027" t="n"/>
+      <c r="BA90" s="1027" t="n"/>
+      <c r="BB90" s="1027" t="n"/>
+      <c r="BC90" s="1027" t="n"/>
+      <c r="BD90" s="1027" t="n"/>
+      <c r="BE90" s="1027" t="n"/>
+      <c r="BF90" s="1027" t="n"/>
+      <c r="BG90" s="1027" t="n"/>
+      <c r="BH90" s="1027" t="n"/>
+      <c r="BI90" s="1027" t="n"/>
+      <c r="BJ90" s="1027" t="n"/>
+      <c r="BK90" s="1027" t="n"/>
+      <c r="BL90" s="1027" t="n"/>
+      <c r="BM90" s="1027" t="n"/>
+      <c r="BN90" s="1027" t="n"/>
+      <c r="BO90" s="1027" t="n"/>
+      <c r="BP90" s="1027" t="n"/>
+      <c r="BQ90" s="1027" t="n"/>
+      <c r="BR90" s="1027" t="n"/>
+      <c r="BS90" s="1027" t="n"/>
+      <c r="BT90" s="1027" t="n"/>
+      <c r="BU90" s="1027" t="n"/>
+      <c r="BV90" s="1027" t="n"/>
+      <c r="BW90" s="1027" t="n"/>
+      <c r="BX90" s="1027" t="n"/>
+      <c r="BY90" s="1027" t="n"/>
+      <c r="BZ90" s="1027" t="n"/>
+      <c r="CA90" s="1027" t="n"/>
+      <c r="CB90" s="1027" t="n"/>
+      <c r="CC90" s="1027" t="n"/>
+      <c r="CD90" s="1027" t="n"/>
+      <c r="CE90" s="1027" t="n"/>
+      <c r="CF90" s="1027" t="n"/>
+      <c r="CG90" s="1027" t="n"/>
+      <c r="CH90" s="1027" t="n"/>
+      <c r="CI90" s="1027" t="n"/>
+      <c r="CJ90" s="1027" t="n"/>
+      <c r="CK90" s="1027" t="n"/>
+      <c r="CL90" s="1027" t="n"/>
+      <c r="CM90" s="1027" t="n"/>
+      <c r="CN90" s="1027" t="n"/>
+      <c r="CO90" s="1027" t="n"/>
+      <c r="CP90" s="1027" t="n"/>
+      <c r="CQ90" s="1027" t="n"/>
+      <c r="CR90" s="1027" t="n"/>
+      <c r="CS90" s="1027" t="n"/>
+      <c r="CT90" s="1027" t="n"/>
+      <c r="CU90" s="1027" t="n"/>
+      <c r="CV90" s="1027" t="n"/>
+      <c r="CW90" s="1027" t="n"/>
+      <c r="CX90" s="1028" t="n"/>
+      <c r="CY90" s="1022" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="131">
+  <mergeCells count="206">
     <mergeCell ref="AJ33:AM33"/>
+    <mergeCell ref="AN63:CS63"/>
     <mergeCell ref="E27:T27"/>
+    <mergeCell ref="AJ65:AM65"/>
     <mergeCell ref="AN25:CS25"/>
     <mergeCell ref="E36:T36"/>
     <mergeCell ref="C17:R17"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="AJ26:AM26"/>
     <mergeCell ref="U32:AF32"/>
+    <mergeCell ref="AN60:CS60"/>
+    <mergeCell ref="AJ63:AM63"/>
     <mergeCell ref="BW3:CB3"/>
     <mergeCell ref="B6:CX6"/>
+    <mergeCell ref="AN42:CS42"/>
     <mergeCell ref="S14:BZ14"/>
+    <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AT3:BV3"/>
-    <mergeCell ref="U24:AF24"/>
+    <mergeCell ref="U58:AF58"/>
     <mergeCell ref="CK4:CN4"/>
     <mergeCell ref="S13:BZ13"/>
-    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AN67:CS67"/>
+    <mergeCell ref="AJ42:AM42"/>
+    <mergeCell ref="E67:T67"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="C14:R14"/>
     <mergeCell ref="AN28:CS28"/>
+    <mergeCell ref="AG42:AI42"/>
     <mergeCell ref="AN37:CS37"/>
     <mergeCell ref="S15:BZ15"/>
+    <mergeCell ref="U63:AF63"/>
     <mergeCell ref="AT4:BV4"/>
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="U35:AF35"/>
+    <mergeCell ref="AJ67:AM67"/>
     <mergeCell ref="AG35:AI35"/>
     <mergeCell ref="E38:T38"/>
     <mergeCell ref="AN30:CS30"/>
+    <mergeCell ref="AN53:CS53"/>
     <mergeCell ref="AJ28:AM28"/>
     <mergeCell ref="U34:AF34"/>
     <mergeCell ref="AG25:AI25"/>
@@ -53474,38 +58273,67 @@
     <mergeCell ref="AI3:AS3"/>
     <mergeCell ref="H2:N2"/>
     <mergeCell ref="E40:T40"/>
+    <mergeCell ref="AN55:CS55"/>
     <mergeCell ref="AJ30:AM30"/>
     <mergeCell ref="U36:AF36"/>
+    <mergeCell ref="AN64:CS64"/>
+    <mergeCell ref="AJ53:AM53"/>
     <mergeCell ref="U30:AF30"/>
+    <mergeCell ref="AJ62:AM62"/>
+    <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="AN54:CS54"/>
     <mergeCell ref="AN32:CS32"/>
     <mergeCell ref="AN41:CS41"/>
+    <mergeCell ref="AJ55:AM55"/>
     <mergeCell ref="O3:AH3"/>
     <mergeCell ref="E26:T26"/>
+    <mergeCell ref="AJ64:AM64"/>
     <mergeCell ref="CK3:CN3"/>
+    <mergeCell ref="AN56:CS56"/>
+    <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="U37:AF37"/>
     <mergeCell ref="CO3:CX3"/>
     <mergeCell ref="E25:T25"/>
     <mergeCell ref="AJ32:AM32"/>
     <mergeCell ref="S17:BZ17"/>
+    <mergeCell ref="AJ54:AM54"/>
     <mergeCell ref="S11:BZ11"/>
     <mergeCell ref="AJ41:AM41"/>
+    <mergeCell ref="E66:T66"/>
     <mergeCell ref="AN27:CS27"/>
     <mergeCell ref="AG37:AI37"/>
+    <mergeCell ref="AN58:CS58"/>
+    <mergeCell ref="E53:T53"/>
+    <mergeCell ref="AJ56:AM56"/>
+    <mergeCell ref="U62:AF62"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="AG39:AI39"/>
+    <mergeCell ref="U54:AF54"/>
     <mergeCell ref="AJ40:AM40"/>
+    <mergeCell ref="U55:AF55"/>
     <mergeCell ref="AJ27:AM27"/>
+    <mergeCell ref="E55:T55"/>
+    <mergeCell ref="AJ58:AM58"/>
+    <mergeCell ref="U64:AF64"/>
     <mergeCell ref="U38:AF38"/>
+    <mergeCell ref="AN66:CS66"/>
     <mergeCell ref="E39:T39"/>
+    <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="U26:AF26"/>
     <mergeCell ref="U40:AF40"/>
     <mergeCell ref="E29:T29"/>
+    <mergeCell ref="AJ66:AM66"/>
+    <mergeCell ref="AG54:AI54"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="AN36:CS36"/>
     <mergeCell ref="CC3:CJ3"/>
     <mergeCell ref="E31:T31"/>
     <mergeCell ref="AJ34:AM34"/>
+    <mergeCell ref="U65:AF65"/>
     <mergeCell ref="C12:R12"/>
+    <mergeCell ref="AG56:AI56"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="U27:AF27"/>
     <mergeCell ref="AN29:CS29"/>
     <mergeCell ref="AJ36:AM36"/>
@@ -53514,68 +58342,104 @@
     <mergeCell ref="U25:AF25"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="AN31:CS31"/>
+    <mergeCell ref="U57:AF57"/>
     <mergeCell ref="AJ29:AM29"/>
+    <mergeCell ref="E57:T57"/>
+    <mergeCell ref="U66:AF66"/>
     <mergeCell ref="O2:AA2"/>
+    <mergeCell ref="E54:T54"/>
+    <mergeCell ref="U53:AF53"/>
     <mergeCell ref="BW4:CB4"/>
     <mergeCell ref="E41:T41"/>
     <mergeCell ref="CO2:CX2"/>
+    <mergeCell ref="AN62:CS62"/>
     <mergeCell ref="AJ31:AM31"/>
     <mergeCell ref="U28:AF28"/>
     <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="E24:T24"/>
+    <mergeCell ref="E56:T56"/>
+    <mergeCell ref="E58:T58"/>
     <mergeCell ref="U39:AF39"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="E33:T33"/>
     <mergeCell ref="O4:AH4"/>
     <mergeCell ref="AI4:AS4"/>
+    <mergeCell ref="E42:T42"/>
+    <mergeCell ref="AG67:AI67"/>
     <mergeCell ref="U29:AF29"/>
+    <mergeCell ref="AN57:CS57"/>
     <mergeCell ref="S9:BZ9"/>
     <mergeCell ref="CO4:CX4"/>
     <mergeCell ref="E35:T35"/>
+    <mergeCell ref="AG55:AI55"/>
     <mergeCell ref="C16:R16"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="U31:AF31"/>
     <mergeCell ref="AN34:CS34"/>
     <mergeCell ref="CK2:CN2"/>
+    <mergeCell ref="AJ57:AM57"/>
     <mergeCell ref="E28:T28"/>
     <mergeCell ref="C9:R9"/>
+    <mergeCell ref="E60:T60"/>
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="E30:T30"/>
+    <mergeCell ref="E59:T59"/>
     <mergeCell ref="C11:R11"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="S12:BZ12"/>
     <mergeCell ref="AJ35:AM35"/>
     <mergeCell ref="AG32:AI32"/>
     <mergeCell ref="U41:AF41"/>
+    <mergeCell ref="E61:T61"/>
     <mergeCell ref="AJ25:AM25"/>
+    <mergeCell ref="U56:AF56"/>
+    <mergeCell ref="AN59:CS59"/>
     <mergeCell ref="AB2:CJ2"/>
     <mergeCell ref="E32:T32"/>
+    <mergeCell ref="AJ60:AM60"/>
     <mergeCell ref="E37:T37"/>
     <mergeCell ref="C13:R13"/>
+    <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="B4:N4"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="U33:AF33"/>
+    <mergeCell ref="AN61:CS61"/>
     <mergeCell ref="AN39:CS39"/>
+    <mergeCell ref="U42:AF42"/>
+    <mergeCell ref="AJ59:AM59"/>
     <mergeCell ref="C15:R15"/>
+    <mergeCell ref="E62:T62"/>
     <mergeCell ref="AN38:CS38"/>
     <mergeCell ref="S10:BZ10"/>
     <mergeCell ref="CC4:CJ4"/>
     <mergeCell ref="AJ39:AM39"/>
+    <mergeCell ref="AG58:AI58"/>
+    <mergeCell ref="AJ61:AM61"/>
+    <mergeCell ref="U67:AF67"/>
+    <mergeCell ref="E64:T64"/>
     <mergeCell ref="AN40:CS40"/>
+    <mergeCell ref="U60:AF60"/>
     <mergeCell ref="AJ38:AM38"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="AG29:AI29"/>
     <mergeCell ref="C10:R10"/>
-    <mergeCell ref="AN24:CS24"/>
+    <mergeCell ref="E63:T63"/>
     <mergeCell ref="AN33:CS33"/>
+    <mergeCell ref="U59:AF59"/>
+    <mergeCell ref="AN65:CS65"/>
+    <mergeCell ref="E65:T65"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="E34:T34"/>
     <mergeCell ref="AJ37:AM37"/>
     <mergeCell ref="AN26:CS26"/>
     <mergeCell ref="AN35:CS35"/>
-    <mergeCell ref="AJ24:AM24"/>
+    <mergeCell ref="U61:AF61"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.25" right="0.25" top="0.7" bottom="0.25" header="0.6" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="48" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -53601,1549 +58465,1549 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1050" t="inlineStr">
+      <c r="A1" s="1063" t="inlineStr">
         <is>
           <t>Sample upload scenarios - Part List Upload</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1051" t="inlineStr">
+      <c r="A2" s="1064" t="inlineStr">
         <is>
           <t>Each scenario is a separate upload file. Today = 13-Sep-2026, mapping of the ongoing calculation period = Sep 2026.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1051" t="inlineStr">
+      <c r="A3" s="1064" t="inlineStr">
         <is>
           <t>Input columns follow sheet Upload of the Export Excel; a blank cell is a blank value in the file.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1052" t="inlineStr">
+      <c r="A5" s="1065" t="inlineStr">
         <is>
           <t>A. Master data before upload</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1053" t="inlineStr">
+      <c r="A6" s="1066" t="inlineStr">
         <is>
           <t>Part No</t>
         </is>
       </c>
-      <c r="B6" s="1053" t="inlineStr">
+      <c r="B6" s="1066" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C6" s="1053" t="inlineStr">
+      <c r="C6" s="1066" t="inlineStr">
         <is>
           <t>MAD</t>
         </is>
       </c>
-      <c r="D6" s="1053" t="inlineStr">
+      <c r="D6" s="1066" t="inlineStr">
         <is>
           <t>Pcs/Case</t>
         </is>
       </c>
-      <c r="E6" s="1053" t="inlineStr">
+      <c r="E6" s="1066" t="inlineStr">
         <is>
           <t>Max Case/Day</t>
         </is>
       </c>
-      <c r="F6" s="1053" t="inlineStr">
+      <c r="F6" s="1066" t="inlineStr">
         <is>
           <t>Effective Date</t>
         </is>
       </c>
-      <c r="G6" s="1053" t="inlineStr">
+      <c r="G6" s="1066" t="inlineStr">
         <is>
           <t>Mapped 123</t>
         </is>
       </c>
-      <c r="H6" s="1053" t="inlineStr">
+      <c r="H6" s="1066" t="inlineStr">
         <is>
           <t>Mapped 456</t>
         </is>
       </c>
-      <c r="I6" s="1053" t="inlineStr">
+      <c r="I6" s="1066" t="inlineStr">
         <is>
           <t>Mapped 789</t>
         </is>
       </c>
-      <c r="J6" s="1053" t="inlineStr">
+      <c r="J6" s="1066" t="inlineStr">
         <is>
           <t>Mapped total</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1054" t="inlineStr">
+      <c r="A7" s="1067" t="inlineStr">
         <is>
           <t>PART-A</t>
         </is>
       </c>
-      <c r="B7" s="1054" t="inlineStr">
+      <c r="B7" s="1067" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="C7" s="1055" t="n">
+      <c r="C7" s="1068" t="n">
         <v>800</v>
       </c>
-      <c r="D7" s="1055" t="n">
+      <c r="D7" s="1068" t="n">
         <v>60</v>
       </c>
-      <c r="E7" s="1055" t="n">
+      <c r="E7" s="1068" t="n">
         <v>24</v>
       </c>
-      <c r="F7" s="1054" t="inlineStr">
+      <c r="F7" s="1067" t="inlineStr">
         <is>
           <t>01-Aug-2026</t>
         </is>
       </c>
-      <c r="G7" s="1055" t="n">
+      <c r="G7" s="1068" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="1055" t="n">
+      <c r="H7" s="1068" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="1055" t="n">
+      <c r="I7" s="1068" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="1055" t="n">
+      <c r="J7" s="1068" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1054" t="inlineStr">
+      <c r="A8" s="1067" t="inlineStr">
         <is>
           <t>PART-C</t>
         </is>
       </c>
-      <c r="B8" s="1054" t="inlineStr">
+      <c r="B8" s="1067" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="C8" s="1055" t="n">
+      <c r="C8" s="1068" t="n">
         <v>200</v>
       </c>
-      <c r="D8" s="1055" t="n">
+      <c r="D8" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="1055" t="n">
+      <c r="E8" s="1068" t="n">
         <v>30</v>
       </c>
-      <c r="F8" s="1054" t="inlineStr">
+      <c r="F8" s="1067" t="inlineStr">
         <is>
           <t>01-Aug-2026</t>
         </is>
       </c>
-      <c r="G8" s="1054" t="n"/>
-      <c r="H8" s="1055" t="n">
+      <c r="G8" s="1067" t="n"/>
+      <c r="H8" s="1068" t="n">
         <v>12</v>
       </c>
-      <c r="I8" s="1055" t="n">
+      <c r="I8" s="1068" t="n">
         <v>18</v>
       </c>
-      <c r="J8" s="1055" t="n">
+      <c r="J8" s="1068" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1054" t="inlineStr">
+      <c r="A9" s="1067" t="inlineStr">
         <is>
           <t>PART-G</t>
         </is>
       </c>
-      <c r="B9" s="1054" t="inlineStr">
+      <c r="B9" s="1067" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="C9" s="1055" t="n">
+      <c r="C9" s="1068" t="n">
         <v>150</v>
       </c>
-      <c r="D9" s="1055" t="n">
+      <c r="D9" s="1068" t="n">
         <v>50</v>
       </c>
-      <c r="E9" s="1055" t="n">
+      <c r="E9" s="1068" t="n">
         <v>22</v>
       </c>
-      <c r="F9" s="1054" t="inlineStr">
+      <c r="F9" s="1067" t="inlineStr">
         <is>
           <t>01-Aug-2026</t>
         </is>
       </c>
-      <c r="G9" s="1054" t="n"/>
-      <c r="H9" s="1054" t="n"/>
-      <c r="I9" s="1054" t="n"/>
-      <c r="J9" s="1055" t="n">
+      <c r="G9" s="1067" t="n"/>
+      <c r="H9" s="1067" t="n"/>
+      <c r="I9" s="1067" t="n"/>
+      <c r="J9" s="1068" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1054" t="inlineStr">
+      <c r="A10" s="1067" t="inlineStr">
         <is>
           <t>PART-I</t>
         </is>
       </c>
-      <c r="B10" s="1054" t="inlineStr">
+      <c r="B10" s="1067" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="C10" s="1055" t="n">
+      <c r="C10" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="D10" s="1055" t="n">
+      <c r="D10" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="1055" t="n">
+      <c r="E10" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="F10" s="1054" t="inlineStr">
+      <c r="F10" s="1067" t="inlineStr">
         <is>
           <t>15-Sep-2026</t>
         </is>
       </c>
-      <c r="G10" s="1054" t="n"/>
-      <c r="H10" s="1054" t="n"/>
-      <c r="I10" s="1054" t="n"/>
-      <c r="J10" s="1055" t="n">
+      <c r="G10" s="1067" t="n"/>
+      <c r="H10" s="1067" t="n"/>
+      <c r="I10" s="1067" t="n"/>
+      <c r="J10" s="1068" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1054" t="inlineStr">
+      <c r="A11" s="1067" t="inlineStr">
         <is>
           <t>PART-M01</t>
         </is>
       </c>
-      <c r="B11" s="1054" t="inlineStr">
+      <c r="B11" s="1067" t="inlineStr">
         <is>
           <t>(not registered)</t>
         </is>
       </c>
-      <c r="C11" s="1054" t="n"/>
-      <c r="D11" s="1054" t="n"/>
-      <c r="E11" s="1054" t="n"/>
-      <c r="F11" s="1054" t="n"/>
-      <c r="G11" s="1054" t="n"/>
-      <c r="H11" s="1054" t="n"/>
-      <c r="I11" s="1054" t="n"/>
-      <c r="J11" s="1054" t="n"/>
+      <c r="C11" s="1067" t="n"/>
+      <c r="D11" s="1067" t="n"/>
+      <c r="E11" s="1067" t="n"/>
+      <c r="F11" s="1067" t="n"/>
+      <c r="G11" s="1067" t="n"/>
+      <c r="H11" s="1067" t="n"/>
+      <c r="I11" s="1067" t="n"/>
+      <c r="J11" s="1067" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="1054" t="inlineStr">
+      <c r="A12" s="1067" t="inlineStr">
         <is>
           <t>PART-M02</t>
         </is>
       </c>
-      <c r="B12" s="1054" t="inlineStr">
+      <c r="B12" s="1067" t="inlineStr">
         <is>
           <t>(not registered)</t>
         </is>
       </c>
-      <c r="C12" s="1054" t="n"/>
-      <c r="D12" s="1054" t="n"/>
-      <c r="E12" s="1054" t="n"/>
-      <c r="F12" s="1054" t="n"/>
-      <c r="G12" s="1054" t="n"/>
-      <c r="H12" s="1054" t="n"/>
-      <c r="I12" s="1054" t="n"/>
-      <c r="J12" s="1054" t="n"/>
+      <c r="C12" s="1067" t="n"/>
+      <c r="D12" s="1067" t="n"/>
+      <c r="E12" s="1067" t="n"/>
+      <c r="F12" s="1067" t="n"/>
+      <c r="G12" s="1067" t="n"/>
+      <c r="H12" s="1067" t="n"/>
+      <c r="I12" s="1067" t="n"/>
+      <c r="J12" s="1067" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="1054" t="inlineStr">
+      <c r="A13" s="1067" t="inlineStr">
         <is>
           <t>PART-M03</t>
         </is>
       </c>
-      <c r="B13" s="1054" t="inlineStr">
+      <c r="B13" s="1067" t="inlineStr">
         <is>
           <t>(not registered)</t>
         </is>
       </c>
-      <c r="C13" s="1054" t="n"/>
-      <c r="D13" s="1054" t="n"/>
-      <c r="E13" s="1054" t="n"/>
-      <c r="F13" s="1054" t="n"/>
-      <c r="G13" s="1054" t="n"/>
-      <c r="H13" s="1054" t="n"/>
-      <c r="I13" s="1054" t="n"/>
-      <c r="J13" s="1054" t="n"/>
+      <c r="C13" s="1067" t="n"/>
+      <c r="D13" s="1067" t="n"/>
+      <c r="E13" s="1067" t="n"/>
+      <c r="F13" s="1067" t="n"/>
+      <c r="G13" s="1067" t="n"/>
+      <c r="H13" s="1067" t="n"/>
+      <c r="I13" s="1067" t="n"/>
+      <c r="J13" s="1067" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="1052" t="inlineStr">
+      <c r="A15" s="1065" t="inlineStr">
         <is>
           <t>B. Normal scenarios (file accepted)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1053" t="inlineStr">
+      <c r="A16" s="1066" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B16" s="1053" t="inlineStr">
+      <c r="B16" s="1066" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C16" s="1053" t="inlineStr">
+      <c r="C16" s="1066" t="inlineStr">
         <is>
           <t>part_no</t>
         </is>
       </c>
-      <c r="D16" s="1053" t="inlineStr">
+      <c r="D16" s="1066" t="inlineStr">
         <is>
           <t>mad</t>
         </is>
       </c>
-      <c r="E16" s="1053" t="inlineStr">
+      <c r="E16" s="1066" t="inlineStr">
         <is>
           <t>pcs_case</t>
         </is>
       </c>
-      <c r="F16" s="1053" t="inlineStr">
+      <c r="F16" s="1066" t="inlineStr">
         <is>
           <t>max_case_day</t>
         </is>
       </c>
-      <c r="G16" s="1053" t="inlineStr">
+      <c r="G16" s="1066" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H16" s="1053" t="inlineStr">
+      <c r="H16" s="1066" t="inlineStr">
         <is>
           <t>flag_add_edit</t>
         </is>
       </c>
-      <c r="I16" s="1053" t="inlineStr">
+      <c r="I16" s="1066" t="inlineStr">
         <is>
           <t>effective_start_date</t>
         </is>
       </c>
-      <c r="J16" s="1053" t="inlineStr">
+      <c r="J16" s="1066" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1054" t="inlineStr">
+      <c r="A17" s="1067" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="B17" s="1054" t="inlineStr">
+      <c r="B17" s="1067" t="inlineStr">
         <is>
           <t>Add a new part</t>
         </is>
       </c>
-      <c r="C17" s="1054" t="inlineStr">
+      <c r="C17" s="1067" t="inlineStr">
         <is>
           <t>PART-M01</t>
         </is>
       </c>
-      <c r="D17" s="1055" t="n">
+      <c r="D17" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E17" s="1055" t="n">
+      <c r="E17" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="F17" s="1055" t="n">
+      <c r="F17" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="G17" s="1054" t="n"/>
-      <c r="H17" s="1054" t="inlineStr">
+      <c r="G17" s="1067" t="n"/>
+      <c r="H17" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I17" s="1054" t="inlineStr">
+      <c r="I17" s="1067" t="inlineStr">
         <is>
           <t>14-Sep-2026</t>
         </is>
       </c>
-      <c r="J17" s="1054" t="inlineStr">
+      <c r="J17" s="1067" t="inlineStr">
         <is>
           <t>Inserted. Status Candidate, Total Pcs/Day 300, Sync Status No Sync, Part Name from TB_M_PART_MASTER.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1054" t="inlineStr">
+      <c r="A18" s="1067" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="B18" s="1054" t="inlineStr">
+      <c r="B18" s="1067" t="inlineStr">
         <is>
           <t>Add another part, later date</t>
         </is>
       </c>
-      <c r="C18" s="1054" t="inlineStr">
+      <c r="C18" s="1067" t="inlineStr">
         <is>
           <t>PART-M02</t>
         </is>
       </c>
-      <c r="D18" s="1055" t="n">
+      <c r="D18" s="1068" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="1055" t="n">
+      <c r="E18" s="1068" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="1055" t="n">
+      <c r="F18" s="1068" t="n">
         <v>40</v>
       </c>
-      <c r="G18" s="1054" t="n"/>
-      <c r="H18" s="1054" t="inlineStr">
+      <c r="G18" s="1067" t="n"/>
+      <c r="H18" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I18" s="1054" t="inlineStr">
+      <c r="I18" s="1067" t="inlineStr">
         <is>
           <t>16-Sep-2026</t>
         </is>
       </c>
-      <c r="J18" s="1054" t="inlineStr">
+      <c r="J18" s="1067" t="inlineStr">
         <is>
           <t>Inserted. Total Pcs/Day 480. Both N1 and N2 can be in one file.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1054" t="inlineStr">
+      <c r="A19" s="1067" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="B19" s="1054" t="inlineStr">
+      <c r="B19" s="1067" t="inlineStr">
         <is>
           <t>Edit a Candidate part, change values and effective date</t>
         </is>
       </c>
-      <c r="C19" s="1054" t="inlineStr">
+      <c r="C19" s="1067" t="inlineStr">
         <is>
           <t>PART-I</t>
         </is>
       </c>
-      <c r="D19" s="1055" t="n">
+      <c r="D19" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E19" s="1055" t="n">
+      <c r="E19" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="F19" s="1055" t="n">
+      <c r="F19" s="1068" t="n">
         <v>18</v>
       </c>
-      <c r="G19" s="1054" t="inlineStr">
+      <c r="G19" s="1067" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="H19" s="1054" t="inlineStr">
+      <c r="H19" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I19" s="1054" t="inlineStr">
+      <c r="I19" s="1067" t="inlineStr">
         <is>
           <t>20-Sep-2026</t>
         </is>
       </c>
-      <c r="J19" s="1054" t="inlineStr">
+      <c r="J19" s="1067" t="inlineStr">
         <is>
           <t>Updated. Max Case/Day 20 -&gt; 18, effective date changed, Total Pcs/Day 270, Sync Status No Sync.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1054" t="inlineStr">
+      <c r="A20" s="1067" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="B20" s="1054" t="inlineStr">
+      <c r="B20" s="1067" t="inlineStr">
         <is>
           <t>Edit an Active part, raise Max Case/Day</t>
         </is>
       </c>
-      <c r="C20" s="1054" t="inlineStr">
+      <c r="C20" s="1067" t="inlineStr">
         <is>
           <t>PART-A</t>
         </is>
       </c>
-      <c r="D20" s="1055" t="n">
+      <c r="D20" s="1068" t="n">
         <v>800</v>
       </c>
-      <c r="E20" s="1055" t="n">
+      <c r="E20" s="1068" t="n">
         <v>60</v>
       </c>
-      <c r="F20" s="1055" t="n">
+      <c r="F20" s="1068" t="n">
         <v>30</v>
       </c>
-      <c r="G20" s="1054" t="n"/>
-      <c r="H20" s="1054" t="inlineStr">
+      <c r="G20" s="1067" t="n"/>
+      <c r="H20" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I20" s="1054" t="n"/>
-      <c r="J20" s="1054" t="inlineStr">
+      <c r="I20" s="1067" t="n"/>
+      <c r="J20" s="1067" t="inlineStr">
         <is>
           <t>Updated. Max Case/Day 24 -&gt; 30, Total Pcs/Day 1,800, Sync Status Success -&gt; No Sync. Mapping is not changed.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1054" t="inlineStr">
+      <c r="A21" s="1067" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="B21" s="1054" t="inlineStr">
+      <c r="B21" s="1067" t="inlineStr">
         <is>
           <t>Edit with the same values as the master</t>
         </is>
       </c>
-      <c r="C21" s="1054" t="inlineStr">
+      <c r="C21" s="1067" t="inlineStr">
         <is>
           <t>PART-A</t>
         </is>
       </c>
-      <c r="D21" s="1055" t="n">
+      <c r="D21" s="1068" t="n">
         <v>800</v>
       </c>
-      <c r="E21" s="1055" t="n">
+      <c r="E21" s="1068" t="n">
         <v>60</v>
       </c>
-      <c r="F21" s="1055" t="n">
+      <c r="F21" s="1068" t="n">
         <v>24</v>
       </c>
-      <c r="G21" s="1054" t="inlineStr">
+      <c r="G21" s="1067" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H21" s="1054" t="inlineStr">
+      <c r="H21" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I21" s="1054" t="n"/>
-      <c r="J21" s="1054" t="inlineStr">
+      <c r="I21" s="1067" t="n"/>
+      <c r="J21" s="1067" t="inlineStr">
         <is>
           <t>NO CHANGE. Row skipped, Sync Status and last update stay.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1054" t="inlineStr">
+      <c r="A22" s="1067" t="inlineStr">
         <is>
           <t>N6</t>
         </is>
       </c>
-      <c r="B22" s="1054" t="inlineStr">
+      <c r="B22" s="1067" t="inlineStr">
         <is>
           <t>File with only some parts (one row)</t>
         </is>
       </c>
-      <c r="C22" s="1054" t="inlineStr">
+      <c r="C22" s="1067" t="inlineStr">
         <is>
           <t>PART-I</t>
         </is>
       </c>
-      <c r="D22" s="1055" t="n">
+      <c r="D22" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E22" s="1055" t="n">
+      <c r="E22" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="F22" s="1055" t="n">
+      <c r="F22" s="1068" t="n">
         <v>18</v>
       </c>
-      <c r="G22" s="1054" t="inlineStr">
+      <c r="G22" s="1067" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="H22" s="1054" t="inlineStr">
+      <c r="H22" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I22" s="1054" t="inlineStr">
+      <c r="I22" s="1067" t="inlineStr">
         <is>
           <t>20-Sep-2026</t>
         </is>
       </c>
-      <c r="J22" s="1054" t="inlineStr">
+      <c r="J22" s="1067" t="inlineStr">
         <is>
           <t>Only PART-I is processed. PART-A, C, G are not in the sheet and are not changed.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1054" t="inlineStr">
+      <c r="A23" s="1067" t="inlineStr">
         <is>
           <t>N7</t>
         </is>
       </c>
-      <c r="B23" s="1054" t="inlineStr">
+      <c r="B23" s="1067" t="inlineStr">
         <is>
           <t>Lower Max Case/Day after the mapping was reduced to 20 in Mapping per Destination</t>
         </is>
       </c>
-      <c r="C23" s="1054" t="inlineStr">
+      <c r="C23" s="1067" t="inlineStr">
         <is>
           <t>PART-A</t>
         </is>
       </c>
-      <c r="D23" s="1055" t="n">
+      <c r="D23" s="1068" t="n">
         <v>800</v>
       </c>
-      <c r="E23" s="1055" t="n">
+      <c r="E23" s="1068" t="n">
         <v>60</v>
       </c>
-      <c r="F23" s="1055" t="n">
+      <c r="F23" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="G23" s="1054" t="n"/>
-      <c r="H23" s="1054" t="inlineStr">
+      <c r="G23" s="1067" t="n"/>
+      <c r="H23" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I23" s="1054" t="n"/>
-      <c r="J23" s="1054" t="inlineStr">
+      <c r="I23" s="1067" t="n"/>
+      <c r="J23" s="1067" t="inlineStr">
         <is>
           <t>Updated. Max Case/Day 24 -&gt; 20 (not below mapped 20).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1054" t="inlineStr">
+      <c r="A24" s="1067" t="inlineStr">
         <is>
           <t>N8</t>
         </is>
       </c>
-      <c r="B24" s="1054" t="inlineStr">
+      <c r="B24" s="1067" t="inlineStr">
         <is>
           <t>Change an Active part to Inactive</t>
         </is>
       </c>
-      <c r="C24" s="1054" t="inlineStr">
+      <c r="C24" s="1067" t="inlineStr">
         <is>
           <t>PART-G</t>
         </is>
       </c>
-      <c r="D24" s="1055" t="n">
+      <c r="D24" s="1068" t="n">
         <v>150</v>
       </c>
-      <c r="E24" s="1055" t="n">
+      <c r="E24" s="1068" t="n">
         <v>50</v>
       </c>
-      <c r="F24" s="1055" t="n">
+      <c r="F24" s="1068" t="n">
         <v>22</v>
       </c>
-      <c r="G24" s="1054" t="inlineStr">
+      <c r="G24" s="1067" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="H24" s="1054" t="inlineStr">
+      <c r="H24" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I24" s="1054" t="n"/>
-      <c r="J24" s="1054" t="inlineStr">
+      <c r="I24" s="1067" t="n"/>
+      <c r="J24" s="1067" t="inlineStr">
         <is>
           <t>Updated. Status Active -&gt; Inactive, Sync Status No Sync. Inactive -&gt; Active works the same way.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1054" t="inlineStr">
+      <c r="A25" s="1067" t="inlineStr">
         <is>
           <t>N9</t>
         </is>
       </c>
-      <c r="B25" s="1054" t="inlineStr">
+      <c r="B25" s="1067" t="inlineStr">
         <is>
           <t>Add a new part without MAD</t>
         </is>
       </c>
-      <c r="C25" s="1054" t="inlineStr">
+      <c r="C25" s="1067" t="inlineStr">
         <is>
           <t>PART-M03</t>
         </is>
       </c>
-      <c r="D25" s="1054" t="n"/>
-      <c r="E25" s="1055" t="n">
+      <c r="D25" s="1067" t="n"/>
+      <c r="E25" s="1068" t="n">
         <v>25</v>
       </c>
-      <c r="F25" s="1055" t="n">
+      <c r="F25" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="G25" s="1054" t="n"/>
-      <c r="H25" s="1054" t="inlineStr">
+      <c r="G25" s="1067" t="n"/>
+      <c r="H25" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I25" s="1054" t="inlineStr">
+      <c r="I25" s="1067" t="inlineStr">
         <is>
           <t>15-Sep-2026</t>
         </is>
       </c>
-      <c r="J25" s="1054" t="inlineStr">
+      <c r="J25" s="1067" t="inlineStr">
         <is>
           <t>Inserted. MAD stays blank until the MAD calculation function fills it.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1052" t="inlineStr">
+      <c r="A27" s="1065" t="inlineStr">
         <is>
           <t>C. Error scenarios (whole file rejected, nothing saved)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1053" t="inlineStr">
+      <c r="A28" s="1066" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B28" s="1053" t="inlineStr">
+      <c r="B28" s="1066" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C28" s="1053" t="inlineStr">
+      <c r="C28" s="1066" t="inlineStr">
         <is>
           <t>part_no</t>
         </is>
       </c>
-      <c r="D28" s="1053" t="inlineStr">
+      <c r="D28" s="1066" t="inlineStr">
         <is>
           <t>mad</t>
         </is>
       </c>
-      <c r="E28" s="1053" t="inlineStr">
+      <c r="E28" s="1066" t="inlineStr">
         <is>
           <t>pcs_case</t>
         </is>
       </c>
-      <c r="F28" s="1053" t="inlineStr">
+      <c r="F28" s="1066" t="inlineStr">
         <is>
           <t>max_case_day</t>
         </is>
       </c>
-      <c r="G28" s="1053" t="inlineStr">
+      <c r="G28" s="1066" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H28" s="1053" t="inlineStr">
+      <c r="H28" s="1066" t="inlineStr">
         <is>
           <t>flag_add_edit</t>
         </is>
       </c>
-      <c r="I28" s="1053" t="inlineStr">
+      <c r="I28" s="1066" t="inlineStr">
         <is>
           <t>effective_start_date</t>
         </is>
       </c>
-      <c r="J28" s="1053" t="inlineStr">
+      <c r="J28" s="1066" t="inlineStr">
         <is>
           <t>Error (4.2 check no.)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1054" t="inlineStr">
+      <c r="A29" s="1067" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="B29" s="1054" t="inlineStr">
+      <c r="B29" s="1067" t="inlineStr">
         <is>
           <t>Flag is not A or E</t>
         </is>
       </c>
-      <c r="C29" s="1054" t="inlineStr">
+      <c r="C29" s="1067" t="inlineStr">
         <is>
           <t>PART-I</t>
         </is>
       </c>
-      <c r="D29" s="1055" t="n">
+      <c r="D29" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E29" s="1055" t="n">
+      <c r="E29" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="F29" s="1055" t="n">
+      <c r="F29" s="1068" t="n">
         <v>18</v>
       </c>
-      <c r="G29" s="1054" t="n"/>
-      <c r="H29" s="1054" t="inlineStr">
+      <c r="G29" s="1067" t="n"/>
+      <c r="H29" s="1067" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I29" s="1054" t="inlineStr">
+      <c r="I29" s="1067" t="inlineStr">
         <is>
           <t>20-Sep-2026</t>
         </is>
       </c>
-      <c r="J29" s="1054" t="inlineStr">
+      <c r="J29" s="1067" t="inlineStr">
         <is>
           <t>Check 1: flag_add_edit must be A or E.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1054" t="inlineStr">
+      <c r="A30" s="1067" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B30" s="1054" t="inlineStr">
+      <c r="B30" s="1067" t="inlineStr">
         <is>
           <t>Part not in part master</t>
         </is>
       </c>
-      <c r="C30" s="1054" t="inlineStr">
+      <c r="C30" s="1067" t="inlineStr">
         <is>
           <t>PART-Z99</t>
         </is>
       </c>
-      <c r="D30" s="1055" t="n">
+      <c r="D30" s="1068" t="n">
         <v>100</v>
       </c>
-      <c r="E30" s="1055" t="n">
+      <c r="E30" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="F30" s="1055" t="n">
+      <c r="F30" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="G30" s="1054" t="n"/>
-      <c r="H30" s="1054" t="inlineStr">
+      <c r="G30" s="1067" t="n"/>
+      <c r="H30" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I30" s="1054" t="n"/>
-      <c r="J30" s="1054" t="inlineStr">
+      <c r="I30" s="1067" t="n"/>
+      <c r="J30" s="1067" t="inlineStr">
         <is>
           <t>Check 2: Part No not found in TB_M_PART_MASTER.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1054" t="inlineStr">
+      <c r="A31" s="1067" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="B31" s="1054" t="inlineStr">
+      <c r="B31" s="1067" t="inlineStr">
         <is>
           <t>Add a part that is already registered</t>
         </is>
       </c>
-      <c r="C31" s="1054" t="inlineStr">
+      <c r="C31" s="1067" t="inlineStr">
         <is>
           <t>PART-A</t>
         </is>
       </c>
-      <c r="D31" s="1055" t="n">
+      <c r="D31" s="1068" t="n">
         <v>800</v>
       </c>
-      <c r="E31" s="1055" t="n">
+      <c r="E31" s="1068" t="n">
         <v>60</v>
       </c>
-      <c r="F31" s="1055" t="n">
+      <c r="F31" s="1068" t="n">
         <v>24</v>
       </c>
-      <c r="G31" s="1054" t="n"/>
-      <c r="H31" s="1054" t="inlineStr">
+      <c r="G31" s="1067" t="n"/>
+      <c r="H31" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I31" s="1054" t="inlineStr">
+      <c r="I31" s="1067" t="inlineStr">
         <is>
           <t>14-Sep-2026</t>
         </is>
       </c>
-      <c r="J31" s="1054" t="inlineStr">
+      <c r="J31" s="1067" t="inlineStr">
         <is>
           <t>Check 3: Part No already registered, use flag E.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1054" t="inlineStr">
+      <c r="A32" s="1067" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
       </c>
-      <c r="B32" s="1054" t="inlineStr">
+      <c r="B32" s="1067" t="inlineStr">
         <is>
           <t>Edit a part that is not registered</t>
         </is>
       </c>
-      <c r="C32" s="1054" t="inlineStr">
+      <c r="C32" s="1067" t="inlineStr">
         <is>
           <t>PART-M03</t>
         </is>
       </c>
-      <c r="D32" s="1055" t="n">
+      <c r="D32" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E32" s="1055" t="n">
+      <c r="E32" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="F32" s="1055" t="n">
+      <c r="F32" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="G32" s="1054" t="n"/>
-      <c r="H32" s="1054" t="inlineStr">
+      <c r="G32" s="1067" t="n"/>
+      <c r="H32" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I32" s="1054" t="n"/>
-      <c r="J32" s="1054" t="inlineStr">
+      <c r="I32" s="1067" t="n"/>
+      <c r="J32" s="1067" t="inlineStr">
         <is>
           <t>Check 3: Part No not registered, use flag A.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1054" t="inlineStr">
+      <c r="A33" s="1067" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="B33" s="1054" t="inlineStr">
+      <c r="B33" s="1067" t="inlineStr">
         <is>
           <t>Same part twice in the file (row 1)</t>
         </is>
       </c>
-      <c r="C33" s="1054" t="inlineStr">
+      <c r="C33" s="1067" t="inlineStr">
         <is>
           <t>PART-I</t>
         </is>
       </c>
-      <c r="D33" s="1055" t="n">
+      <c r="D33" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E33" s="1055" t="n">
+      <c r="E33" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="F33" s="1055" t="n">
+      <c r="F33" s="1068" t="n">
         <v>18</v>
       </c>
-      <c r="G33" s="1054" t="inlineStr">
+      <c r="G33" s="1067" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="H33" s="1054" t="inlineStr">
+      <c r="H33" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I33" s="1054" t="inlineStr">
+      <c r="I33" s="1067" t="inlineStr">
         <is>
           <t>20-Sep-2026</t>
         </is>
       </c>
-      <c r="J33" s="1054" t="inlineStr">
+      <c r="J33" s="1067" t="inlineStr">
         <is>
           <t>Check 4: Part No appears more than once.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1054" t="inlineStr">
+      <c r="A34" s="1067" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="B34" s="1054" t="inlineStr">
+      <c r="B34" s="1067" t="inlineStr">
         <is>
           <t>Same part twice in the file (row 2)</t>
         </is>
       </c>
-      <c r="C34" s="1054" t="inlineStr">
+      <c r="C34" s="1067" t="inlineStr">
         <is>
           <t>PART-I</t>
         </is>
       </c>
-      <c r="D34" s="1055" t="n">
+      <c r="D34" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E34" s="1055" t="n">
+      <c r="E34" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="F34" s="1055" t="n">
+      <c r="F34" s="1068" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="1054" t="inlineStr">
+      <c r="G34" s="1067" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="H34" s="1054" t="inlineStr">
+      <c r="H34" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I34" s="1054" t="inlineStr">
+      <c r="I34" s="1067" t="inlineStr">
         <is>
           <t>20-Sep-2026</t>
         </is>
       </c>
-      <c r="J34" s="1054" t="inlineStr">
+      <c r="J34" s="1067" t="inlineStr">
         <is>
           <t>Check 4: Part No appears more than once.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1054" t="inlineStr">
+      <c r="A35" s="1067" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="B35" s="1054" t="inlineStr">
+      <c r="B35" s="1067" t="inlineStr">
         <is>
           <t>Invalid number</t>
         </is>
       </c>
-      <c r="C35" s="1054" t="inlineStr">
+      <c r="C35" s="1067" t="inlineStr">
         <is>
           <t>PART-M03</t>
         </is>
       </c>
-      <c r="D35" s="1055" t="n">
+      <c r="D35" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E35" s="1055" t="n">
+      <c r="E35" s="1068" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="1055" t="n">
+      <c r="F35" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="G35" s="1054" t="n"/>
-      <c r="H35" s="1054" t="inlineStr">
+      <c r="G35" s="1067" t="n"/>
+      <c r="H35" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I35" s="1054" t="inlineStr">
+      <c r="I35" s="1067" t="inlineStr">
         <is>
           <t>14-Sep-2026</t>
         </is>
       </c>
-      <c r="J35" s="1054" t="inlineStr">
+      <c r="J35" s="1067" t="inlineStr">
         <is>
           <t>Check 5: pcs_case must be greater than 0. A blank pcs_case or max_case_day is also an error (a blank mad is allowed).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1054" t="inlineStr">
+      <c r="A36" s="1067" t="inlineStr">
         <is>
           <t>E7</t>
         </is>
       </c>
-      <c r="B36" s="1054" t="inlineStr">
+      <c r="B36" s="1067" t="inlineStr">
         <is>
           <t>Change the status of a Candidate part</t>
         </is>
       </c>
-      <c r="C36" s="1054" t="inlineStr">
+      <c r="C36" s="1067" t="inlineStr">
         <is>
           <t>PART-I</t>
         </is>
       </c>
-      <c r="D36" s="1055" t="n">
+      <c r="D36" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E36" s="1055" t="n">
+      <c r="E36" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="F36" s="1055" t="n">
+      <c r="F36" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="G36" s="1054" t="inlineStr">
+      <c r="G36" s="1067" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H36" s="1054" t="inlineStr">
+      <c r="H36" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I36" s="1054" t="inlineStr">
+      <c r="I36" s="1067" t="inlineStr">
         <is>
           <t>15-Sep-2026</t>
         </is>
       </c>
-      <c r="J36" s="1054" t="inlineStr">
+      <c r="J36" s="1067" t="inlineStr">
         <is>
           <t>Check 6: the status of a Candidate part cannot be changed by upload. Change it in the Edit part data modal.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1054" t="inlineStr">
+      <c r="A37" s="1067" t="inlineStr">
         <is>
           <t>E8</t>
         </is>
       </c>
-      <c r="B37" s="1054" t="inlineStr">
+      <c r="B37" s="1067" t="inlineStr">
         <is>
           <t>Change an Active part to Candidate</t>
         </is>
       </c>
-      <c r="C37" s="1054" t="inlineStr">
+      <c r="C37" s="1067" t="inlineStr">
         <is>
           <t>PART-C</t>
         </is>
       </c>
-      <c r="D37" s="1055" t="n">
+      <c r="D37" s="1068" t="n">
         <v>200</v>
       </c>
-      <c r="E37" s="1055" t="n">
+      <c r="E37" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="1055" t="n">
+      <c r="F37" s="1068" t="n">
         <v>30</v>
       </c>
-      <c r="G37" s="1054" t="inlineStr">
+      <c r="G37" s="1067" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="H37" s="1054" t="inlineStr">
+      <c r="H37" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I37" s="1054" t="n"/>
-      <c r="J37" s="1054" t="inlineStr">
+      <c r="I37" s="1067" t="n"/>
+      <c r="J37" s="1067" t="inlineStr">
         <is>
           <t>Check 6: no part can be changed to Candidate.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1054" t="inlineStr">
+      <c r="A38" s="1067" t="inlineStr">
         <is>
           <t>E9</t>
         </is>
       </c>
-      <c r="B38" s="1054" t="inlineStr">
+      <c r="B38" s="1067" t="inlineStr">
         <is>
           <t>Add with a status</t>
         </is>
       </c>
-      <c r="C38" s="1054" t="inlineStr">
+      <c r="C38" s="1067" t="inlineStr">
         <is>
           <t>PART-M03</t>
         </is>
       </c>
-      <c r="D38" s="1055" t="n">
+      <c r="D38" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E38" s="1055" t="n">
+      <c r="E38" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="1055" t="n">
+      <c r="F38" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="G38" s="1054" t="inlineStr">
+      <c r="G38" s="1067" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H38" s="1054" t="inlineStr">
+      <c r="H38" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I38" s="1054" t="inlineStr">
+      <c r="I38" s="1067" t="inlineStr">
         <is>
           <t>14-Sep-2026</t>
         </is>
       </c>
-      <c r="J38" s="1054" t="inlineStr">
+      <c r="J38" s="1067" t="inlineStr">
         <is>
           <t>Check 6: status of a new part is always Candidate, leave it blank.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1054" t="inlineStr">
+      <c r="A39" s="1067" t="inlineStr">
         <is>
           <t>E10</t>
         </is>
       </c>
-      <c r="B39" s="1054" t="inlineStr">
+      <c r="B39" s="1067" t="inlineStr">
         <is>
           <t>Add without effective date</t>
         </is>
       </c>
-      <c r="C39" s="1054" t="inlineStr">
+      <c r="C39" s="1067" t="inlineStr">
         <is>
           <t>PART-M02</t>
         </is>
       </c>
-      <c r="D39" s="1055" t="n">
+      <c r="D39" s="1068" t="n">
         <v>500</v>
       </c>
-      <c r="E39" s="1055" t="n">
+      <c r="E39" s="1068" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="1055" t="n">
+      <c r="F39" s="1068" t="n">
         <v>40</v>
       </c>
-      <c r="G39" s="1054" t="n"/>
-      <c r="H39" s="1054" t="inlineStr">
+      <c r="G39" s="1067" t="n"/>
+      <c r="H39" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I39" s="1054" t="n"/>
-      <c r="J39" s="1054" t="inlineStr">
+      <c r="I39" s="1067" t="n"/>
+      <c r="J39" s="1067" t="inlineStr">
         <is>
           <t>Check 7: Effective Start Date is required for Candidate.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1054" t="inlineStr">
+      <c r="A40" s="1067" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B40" s="1054" t="inlineStr">
+      <c r="B40" s="1067" t="inlineStr">
         <is>
           <t>Effective date in the past</t>
         </is>
       </c>
-      <c r="C40" s="1054" t="inlineStr">
+      <c r="C40" s="1067" t="inlineStr">
         <is>
           <t>PART-M02</t>
         </is>
       </c>
-      <c r="D40" s="1055" t="n">
+      <c r="D40" s="1068" t="n">
         <v>500</v>
       </c>
-      <c r="E40" s="1055" t="n">
+      <c r="E40" s="1068" t="n">
         <v>12</v>
       </c>
-      <c r="F40" s="1055" t="n">
+      <c r="F40" s="1068" t="n">
         <v>40</v>
       </c>
-      <c r="G40" s="1054" t="n"/>
-      <c r="H40" s="1054" t="inlineStr">
+      <c r="G40" s="1067" t="n"/>
+      <c r="H40" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I40" s="1054" t="inlineStr">
+      <c r="I40" s="1067" t="inlineStr">
         <is>
           <t>12-Sep-2026</t>
         </is>
       </c>
-      <c r="J40" s="1054" t="inlineStr">
+      <c r="J40" s="1067" t="inlineStr">
         <is>
           <t>Check 7: Effective Start Date must be today or later.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1054" t="inlineStr">
+      <c r="A41" s="1067" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B41" s="1054" t="inlineStr">
+      <c r="B41" s="1067" t="inlineStr">
         <is>
           <t>Change effective date of an Active part</t>
         </is>
       </c>
-      <c r="C41" s="1054" t="inlineStr">
+      <c r="C41" s="1067" t="inlineStr">
         <is>
           <t>PART-C</t>
         </is>
       </c>
-      <c r="D41" s="1055" t="n">
+      <c r="D41" s="1068" t="n">
         <v>200</v>
       </c>
-      <c r="E41" s="1055" t="n">
+      <c r="E41" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="F41" s="1055" t="n">
+      <c r="F41" s="1068" t="n">
         <v>30</v>
       </c>
-      <c r="G41" s="1054" t="n"/>
-      <c r="H41" s="1054" t="inlineStr">
+      <c r="G41" s="1067" t="n"/>
+      <c r="H41" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I41" s="1054" t="inlineStr">
+      <c r="I41" s="1067" t="inlineStr">
         <is>
           <t>20-Sep-2026</t>
         </is>
       </c>
-      <c r="J41" s="1054" t="inlineStr">
+      <c r="J41" s="1067" t="inlineStr">
         <is>
           <t>Check 8: effective date can only change while the part is Candidate.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1054" t="inlineStr">
+      <c r="A42" s="1067" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B42" s="1054" t="inlineStr">
+      <c r="B42" s="1067" t="inlineStr">
         <is>
           <t>Max Case/Day below existing mapping</t>
         </is>
       </c>
-      <c r="C42" s="1054" t="inlineStr">
+      <c r="C42" s="1067" t="inlineStr">
         <is>
           <t>PART-A</t>
         </is>
       </c>
-      <c r="D42" s="1055" t="n">
+      <c r="D42" s="1068" t="n">
         <v>800</v>
       </c>
-      <c r="E42" s="1055" t="n">
+      <c r="E42" s="1068" t="n">
         <v>60</v>
       </c>
-      <c r="F42" s="1055" t="n">
+      <c r="F42" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="G42" s="1054" t="n"/>
-      <c r="H42" s="1054" t="inlineStr">
+      <c r="G42" s="1067" t="n"/>
+      <c r="H42" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I42" s="1054" t="n"/>
-      <c r="J42" s="1054" t="inlineStr">
+      <c r="I42" s="1067" t="n"/>
+      <c r="J42" s="1067" t="inlineStr">
         <is>
           <t>Check 9: Max Case/Day 20 is below mapped 24. Reduce the mapping first in Mapping per Destination.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1054" t="inlineStr">
+      <c r="A43" s="1067" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B43" s="1054" t="inlineStr">
+      <c r="B43" s="1067" t="inlineStr">
         <is>
           <t>Valid row (= N1) mixed with an error row (= E2), row 1</t>
         </is>
       </c>
-      <c r="C43" s="1054" t="inlineStr">
+      <c r="C43" s="1067" t="inlineStr">
         <is>
           <t>PART-M01</t>
         </is>
       </c>
-      <c r="D43" s="1055" t="n">
+      <c r="D43" s="1068" t="n">
         <v>300</v>
       </c>
-      <c r="E43" s="1055" t="n">
+      <c r="E43" s="1068" t="n">
         <v>20</v>
       </c>
-      <c r="F43" s="1055" t="n">
+      <c r="F43" s="1068" t="n">
         <v>15</v>
       </c>
-      <c r="G43" s="1054" t="n"/>
-      <c r="H43" s="1054" t="inlineStr">
+      <c r="G43" s="1067" t="n"/>
+      <c r="H43" s="1067" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I43" s="1054" t="inlineStr">
+      <c r="I43" s="1067" t="inlineStr">
         <is>
           <t>14-Sep-2026</t>
         </is>
       </c>
-      <c r="J43" s="1054" t="inlineStr">
+      <c r="J43" s="1067" t="inlineStr">
         <is>
           <t>Whole file rejected. The valid row is NOT saved.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1054" t="inlineStr">
+      <c r="A44" s="1067" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B44" s="1054" t="inlineStr">
+      <c r="B44" s="1067" t="inlineStr">
         <is>
           <t>Valid row mixed with an error row, row 2</t>
         </is>
       </c>
-      <c r="C44" s="1054" t="inlineStr">
+      <c r="C44" s="1067" t="inlineStr">
         <is>
           <t>PART-Z99</t>
         </is>
       </c>
-      <c r="D44" s="1055" t="n">
+      <c r="D44" s="1068" t="n">
         <v>100</v>
       </c>
-      <c r="E44" s="1055" t="n">
+      <c r="E44" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="F44" s="1055" t="n">
+      <c r="F44" s="1068" t="n">
         <v>10</v>
       </c>
-      <c r="G44" s="1054" t="n"/>
-      <c r="H44" s="1054" t="inlineStr">
+      <c r="G44" s="1067" t="n"/>
+      <c r="H44" s="1067" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I44" s="1054" t="n"/>
-      <c r="J44" s="1054" t="inlineStr">
+      <c r="I44" s="1067" t="n"/>
+      <c r="J44" s="1067" t="inlineStr">
         <is>
           <t>Check 2 on this row. Result report sheet Re-upload lists the rows to correct.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1052" t="inlineStr">
+      <c r="A46" s="1065" t="inlineStr">
         <is>
           <t>D. File-level errors (file check 4.1)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1053" t="inlineStr">
+      <c r="A47" s="1066" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B47" s="1053" t="inlineStr">
+      <c r="B47" s="1066" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C47" s="1053" t="inlineStr">
+      <c r="C47" s="1066" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1054" t="inlineStr">
+      <c r="A48" s="1067" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B48" s="1054" t="inlineStr">
+      <c r="B48" s="1067" t="inlineStr">
         <is>
           <t>File is .xls or .csv</t>
         </is>
       </c>
-      <c r="C48" s="1054" t="inlineStr">
+      <c r="C48" s="1067" t="inlineStr">
         <is>
           <t>Rejected: file must be .xlsx.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1054" t="inlineStr">
+      <c r="A49" s="1067" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B49" s="1054" t="inlineStr">
+      <c r="B49" s="1067" t="inlineStr">
         <is>
           <t>File larger than 5 MB</t>
         </is>
       </c>
-      <c r="C49" s="1054" t="inlineStr">
+      <c r="C49" s="1067" t="inlineStr">
         <is>
           <t>Rejected: file size exceeds 5 MB.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1054" t="inlineStr">
+      <c r="A50" s="1067" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B50" s="1054" t="inlineStr">
+      <c r="B50" s="1067" t="inlineStr">
         <is>
           <t>More than 5,000 data rows, or no data row</t>
         </is>
       </c>
-      <c r="C50" s="1054" t="inlineStr">
+      <c r="C50" s="1067" t="inlineStr">
         <is>
           <t>Rejected: row count out of range.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1054" t="inlineStr">
+      <c r="A51" s="1067" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B51" s="1054" t="inlineStr">
+      <c r="B51" s="1067" t="inlineStr">
         <is>
           <t>No sheet named Upload (e.g. only sheet Part List)</t>
         </is>
       </c>
-      <c r="C51" s="1054" t="inlineStr">
+      <c r="C51" s="1067" t="inlineStr">
         <is>
           <t>Rejected: sheet Upload not found.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1054" t="inlineStr">
+      <c r="A52" s="1067" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B52" s="1054" t="inlineStr">
+      <c r="B52" s="1067" t="inlineStr">
         <is>
           <t>A template column is missing (e.g. flag_add_edit deleted)</t>
         </is>
       </c>
-      <c r="C52" s="1054" t="inlineStr">
+      <c r="C52" s="1067" t="inlineStr">
         <is>
           <t>Rejected: required column not found.</t>
         </is>
